--- a/results/scraped_Cape_Town_Emergency_and_Rescue.xlsx
+++ b/results/scraped_Cape_Town_Emergency_and_Rescue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="188">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -40,90 +40,90 @@
     <t>Source</t>
   </si>
   <si>
+    <t>Incidents| CALFIRE</t>
+  </si>
+  <si>
+    <t>California Wildfire Live Map — Real-TimeFireTracking | CWT</t>
+  </si>
+  <si>
     <t>Fire-Wikipedia</t>
   </si>
   <si>
+    <t>Watch Duty - Wildfire Maps &amp; Alerts</t>
+  </si>
+  <si>
+    <t>Wildfire/Smoke Map - Live Tracking</t>
+  </si>
+  <si>
+    <t>Firefox: The fast, private browser that keeps you safe</t>
+  </si>
+  <si>
+    <t>GradeFire| CALFIRE</t>
+  </si>
+  <si>
     <t>AirNowFireand Smoke Map</t>
   </si>
   <si>
-    <t>Wildfire/Smoke Map - Live Tracking</t>
-  </si>
-  <si>
-    <t>FIRE| Foundation for Individual Rights and Expression</t>
-  </si>
-  <si>
-    <t>Firefox: The fast, private browser that keeps you safe</t>
+    <t>Current Fires in California | WFCAFireMap</t>
   </si>
   <si>
     <t>FireMap: Track Wildfires in Real-Time with NASA &amp; Local Data</t>
   </si>
   <si>
-    <t>NIFCMaps-National Interagency Fire Center</t>
-  </si>
-  <si>
-    <t>Live Wildfire Map &amp; Tracker – Wildfires Near Me | AllFirefighter</t>
-  </si>
-  <si>
-    <t>NationalFireNews -National Interagency Fire Center</t>
-  </si>
-  <si>
-    <t>NASA | LANCE |FIRMS</t>
-  </si>
-  <si>
-    <t>AO-HELPEmergencyPlan -AmblesideOnline- Charlotte Mason …</t>
-  </si>
-  <si>
-    <t>Home - AmblesideOnline - Charlotte Mason Curriculum</t>
-  </si>
-  <si>
-    <t>AmblesideOnlineYear 10 36-Week Schedule</t>
-  </si>
-  <si>
-    <t>Study Guide for Plutarch's Life of Crassus</t>
-  </si>
-  <si>
-    <t>Study Guide for Plutarch's Life of Coriolanus</t>
-  </si>
-  <si>
-    <t>Study Guide for Plutarch's Life of Marcus Brutus</t>
-  </si>
-  <si>
-    <t>Printing the editable schedule!? - Printable Version</t>
-  </si>
-  <si>
-    <t>AmblesideOnline Year 2 Booklist</t>
-  </si>
-  <si>
-    <t>Exam Questions: Form 1A, Term 2- AmblesideOnline - Charlotte …</t>
-  </si>
-  <si>
-    <t>AmblesideOnline for Groups Form 1A 36-Week Schedule</t>
+    <t>Emergency! (TV Series 1972–1979) - IMDb</t>
+  </si>
+  <si>
+    <t>Emergency! -Wikipedia</t>
+  </si>
+  <si>
+    <t>Emergency– COUNTY OF LOS ANGELES</t>
+  </si>
+  <si>
+    <t>Emergency-Wikipedia</t>
+  </si>
+  <si>
+    <t>EMERGENCYDefinition &amp; Meaning -Merriam-Webster</t>
+  </si>
+  <si>
+    <t>Home |EmergencyManagement Department</t>
+  </si>
+  <si>
+    <t>Emergency! | The Complete Series -YouTube</t>
+  </si>
+  <si>
+    <t>The 'Emergency' Cast: Looking at the Actors, Then and Now 2024</t>
+  </si>
+  <si>
+    <t>California declares statewideemergencybefore projected super El …</t>
+  </si>
+  <si>
+    <t>Emergency! (TV Series 1972–1979) - Full cast &amp; crew - IMDb</t>
   </si>
   <si>
     <t>Sea-Wikipedia</t>
   </si>
   <si>
-    <t>Do you know the difference between ocean,sea, bay and gulf?</t>
-  </si>
-  <si>
-    <t>List of seas on Earth - Wikipedia</t>
+    <t>Ocean- Wikipedia</t>
+  </si>
+  <si>
+    <t>Sea- National Geographic Society</t>
+  </si>
+  <si>
+    <t>Ocean vs.Sea: What’s the Difference? - Encyclopedia Britannica</t>
   </si>
   <si>
     <t>Sea- SimpleEnglish Wikipedia, the free encyclopedia</t>
   </si>
   <si>
-    <t>Ocean vs.Sea: What’s the Difference? - Encyclopedia Britannica</t>
-  </si>
-  <si>
-    <t>Sea- National Geographic Society</t>
+    <t>Sea| Investor Relations</t>
+  </si>
+  <si>
+    <t>Sea| Home</t>
   </si>
   <si>
     <t>SeaEducation Association</t>
   </si>
   <si>
-    <t>Sea| Investor Relations</t>
-  </si>
-  <si>
     <t>SEADefinition &amp; Meaning - Merriam-Webster</t>
   </si>
   <si>
@@ -136,118 +136,118 @@
     <t>Mountain| Definition, Characteristics, Types, &amp; Facts | Britannica</t>
   </si>
   <si>
-    <t>What is a Mountain? -WorldAtlas</t>
-  </si>
-  <si>
-    <t>MOUNTAINDefinition &amp; Meaning -Merriam-Webster</t>
+    <t>Superstition Mountain Arizona| Hiking, Apache Trail &amp; Lakes</t>
+  </si>
+  <si>
+    <t>Superstition Mountains | Phoenix,AZHiking &amp; Apache Trail</t>
+  </si>
+  <si>
+    <t>Superstition Mountains-Wikipedia</t>
+  </si>
+  <si>
+    <t>Mountains -WorldAtlas</t>
+  </si>
+  <si>
+    <t>Apache Junction Arizona| Things To Do, Hiking, Lakes &amp; Superstition ...</t>
+  </si>
+  <si>
+    <t>What is amountain? Here’s how they form | National Geographic</t>
   </si>
   <si>
     <t>Mountain- Simple EnglishWikipedia, the free encyclopedia</t>
   </si>
   <si>
-    <t>What is amountain? Here’s how they form | National Geographic</t>
-  </si>
-  <si>
-    <t>MountainHabitat - National Geographic Kids</t>
-  </si>
-  <si>
-    <t>Mount Everest -Wikipedia</t>
-  </si>
-  <si>
-    <t>Mountains (U.S.National Park Service)</t>
-  </si>
-  <si>
-    <t>MOUNTAIN| English meaning - Cambridge Dictionary</t>
+    <t>Mountain: what they are, how they are formed and more</t>
   </si>
   <si>
     <t>Disaster-Wikipedia</t>
   </si>
   <si>
+    <t>disaster是什么意思_disaster的翻译_音标_读音_用法_例句_爱词霸在 …</t>
+  </si>
+  <si>
+    <t>DISASTER中文 (简体)翻译：剑桥词典 - Cambridge Dictionary</t>
+  </si>
+  <si>
+    <t>disaster（英语单词）_百度百科</t>
+  </si>
+  <si>
+    <t>disaster- 搜索 词典</t>
+  </si>
+  <si>
+    <t>Disasters - Wiley Online Library</t>
+  </si>
+  <si>
+    <t>Definition:Disaster| UNDRR</t>
+  </si>
+  <si>
+    <t>Free Humanitarian Training | DisasterReady</t>
+  </si>
+  <si>
     <t>Disaster| Definition &amp; Types | Britannica</t>
   </si>
   <si>
-    <t>Disaster Information-FEMA.gov</t>
-  </si>
-  <si>
-    <t>Home | disasterassistance.gov</t>
-  </si>
-  <si>
-    <t>DISASTERDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>Definition:Disaster| UNDRR</t>
-  </si>
-  <si>
-    <t>Naturaldisaster| Causes, Types, &amp; Facts | Britannica</t>
-  </si>
-  <si>
-    <t>Home |FEMA.gov</t>
-  </si>
-  <si>
-    <t>What is adisaster? - IFRC</t>
-  </si>
-  <si>
-    <t>DISASTER| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>Home - Members1st Community Credit Union</t>
-  </si>
-  <si>
-    <t>First Evangelical Free Church Boone|Boone IA- Facebook</t>
-  </si>
-  <si>
-    <t>FirstFreeBoone- Home</t>
-  </si>
-  <si>
-    <t>Locations &amp; Hours -Members1st Community Credit Union</t>
-  </si>
-  <si>
-    <t>Boone FirstUnited Methodist Church</t>
-  </si>
-  <si>
-    <t>FirstEvangelical Free ChurchBoone Boone IA</t>
-  </si>
-  <si>
-    <t>Members 1st Community Credit Union Boone,IA</t>
-  </si>
-  <si>
-    <t>First IowaDivision Ride Schedule</t>
-  </si>
-  <si>
-    <t>Home Page -First IowaTitle Corporation</t>
-  </si>
-  <si>
-    <t>First Baptist Church of Boone|Boone IA- Facebook</t>
-  </si>
-  <si>
-    <t>Emergency Medical Services (EMS) - City ofSan Antonio</t>
-  </si>
-  <si>
-    <t>Home - ShurMed EMS -San Antonio,Texas</t>
-  </si>
-  <si>
-    <t>AmbulanceService inSan Antonio,Texas| Medical Transportation …</t>
-  </si>
-  <si>
-    <t>Ambulance Services in San Antonio,TX- The Real Yellow Pages</t>
+    <t>Natural disaster-Wikipedia</t>
+  </si>
+  <si>
+    <t>Personal Banking, Credit Cards &amp; Loans |FirstCitizens Bank</t>
+  </si>
+  <si>
+    <t>FIRSTDefinition &amp; Meaning - Merriam-Webster</t>
+  </si>
+  <si>
+    <t>FIRST| For Inspiration and Recognition of Science and Technology</t>
+  </si>
+  <si>
+    <t>FirstSF - HOME</t>
+  </si>
+  <si>
+    <t>FIRST| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
+    <t>San FranciscoBranch |CAPersonal Loans &amp; IRAs |FirstBank</t>
+  </si>
+  <si>
+    <t>FIRST| definition in the Cambridge English Dictionary</t>
+  </si>
+  <si>
+    <t>San Francisco- Wikipedia</t>
+  </si>
+  <si>
+    <t>FIRST- Improving Security Together</t>
+  </si>
+  <si>
+    <t>first- Wiktionary, the free dictionary</t>
   </si>
   <si>
     <t>Ambulance- Wikipedia</t>
   </si>
   <si>
-    <t>Services – CityAmbulance</t>
-  </si>
-  <si>
-    <t>Lone Star Ambulance, Inc|San Antonio TX- Facebook</t>
-  </si>
-  <si>
-    <t>Texas-Acadian Ambulance Service</t>
-  </si>
-  <si>
-    <t>AcadianAmbulanceService | Medical Transport When You Need It</t>
-  </si>
-  <si>
-    <t>EMS Billing- City ofSan Antonio</t>
+    <t>Ambulance Services in Simi Valley,CA- The Real Yellow Pages</t>
+  </si>
+  <si>
+    <t>AMR - EMS &amp;AmbulanceCare</t>
+  </si>
+  <si>
+    <t>Emergency Services -City of Simi Valley,CA</t>
+  </si>
+  <si>
+    <t>AmbulanceServices inSimi Valley,CA- superpages.com</t>
+  </si>
+  <si>
+    <t>TOP 10 BESTAmbulanceService inSimi Valley,CA- (2026 Guide</t>
+  </si>
+  <si>
+    <t>AMR - AMR/Gold Coast - Moorpark,California</t>
+  </si>
+  <si>
+    <t>TOP 10 BESTAmbulanceinSimi Valley,CA- Yelp</t>
+  </si>
+  <si>
+    <t>Emergency medical services- Wikipedia</t>
+  </si>
+  <si>
+    <t>ICS PARAMEDIC/EMT STANDBYAMBULANCESERVICE |SIMI VALLEY,CA…</t>
   </si>
   <si>
     <t>Google</t>
@@ -265,73 +265,43 @@
     <t>Yahoo</t>
   </si>
   <si>
+    <t>DuckDuckGo- Protection. Privacy. Peace of mind.</t>
+  </si>
+  <si>
     <t>PrivateSearchEngine - BraveSearch</t>
   </si>
   <si>
-    <t>DuckDuckGo- Protection. Privacy. Peace of mind.</t>
-  </si>
-  <si>
     <t>GoogleSearch</t>
   </si>
   <si>
-    <t>Records | Bexar County,TX- Official Website</t>
-  </si>
-  <si>
-    <t>Civil District Courts| Bexar County,TX- Official Website</t>
-  </si>
-  <si>
-    <t>Lone StarCivil- Top RatedSan AntonioGeneral Contractor</t>
-  </si>
-  <si>
-    <t>CivilEngineering Firm inSan Antonio,TX|CivilTech, PLLC</t>
-  </si>
-  <si>
-    <t>CivilEngineeringSan Antonio TX- Givler Engineering Inc.</t>
+    <t>CIVIL中文 (简体)翻译：剑桥词典</t>
+  </si>
+  <si>
+    <t>civil是什么意思_civil的翻译_音标_读音_用法_例句_爱词霸在线词典</t>
+  </si>
+  <si>
+    <t>civil（英文单词）_百度百科</t>
+  </si>
+  <si>
+    <t>AutodeskCivil3D 2025 - 获取价格和购买Civil3D 软件</t>
+  </si>
+  <si>
+    <t>CIVIL在剑桥英语词典中的解释及翻译 - Cambridge Dictionary</t>
   </si>
   <si>
     <t>CIVILDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>Civil Engineers in San Antonio, TX- The RealYellow Pages</t>
-  </si>
-  <si>
-    <t>Bachelor's Degree inCivilEngineering | UTSan Antonio</t>
-  </si>
-  <si>
-    <t>CivilEngineering Company inSan Antonio| Pape-Dawson</t>
-  </si>
-  <si>
-    <t>San Antonio, TX Civil Litigation Law Firms&amp; Lawyers</t>
-  </si>
-  <si>
-    <t>Crisis-Wikipedia</t>
-  </si>
-  <si>
-    <t>CRISISDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>CRISIS| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>Crisis| Social Sciences and Humanities | Research Starters - EBSCO</t>
-  </si>
-  <si>
-    <t>Crisis- definition ofcrisisby The Free Dictionary</t>
-  </si>
-  <si>
-    <t>Crisis (2021 film) -Wikipedia</t>
-  </si>
-  <si>
-    <t>Crisis- Simple EnglishWikipedia, the free encyclopedia</t>
-  </si>
-  <si>
-    <t>The Different Types ofCrisis- Verywell Mind</t>
-  </si>
-  <si>
-    <t>CRISISDefinition &amp; Meaning |Dictionary.com</t>
-  </si>
-  <si>
-    <t>CRISIS| definition in the Cambridge English Dictionary</t>
+    <t>Civil engineering-Wikipedia</t>
+  </si>
+  <si>
+    <t>civil engineering为什么翻译为「土木工程」？ - 知乎</t>
+  </si>
+  <si>
+    <t>CIVIL释义 | 柯林斯英语词典</t>
+  </si>
+  <si>
+    <t>Download &amp; Buy OfficialCivil3D Software -Autodesk</t>
   </si>
   <si>
     <t>Emergency &amp; Rescue</t>
@@ -340,298 +310,268 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0928add8b3627988d92181cb01d875cdb533c9e1eac6388965f9863eb7506560JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ced471c-8aa1-6e85-124b-50fd8b246f78&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmlyZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=82d3eb2160d0c6848359ddbb2b7023a39c8b3caafed55e1ef61955431a0ebff9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ced471c-8aa1-6e85-124b-50fd8b246f78&amp;u=a1aHR0cHM6Ly9maXJlLmFpcm5vdy5nb3YvP2xhbmc9ZW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=41924e23fb25bb59853e8ed2b921d2e95c8d9fd433fc98b047e19affc3a4fe5dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ced471c-8aa1-6e85-124b-50fd8b246f78&amp;u=a1aHR0cHM6Ly93aWxkZmlyZXRyYWNrZXJzLmNvbS9mL21hcA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=66f9355a79bc10dcba68bb3fdaf0d70fbdce7386addffd9bcd79b4110fac62acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ced471c-8aa1-6e85-124b-50fd8b246f78&amp;u=a1aHR0cHM6Ly93d3cuZmlyZS5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=84d7a7b8da2b955e6786db3c9938c9c9b19a925c5947c98a01628fec4df81d1dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ced471c-8aa1-6e85-124b-50fd8b246f78&amp;u=a1aHR0cHM6Ly93d3cuZmlyZWZveC5jb20vZW4tVVMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6ba04c448a69d0cca56b8785e3abd5b36acca7f54dd6e5c58b42d646c0bab4dbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ced471c-8aa1-6e85-124b-50fd8b246f78&amp;u=a1aHR0cHM6Ly93d3cuZmlyZW1hcC5saXZlLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b1519143eebcd033d63e8c8cc164ca779d645e0ef08a6f52408dee04f081a904JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ced471c-8aa1-6e85-124b-50fd8b246f78&amp;u=a1aHR0cHM6Ly93d3cubmlmYy5nb3YvZmlyZS1pbmZvcm1hdGlvbi9tYXBz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=423cd3a6e7f635ccf45ea40bb45fbd26786333d573048b87d366216093d756c2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ced471c-8aa1-6e85-124b-50fd8b246f78&amp;u=a1aHR0cHM6Ly9hbGxmaXJlZmlnaHRlci5jb20vd2lsZGZpcmVzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bc124fe0171e48332b134048cb4880b3c345ea7b64328ab7881cf48689665b57JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ced471c-8aa1-6e85-124b-50fd8b246f78&amp;u=a1aHR0cHM6Ly93d3cubmlmYy5nb3YvZmlyZS1pbmZvcm1hdGlvbi9uZm4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8e9c8fa02056ff2f1e8978ea1b808f5f5d4216de936bfc94050734bfdac0a024JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ced471c-8aa1-6e85-124b-50fd8b246f78&amp;u=a1aHR0cHM6Ly9maXJtcy5tb2RhcHMuZW9zZGlzLm5hc2EuZ292L21hcC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=97c39c4d2fb62eafed08ab7975ecc6f6e6c1c5d7013b33a5bf594c63061ebe64JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2021de57-36ae-640c-018c-c9b637fc65e8&amp;u=a1aHR0cHM6Ly9hbWJsZXNpZGVvbmxpbmUub3JnL2hlbHA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b74f11bd087f61ef7f71bd0a064dedae7c72a79bff902834c74183943ab9dc06JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2021de57-36ae-640c-018c-c9b637fc65e8&amp;u=a1aHR0cHM6Ly9hbWJsZXNpZGVvbmxpbmUub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=559f78f56ae90be4e789160e13633508bbe7bd8763a5409b7955d6928d3d1252JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2021de57-36ae-640c-018c-c9b637fc65e8&amp;u=a1aHR0cHM6Ly9hbWJsZXNpZGVvbmxpbmUub3JnL2FvLXkxMC1zY2g&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c58e69719dc6499346e74ccc623964676ed1df226a10021e1515fb0742b5a719JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2021de57-36ae-640c-018c-c9b637fc65e8&amp;u=a1aHR0cHM6Ly9hbWJsZXNpZGVvbmxpbmUub3JnL3BsdXRhcmNoLWNyYXNzdXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=227ec30dc3b9c845593b75107f9e757cbbed53f85469e220521276ec1789407aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2021de57-36ae-640c-018c-c9b637fc65e8&amp;u=a1aHR0cHM6Ly9hbWJsZXNpZGVvbmxpbmUub3JnL3BsdXRhcmNoLWNvcmlvbGFudXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=535d862e18d26fbde20d2c9bb548124dddf785f1dc0a545a56f3e66cf022c40fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2021de57-36ae-640c-018c-c9b637fc65e8&amp;u=a1aHR0cHM6Ly9hbWJsZXNpZGVvbmxpbmUub3JnL3BsdXRhcmNoLWJydXR1cy9jbS9mb3J1bS9mb3J1bS9mb3J1bS9wbHV0YXJjaC1jb3Jpb2xhbnVzLXRleHQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b4a085a0417ab9681a2889b8cfc7be859807dca878d431c3b38166a1f20716c0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2021de57-36ae-640c-018c-c9b637fc65e8&amp;u=a1aHR0cHM6Ly9hbWJsZXNpZGVvbmxpbmUub3JnL2ZvcnVtL3ByaW50dGhyZWFkLnBocD90aWQ9NjM3MDI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b034e930087be793336874a04a828646ce32acd3f923b572a3af6be2b598dbf8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2021de57-36ae-640c-018c-c9b637fc65e8&amp;u=a1aHR0cHM6Ly9hbWJsZXNpZGVvbmxpbmUub3JnL2FvLXkyLWJrcy9DTS9QYXJlbnRzUmV2aWV3L1BhcmVudHNSZXZpZXcvQ00vUGFyZW50c1Jldmlldy9hby15MzUtYmtz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5de82eea33c01376e0d30e2e2423d28321faf535ac237f53c89c5a8750e1d59aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2021de57-36ae-640c-018c-c9b637fc65e8&amp;u=a1aHR0cHM6Ly9hbWJsZXNpZGVvbmxpbmUub3JnL2dyb3Vwcy0xYS1leGFtLWI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b66b89b76f242c736e5e3f90b3e68a38a85e26d34200c323cdb686009d0789f5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2021de57-36ae-640c-018c-c9b637fc65e8&amp;u=a1aHR0cHM6Ly9hbWJsZXNpZGVvbmxpbmUub3JnL2FvLWcxYS1zY2g&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8345c3a0252456246fab467b9d200787a389e8cf8bc830b442036e8ccac644c0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311c6d60-4839-6533-3528-7a8149b664c7&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9TZWE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8b4bbcf6f36b2c0b3b3a17b925654d2eba78f06973c4eed7b829f59c1945486JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311c6d60-4839-6533-3528-7a8149b664c7&amp;u=a1aHR0cHM6Ly90aW1lc29maW5kaWEuaW5kaWF0aW1lcy5jb20vdHJhdmVsL2Rlc3RpbmF0aW9ucy9kby15b3Uta25vdy10aGUtZGlmZmVyZW5jZS1iZXR3ZWVuLW9jZWFuLXNlYS1iYXktYW5kLWd1bGYvYXJ0aWNsZXNob3cvMTEwOTY1MTM0LmNtcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b693e42cc1132e73b7fa22cae038ff38e8f4a01f99dbd6813cd6d5bb89137007JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311c6d60-4839-6533-3528-7a8149b664c7&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9MaXN0X29mX3NlYXNfb25fRWFydGg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef938bf9364cc4f066b1c47cd2e90d857c5cd2d4b53c7b37e02bbad00b414350JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311c6d60-4839-6533-3528-7a8149b664c7&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvU2Vh&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b6ecff8a5983fb194d94578c8d4952734ba432e5b05b834ff5396f402876159dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311c6d60-4839-6533-3528-7a8149b664c7&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9PY2Vhbi12cy1TZWEtV2hhdHMtdGhlLURpZmZlcmVuY2U&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=59412f60131571c53b9b2cd6cde6f75b306fadf401cca2df82ba30d9dc78be19JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311c6d60-4839-6533-3528-7a8149b664c7&amp;u=a1aHR0cHM6Ly9lZHVjYXRpb24ubmF0aW9uYWxnZW9ncmFwaGljLm9yZy9yZXNvdXJjZS9zZWEv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4e3836083d2ef5f2d53d0ab0ab6942215a3af69a8f677febf9b9bc06e115f93eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311c6d60-4839-6533-3528-7a8149b664c7&amp;u=a1aHR0cHM6Ly9zZWEuZWR1Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4f28bccb59ec9f1a45bcafc80ad92da0cb0df4bbfbfaa756f3dd8bb39c54c7c4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311c6d60-4839-6533-3528-7a8149b664c7&amp;u=a1aHR0cHM6Ly93d3cuc2VhLmNvbS9pbnZlc3Rvci9ob21l&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9815358b755eb59977bedf4dc8fae90021d67a4921b0abe4d15bbf201f28b43dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311c6d60-4839-6533-3528-7a8149b664c7&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NlYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d802ee67c81f07ebaa3e147b8f1a64bf29b5f004bc3eb8ffede26a7a967b2f86JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311c6d60-4839-6533-3528-7a8149b664c7&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9zZWE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b0b27de1afc711fd69c707b4b646324aad13901b4abd75ca5948f1323ece29cdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=239f22b5-641b-6d73-35d5-3554654b6cd1&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Nb3VudGFpbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c7424b8c55582bb01dd9ac46d1e3b858d453c8366f86223579805318328ab42dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=239f22b5-641b-6d73-35d5-3554654b6cd1&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9tb3VudGFpbi1sYW5kZm9ybQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47f3b8656e6d97c0cd6bf298f7687610a47fe220656cbcaaa4b47941d4389230JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=239f22b5-641b-6d73-35d5-3554654b6cd1&amp;u=a1aHR0cHM6Ly93d3cud29ybGRhdGxhcy5jb20vYXJ0aWNsZXMvd2hhdC1pcy1hLW1vdW50YWluLmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=415116e42334e1cda5fe870bf134bc58d98fba1fe7dfd217f13f8e04e37b2907JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=239f22b5-641b-6d73-35d5-3554654b6cd1&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L21vdW50YWlu&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0574f49c6b277c541db3e72d271353750565b6255e24064e602e1f809a5fa504JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=239f22b5-641b-6d73-35d5-3554654b6cd1&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvTW91bnRhaW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e5f29ef91c5b4223959a76a2ba5382e730e05ade62c27c1ac17ff714a09b68bfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=239f22b5-641b-6d73-35d5-3554654b6cd1&amp;u=a1aHR0cHM6Ly93d3cubmF0aW9uYWxnZW9ncmFwaGljLmNvbS9zY2llbmNlL2FydGljbGUvbW91bnRhaW5z&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5351b3613cfa01993b63b2442aa793279621fb06bf3322615e34663d31726696JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=239f22b5-641b-6d73-35d5-3554654b6cd1&amp;u=a1aHR0cHM6Ly9raWRzLm5hdGlvbmFsZ2VvZ3JhcGhpYy5jb20vbmF0dXJlL2hhYml0YXRzL2FydGljbGUvbW91bnRhaW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5e9364a5b3de7ee190930201a1bd861880986c22e2b4578e22599a7a3c6b984fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=239f22b5-641b-6d73-35d5-3554654b6cd1&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Nb3VudF9FdmVyZXN0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=32290fd4428808407577819f76f9470e8efbf3a739488c1f90e0fada038170f8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=239f22b5-641b-6d73-35d5-3554654b6cd1&amp;u=a1aHR0cHM6Ly93d3cubnBzLmdvdi9zdWJqZWN0cy9tb3VudGFpbnMvaW5kZXguaHRt&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4672a37fae19ad03e9da155770a428b1638c3908ded3250efda7bf7a30954b9cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=239f22b5-641b-6d73-35d5-3554654b6cd1&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL21vdW50YWlu&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cefb4859eebc736a7627c20555446d75ebd349df28680c9a5f9fbf78ab7fcae4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1604166e-dc96-67be-3412-018fdd176656&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRGlzYXN0ZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=92620ba50b0686a8e8e73a4f4d23c18f20d177ee2d238972c943a88d3fe88b85JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1604166e-dc96-67be-3412-018fdd176656&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9kaXNhc3Rlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=39634db30b3b9e0cc99daada9df6199496e2dcb70333fd12865118da8f0e813cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1604166e-dc96-67be-3412-018fdd176656&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3YvZGlzYXN0ZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=de01bd683462bc75b464980818faf7eb25d38611463fd107edf45130a36db82bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1604166e-dc96-67be-3412-018fdd176656&amp;u=a1aHR0cHM6Ly93d3cuZGlzYXN0ZXJhc3Npc3RhbmNlLmdvdi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f064831a48356153dd6d3c0e8325c44d9c385fe22d02df7eae4eda5c9a020f65JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1604166e-dc96-67be-3412-018fdd176656&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Rpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a6d8d90b5898e181470ec98a3f28c7719623be4694a9049927903c7d3caa9c8cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1604166e-dc96-67be-3412-018fdd176656&amp;u=a1aHR0cHM6Ly93d3cudW5kcnIub3JnL3Rlcm1pbm9sb2d5L2Rpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0acb260f32ddf30434de4cd9d46f5980085fae3fa0d14047ef83460627250225JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1604166e-dc96-67be-3412-018fdd176656&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9uYXR1cmFsLWRpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2b53cba4d1c29828075a2bede49beea6e1a8292b203ffc478f5927af46300eedJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1604166e-dc96-67be-3412-018fdd176656&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2b4a2b7a18a0d873cde131bddc9cd0bd5376295e1a075c418e249fdf07cf5d71JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1604166e-dc96-67be-3412-018fdd176656&amp;u=a1aHR0cHM6Ly93d3cuaWZyYy5vcmcvb3VyLXdvcmsvZGlzYXN0ZXJzLWNsaW1hdGUtYW5kLWNyaXNlcy93aGF0LWRpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=edbb126a465398df0c42c00fdfac475fc17522c836855713ce365caa45ef2b1cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1604166e-dc96-67be-3412-018fdd176656&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Rpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5e6dc28beb47901580f35d498f146fddf12723cca592b5c315f9a2f2d691d84eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba4eab2-cab4-6de3-0b14-fd53cba76c35&amp;u=a1aHR0cHM6Ly93d3cubWVtYmVyczFzdC5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c2cbe26a4b39ccf7742870cb9836bda4b52b53b1af5235e844ead167c87099cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba4eab2-cab4-6de3-0b14-fd53cba76c35&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL2Jvb25lZWZyZWUv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=96406b5dfccb2320d4e9d6aa467e8668af56fe310ffb543d9e73c1fc0624f1dfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba4eab2-cab4-6de3-0b14-fd53cba76c35&amp;u=a1aHR0cHM6Ly9maXJzdGJvb25lLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0b5251a852f71e9dcd0b103286b2431d76ffa60d28b06a9a8ce807faa67f392eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba4eab2-cab4-6de3-0b14-fd53cba76c35&amp;u=a1aHR0cHM6Ly93d3cubWVtYmVyczFzdC5jb20vbG9jYXRpb25zLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=91638d4f5032c2dd6ed97defb76e9bba3e65dce1ab28ae53e093e3ee22378b14JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba4eab2-cab4-6de3-0b14-fd53cba76c35&amp;u=a1aHR0cHM6Ly93d3cuYm9vbmVmdW1jLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7691f108378244575a4cbc1de0321089f7b000755715b0714694fa1a644664abJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba4eab2-cab4-6de3-0b14-fd53cba76c35&amp;u=a1aHR0cHM6Ly93d3cuam9pbm15Y2h1cmNoLmNvbS9jaHVyY2hlcy9GaXJzdC1FdmFuZ2VsaWNhbC1GcmVlLUNodXJjaC1Cb29uZS1Cb29uZS1Jb3dhLVVuaXRlZC1TdGF0ZXMvMTc4Nzg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=43df38c9a0c24149f4e3128e2447388e3305f013d2f198d5eb2c8ec183fdd3cfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba4eab2-cab4-6de3-0b14-fd53cba76c35&amp;u=a1aHR0cHM6Ly93d3cuY3JlZGl0dW5pb25zb25saW5lLmNvbS9jcmVkaXQtdW5pb24tNjcwMC0yNTQ5NC5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=252c0a1537a9ef348cf3b172ad15b0ec1176a8039027a84fe76aa9e670eb3a1bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba4eab2-cab4-6de3-0b14-fd53cba76c35&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3Rpb3dhZGl2aXNpb24uY29tL3JpZGUtc2NoZWR1bGUuYXNw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=95c5bdb5beda6a256aa01328c0c5e44478c9a60636cfaf3dc87da34de03658caJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba4eab2-cab4-6de3-0b14-fd53cba76c35&amp;u=a1aHR0cHM6Ly9maXJzdGlvd2F0aXRsZS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=390f157ab8a0b9dde9f4f830e123dc7a8ac6c46d8f2161f4271fa03ecbe546b7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ba4eab2-cab4-6de3-0b14-fd53cba76c35&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL2ZpcnN0YmFwdGlzdGJvb25lLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3b0e16229bbdc918a9e323e806ac288d45076c5a29e36eb9878986946fb2abffJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ea78fbc-e470-60c8-21d5-985de5c16100&amp;u=a1aHR0cHM6Ly93d3cuc2EuZ292L0RpcmVjdG9yeS9EZXBhcnRtZW50cy9TQUZEL0Fib3V0L0RpdmlzaW9ucy9FTVM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11bfddabb2eb10f41fdaffdcdb022d8604c832036ff104669b885ab8e05fb987JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ea78fbc-e470-60c8-21d5-985de5c16100&amp;u=a1aHR0cHM6Ly93d3cuc2h1cm1lZC5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ff06caaa146098e60ee7a8550d9acd90c30e7d08adff9397a6e0d5d9ad03af8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ea78fbc-e470-60c8-21d5-985de5c16100&amp;u=a1aHR0cHM6Ly9sb25lc3RhcmFtYnVsYW5jZS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7fc6521fc9c37d6f5e48f6180f249e14dc568aa6e9b3f67d6640882d0cd7ced8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ea78fbc-e470-60c8-21d5-985de5c16100&amp;u=a1aHR0cHM6Ly93d3cueWVsbG93cGFnZXMuY29tL3Nhbi1hbnRvbmlvLXR4L2FtYnVsYW5jZS1zZXJ2aWNlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8accade3e82d2e26de342e133e28474df54a4b3707f4838940e2977d51d50dc3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ea78fbc-e470-60c8-21d5-985de5c16100&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9BbWJ1bGFuY2U&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dca694a5b4eb09111fe546a1af49fdb35a08e29e6d2fc9f1eb66a6326b767facJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ea78fbc-e470-60c8-21d5-985de5c16100&amp;u=a1aHR0cHM6Ly9jaXR5YW1idWxhbmNlLm5ldC9zZXJ2aWNlcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4db98bb6d9ff51e85227b96947c6396cb5f0afdcd3d2be6ac54633463d3cb583JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ea78fbc-e470-60c8-21d5-985de5c16100&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL2xvbnN0YXJlbXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87a0a6fbd5f13ca748958be6d54d6e688a973ef027ed2c762bd883329a1f69caJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ea78fbc-e470-60c8-21d5-985de5c16100&amp;u=a1aHR0cHM6Ly9hY2FkaWFuYW1idWxhbmNlLmNvbS9sb2NhdGlvbnMvdGV4YXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9b81d055a402d799a173069eda7107328fc7708a45f005853b41d612725a1e99JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ea78fbc-e470-60c8-21d5-985de5c16100&amp;u=a1aHR0cHM6Ly9hY2FkaWFuYW1idWxhbmNlLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c61a7d7c7582a191bffdf44be62f4e623525632a7f26768c81d0ad7e05be6529JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0ea78fbc-e470-60c8-21d5-985de5c16100&amp;u=a1aHR0cHM6Ly93d3cuc2EuZ292L0RpcmVjdG9yeS9EZXBhcnRtZW50cy9TQUZEL1JlcG9ydHMtQmlsbGluZy9FTVMtUmVwb3J0cy9FTVMtQmlsbGluZw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f6f687345b256aee73038f60ee30aca4904bec61895e4d5fc08b9bb1e89f3886JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0caf237f-6238-63cc-0dd5-349e63e162b8&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS8&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6119c8133bc7757ef302f04cf3ac91c18176b529981f0e239c96edc673e9c506JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ff304ab-99b5-656b-0f45-134a980c6433&amp;u=a1aHR0cHM6Ly93d3cuZmlyZS5jYS5nb3YvaW5jaWRlbnRzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=912c5ec0ddc0117708835f14df0bc8da54bd5f53451b8b5eed86c8fa4a61bfe0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ff304ab-99b5-656b-0f45-134a980c6433&amp;u=a1aHR0cHM6Ly93d3cuY2FmaXJlLm9yZy9kYXNoYm9hcmQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e2862d54bda234f68796a64fb40eeba94d48d8b58dde81fe07960dd5175f1c13JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ff304ab-99b5-656b-0f45-134a980c6433&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmlyZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=14d539d510555fc34ba475032881eca4db71dad5285a4e345f54b8928e046e3fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ff304ab-99b5-656b-0f45-134a980c6433&amp;u=a1aHR0cHM6Ly9hcHAud2F0Y2hkdXR5Lm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dd74768f5a5f9ee46f493396fa85959b6c357bc8926cb23fa19c59d01a826a26JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ff304ab-99b5-656b-0f45-134a980c6433&amp;u=a1aHR0cHM6Ly93aWxkZmlyZXRyYWNrZXJzLmNvbS9mL21hcA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=498cd5f30b97534ed9a7023bf88c8003edcbd576a1bf5c497e05b29537e2f7d7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ff304ab-99b5-656b-0f45-134a980c6433&amp;u=a1aHR0cHM6Ly93d3cuZmlyZWZveC5jb20vZW4tVVMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e69e4aa074680a76e427f687953ada5ae8f80d071109f1624f5725720933d480JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ff304ab-99b5-656b-0f45-134a980c6433&amp;u=a1aHR0cHM6Ly93d3cuZmlyZS5jYS5nb3YvaW5jaWRlbnRzLzIwMjYvOS8yMy9ncmFkZS1maXJlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b8d032c39f49dcbecc85bba72cbd66906379748050bc4f51e5146c422f6140e1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ff304ab-99b5-656b-0f45-134a980c6433&amp;u=a1aHR0cHM6Ly9maXJlLmFpcm5vdy5nb3YvP2xhbmc9ZW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f6a837465a7ddaddf58e09a2b51ad07761081d6ae30a601be8654d4298ea044dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ff304ab-99b5-656b-0f45-134a980c6433&amp;u=a1aHR0cHM6Ly93ZmNhLmNvbS9maXJlLW1hcC9jYWxpZm9ybmlh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9b3dcf201c529a4b24a98f2d22c679617156fa77ab8ff4d24a387cfc3f79b34cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ff304ab-99b5-656b-0f45-134a980c6433&amp;u=a1aHR0cHM6Ly93d3cuZmlyZW1hcC5saXZlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=872428884e76def34be032e6840c80df1a9cd539128b99d5e8c1da6bd13cf950JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ac67cac-73f3-680e-0730-6b4d722f69e3&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQwMDY4MDY3Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a8f6e12d1bedc54a4eb606fbc9689bff05ac57732df0d6f4b1443816720e4c19JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ac67cac-73f3-680e-0730-6b4d722f69e3&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5IQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=159eff938201f88885397bc8712b86c767b2eae40a98e04f730aeea529c67873JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ac67cac-73f3-680e-0730-6b4d722f69e3&amp;u=a1aHR0cHM6Ly9sYWNvdW50eS5nb3YvZW1lcmdlbmN5Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f55856c22f29e5b33b071db322feb050dc64bb3f54255e92ff0e49efbb8f75daJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ac67cac-73f3-680e-0730-6b4d722f69e3&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fdcb278442f0505a6dd02a19034f926b3a12ca37e267fbade75c25815e9ae0a0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ac67cac-73f3-680e-0730-6b4d722f69e3&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VtZXJnZW5jeQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=07c27c76e42ef2cbcd83602ca21563b41a454cd6b55a697b6f224ce340c801faJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ac67cac-73f3-680e-0730-6b4d722f69e3&amp;u=a1aHR0cHM6Ly9lbWVyZ2VuY3kubGFjaXR5Lmdvdi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c05d4e3a36df0d2f4ac82144ef0990554926dc6ddd4271067abf5af938e7f50JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ac67cac-73f3-680e-0730-6b4d722f69e3&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1sQnJSQTVSQ1lUVQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=28ea7003a79444fa4a71e981c3f3213ff52a16443506a2f3474fd0ee0adaa844JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ac67cac-73f3-680e-0730-6b4d722f69e3&amp;u=a1aHR0cHM6Ly9kb3lvdXJlbWVtYmVyLmNvbS8xNTg1NjEvZW1lcmdlbmN5LWNhc3QtdGhlbi1ub3c&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=97f9bb427c248b6293cb86f942a83c911ab341e375c6297516b92c144792fffbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ac67cac-73f3-680e-0730-6b4d722f69e3&amp;u=a1aHR0cHM6Ly93d3cubGF0aW1lcy5jb20vY2FsaWZvcm5pYS9zdG9yeS8yMDI2LTA5LTIxL2dvdi1uZXdzb20tZGVjbGFyZXMtc3RhdGV3aWRlLWVtZXJnZW5jeS1lbC1uaW5vLXN0b3Jtcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bc7f0dfdd7740844b0592afa66b44f6f709a5b532b76f47c8bacb7da1e58e40fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ac67cac-73f3-680e-0730-6b4d722f69e3&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQwMDY4MDY3L2Z1bGxjcmVkaXRzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=549a472e653f3c2a0214e58dcf4260c533ccd75437a5822679dc98822a464437JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0352ac47-310e-6374-11b0-bba6305862d6&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9TZWE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=673c3b75411dbc8b534997c481781a0c22a4729cb4fa40080872d5714996f82fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0352ac47-310e-6374-11b0-bba6305862d6&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9PY2Vhbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aab4ac26afe565eeb35fa8b969c51372b2d5dd871e7055f9df761a1e00ef52bcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0352ac47-310e-6374-11b0-bba6305862d6&amp;u=a1aHR0cHM6Ly9lZHVjYXRpb24ubmF0aW9uYWxnZW9ncmFwaGljLm9yZy9yZXNvdXJjZS9zZWEv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7d11da2b1db4ab32a7ebda9d88e944e0739db8a39ac9f4498bc5136bb99c158eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0352ac47-310e-6374-11b0-bba6305862d6&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9PY2Vhbi12cy1TZWEtV2hhdHMtdGhlLURpZmZlcmVuY2U&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=db4e519320a2ff2491406727d7b41e46ddbd82ce43c9161a19c5231db718be0aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0352ac47-310e-6374-11b0-bba6305862d6&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvU2Vh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0dda9bbe24afa5c920628b9c2bd809b651efe9e8e2b5f4efa00700c37b3e3d91JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0352ac47-310e-6374-11b0-bba6305862d6&amp;u=a1aHR0cHM6Ly93d3cuc2VhLmNvbS9pbnZlc3Rvci9ob21l&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9d48fce0a720084fece910584365e49ba30451a56d6b805fbb110c1700d21d58JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0352ac47-310e-6374-11b0-bba6305862d6&amp;u=a1aHR0cHM6Ly93d3cuc2VhLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=035434013256ac0467a7f84a32793697c61ebaed49f261c83108014440a076e0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0352ac47-310e-6374-11b0-bba6305862d6&amp;u=a1aHR0cHM6Ly9zZWEuZWR1Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d2348509b28b327a5260f7b0e512f63085b9e0084ef13493dc3c2a79ff861b0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0352ac47-310e-6374-11b0-bba6305862d6&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NlYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1a67ee8737c26f03e36c1726a087ddb1b8dccb40e867238f218605ea3340cc11JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0352ac47-310e-6374-11b0-bba6305862d6&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9zZWE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2d4ceaf780e0cca27def7756aadbc78797262f651edee1b2a087f99e26d5fffcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=272493c4-5e14-643b-3d34-84255f266532&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTW91bnRhaW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=054c3a606d3fd83ac805a7ef0a1e6f5d45626b5543e5dfcd78f6a1dac127d0eeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=272493c4-5e14-643b-3d34-84255f266532&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9tb3VudGFpbi1sYW5kZm9ybQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fc5cbfe7e359ef25f0f8e0ae4a98343f28811c6460cb1466ef7f4e86f9557051JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=272493c4-5e14-643b-3d34-84255f266532&amp;u=a1aHR0cHM6Ly93d3cuYXJpem9uYS1sZWlzdXJlLmNvbS9zdXBlcnN0aXRpb24tbW91bnRhaW4uaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8851948b9138961b27c152d3941b826c830244f58d994896ea1f9f1298e5b0fdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=272493c4-5e14-643b-3d34-84255f266532&amp;u=a1aHR0cHM6Ly93d3cudmlzaXRwaG9lbml4LmNvbS9zb25vcmFuLWRlc2VydC9wYXJrcy9zdXBlcnN0aXRpb24tbW91bnRhaW5zLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6958cf1a2601d804b72ceff6a211369fbddf92943c755b3b5c3601f54d1e15b3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=272493c4-5e14-643b-3d34-84255f266532&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU3VwZXJzdGl0aW9uX01vdW50YWlucw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=db2cf093d57436d142e89b5a95ace76e39754c516a9b8fcbbb33529b49955308JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=272493c4-5e14-643b-3d34-84255f266532&amp;u=a1aHR0cHM6Ly93d3cud29ybGRhdGxhcy5jb20vbW91bnRhaW5zLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=de263060921bd28c0c52c9e3960d585159a850355f6b8dff8ffec9e4b219b595JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=272493c4-5e14-643b-3d34-84255f266532&amp;u=a1aHR0cHM6Ly93d3cuYXJpem9uYS1sZWlzdXJlLmNvbS9hcGFjaGUtanVuY3Rpb24tYXJpem9uYS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=976d14cf7f2054f8501ae2b5472f05d70e9b7c2aac280b1ef6b2845dd4748a38JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=272493c4-5e14-643b-3d34-84255f266532&amp;u=a1aHR0cHM6Ly93d3cubmF0aW9uYWxnZW9ncmFwaGljLmNvbS9zY2llbmNlL2FydGljbGUvbW91bnRhaW5z&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a629f67b5b37214df53c84dc4d6f0fd5b38e4b5be631d3fc627b387c8322af3bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=272493c4-5e14-643b-3d34-84255f266532&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL01vdW50YWlu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=757e1c2114d3260991466b251479e60ce6b14cdc04106e1c864ee4b00dfae8aeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=272493c4-5e14-643b-3d34-84255f266532&amp;u=a1aHR0cHM6Ly9odW1hbmlkYWRlcy5jb20vZW4vbW91bnRhaW4v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7e7552c30315f9d1fd6a36c3e165be0e4c28ee8954604d99d19ac47d449c6343JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cf4bfb2-f001-6b78-00fc-a853f1906a3c&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRGlzYXN0ZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=74c27d4e401eec7ee15d6a3762845f1b8c6aebdbcdb3a0e4d82ed0dd93b9a5f8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cf4bfb2-f001-6b78-00fc-a853f1906a3c&amp;u=a1aHR0cHM6Ly93d3cuaWNpYmEuY29tL3dvcmQ_dz1kaXNhc3Rlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b2d4645b1c6513fff0a358bf2d6879695473ca223cd1151a2122a42037d35f13JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cf4bfb2-f001-6b78-00fc-a853f1906a3c&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvemhzLyVFOCVBRiU4RCVFNSU4NSVCOC8lRTglOEIlQjElRTglQUYlQUQtJUU2JUIxJTg5JUU4JUFGJUFELSVFNyVBRSU4MCVFNCVCRCU5My9kaXNhc3Rlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7df3d63702b064539fcd0a0dc8384d553aa31264d6ed18af567f37f45610ca70JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cf4bfb2-f001-6b78-00fc-a853f1906a3c&amp;u=a1aHR0cHM6Ly9iYWlrZS5iYWlkdS5jb20vaXRlbS9kaXNhc3Rlci8xMDIxMzIxOQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c46a994a40350635f4fe214bcb2065f502fee9118b8ed5c4cba43de3786d0f85JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cf4bfb2-f001-6b78-00fc-a853f1906a3c&amp;u=a1aHR0cHM6Ly9nbG9iYWwuYmluZy5jb20vZGljdC9zZWFyY2g_cT1kaXNhc3RlciZGT1JNPUJEVlNQNiZjYz1jbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2a73a3fbee2ddf8dca61f7b1429976bb912f1eb87cf4994d23eee69194e6fc9fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cf4bfb2-f001-6b78-00fc-a853f1906a3c&amp;u=a1aHR0cHM6Ly9vbmxpbmVsaWJyYXJ5LndpbGV5LmNvbS9qb3VybmFsLzE0Njc3NzE3P21zb2NraWQ9M2NmNGJmYjJmMDAxNmI3ODAwZmNhODUzZjE5MDZhM2M&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ff7ec0a694e97d1475ac58f40b4dae83d1f6010fc87eea21154818c2a228a0fbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cf4bfb2-f001-6b78-00fc-a853f1906a3c&amp;u=a1aHR0cHM6Ly93d3cudW5kcnIub3JnL3Rlcm1pbm9sb2d5L2Rpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2ce113936a04c7669ebd932a00940a831c5ffcd9f8b40c1b144ce03c5dafa858JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cf4bfb2-f001-6b78-00fc-a853f1906a3c&amp;u=a1aHR0cHM6Ly93d3cuZGlzYXN0ZXJyZWFkeS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=45c19c527874b007ff39b4919d9131d61b85f4e12d96cc8fb038d67ab89af45aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cf4bfb2-f001-6b78-00fc-a853f1906a3c&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9kaXNhc3Rlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=60c8879d22ba4b621904298dc44f2590bf5a8c1b3805bfcf6554026308652101JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cf4bfb2-f001-6b78-00fc-a853f1906a3c&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTmF0dXJhbF9kaXNhc3Rlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=52eba785e67049073f94c158a51dcc3795028c48f9638f91fa084db3ded1590bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f06dfb8-caa1-6d6b-3058-c859cb0a6c5a&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RjaXRpemVucy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6b80577c36f7ed9b855eebfe7b2c731aa14c511b94d80bfa59dc4d6b1283e05dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f06dfb8-caa1-6d6b-3058-c859cb0a6c5a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZpcnN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ef8a9010ed301d1989835dbb305e38c46ef786268c86e0a45abd17295587842JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f06dfb8-caa1-6d6b-3058-c859cb0a6c5a&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RpbnNwaXJlcy5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9888b6c4b0eebdb8d64e778609d1cc32191c37dc7459b3206ca42d926d5661eeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f06dfb8-caa1-6d6b-3058-c859cb0a6c5a&amp;u=a1aHR0cHM6Ly9maXJzdHNmLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=22ad921150a438ff562e0486b4b9853dc7fe9ccfe9722124c75489ca19629c1eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f06dfb8-caa1-6d6b-3058-c859cb0a6c5a&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZpcnN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7f21fe65acc81e3a2f6773605152d77d8a22a816c4052cc1280e06993a37c088JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f06dfb8-caa1-6d6b-3058-c859cb0a6c5a&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3QuYmFuay9BYm91dC9Mb2NhdGlvbnMvU2FuLUZyYW5jaXNjby1NYWlu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=77e2ab06b3396517d6efe2f9e11f13de20b4a7e6906a883fb130967671f996cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f06dfb8-caa1-6d6b-3058-c859cb0a6c5a&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2ZpcnN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=52c338456fc023e25a04f309856da729f1f4d71f029b21ac076784bbfdd9dd00JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f06dfb8-caa1-6d6b-3058-c859cb0a6c5a&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU2FuX2ZyYW5jaXNjbw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2928b37dd11dd107f2d9793b17dea67dda06dae7f4a97f01ffce0fe97dbeb721JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f06dfb8-caa1-6d6b-3058-c859cb0a6c5a&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3Qub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=86e7dce64fbd5773e824a189ae09454d89ef7484a91bba55a9181fda37136b03JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f06dfb8-caa1-6d6b-3058-c859cb0a6c5a&amp;u=a1aHR0cHM6Ly9lbi53aWt0aW9uYXJ5Lm9yZy93aWtpL2ZpcnN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a1457fb7148a97f45a6e083f35e4293212ce49ad5e2643fd14c1dc849692fff2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=062bde27-8090-65da-19e3-c9c6819e64ae&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQW1idWxhbmNl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=85766f9ad2bf6beba087234b14e3a223c1e99bea342b7412a587013ba16a26d2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=062bde27-8090-65da-19e3-c9c6819e64ae&amp;u=a1aHR0cHM6Ly93d3cueWVsbG93cGFnZXMuY29tL3NpbWktdmFsbGV5LWNhL2FtYnVsYW5jZS1zZXJ2aWNlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9da7814c013a874bb20a48422d7099c4ecb985d9de2c3ab6e375f8ee70071e49JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=062bde27-8090-65da-19e3-c9c6819e64ae&amp;u=a1aHR0cHM6Ly93d3cuYW1yLm5ldC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ca70edb74c770ee26a925207fb00e6e17ac639a88fcc2f6e1cd9719675f76fc4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=062bde27-8090-65da-19e3-c9c6819e64ae&amp;u=a1aHR0cHM6Ly93d3cuc2ltaXZhbGxleS5vcmcvZGVwYXJ0bWVudHMvcG9saWNlLWRlcGFydG1lbnQvZW1lcmdlbmN5LXNlcnZpY2Vz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a7c1a5ac11c85bfdfbca8ac36767d9cac20c15e31355a4a86656db846e2c1834JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=062bde27-8090-65da-19e3-c9c6819e64ae&amp;u=a1aHR0cHM6Ly93d3cuc3VwZXJwYWdlcy5jb20vc2ltaS12YWxsZXktY2EvYW1idWxhbmNlLXNlcnZpY2Vz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0348c7cb690cb512a082c5ab24dd151526c80429bf766ab586256a8acc2dfc70JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=062bde27-8090-65da-19e3-c9c6819e64ae&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2ZpbmRfZGVzYz1BbWJ1bGFuY2UrU2VydmljZSZmaW5kX2xvYz1TaW1pK1ZhbGxleSUyQytDQSZtc29ja2lkPTA2MmJkZTI3ODA5MDY1ZGExOWUzYzljNjgxOWU2NGFl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c13414910db2c9cab66843e1046833aa17c7ada348cd4aded9e7bd536a052b0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=062bde27-8090-65da-19e3-c9c6819e64ae&amp;u=a1aHR0cHM6Ly93d3cuYW1yLm5ldC9sb2NhdGlvbnMvY2FsaWZvcm5pYS92ZW50dXJhLWNvdW50eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b36c5a05db062f0f517a5e25af9e5b348291e4d7f5fd7b9d6fdd3497576d1c79JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=062bde27-8090-65da-19e3-c9c6819e64ae&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2ZpbmRfZGVzYz1BbWJ1bGFuY2UmZmluZF9sb2M9U2ltaStWYWxsZXklMkMrQ0EmbXNvY2tpZD0wNjJiZGUyNzgwOTA2NWRhMTllM2M5YzY4MTllNjRhZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dc925226fe77ae33c9ab7009401e7947bd6eb577dbc8d59284d4e1ee43193100JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=062bde27-8090-65da-19e3-c9c6819e64ae&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5X21lZGljYWxfc2VydmljZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4695372faeed54b23ca44d9b95e7f8599939cd9c8c9f06acf822c456230c5a49JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=062bde27-8090-65da-19e3-c9c6819e64ae&amp;u=a1aHR0cDovL3d3dy5pY3NzZXJ2aWNlc3N0YW5kYnlhbWJ1bGFuY2UuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ff5279873f8c15c8fc76f545ad0bf845a395e0a9df9fc9c26543088e9441897bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b80472-6838-61ca-336f-1393699c606b&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS94aHRtbC9zZWFyY2g&amp;ntb=1</t>
   </si>
   <si>
     <t>https://www.bing.com/</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bab48ba6b93c2a705bf1a9ff884f30adccf951e0ee77ef69a694f9b4ac911feeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0caf237f-6238-63cc-0dd5-349e63e162b8&amp;u=a1aHR0cHM6Ly9zZWFyY2gueWFob28uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=84a025810965d8b2279fbcb1877b7f3dcb89d0de9622d77636c86fe0ee044202JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0caf237f-6238-63cc-0dd5-349e63e162b8&amp;u=a1aHR0cHM6Ly9zZWFyY2guZ29vZ2xlLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=af108023367f056aa23b90b11730feb2f6fc396e3ac84f19e4cf64ed789cf5b4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0caf237f-6238-63cc-0dd5-349e63e162b8&amp;u=a1aHR0cHM6Ly93d3cueWFob28uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=83547c33fba041a908dd0923b1de8e908716e6c17a4ce4f0b8f194f531193defJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0caf237f-6238-63cc-0dd5-349e63e162b8&amp;u=a1aHR0cHM6Ly9zZWFyY2guYnJhdmUuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7a0320a2b0f4e6a193ed43eb0fae8c5ad3ddeafe0d0cf5b96769f3080ae0451dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0caf237f-6238-63cc-0dd5-349e63e162b8&amp;u=a1aHR0cHM6Ly9kdWNrZHVja2dvLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=23d894d4f9e84f1fcc84e3f8a14b5ffcc4e14474acb9f6a6ee4703b06763c35eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0caf237f-6238-63cc-0dd5-349e63e162b8&amp;u=a1aHR0cHM6Ly9hY2NvdW50cy5nb29nbGUuY29tL0ludGVyYWN0aXZlTG9naW4_c2VydmljZT1zYWZlc2VhcmNobG9jaw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=107c0dfc4a3b6538f1a33addeecb6fb267794bef48f32d80d8bbad134ebae957JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f9b1eac-52b4-6867-2ab2-094d539169d1&amp;u=a1aHR0cHM6Ly93d3cuYmV4YXIub3JnLzM3MDMvUmVjb3Jkcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a8d1e35ac28cf5e6bb1dbe7a5e80a48e60b944a9ca5c1f954aa8f7980744f45cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f9b1eac-52b4-6867-2ab2-094d539169d1&amp;u=a1aHR0cHM6Ly93d3cuYmV4YXIub3JnLzE3MDMvQ2l2aWwtRGlzdHJpY3QtQ291cnRz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5cddcd4c521f22c1e15296dc0499135bfc00b45f2143c15f5f9cce0852ef92beJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f9b1eac-52b4-6867-2ab2-094d539169d1&amp;u=a1aHR0cHM6Ly93d3cubG9uZXN0YXJjaXZpbC5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a0a77b3d13a2d854ca5b6b8890ba9b141645ba93b1a46d0683f9eb152fc2b1a4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f9b1eac-52b4-6867-2ab2-094d539169d1&amp;u=a1aHR0cHM6Ly9jaXZpbHRlY2htYy5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7ea114394c5e918ab241bd599e75352e24521dc9ab84fa5e022fa4aefd2886e8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f9b1eac-52b4-6867-2ab2-094d539169d1&amp;u=a1aHR0cHM6Ly9naXZsZXJlbmdpbmVlcmluZy5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9a8ec54a199eed2723e09f342b1074a47f7001dddabd7dd828985d4ca021e13fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f9b1eac-52b4-6867-2ab2-094d539169d1&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Npdmls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=142966c0b2d1356771fbc36fb8192f4540920b15168bff2ae2c50fcaffdaafc3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f9b1eac-52b4-6867-2ab2-094d539169d1&amp;u=a1aHR0cHM6Ly93d3cueWVsbG93cGFnZXMuY29tL3Nhbi1hbnRvbmlvLXR4L2NpdmlsLWVuZ2luZWVycw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2ac35c3fde1f29a39e5942975b37626359e933c9c8f2003bb3e8889ee926b8efJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f9b1eac-52b4-6867-2ab2-094d539169d1&amp;u=a1aHR0cHM6Ly9mdXR1cmUudXRzYS5lZHUvcHJvZ3JhbXMvdW5kZXJncmFkdWF0ZS9jaXZpbC1lbmdpbmVlcmluZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb8f14c1e28ce3d0afcee82e7ce915e3581b54062ff6a351100d69e5362e5dd8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f9b1eac-52b4-6867-2ab2-094d539169d1&amp;u=a1aHR0cHM6Ly93d3cucGFwZS1kYXdzb24uY29tL2xvY2F0aW9ucy9zYW4tYW50b25pby8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c371f0cb3d867fae7de40143ed778a8ff8044f710ed58f56a0aa2e82c4a63676JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f9b1eac-52b4-6867-2ab2-094d539169d1&amp;u=a1aHR0cHM6Ly93d3cubGF3eWVycy5jb20vY2l2aWwtbGl0aWdhdGlvbi9zYW4tYW50b25pby90ZXhhcy9sYXctZmlybXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6b60c770ebd60296b668e32553de99f5df47589dbba1147d604b7981bfb261e9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13622ff1-24ea-60ca-1055-3810255a617b&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ3Jpc2lz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3a06c938f1c36585b198a8c9e96054e69b6db008803051f9a43b2ff6821dea58JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13622ff1-24ea-60ca-1055-3810255a617b&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NyaXNpcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d7e0a500de6fe780a30c40d2c446da5cffc98d7309104b4312255cd728ba320JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13622ff1-24ea-60ca-1055-3810255a617b&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2NyaXNpcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=72a5856e4ab875a9107756a499a14b2a05eb90a4e9e73706029a76cfdeb4445bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13622ff1-24ea-60ca-1055-3810255a617b&amp;u=a1aHR0cHM6Ly93d3cuZWJzY28uY29tL3Jlc2VhcmNoLXN0YXJ0ZXJzL3NvY2lhbC1zY2llbmNlcy1hbmQtaHVtYW5pdGllcy9jcmlzaXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=14bdae799a208a621f0d6f9a6ce19e5458c17880aa1fe282713e6a9801166416JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13622ff1-24ea-60ca-1055-3810255a617b&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2NyaXNpcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3eca0674c4a58654547eabfeeafc6fadd85b3bbe736da3e2e24a77f5583f1edcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13622ff1-24ea-60ca-1055-3810255a617b&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ3Jpc2lzXygyMDIxX2ZpbG0p&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=97f1a14ba24beddd348ded19c10b14ff307a2a1b01b966b26f14d6713dfcc9f0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13622ff1-24ea-60ca-1055-3810255a617b&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL0NyaXNpcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=65cfb77392ba86c6fae357dc2c4e9d103d28ea856bf38d97fb3ef3c7106ff006JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13622ff1-24ea-60ca-1055-3810255a617b&amp;u=a1aHR0cHM6Ly93d3cudmVyeXdlbGxtaW5kLmNvbS93aGF0LWlzLWEtY3Jpc2lzLTI3OTUwNjE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e37aeae163a438d9bc7c23dc0b82da21a7c7a151e162837382b34d84db17fed6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13622ff1-24ea-60ca-1055-3810255a617b&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2NyaXNpcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=96b9d51899b9596c1db5b43b40c490336c2e0e8b3e539091212186b887ce571dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=13622ff1-24ea-60ca-1055-3810255a617b&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2NyaXNpcw&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=33c024b7521d19b99f921e745f14d10e809d0999816a0d5e5fff6dd49839bc9bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b80472-6838-61ca-336f-1393699c606b&amp;u=a1aHR0cHM6Ly9zZWFyY2gueWFob28uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ce983f8e463e6c9f2c4fb9c53ec8baaba4a28278dc55a4e7f9eace45dc784845JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b80472-6838-61ca-336f-1393699c606b&amp;u=a1aHR0cHM6Ly9zZWFyY2guZ29vZ2xlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5f1d0f14e4c7670eb5b9fcadd7492e7847bee1c56b7effc5421032c62307a4adJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b80472-6838-61ca-336f-1393699c606b&amp;u=a1aHR0cHM6Ly93d3cueWFob28uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0a2c1d3345802a1bac6840be877be4744d66991bbc09d0dc3127570661194005JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b80472-6838-61ca-336f-1393699c606b&amp;u=a1aHR0cHM6Ly9kdWNrZHVja2dvLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=16ca9964ff5eaa9c58b6f3551f1041d0dd464883abc74d14aab390912122e95dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b80472-6838-61ca-336f-1393699c606b&amp;u=a1aHR0cHM6Ly9zZWFyY2guYnJhdmUuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4d65768e18b3874cddd79ea4061036740c8d0db0e606ab24d1cbd558dfee16e3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b80472-6838-61ca-336f-1393699c606b&amp;u=a1aHR0cHM6Ly9hY2NvdW50cy5nb29nbGUuY29tL0ludGVyYWN0aXZlTG9naW4_c2VydmljZT1zYWZlc2VhcmNobG9jaw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5c228b04b18f6b5db9afbd3fdc1bc580d0d4b1166164b23557455d588a6e0231JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32137556-54d8-64ce-1458-62b7559965d4&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvemhzLyVFOCVBRiU4RCVFNSU4NSVCOC8lRTglOEIlQjElRTglQUYlQUQtJUU2JUIxJTg5JUU4JUFGJUFELSVFNyVBRSU4MCVFNCVCRCU5My9jaXZpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2bf61fa3a2d40eb5dd0199a3847addc509a93f6c239cfbcfd07b157255cd4cb1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32137556-54d8-64ce-1458-62b7559965d4&amp;u=a1aHR0cHM6Ly93d3cuaWNpYmEuY29tL3dvcmQ_dz1jaXZpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=05e06e03044adca473e42a2c9c170af7e2955b1f4d351f8b5e439827503ccf49JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32137556-54d8-64ce-1458-62b7559965d4&amp;u=a1aHR0cHM6Ly9iYWlrZS5iYWlkdS5jb20vaXRlbS9DaXZpbC8zMTUzMzk0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dd1b6c64dd328893a0a8cd387c2fd12b25795b4ab32e19adbabf0b131c825834JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32137556-54d8-64ce-1458-62b7559965d4&amp;u=a1aHR0cHM6Ly93d3cuYXV0b2Rlc2suY29tLmNuL3Byb2R1Y3RzL2NpdmlsLTNkL292ZXJ2aWV3&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5fefa1c3bbad8bcbdc9d90072b60ed9fbabf279aa6eed49d4570acdb6e603803JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32137556-54d8-64ce-1458-62b7559965d4&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvemhzLyVFOCVBRiU4RCVFNSU4NSVCOC8lRTglOEIlQjElRTglQUYlQUQvY2l2aWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3e721aad81995c5174624116d0c885f2f09a2264c0ee7946e3839895561a9f55JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32137556-54d8-64ce-1458-62b7559965d4&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6a82da12c8f9728be223e6370ccd7a2a7b91f47814ebebcc89bf775bddeba4edJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32137556-54d8-64ce-1458-62b7559965d4&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9DaXZpbF9lbmdpbmVlcmluZw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=391fe2e8ec0cfa54ec447e3dee8844c12535fc702bcc08bbf2e32571c5d85a62JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32137556-54d8-64ce-1458-62b7559965d4&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzIzNTg2Mjg2&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f6ab48d99f9e00dc0aa03e3e888843c3b740ba0e7f539d486e6252cb2526f956JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32137556-54d8-64ce-1458-62b7559965d4&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL3poL2RpY3Rpb25hcnkvZW5nbGlzaC9jaXZpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3d15e72f9e4232d3c1e9b9e83e567116e48fb18747a949654976fee6ef0e5361JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32137556-54d8-64ce-1458-62b7559965d4&amp;u=a1aHR0cHM6Ly93d3cuYXV0b2Rlc2suY29tL3Byb2R1Y3RzL2NpdmlsLTNkL292ZXJ2aWV3P21zb2NraWQ9MzIxMzc1NTY1NGQ4NjRjZTE0NTg2MmI3NTU5OTY1ZDQ&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
@@ -982,7 +922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1016,19 +956,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="G2" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H2" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1036,19 +976,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="G3" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H3" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1056,19 +996,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="G4" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H4" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1076,19 +1016,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="G5" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H5" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1096,19 +1036,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="G6" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H6" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1116,19 +1056,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="G7" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H7" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1136,19 +1076,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="G8" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H8" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1156,19 +1096,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="G9" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H9" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1176,19 +1116,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C10" t="s">
-        <v>107</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="G10" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H10" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1196,19 +1136,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
+        <v>97</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="G11" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H11" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1216,19 +1156,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="G12" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H12" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1236,19 +1176,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="G13" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H13" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1256,19 +1196,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="G14" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H14" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1276,19 +1216,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="G15" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H15" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1296,19 +1236,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="G16" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H16" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1316,19 +1256,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="G17" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H17" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1336,19 +1276,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="G18" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H18" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1356,19 +1296,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G19" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H19" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1376,19 +1316,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="G20" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H20" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1396,19 +1336,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G21" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H21" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1416,19 +1356,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G22" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H22" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1436,19 +1376,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C23" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="G23" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H23" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1456,19 +1396,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="G24" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H24" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1476,19 +1416,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="G25" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H25" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1496,19 +1436,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="G26" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H26" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1516,19 +1456,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="G27" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H27" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1536,19 +1476,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="G28" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H28" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1556,19 +1496,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="G29" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H29" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1576,19 +1516,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="G30" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H30" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1596,19 +1536,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="G31" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H31" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1616,19 +1556,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="G32" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H32" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1636,19 +1576,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="G33" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H33" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1656,19 +1596,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="G34" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H34" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1676,19 +1616,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C35" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="G35" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H35" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1696,19 +1636,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C36" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="G36" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H36" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1716,19 +1656,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C37" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="G37" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H37" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1736,19 +1676,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C38" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="G38" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H38" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1756,19 +1696,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C39" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="G39" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H39" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1776,19 +1716,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C40" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="G40" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H40" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1796,19 +1736,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C41" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="G41" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H41" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1816,19 +1756,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C42" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="G42" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H42" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1836,19 +1776,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C43" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="G43" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H43" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1856,19 +1796,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C44" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="G44" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H44" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1876,19 +1816,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C45" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G45" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H45" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1896,19 +1836,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C46" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="G46" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H46" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1916,19 +1856,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C47" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="G47" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H47" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1936,19 +1876,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C48" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="G48" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H48" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1956,19 +1896,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C49" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="G49" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H49" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1976,19 +1916,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C50" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="G50" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H50" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1996,19 +1936,19 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C51" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="G51" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H51" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -2016,19 +1956,19 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C52" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="G52" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H52" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -2036,19 +1976,19 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C53" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="G53" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H53" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -2056,19 +1996,19 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C54" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="G54" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H54" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2076,19 +2016,19 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C55" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="G55" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H55" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2096,19 +2036,19 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C56" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="G56" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H56" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2116,19 +2056,19 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C57" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="G57" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H57" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2136,19 +2076,19 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C58" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="G58" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H58" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2156,19 +2096,19 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C59" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="G59" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H59" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2176,19 +2116,19 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C60" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="G60" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H60" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2196,19 +2136,19 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C61" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="G61" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H61" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2216,19 +2156,19 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C62" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="G62" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H62" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2236,19 +2176,19 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C63" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="G63" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H63" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2256,19 +2196,19 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C64" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="G64" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H64" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2276,19 +2216,19 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C65" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="G65" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H65" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2296,19 +2236,19 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C66" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="G66" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H66" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2316,19 +2256,19 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C67" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="G67" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H67" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2336,19 +2276,19 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C68" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="G68" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H68" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2356,19 +2296,19 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C69" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="G69" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H69" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2376,19 +2316,19 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C70" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="G70" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H70" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2396,19 +2336,19 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C71" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="G71" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H71" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2416,19 +2356,19 @@
         <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C72" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="G72" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H72" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2436,19 +2376,19 @@
         <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C73" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="G73" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H73" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2456,19 +2396,19 @@
         <v>80</v>
       </c>
       <c r="B74" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C74" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="G74" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H74" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2476,19 +2416,19 @@
         <v>81</v>
       </c>
       <c r="B75" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C75" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="G75" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H75" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2496,19 +2436,19 @@
         <v>82</v>
       </c>
       <c r="B76" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C76" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="G76" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H76" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2516,19 +2456,19 @@
         <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C77" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="G77" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H77" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -2536,19 +2476,19 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C78" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="G78" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H78" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -2556,19 +2496,19 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C79" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H79" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -2576,19 +2516,19 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C80" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="G80" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H80" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -2596,19 +2536,19 @@
         <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C81" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="G81" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H81" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -2616,19 +2556,19 @@
         <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C82" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="G82" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H82" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -2636,19 +2576,19 @@
         <v>89</v>
       </c>
       <c r="B83" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C83" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="G83" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H83" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -2656,19 +2596,19 @@
         <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C84" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="G84" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H84" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -2676,19 +2616,19 @@
         <v>91</v>
       </c>
       <c r="B85" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C85" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="G85" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H85" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -2696,19 +2636,19 @@
         <v>92</v>
       </c>
       <c r="B86" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C86" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="G86" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H86" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -2716,19 +2656,19 @@
         <v>93</v>
       </c>
       <c r="B87" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C87" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="G87" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H87" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -2736,19 +2676,19 @@
         <v>94</v>
       </c>
       <c r="B88" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C88" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="G88" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H88" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -2756,219 +2696,19 @@
         <v>95</v>
       </c>
       <c r="B89" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C89" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="G89" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H89" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8">
-      <c r="A90" t="s">
-        <v>96</v>
-      </c>
-      <c r="B90" t="s">
-        <v>106</v>
-      </c>
-      <c r="C90" t="s">
-        <v>107</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="G90" t="s">
-        <v>206</v>
-      </c>
-      <c r="H90" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8">
-      <c r="A91" t="s">
-        <v>97</v>
-      </c>
-      <c r="B91" t="s">
-        <v>106</v>
-      </c>
-      <c r="C91" t="s">
-        <v>107</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="G91" t="s">
-        <v>206</v>
-      </c>
-      <c r="H91" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8">
-      <c r="A92" t="s">
-        <v>98</v>
-      </c>
-      <c r="B92" t="s">
-        <v>106</v>
-      </c>
-      <c r="C92" t="s">
-        <v>107</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G92" t="s">
-        <v>206</v>
-      </c>
-      <c r="H92" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8">
-      <c r="A93" t="s">
-        <v>99</v>
-      </c>
-      <c r="B93" t="s">
-        <v>106</v>
-      </c>
-      <c r="C93" t="s">
-        <v>107</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G93" t="s">
-        <v>206</v>
-      </c>
-      <c r="H93" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8">
-      <c r="A94" t="s">
-        <v>100</v>
-      </c>
-      <c r="B94" t="s">
-        <v>106</v>
-      </c>
-      <c r="C94" t="s">
-        <v>107</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="G94" t="s">
-        <v>206</v>
-      </c>
-      <c r="H94" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8">
-      <c r="A95" t="s">
-        <v>101</v>
-      </c>
-      <c r="B95" t="s">
-        <v>106</v>
-      </c>
-      <c r="C95" t="s">
-        <v>107</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="G95" t="s">
-        <v>206</v>
-      </c>
-      <c r="H95" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8">
-      <c r="A96" t="s">
-        <v>102</v>
-      </c>
-      <c r="B96" t="s">
-        <v>106</v>
-      </c>
-      <c r="C96" t="s">
-        <v>107</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G96" t="s">
-        <v>206</v>
-      </c>
-      <c r="H96" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
-      <c r="A97" t="s">
-        <v>103</v>
-      </c>
-      <c r="B97" t="s">
-        <v>106</v>
-      </c>
-      <c r="C97" t="s">
-        <v>107</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="G97" t="s">
-        <v>206</v>
-      </c>
-      <c r="H97" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8">
-      <c r="A98" t="s">
-        <v>104</v>
-      </c>
-      <c r="B98" t="s">
-        <v>106</v>
-      </c>
-      <c r="C98" t="s">
-        <v>107</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G98" t="s">
-        <v>206</v>
-      </c>
-      <c r="H98" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8">
-      <c r="A99" t="s">
-        <v>105</v>
-      </c>
-      <c r="B99" t="s">
-        <v>106</v>
-      </c>
-      <c r="C99" t="s">
-        <v>107</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="G99" t="s">
-        <v>206</v>
-      </c>
-      <c r="H99" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -3061,16 +2801,6 @@
     <hyperlink ref="F87" r:id="rId86"/>
     <hyperlink ref="F88" r:id="rId87"/>
     <hyperlink ref="F89" r:id="rId88"/>
-    <hyperlink ref="F90" r:id="rId89"/>
-    <hyperlink ref="F91" r:id="rId90"/>
-    <hyperlink ref="F92" r:id="rId91"/>
-    <hyperlink ref="F93" r:id="rId92"/>
-    <hyperlink ref="F94" r:id="rId93"/>
-    <hyperlink ref="F95" r:id="rId94"/>
-    <hyperlink ref="F96" r:id="rId95"/>
-    <hyperlink ref="F97" r:id="rId96"/>
-    <hyperlink ref="F98" r:id="rId97"/>
-    <hyperlink ref="F99" r:id="rId98"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/scraped_Cape_Town_Emergency_and_Rescue.xlsx
+++ b/results/scraped_Cape_Town_Emergency_and_Rescue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="184">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -40,34 +40,34 @@
     <t>Source</t>
   </si>
   <si>
-    <t>Incidents| CALFIRE</t>
-  </si>
-  <si>
-    <t>California Wildfire Live Map — Real-TimeFireTracking | CWT</t>
-  </si>
-  <si>
     <t>Fire-Wikipedia</t>
   </si>
   <si>
+    <t>Wildfire/Smoke Map - Live Tracking</t>
+  </si>
+  <si>
+    <t>Firefox: The fast, private browser that keeps you safe</t>
+  </si>
+  <si>
+    <t>FIRE| Foundation for Individual Rights and Expression</t>
+  </si>
+  <si>
+    <t>AirNowFireand Smoke Map</t>
+  </si>
+  <si>
+    <t>NIFCMaps-National Interagency Fire Center</t>
+  </si>
+  <si>
+    <t>Live Wildfire Map &amp; Tracker – Wildfires Near Me | AllFirefighter</t>
+  </si>
+  <si>
+    <t>FireMap: Track Wildfires in Real-Time with NASA &amp; Local Data</t>
+  </si>
+  <si>
     <t>Watch Duty - Wildfire Maps &amp; Alerts</t>
   </si>
   <si>
-    <t>Wildfire/Smoke Map - Live Tracking</t>
-  </si>
-  <si>
-    <t>Firefox: The fast, private browser that keeps you safe</t>
-  </si>
-  <si>
-    <t>GradeFire| CALFIRE</t>
-  </si>
-  <si>
-    <t>AirNowFireand Smoke Map</t>
-  </si>
-  <si>
-    <t>Current Fires in California | WFCAFireMap</t>
-  </si>
-  <si>
-    <t>FireMap: Track Wildfires in Real-Time with NASA &amp; Local Data</t>
+    <t>NationalFireNews -National Interagency Fire Center</t>
   </si>
   <si>
     <t>Emergency! (TV Series 1972–1979) - IMDb</t>
@@ -76,54 +76,54 @@
     <t>Emergency! -Wikipedia</t>
   </si>
   <si>
-    <t>Emergency– COUNTY OF LOS ANGELES</t>
-  </si>
-  <si>
     <t>Emergency-Wikipedia</t>
   </si>
   <si>
+    <t>Emergency! | The Complete Series -YouTube</t>
+  </si>
+  <si>
     <t>EMERGENCYDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>Home |EmergencyManagement Department</t>
-  </si>
-  <si>
-    <t>Emergency! | The Complete Series -YouTube</t>
-  </si>
-  <si>
     <t>The 'Emergency' Cast: Looking at the Actors, Then and Now 2024</t>
   </si>
   <si>
-    <t>California declares statewideemergencybefore projected super El …</t>
-  </si>
-  <si>
     <t>Emergency! (TV Series 1972–1979) - Full cast &amp; crew - IMDb</t>
   </si>
   <si>
+    <t>EMERGENCY| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
+    <t>Home |FEMA.gov</t>
+  </si>
+  <si>
+    <t>The Office ofEmergencyManagement | The City of Del City</t>
+  </si>
+  <si>
     <t>Sea-Wikipedia</t>
   </si>
   <si>
-    <t>Ocean- Wikipedia</t>
+    <t>Do you know the difference between ocean,sea, bay and gulf?</t>
+  </si>
+  <si>
+    <t>List of seas on Earth - Wikipedia</t>
+  </si>
+  <si>
+    <t>Sea- SimpleEnglish Wikipedia, the free encyclopedia</t>
+  </si>
+  <si>
+    <t>Ocean vs.Sea: What’s the Difference? - Encyclopedia Britannica</t>
   </si>
   <si>
     <t>Sea- National Geographic Society</t>
   </si>
   <si>
-    <t>Ocean vs.Sea: What’s the Difference? - Encyclopedia Britannica</t>
-  </si>
-  <si>
-    <t>Sea- SimpleEnglish Wikipedia, the free encyclopedia</t>
+    <t>SeaEducation Association</t>
   </si>
   <si>
     <t>Sea| Investor Relations</t>
   </si>
   <si>
-    <t>Sea| Home</t>
-  </si>
-  <si>
-    <t>SeaEducation Association</t>
-  </si>
-  <si>
     <t>SEADefinition &amp; Meaning - Merriam-Webster</t>
   </si>
   <si>
@@ -136,118 +136,115 @@
     <t>Mountain| Definition, Characteristics, Types, &amp; Facts | Britannica</t>
   </si>
   <si>
-    <t>Superstition Mountain Arizona| Hiking, Apache Trail &amp; Lakes</t>
-  </si>
-  <si>
-    <t>Superstition Mountains | Phoenix,AZHiking &amp; Apache Trail</t>
-  </si>
-  <si>
-    <t>Superstition Mountains-Wikipedia</t>
-  </si>
-  <si>
-    <t>Mountains -WorldAtlas</t>
-  </si>
-  <si>
-    <t>Apache Junction Arizona| Things To Do, Hiking, Lakes &amp; Superstition ...</t>
+    <t>What is a Mountain? -WorldAtlas</t>
+  </si>
+  <si>
+    <t>MOUNTAINDefinition &amp; Meaning -Merriam-Webster</t>
+  </si>
+  <si>
+    <t>Mountain- Simple EnglishWikipedia, the free encyclopedia</t>
   </si>
   <si>
     <t>What is amountain? Here’s how they form | National Geographic</t>
   </si>
   <si>
-    <t>Mountain- Simple EnglishWikipedia, the free encyclopedia</t>
-  </si>
-  <si>
-    <t>Mountain: what they are, how they are formed and more</t>
+    <t>MountainHabitat - National Geographic Kids</t>
+  </si>
+  <si>
+    <t>Mount Everest -Wikipedia</t>
+  </si>
+  <si>
+    <t>Mountains (U.S.National Park Service)</t>
+  </si>
+  <si>
+    <t>MOUNTAIN| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
     <t>Disaster-Wikipedia</t>
   </si>
   <si>
-    <t>disaster是什么意思_disaster的翻译_音标_读音_用法_例句_爱词霸在 …</t>
-  </si>
-  <si>
-    <t>DISASTER中文 (简体)翻译：剑桥词典 - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>disaster（英语单词）_百度百科</t>
-  </si>
-  <si>
-    <t>disaster- 搜索 词典</t>
-  </si>
-  <si>
-    <t>Disasters - Wiley Online Library</t>
+    <t>Disaster| Definition &amp; Types | Britannica</t>
+  </si>
+  <si>
+    <t>Disaster Information-FEMA.gov</t>
+  </si>
+  <si>
+    <t>Home | disasterassistance.gov</t>
+  </si>
+  <si>
+    <t>DISASTERDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
     <t>Definition:Disaster| UNDRR</t>
   </si>
   <si>
-    <t>Free Humanitarian Training | DisasterReady</t>
-  </si>
-  <si>
-    <t>Disaster| Definition &amp; Types | Britannica</t>
-  </si>
-  <si>
-    <t>Natural disaster-Wikipedia</t>
-  </si>
-  <si>
-    <t>Personal Banking, Credit Cards &amp; Loans |FirstCitizens Bank</t>
+    <t>Naturaldisaster| Causes, Types, &amp; Facts | Britannica</t>
+  </si>
+  <si>
+    <t>What is adisaster? - IFRC</t>
+  </si>
+  <si>
+    <t>DISASTER| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
     <t>FIRSTDefinition &amp; Meaning - Merriam-Webster</t>
   </si>
   <si>
+    <t>FIRST| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
+    <t>Personal Banking, Loans, &amp; Insurance |Texas FirstBank</t>
+  </si>
+  <si>
     <t>FIRST| For Inspiration and Recognition of Science and Technology</t>
   </si>
   <si>
-    <t>FirstSF - HOME</t>
-  </si>
-  <si>
-    <t>FIRST| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>San FranciscoBranch |CAPersonal Loans &amp; IRAs |FirstBank</t>
-  </si>
-  <si>
-    <t>FIRST| definition in the Cambridge English Dictionary</t>
-  </si>
-  <si>
-    <t>San Francisco- Wikipedia</t>
-  </si>
-  <si>
-    <t>FIRST- Improving Security Together</t>
-  </si>
-  <si>
     <t>first- Wiktionary, the free dictionary</t>
   </si>
   <si>
-    <t>Ambulance- Wikipedia</t>
-  </si>
-  <si>
-    <t>Ambulance Services in Simi Valley,CA- The Real Yellow Pages</t>
-  </si>
-  <si>
-    <t>AMR - EMS &amp;AmbulanceCare</t>
-  </si>
-  <si>
-    <t>Emergency Services -City of Simi Valley,CA</t>
-  </si>
-  <si>
-    <t>AmbulanceServices inSimi Valley,CA- superpages.com</t>
-  </si>
-  <si>
-    <t>TOP 10 BESTAmbulanceService inSimi Valley,CA- (2026 Guide</t>
-  </si>
-  <si>
-    <t>AMR - AMR/Gold Coast - Moorpark,California</t>
-  </si>
-  <si>
-    <t>TOP 10 BESTAmbulanceinSimi Valley,CA- Yelp</t>
-  </si>
-  <si>
-    <t>Emergency medical services- Wikipedia</t>
-  </si>
-  <si>
-    <t>ICS PARAMEDIC/EMT STANDBYAMBULANCESERVICE |SIMI VALLEY,CA…</t>
+    <t>Digital Banking | Personal Online Banking |FirstCitizens Bank</t>
+  </si>
+  <si>
+    <t>First- Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
+  </si>
+  <si>
+    <t>First- definition offirstby The Free Dictionary</t>
+  </si>
+  <si>
+    <t>FIRSTDefinition &amp; Meaning |Dictionary.com</t>
+  </si>
+  <si>
+    <t>Find Teams &amp; Events |FIRST</t>
+  </si>
+  <si>
+    <t>WINDSOR -AmbulanceService,HoustonEmergency Medical Services</t>
+  </si>
+  <si>
+    <t>AMR -Houston</t>
+  </si>
+  <si>
+    <t>HFD MD – HFD | EMERGENCY MEDICAL SERVICES</t>
+  </si>
+  <si>
+    <t>Ambulance Services in Houston, TX- The Real Yellow Pages</t>
+  </si>
+  <si>
+    <t>Orion EMS</t>
+  </si>
+  <si>
+    <t>Emergency Medical Services - Harris Health System</t>
+  </si>
+  <si>
+    <t>HCEC - Harris County Emergency Corps</t>
+  </si>
+  <si>
+    <t>Houston AmbulanceService — ER, Discharge &amp; Facility Transfers ...</t>
+  </si>
+  <si>
+    <t>Texas-Acadian Ambulance Service</t>
+  </si>
+  <si>
+    <t>Frazer - Custom Emergency Vehicles</t>
   </si>
   <si>
     <t>Google</t>
@@ -268,40 +265,37 @@
     <t>DuckDuckGo- Protection. Privacy. Peace of mind.</t>
   </si>
   <si>
-    <t>PrivateSearchEngine - BraveSearch</t>
-  </si>
-  <si>
-    <t>GoogleSearch</t>
-  </si>
-  <si>
-    <t>CIVIL中文 (简体)翻译：剑桥词典</t>
-  </si>
-  <si>
-    <t>civil是什么意思_civil的翻译_音标_读音_用法_例句_爱词霸在线词典</t>
-  </si>
-  <si>
-    <t>civil（英文单词）_百度百科</t>
-  </si>
-  <si>
-    <t>AutodeskCivil3D 2025 - 获取价格和购买Civil3D 软件</t>
-  </si>
-  <si>
-    <t>CIVIL在剑桥英语词典中的解释及翻译 - Cambridge Dictionary</t>
+    <t>Startpage.com</t>
+  </si>
+  <si>
+    <t>Records | Bexar County,TX- Official Website</t>
+  </si>
+  <si>
+    <t>Civil District Courts| Bexar County,TX- Official Website</t>
+  </si>
+  <si>
+    <t>Lone StarCivil- Top RatedSan AntonioGeneral Contractor</t>
+  </si>
+  <si>
+    <t>CivilEngineering Firm inSan Antonio,TX|CivilTech, PLLC</t>
+  </si>
+  <si>
+    <t>CivilEngineeringSan Antonio TX- Givler Engineering Inc.</t>
   </si>
   <si>
     <t>CIVILDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>Civil engineering-Wikipedia</t>
-  </si>
-  <si>
-    <t>civil engineering为什么翻译为「土木工程」？ - 知乎</t>
-  </si>
-  <si>
-    <t>CIVIL释义 | 柯林斯英语词典</t>
-  </si>
-  <si>
-    <t>Download &amp; Buy OfficialCivil3D Software -Autodesk</t>
+    <t>Civil Engineers in San Antonio, TX- The RealYellow Pages</t>
+  </si>
+  <si>
+    <t>Bachelor's Degree inCivilEngineering | UTSan Antonio</t>
+  </si>
+  <si>
+    <t>CivilEngineering Company inSan Antonio| Pape-Dawson</t>
+  </si>
+  <si>
+    <t>San Antonio, TX Civil Litigation Law Firms&amp; Lawyers</t>
   </si>
   <si>
     <t>Emergency &amp; Rescue</t>
@@ -310,268 +304,262 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6119c8133bc7757ef302f04cf3ac91c18176b529981f0e239c96edc673e9c506JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ff304ab-99b5-656b-0f45-134a980c6433&amp;u=a1aHR0cHM6Ly93d3cuZmlyZS5jYS5nb3YvaW5jaWRlbnRzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=912c5ec0ddc0117708835f14df0bc8da54bd5f53451b8b5eed86c8fa4a61bfe0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ff304ab-99b5-656b-0f45-134a980c6433&amp;u=a1aHR0cHM6Ly93d3cuY2FmaXJlLm9yZy9kYXNoYm9hcmQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e2862d54bda234f68796a64fb40eeba94d48d8b58dde81fe07960dd5175f1c13JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ff304ab-99b5-656b-0f45-134a980c6433&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmlyZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=14d539d510555fc34ba475032881eca4db71dad5285a4e345f54b8928e046e3fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ff304ab-99b5-656b-0f45-134a980c6433&amp;u=a1aHR0cHM6Ly9hcHAud2F0Y2hkdXR5Lm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dd74768f5a5f9ee46f493396fa85959b6c357bc8926cb23fa19c59d01a826a26JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ff304ab-99b5-656b-0f45-134a980c6433&amp;u=a1aHR0cHM6Ly93aWxkZmlyZXRyYWNrZXJzLmNvbS9mL21hcA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=498cd5f30b97534ed9a7023bf88c8003edcbd576a1bf5c497e05b29537e2f7d7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ff304ab-99b5-656b-0f45-134a980c6433&amp;u=a1aHR0cHM6Ly93d3cuZmlyZWZveC5jb20vZW4tVVMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e69e4aa074680a76e427f687953ada5ae8f80d071109f1624f5725720933d480JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ff304ab-99b5-656b-0f45-134a980c6433&amp;u=a1aHR0cHM6Ly93d3cuZmlyZS5jYS5nb3YvaW5jaWRlbnRzLzIwMjYvOS8yMy9ncmFkZS1maXJlLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b8d032c39f49dcbecc85bba72cbd66906379748050bc4f51e5146c422f6140e1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ff304ab-99b5-656b-0f45-134a980c6433&amp;u=a1aHR0cHM6Ly9maXJlLmFpcm5vdy5nb3YvP2xhbmc9ZW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f6a837465a7ddaddf58e09a2b51ad07761081d6ae30a601be8654d4298ea044dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ff304ab-99b5-656b-0f45-134a980c6433&amp;u=a1aHR0cHM6Ly93ZmNhLmNvbS9maXJlLW1hcC9jYWxpZm9ybmlh&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9b3dcf201c529a4b24a98f2d22c679617156fa77ab8ff4d24a387cfc3f79b34cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ff304ab-99b5-656b-0f45-134a980c6433&amp;u=a1aHR0cHM6Ly93d3cuZmlyZW1hcC5saXZlLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=872428884e76def34be032e6840c80df1a9cd539128b99d5e8c1da6bd13cf950JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ac67cac-73f3-680e-0730-6b4d722f69e3&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQwMDY4MDY3Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a8f6e12d1bedc54a4eb606fbc9689bff05ac57732df0d6f4b1443816720e4c19JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ac67cac-73f3-680e-0730-6b4d722f69e3&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5IQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=159eff938201f88885397bc8712b86c767b2eae40a98e04f730aeea529c67873JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ac67cac-73f3-680e-0730-6b4d722f69e3&amp;u=a1aHR0cHM6Ly9sYWNvdW50eS5nb3YvZW1lcmdlbmN5Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f55856c22f29e5b33b071db322feb050dc64bb3f54255e92ff0e49efbb8f75daJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ac67cac-73f3-680e-0730-6b4d722f69e3&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fdcb278442f0505a6dd02a19034f926b3a12ca37e267fbade75c25815e9ae0a0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ac67cac-73f3-680e-0730-6b4d722f69e3&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VtZXJnZW5jeQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=07c27c76e42ef2cbcd83602ca21563b41a454cd6b55a697b6f224ce340c801faJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ac67cac-73f3-680e-0730-6b4d722f69e3&amp;u=a1aHR0cHM6Ly9lbWVyZ2VuY3kubGFjaXR5Lmdvdi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c05d4e3a36df0d2f4ac82144ef0990554926dc6ddd4271067abf5af938e7f50JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ac67cac-73f3-680e-0730-6b4d722f69e3&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1sQnJSQTVSQ1lUVQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=28ea7003a79444fa4a71e981c3f3213ff52a16443506a2f3474fd0ee0adaa844JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ac67cac-73f3-680e-0730-6b4d722f69e3&amp;u=a1aHR0cHM6Ly9kb3lvdXJlbWVtYmVyLmNvbS8xNTg1NjEvZW1lcmdlbmN5LWNhc3QtdGhlbi1ub3c&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=97f9bb427c248b6293cb86f942a83c911ab341e375c6297516b92c144792fffbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ac67cac-73f3-680e-0730-6b4d722f69e3&amp;u=a1aHR0cHM6Ly93d3cubGF0aW1lcy5jb20vY2FsaWZvcm5pYS9zdG9yeS8yMDI2LTA5LTIxL2dvdi1uZXdzb20tZGVjbGFyZXMtc3RhdGV3aWRlLWVtZXJnZW5jeS1lbC1uaW5vLXN0b3Jtcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bc7f0dfdd7740844b0592afa66b44f6f709a5b532b76f47c8bacb7da1e58e40fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ac67cac-73f3-680e-0730-6b4d722f69e3&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQwMDY4MDY3L2Z1bGxjcmVkaXRzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=549a472e653f3c2a0214e58dcf4260c533ccd75437a5822679dc98822a464437JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0352ac47-310e-6374-11b0-bba6305862d6&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9TZWE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=673c3b75411dbc8b534997c481781a0c22a4729cb4fa40080872d5714996f82fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0352ac47-310e-6374-11b0-bba6305862d6&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9PY2Vhbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aab4ac26afe565eeb35fa8b969c51372b2d5dd871e7055f9df761a1e00ef52bcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0352ac47-310e-6374-11b0-bba6305862d6&amp;u=a1aHR0cHM6Ly9lZHVjYXRpb24ubmF0aW9uYWxnZW9ncmFwaGljLm9yZy9yZXNvdXJjZS9zZWEv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7d11da2b1db4ab32a7ebda9d88e944e0739db8a39ac9f4498bc5136bb99c158eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0352ac47-310e-6374-11b0-bba6305862d6&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9PY2Vhbi12cy1TZWEtV2hhdHMtdGhlLURpZmZlcmVuY2U&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=db4e519320a2ff2491406727d7b41e46ddbd82ce43c9161a19c5231db718be0aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0352ac47-310e-6374-11b0-bba6305862d6&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvU2Vh&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0dda9bbe24afa5c920628b9c2bd809b651efe9e8e2b5f4efa00700c37b3e3d91JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0352ac47-310e-6374-11b0-bba6305862d6&amp;u=a1aHR0cHM6Ly93d3cuc2VhLmNvbS9pbnZlc3Rvci9ob21l&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9d48fce0a720084fece910584365e49ba30451a56d6b805fbb110c1700d21d58JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0352ac47-310e-6374-11b0-bba6305862d6&amp;u=a1aHR0cHM6Ly93d3cuc2VhLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=035434013256ac0467a7f84a32793697c61ebaed49f261c83108014440a076e0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0352ac47-310e-6374-11b0-bba6305862d6&amp;u=a1aHR0cHM6Ly9zZWEuZWR1Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d2348509b28b327a5260f7b0e512f63085b9e0084ef13493dc3c2a79ff861b0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0352ac47-310e-6374-11b0-bba6305862d6&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NlYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1a67ee8737c26f03e36c1726a087ddb1b8dccb40e867238f218605ea3340cc11JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0352ac47-310e-6374-11b0-bba6305862d6&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9zZWE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2d4ceaf780e0cca27def7756aadbc78797262f651edee1b2a087f99e26d5fffcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=272493c4-5e14-643b-3d34-84255f266532&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTW91bnRhaW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=054c3a606d3fd83ac805a7ef0a1e6f5d45626b5543e5dfcd78f6a1dac127d0eeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=272493c4-5e14-643b-3d34-84255f266532&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9tb3VudGFpbi1sYW5kZm9ybQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fc5cbfe7e359ef25f0f8e0ae4a98343f28811c6460cb1466ef7f4e86f9557051JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=272493c4-5e14-643b-3d34-84255f266532&amp;u=a1aHR0cHM6Ly93d3cuYXJpem9uYS1sZWlzdXJlLmNvbS9zdXBlcnN0aXRpb24tbW91bnRhaW4uaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8851948b9138961b27c152d3941b826c830244f58d994896ea1f9f1298e5b0fdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=272493c4-5e14-643b-3d34-84255f266532&amp;u=a1aHR0cHM6Ly93d3cudmlzaXRwaG9lbml4LmNvbS9zb25vcmFuLWRlc2VydC9wYXJrcy9zdXBlcnN0aXRpb24tbW91bnRhaW5zLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6958cf1a2601d804b72ceff6a211369fbddf92943c755b3b5c3601f54d1e15b3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=272493c4-5e14-643b-3d34-84255f266532&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU3VwZXJzdGl0aW9uX01vdW50YWlucw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=db2cf093d57436d142e89b5a95ace76e39754c516a9b8fcbbb33529b49955308JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=272493c4-5e14-643b-3d34-84255f266532&amp;u=a1aHR0cHM6Ly93d3cud29ybGRhdGxhcy5jb20vbW91bnRhaW5zLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=de263060921bd28c0c52c9e3960d585159a850355f6b8dff8ffec9e4b219b595JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=272493c4-5e14-643b-3d34-84255f266532&amp;u=a1aHR0cHM6Ly93d3cuYXJpem9uYS1sZWlzdXJlLmNvbS9hcGFjaGUtanVuY3Rpb24tYXJpem9uYS5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=976d14cf7f2054f8501ae2b5472f05d70e9b7c2aac280b1ef6b2845dd4748a38JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=272493c4-5e14-643b-3d34-84255f266532&amp;u=a1aHR0cHM6Ly93d3cubmF0aW9uYWxnZW9ncmFwaGljLmNvbS9zY2llbmNlL2FydGljbGUvbW91bnRhaW5z&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a629f67b5b37214df53c84dc4d6f0fd5b38e4b5be631d3fc627b387c8322af3bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=272493c4-5e14-643b-3d34-84255f266532&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL01vdW50YWlu&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=757e1c2114d3260991466b251479e60ce6b14cdc04106e1c864ee4b00dfae8aeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=272493c4-5e14-643b-3d34-84255f266532&amp;u=a1aHR0cHM6Ly9odW1hbmlkYWRlcy5jb20vZW4vbW91bnRhaW4v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7e7552c30315f9d1fd6a36c3e165be0e4c28ee8954604d99d19ac47d449c6343JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cf4bfb2-f001-6b78-00fc-a853f1906a3c&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRGlzYXN0ZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=74c27d4e401eec7ee15d6a3762845f1b8c6aebdbcdb3a0e4d82ed0dd93b9a5f8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cf4bfb2-f001-6b78-00fc-a853f1906a3c&amp;u=a1aHR0cHM6Ly93d3cuaWNpYmEuY29tL3dvcmQ_dz1kaXNhc3Rlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b2d4645b1c6513fff0a358bf2d6879695473ca223cd1151a2122a42037d35f13JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cf4bfb2-f001-6b78-00fc-a853f1906a3c&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvemhzLyVFOCVBRiU4RCVFNSU4NSVCOC8lRTglOEIlQjElRTglQUYlQUQtJUU2JUIxJTg5JUU4JUFGJUFELSVFNyVBRSU4MCVFNCVCRCU5My9kaXNhc3Rlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7df3d63702b064539fcd0a0dc8384d553aa31264d6ed18af567f37f45610ca70JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cf4bfb2-f001-6b78-00fc-a853f1906a3c&amp;u=a1aHR0cHM6Ly9iYWlrZS5iYWlkdS5jb20vaXRlbS9kaXNhc3Rlci8xMDIxMzIxOQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c46a994a40350635f4fe214bcb2065f502fee9118b8ed5c4cba43de3786d0f85JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cf4bfb2-f001-6b78-00fc-a853f1906a3c&amp;u=a1aHR0cHM6Ly9nbG9iYWwuYmluZy5jb20vZGljdC9zZWFyY2g_cT1kaXNhc3RlciZGT1JNPUJEVlNQNiZjYz1jbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2a73a3fbee2ddf8dca61f7b1429976bb912f1eb87cf4994d23eee69194e6fc9fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cf4bfb2-f001-6b78-00fc-a853f1906a3c&amp;u=a1aHR0cHM6Ly9vbmxpbmVsaWJyYXJ5LndpbGV5LmNvbS9qb3VybmFsLzE0Njc3NzE3P21zb2NraWQ9M2NmNGJmYjJmMDAxNmI3ODAwZmNhODUzZjE5MDZhM2M&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ff7ec0a694e97d1475ac58f40b4dae83d1f6010fc87eea21154818c2a228a0fbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cf4bfb2-f001-6b78-00fc-a853f1906a3c&amp;u=a1aHR0cHM6Ly93d3cudW5kcnIub3JnL3Rlcm1pbm9sb2d5L2Rpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2ce113936a04c7669ebd932a00940a831c5ffcd9f8b40c1b144ce03c5dafa858JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cf4bfb2-f001-6b78-00fc-a853f1906a3c&amp;u=a1aHR0cHM6Ly93d3cuZGlzYXN0ZXJyZWFkeS5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=45c19c527874b007ff39b4919d9131d61b85f4e12d96cc8fb038d67ab89af45aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cf4bfb2-f001-6b78-00fc-a853f1906a3c&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9kaXNhc3Rlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=60c8879d22ba4b621904298dc44f2590bf5a8c1b3805bfcf6554026308652101JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3cf4bfb2-f001-6b78-00fc-a853f1906a3c&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTmF0dXJhbF9kaXNhc3Rlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=52eba785e67049073f94c158a51dcc3795028c48f9638f91fa084db3ded1590bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f06dfb8-caa1-6d6b-3058-c859cb0a6c5a&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RjaXRpemVucy5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6b80577c36f7ed9b855eebfe7b2c731aa14c511b94d80bfa59dc4d6b1283e05dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f06dfb8-caa1-6d6b-3058-c859cb0a6c5a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZpcnN0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ef8a9010ed301d1989835dbb305e38c46ef786268c86e0a45abd17295587842JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f06dfb8-caa1-6d6b-3058-c859cb0a6c5a&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RpbnNwaXJlcy5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9888b6c4b0eebdb8d64e778609d1cc32191c37dc7459b3206ca42d926d5661eeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f06dfb8-caa1-6d6b-3058-c859cb0a6c5a&amp;u=a1aHR0cHM6Ly9maXJzdHNmLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=22ad921150a438ff562e0486b4b9853dc7fe9ccfe9722124c75489ca19629c1eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f06dfb8-caa1-6d6b-3058-c859cb0a6c5a&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZpcnN0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7f21fe65acc81e3a2f6773605152d77d8a22a816c4052cc1280e06993a37c088JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f06dfb8-caa1-6d6b-3058-c859cb0a6c5a&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3QuYmFuay9BYm91dC9Mb2NhdGlvbnMvU2FuLUZyYW5jaXNjby1NYWlu&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=77e2ab06b3396517d6efe2f9e11f13de20b4a7e6906a883fb130967671f996cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f06dfb8-caa1-6d6b-3058-c859cb0a6c5a&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2ZpcnN0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=52c338456fc023e25a04f309856da729f1f4d71f029b21ac076784bbfdd9dd00JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f06dfb8-caa1-6d6b-3058-c859cb0a6c5a&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU2FuX2ZyYW5jaXNjbw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2928b37dd11dd107f2d9793b17dea67dda06dae7f4a97f01ffce0fe97dbeb721JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f06dfb8-caa1-6d6b-3058-c859cb0a6c5a&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3Qub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=86e7dce64fbd5773e824a189ae09454d89ef7484a91bba55a9181fda37136b03JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f06dfb8-caa1-6d6b-3058-c859cb0a6c5a&amp;u=a1aHR0cHM6Ly9lbi53aWt0aW9uYXJ5Lm9yZy93aWtpL2ZpcnN0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a1457fb7148a97f45a6e083f35e4293212ce49ad5e2643fd14c1dc849692fff2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=062bde27-8090-65da-19e3-c9c6819e64ae&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQW1idWxhbmNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=85766f9ad2bf6beba087234b14e3a223c1e99bea342b7412a587013ba16a26d2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=062bde27-8090-65da-19e3-c9c6819e64ae&amp;u=a1aHR0cHM6Ly93d3cueWVsbG93cGFnZXMuY29tL3NpbWktdmFsbGV5LWNhL2FtYnVsYW5jZS1zZXJ2aWNlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9da7814c013a874bb20a48422d7099c4ecb985d9de2c3ab6e375f8ee70071e49JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=062bde27-8090-65da-19e3-c9c6819e64ae&amp;u=a1aHR0cHM6Ly93d3cuYW1yLm5ldC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ca70edb74c770ee26a925207fb00e6e17ac639a88fcc2f6e1cd9719675f76fc4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=062bde27-8090-65da-19e3-c9c6819e64ae&amp;u=a1aHR0cHM6Ly93d3cuc2ltaXZhbGxleS5vcmcvZGVwYXJ0bWVudHMvcG9saWNlLWRlcGFydG1lbnQvZW1lcmdlbmN5LXNlcnZpY2Vz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a7c1a5ac11c85bfdfbca8ac36767d9cac20c15e31355a4a86656db846e2c1834JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=062bde27-8090-65da-19e3-c9c6819e64ae&amp;u=a1aHR0cHM6Ly93d3cuc3VwZXJwYWdlcy5jb20vc2ltaS12YWxsZXktY2EvYW1idWxhbmNlLXNlcnZpY2Vz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0348c7cb690cb512a082c5ab24dd151526c80429bf766ab586256a8acc2dfc70JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=062bde27-8090-65da-19e3-c9c6819e64ae&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2ZpbmRfZGVzYz1BbWJ1bGFuY2UrU2VydmljZSZmaW5kX2xvYz1TaW1pK1ZhbGxleSUyQytDQSZtc29ja2lkPTA2MmJkZTI3ODA5MDY1ZGExOWUzYzljNjgxOWU2NGFl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6c13414910db2c9cab66843e1046833aa17c7ada348cd4aded9e7bd536a052b0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=062bde27-8090-65da-19e3-c9c6819e64ae&amp;u=a1aHR0cHM6Ly93d3cuYW1yLm5ldC9sb2NhdGlvbnMvY2FsaWZvcm5pYS92ZW50dXJhLWNvdW50eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b36c5a05db062f0f517a5e25af9e5b348291e4d7f5fd7b9d6fdd3497576d1c79JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=062bde27-8090-65da-19e3-c9c6819e64ae&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2ZpbmRfZGVzYz1BbWJ1bGFuY2UmZmluZF9sb2M9U2ltaStWYWxsZXklMkMrQ0EmbXNvY2tpZD0wNjJiZGUyNzgwOTA2NWRhMTllM2M5YzY4MTllNjRhZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dc925226fe77ae33c9ab7009401e7947bd6eb577dbc8d59284d4e1ee43193100JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=062bde27-8090-65da-19e3-c9c6819e64ae&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5X21lZGljYWxfc2VydmljZXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4695372faeed54b23ca44d9b95e7f8599939cd9c8c9f06acf822c456230c5a49JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=062bde27-8090-65da-19e3-c9c6819e64ae&amp;u=a1aHR0cDovL3d3dy5pY3NzZXJ2aWNlc3N0YW5kYnlhbWJ1bGFuY2UuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ff5279873f8c15c8fc76f545ad0bf845a395e0a9df9fc9c26543088e9441897bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b80472-6838-61ca-336f-1393699c606b&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS94aHRtbC9zZWFyY2g&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=405c086ea9167d1470ad46de17e922d2413cfa06baf0f8c0c8d62f2a19939089JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c51d177-a610-6353-2b05-c696a73962fc&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GaXJl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dd5da7287d9539c7f98b9646bb74741e10c9b676406f2cdd12d35713db304467JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c51d177-a610-6353-2b05-c696a73962fc&amp;u=a1aHR0cHM6Ly93aWxkZmlyZXRyYWNrZXJzLmNvbS9mL21hcA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=34cfc88e9151cf148172b4f171f3a285e70f9ae779dea86fa72f0e0d93416babJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c51d177-a610-6353-2b05-c696a73962fc&amp;u=a1aHR0cHM6Ly93d3cuZmlyZWZveC5jb20vZW4tVVMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=50e0b431db64d6f5ac40565b9565503e871e0c307a10eda9091988c46683df96JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c51d177-a610-6353-2b05-c696a73962fc&amp;u=a1aHR0cHM6Ly93d3cuZmlyZS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=89ff7a91789fddfb0bd3183283957a3d80bff885fcf404b1c4e3447ed9b626cfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c51d177-a610-6353-2b05-c696a73962fc&amp;u=a1aHR0cHM6Ly9maXJlLmFpcm5vdy5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6993a118b7f2b5202644d8075d4c60702b3c4b8b37c6324128346b1913ff8746JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c51d177-a610-6353-2b05-c696a73962fc&amp;u=a1aHR0cHM6Ly93d3cubmlmYy5nb3YvZmlyZS1pbmZvcm1hdGlvbi9tYXBz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a4d503361b8f92fb6bb11e8db6ec3575e5c1a4b3bd8fc3faa727d8d63c0df703JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c51d177-a610-6353-2b05-c696a73962fc&amp;u=a1aHR0cHM6Ly9hbGxmaXJlZmlnaHRlci5jb20vd2lsZGZpcmVzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=96687f5390260ae0976f0ed3ccfbc44015d3b6ab822d8412a51c50c320d6b242JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c51d177-a610-6353-2b05-c696a73962fc&amp;u=a1aHR0cHM6Ly93d3cuZmlyZW1hcC5saXZlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6a3eb76963dfae9d117191bc734f75286d2e3c889e64d50ce9f9d705135700bdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c51d177-a610-6353-2b05-c696a73962fc&amp;u=a1aHR0cHM6Ly9hcHAud2F0Y2hkdXR5Lm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=86bd1ddcbe914d34d40d8dcfcdc9a2247b90998d29d3cf7ad84ed5a063747700JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c51d177-a610-6353-2b05-c696a73962fc&amp;u=a1aHR0cHM6Ly93d3cubmlmYy5nb3YvZmlyZS1pbmZvcm1hdGlvbi9uZm4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=36a67ae63635ec2502e5acdf8c3d51de1dde537dd0556fa943a6ada2ea06f474JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f075b96-0559-6d9e-2590-4c7704d76c47&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MDA2ODA2Ny8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e3f2621211921685fa517f0f734e8ce72c1575d403e5d4f47532bd6c5f3709ddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f075b96-0559-6d9e-2590-4c7704d76c47&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9FbWVyZ2VuY3kh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=30a59a91d09e2b04ded839a793eec88ab2acb8da939eb12ae43c6cc3d4f198bbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f075b96-0559-6d9e-2590-4c7704d76c47&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9FbWVyZ2VuY3k&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=381303bc507aad26a1f70efc42dd053a677edc2406a0af5b735983efdb18e420JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f075b96-0559-6d9e-2590-4c7704d76c47&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9bEJyUkE1UkNZVFU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ae0feb5e6fa05f0b674341861d05e7ddc5dc94123f172d514390da003c807932JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f075b96-0559-6d9e-2590-4c7704d76c47&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VtZXJnZW5jeQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bb8f4fb1272f201c7e8ca31c6e6bf79f7647234c106db76473799a44bde69b08JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f075b96-0559-6d9e-2590-4c7704d76c47&amp;u=a1aHR0cHM6Ly9kb3lvdXJlbWVtYmVyLmNvbS8xNTg1NjEvZW1lcmdlbmN5LWNhc3QtdGhlbi1ub3c&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2e7af76bb4a88450803d0477707d8ce2e5be4edfc98bc2ece9b0e69909346193JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f075b96-0559-6d9e-2590-4c7704d76c47&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MDA2ODA2Ny9mdWxsY3JlZGl0cy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0e14b6db5be07f69c672cabe8a21c417ac168f71f0f78d346b38b499aecde68bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f075b96-0559-6d9e-2590-4c7704d76c47&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2VtZXJnZW5jeQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=068bfe31cd8c80b731514fff4218e988f9e2e45a6edc67c6ecc92634adf753e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f075b96-0559-6d9e-2590-4c7704d76c47&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bb3d3dc1385900f69f4ea6bf16b5cd6017301e544bc6655f098ed35606e322b1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f075b96-0559-6d9e-2590-4c7704d76c47&amp;u=a1aHR0cHM6Ly9jaXR5b2ZkZWxjaXR5Lmdvdi9kZXBhcnRtZW50cy9hbGwtZGVwYXJ0bWVudHMvZmlyZS1kZXBhcnRtZW50L2VtZXJnZW5jeS1tYW5hZ2VtZW50Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0032cc8d1631388416b01f50bf8da0f5ad0eb2da61cf636397cfa79523d96d0fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=328c38f2-d9f4-63b4-279d-2f13d8be6282&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9TZWE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bd21545319167b7df22bf8c418893e8d2a3cc75b6203b96b3c85ae165b3d93aeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=328c38f2-d9f4-63b4-279d-2f13d8be6282&amp;u=a1aHR0cHM6Ly90aW1lc29maW5kaWEuaW5kaWF0aW1lcy5jb20vdHJhdmVsL2Rlc3RpbmF0aW9ucy9kby15b3Uta25vdy10aGUtZGlmZmVyZW5jZS1iZXR3ZWVuLW9jZWFuLXNlYS1iYXktYW5kLWd1bGYvYXJ0aWNsZXNob3cvMTEwOTY1MTM0LmNtcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0e8187166b560ffcc44cc05912c75065b35b8e1baa635f04a4736f89dd5920d7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=328c38f2-d9f4-63b4-279d-2f13d8be6282&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9MaXN0X29mX3NlYXNfb25fRWFydGg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=43628bab3825457a8f825a94ede3a0d2112b4ea343445069402247b55f60e01aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=328c38f2-d9f4-63b4-279d-2f13d8be6282&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvU2Vh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=54833c76efa0de8ab3cb0464b7131b4405e9a9d5bc8c1d60583d9d469a96fe3fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=328c38f2-d9f4-63b4-279d-2f13d8be6282&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9PY2Vhbi12cy1TZWEtV2hhdHMtdGhlLURpZmZlcmVuY2U&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=482ff20c64c4570c6411cb469a9b4104d59ec3184146ed02b0abf7c85642b5bcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=328c38f2-d9f4-63b4-279d-2f13d8be6282&amp;u=a1aHR0cHM6Ly9lZHVjYXRpb24ubmF0aW9uYWxnZW9ncmFwaGljLm9yZy9yZXNvdXJjZS9zZWEv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=74e81667e24310256ced9b094c2bec0d1f4927bce75de3c8989e9e68ee555b9dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=328c38f2-d9f4-63b4-279d-2f13d8be6282&amp;u=a1aHR0cHM6Ly9zZWEuZWR1Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a3e840faf6809cf3146f8646b29f21608e1683985406040cb384e7e338bf7befJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=328c38f2-d9f4-63b4-279d-2f13d8be6282&amp;u=a1aHR0cHM6Ly93d3cuc2VhLmNvbS9pbnZlc3Rvci9ob21l&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b459c1161febbad875b7dc9ff67694e1df2f107e9a46b45f8c652560bf33925bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=328c38f2-d9f4-63b4-279d-2f13d8be6282&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NlYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=69d631ac609da2648807457904c4f31a4afb231c71ef29458b7ccfbae3ed7a25JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=328c38f2-d9f4-63b4-279d-2f13d8be6282&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9zZWE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f01a9da68c43ee1f22a35d17a1e9fc9ccc1545ce83a57bb04b70f8680071ed23JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=252668b8-f30b-65f8-1193-7f59f2136439&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Nb3VudGFpbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d7b04a9b209634c4d7c86a1712654c32035ee6ef9e01725fafe12e687b02e03cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=252668b8-f30b-65f8-1193-7f59f2136439&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9tb3VudGFpbi1sYW5kZm9ybQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9367e089267867a5cecb40c21aa7c29a62ccf9a9464c85749a9eda3d213f8d3cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=252668b8-f30b-65f8-1193-7f59f2136439&amp;u=a1aHR0cHM6Ly93d3cud29ybGRhdGxhcy5jb20vYXJ0aWNsZXMvd2hhdC1pcy1hLW1vdW50YWluLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d835a15020712401fe32d5b9af980595609783bdd8a04c9c58731af83942f1cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=252668b8-f30b-65f8-1193-7f59f2136439&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L21vdW50YWlu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8219e4dbf5efc7195da40eab465813a1c57bb80065add0276a36398c77185919JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=252668b8-f30b-65f8-1193-7f59f2136439&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvTW91bnRhaW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3cd8ae655448f0d709b403f320b2d199b24d925774781222f8e95d8a08a4c991JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=252668b8-f30b-65f8-1193-7f59f2136439&amp;u=a1aHR0cHM6Ly93d3cubmF0aW9uYWxnZW9ncmFwaGljLmNvbS9zY2llbmNlL2FydGljbGUvbW91bnRhaW5z&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5a44d865e95948301b63fc9831c01dd7eb97adf69e71d2101f2979cbeeba68a2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=252668b8-f30b-65f8-1193-7f59f2136439&amp;u=a1aHR0cHM6Ly9raWRzLm5hdGlvbmFsZ2VvZ3JhcGhpYy5jb20vbmF0dXJlL2hhYml0YXRzL2FydGljbGUvbW91bnRhaW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=603a768d5cf32715d928884576e28ab8fc07a44a2590551e07663f44a864e9f7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=252668b8-f30b-65f8-1193-7f59f2136439&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Nb3VudF9FdmVyZXN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=108226ede3543147ff1c9cc63b2bcb1076d1b39d711e744a2f95b35041c75361JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=252668b8-f30b-65f8-1193-7f59f2136439&amp;u=a1aHR0cHM6Ly93d3cubnBzLmdvdi9zdWJqZWN0cy9tb3VudGFpbnMvaW5kZXguaHRt&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d491cc3ce3005ccb42735cca178c09292cc80dad32d358b087dbc1a522993a85JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=252668b8-f30b-65f8-1193-7f59f2136439&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL21vdW50YWlu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b262da16678b6a266e5785c72bd6d96f9f9d95e615250551741422572f081539JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22cf30f0-d95c-665c-26eb-2711d8a96743&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRGlzYXN0ZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=23fdd020aea652d7bb72fc7c06af2f7cde5edcb2d659553c23923e9094f6def0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22cf30f0-d95c-665c-26eb-2711d8a96743&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9kaXNhc3Rlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6b7e27eedbcffddb9fc0c27cd97cde11062d8346414eb9f73ba15ae0e6b706faJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22cf30f0-d95c-665c-26eb-2711d8a96743&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3YvZGlzYXN0ZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=df1c4809113302082550de7ac344b74f835f5fb2674d8cfb169090818f5f26adJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22cf30f0-d95c-665c-26eb-2711d8a96743&amp;u=a1aHR0cHM6Ly93d3cuZGlzYXN0ZXJhc3Npc3RhbmNlLmdvdi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e29a541cdc0054490611b20e607fcfb2d027607095c891435b4194c131996513JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22cf30f0-d95c-665c-26eb-2711d8a96743&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Rpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=60df653a9d0c4cd1f1c0a3276970a51bd09c0c8ce65b26c3fd6e0e660b9cb9ceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22cf30f0-d95c-665c-26eb-2711d8a96743&amp;u=a1aHR0cHM6Ly93d3cudW5kcnIub3JnL3Rlcm1pbm9sb2d5L2Rpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b7b550026e6d763d970cce606182c2e232a473349dec958045f102add67aee3aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22cf30f0-d95c-665c-26eb-2711d8a96743&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9uYXR1cmFsLWRpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0164a5d646c86d721a014c240530ade14ebf7ee7ccee887a7e3b2b679f7d0c5cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22cf30f0-d95c-665c-26eb-2711d8a96743&amp;u=a1aHR0cHM6Ly93d3cuaWZyYy5vcmcvb3VyLXdvcmsvZGlzYXN0ZXJzLWNsaW1hdGUtYW5kLWNyaXNlcy93aGF0LWRpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2d3c892ea5a9c2ac43da0735a7a848b6d579369a878363fa9a6f7de25437260fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22cf30f0-d95c-665c-26eb-2711d8a96743&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Rpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b82e41fc91f53a592a5a8d6afd35a6ca8440d867016af34fca737cae1390a7cdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21cab581-9f2c-6a0d-101b-a2609ed46b5a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZpcnN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0608ddb9119978ce9682bb1f8e45de5be414581b3c97e6d18721de27be1ffe51JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21cab581-9f2c-6a0d-101b-a2609ed46b5a&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZpcnN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3fc4e8dfc69ad02be798fec82a4370556aa4d5d61bd4d7350dda576562739277JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21cab581-9f2c-6a0d-101b-a2609ed46b5a&amp;u=a1aHR0cHM6Ly90ZXhhc2ZpcnN0LmJhbmsvcGVyc29uYWwv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=77fdb832fff67509b316bd07a6ab9b260d60e0f0bb8392d31ec86b6885a6386fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21cab581-9f2c-6a0d-101b-a2609ed46b5a&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RpbnNwaXJlcy5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=24e34594cfd7a6a820ac3165561f3289d7463acc8ae87809f197ea692169e1a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21cab581-9f2c-6a0d-101b-a2609ed46b5a&amp;u=a1aHR0cHM6Ly9lbi53aWt0aW9uYXJ5Lm9yZy93aWtpL2ZpcnN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ec2f10bba79cfa9f03fe04f75951b6e5c12bbd32e6c26ae447b9d9f3c684970dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21cab581-9f2c-6a0d-101b-a2609ed46b5a&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RjaXRpemVucy5jb20vcGVyc29uYWwvZGlnaXRhbC1iYW5raW5n&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f33604c7da804c336661be0b82a85a5b82fad724fcc0cf42cf29a159a34ffa2fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21cab581-9f2c-6a0d-101b-a2609ed46b5a&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9maXJzdA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ecd6aa817e287b7e576b5efc09750b8c4317e7a60950da524ded0e710b315b83JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21cab581-9f2c-6a0d-101b-a2609ed46b5a&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2ZpcnN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=429a7c230c929a48dc2f8f5c80f4680cf372adc5eeb9019d84338fe091df4873JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21cab581-9f2c-6a0d-101b-a2609ed46b5a&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2ZpcnN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d756bf3d689758319827c0cf7043332b52a13814666fbc3708b707b3c6e7b1d2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21cab581-9f2c-6a0d-101b-a2609ed46b5a&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RpbnNwaXJlcy5vcmcvdGVhbS1ldmVudC1zZWFyY2g&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=611cfa3c724ded5695e1f615ab70525297c64c74e9ba69ce71c3fe119055e438JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3a3ca-be59-6b76-1b30-b42bbf416a3e&amp;u=a1aHR0cHM6Ly93aW5kc29yZW1zLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a5ac2211d9ca8568ffd0ad3061f31c0cb502225956656388705f1d03d787e15eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3a3ca-be59-6b76-1b30-b42bbf416a3e&amp;u=a1aHR0cHM6Ly93d3cuYW1yLm5ldC9sb2NhdGlvbnMvdGV4YXMvaG91c3Rvbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=227bfcc3b0bc453f4afe3bc60cf4c94a6b2eed3602671f543631bd648bdc6e5aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3a3ca-be59-6b76-1b30-b42bbf416a3e&amp;u=a1aHR0cHM6Ly93d3cuaGZkbWQub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11e48ace6034219e97c3d9738b24582450bf989c60c3277d77c8675b0736ebe7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3a3ca-be59-6b76-1b30-b42bbf416a3e&amp;u=a1aHR0cHM6Ly93d3cueWVsbG93cGFnZXMuY29tL2hvdXN0b24tdHgvYW1idWxhbmNlLXNlcnZpY2Vz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=796f8ebc13e406838a129d7dbac1dd56156394ff47fa776848d915017fc3d61aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3a3ca-be59-6b76-1b30-b42bbf416a3e&amp;u=a1aHR0cHM6Ly93d3cub3Jpb25lbXMuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be9ce6f5be180c0101e1b24554580a6872666260e276893912f6e18cd4fb6170JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3a3ca-be59-6b76-1b30-b42bbf416a3e&amp;u=a1aHR0cHM6Ly93d3cuaGFycmlzaGVhbHRoLm9yZy9zZXJ2aWNlcy1oaC9jbGluaWNhbC1zZXJ2aWNlcy9QYWdlcy9lbXMuYXNweA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=012c0cd696afeed452b9049b05c283e00940f271ac58e0070a01785854e8d510JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3a3ca-be59-6b76-1b30-b42bbf416a3e&amp;u=a1aHR0cHM6Ly9oY2VjLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a26fb53cadb20c7040689cf9c92ff50059fc5a2be4435e621f4117fead3fb7cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3a3ca-be59-6b76-1b30-b42bbf416a3e&amp;u=a1aHR0cHM6Ly9wcmVmZXJyZWRlbXMuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d79e796754af602cfae082a238b9b24000d61a1cf19bd5814edc1a1c8752cdccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3a3ca-be59-6b76-1b30-b42bbf416a3e&amp;u=a1aHR0cHM6Ly9hY2FkaWFuYW1idWxhbmNlLmNvbS9sb2NhdGlvbnMvdGV4YXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c9d1d0ea586afa1347b66b88fc28e0a61dac8a41c93feee702b5496d4e7ca84eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3a3ca-be59-6b76-1b30-b42bbf416a3e&amp;u=a1aHR0cHM6Ly93d3cuZnJhemVyYmlsdC5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb3b799f222ecb0ab7dc572b0d5fbcef501abbf355a865e9a9832adef4b6a066JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ae39531-4b09-6d8c-0fd9-82d04a5a6c20&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS94aHRtbC9zZWFyY2g&amp;ntb=1</t>
   </si>
   <si>
     <t>https://www.bing.com/</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=33c024b7521d19b99f921e745f14d10e809d0999816a0d5e5fff6dd49839bc9bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b80472-6838-61ca-336f-1393699c606b&amp;u=a1aHR0cHM6Ly9zZWFyY2gueWFob28uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ce983f8e463e6c9f2c4fb9c53ec8baaba4a28278dc55a4e7f9eace45dc784845JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b80472-6838-61ca-336f-1393699c606b&amp;u=a1aHR0cHM6Ly9zZWFyY2guZ29vZ2xlLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5f1d0f14e4c7670eb5b9fcadd7492e7847bee1c56b7effc5421032c62307a4adJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b80472-6838-61ca-336f-1393699c606b&amp;u=a1aHR0cHM6Ly93d3cueWFob28uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0a2c1d3345802a1bac6840be877be4744d66991bbc09d0dc3127570661194005JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b80472-6838-61ca-336f-1393699c606b&amp;u=a1aHR0cHM6Ly9kdWNrZHVja2dvLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=16ca9964ff5eaa9c58b6f3551f1041d0dd464883abc74d14aab390912122e95dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b80472-6838-61ca-336f-1393699c606b&amp;u=a1aHR0cHM6Ly9zZWFyY2guYnJhdmUuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4d65768e18b3874cddd79ea4061036740c8d0db0e606ab24d1cbd558dfee16e3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10b80472-6838-61ca-336f-1393699c606b&amp;u=a1aHR0cHM6Ly9hY2NvdW50cy5nb29nbGUuY29tL0ludGVyYWN0aXZlTG9naW4_c2VydmljZT1zYWZlc2VhcmNobG9jaw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5c228b04b18f6b5db9afbd3fdc1bc580d0d4b1166164b23557455d588a6e0231JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32137556-54d8-64ce-1458-62b7559965d4&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvemhzLyVFOCVBRiU4RCVFNSU4NSVCOC8lRTglOEIlQjElRTglQUYlQUQtJUU2JUIxJTg5JUU4JUFGJUFELSVFNyVBRSU4MCVFNCVCRCU5My9jaXZpbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2bf61fa3a2d40eb5dd0199a3847addc509a93f6c239cfbcfd07b157255cd4cb1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32137556-54d8-64ce-1458-62b7559965d4&amp;u=a1aHR0cHM6Ly93d3cuaWNpYmEuY29tL3dvcmQ_dz1jaXZpbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=05e06e03044adca473e42a2c9c170af7e2955b1f4d351f8b5e439827503ccf49JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32137556-54d8-64ce-1458-62b7559965d4&amp;u=a1aHR0cHM6Ly9iYWlrZS5iYWlkdS5jb20vaXRlbS9DaXZpbC8zMTUzMzk0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dd1b6c64dd328893a0a8cd387c2fd12b25795b4ab32e19adbabf0b131c825834JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32137556-54d8-64ce-1458-62b7559965d4&amp;u=a1aHR0cHM6Ly93d3cuYXV0b2Rlc2suY29tLmNuL3Byb2R1Y3RzL2NpdmlsLTNkL292ZXJ2aWV3&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5fefa1c3bbad8bcbdc9d90072b60ed9fbabf279aa6eed49d4570acdb6e603803JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32137556-54d8-64ce-1458-62b7559965d4&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvemhzLyVFOCVBRiU4RCVFNSU4NSVCOC8lRTglOEIlQjElRTglQUYlQUQvY2l2aWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3e721aad81995c5174624116d0c885f2f09a2264c0ee7946e3839895561a9f55JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32137556-54d8-64ce-1458-62b7559965d4&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Npdmls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6a82da12c8f9728be223e6370ccd7a2a7b91f47814ebebcc89bf775bddeba4edJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32137556-54d8-64ce-1458-62b7559965d4&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9DaXZpbF9lbmdpbmVlcmluZw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=391fe2e8ec0cfa54ec447e3dee8844c12535fc702bcc08bbf2e32571c5d85a62JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32137556-54d8-64ce-1458-62b7559965d4&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzIzNTg2Mjg2&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f6ab48d99f9e00dc0aa03e3e888843c3b740ba0e7f539d486e6252cb2526f956JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32137556-54d8-64ce-1458-62b7559965d4&amp;u=a1aHR0cHM6Ly93d3cuY29sbGluc2RpY3Rpb25hcnkuY29tL3poL2RpY3Rpb25hcnkvZW5nbGlzaC9jaXZpbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3d15e72f9e4232d3c1e9b9e83e567116e48fb18747a949654976fee6ef0e5361JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32137556-54d8-64ce-1458-62b7559965d4&amp;u=a1aHR0cHM6Ly93d3cuYXV0b2Rlc2suY29tL3Byb2R1Y3RzL2NpdmlsLTNkL292ZXJ2aWV3P21zb2NraWQ9MzIxMzc1NTY1NGQ4NjRjZTE0NTg2MmI3NTU5OTY1ZDQ&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=400bc358e6d1faa79876e99e88b93ba96389222b2492b562d8f3739ac140090cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ae39531-4b09-6d8c-0fd9-82d04a5a6c20&amp;u=a1aHR0cHM6Ly9zZWFyY2gueWFob28uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9848dc654cf9e584bc605af2e9073193cf3bdc0d4b95c7d4ff56afd1e5426d1dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ae39531-4b09-6d8c-0fd9-82d04a5a6c20&amp;u=a1aHR0cHM6Ly9zZWFyY2guZ29vZ2xlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c88b988d8eeefccb43e1442516b1820770b9d0bc2d3072538ba47f75a932816bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ae39531-4b09-6d8c-0fd9-82d04a5a6c20&amp;u=a1aHR0cHM6Ly93d3cueWFob28uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6885ca8e465fbaae6c85fb7837237cf175590c7b0bfc033914f5b6985397b5ceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ae39531-4b09-6d8c-0fd9-82d04a5a6c20&amp;u=a1aHR0cHM6Ly9kdWNrZHVja2dvLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=49a1ce2e9c895911f0f612e9c8118a3402208beb487677775dca54dfdf62b535JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ae39531-4b09-6d8c-0fd9-82d04a5a6c20&amp;u=a1aHR0cHM6Ly93d3cuc3RhcnRwYWdlLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0569a219d07146ba802b2c88061e3eb1d9ca1c30207d37afaff9916d00c5463bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d141ea8-762f-6d55-26e0-094977966c15&amp;u=a1aHR0cHM6Ly93d3cuYmV4YXIub3JnLzM3MDMvUmVjb3Jkcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=438f78110ef95fbc7e86988d089b2ac21d3709fdbd1d1b1b521e0ce8ea2c5cdcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d141ea8-762f-6d55-26e0-094977966c15&amp;u=a1aHR0cHM6Ly93d3cuYmV4YXIub3JnLzE3MDMvQ2l2aWwtRGlzdHJpY3QtQ291cnRz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=79f01036f21ec82ea613ab4cdf9439b7093abde0806738e71c18874bf4536aeeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d141ea8-762f-6d55-26e0-094977966c15&amp;u=a1aHR0cHM6Ly93d3cubG9uZXN0YXJjaXZpbC5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0666923992ba06dc4f70d5d0ce800281782d65582b834b3ed49b7f68d2b30ab2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d141ea8-762f-6d55-26e0-094977966c15&amp;u=a1aHR0cHM6Ly9jaXZpbHRlY2htYy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6926e0665ede44d16425ea35b8b99f12a1aa4697db24b44f75f4bac520786695JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d141ea8-762f-6d55-26e0-094977966c15&amp;u=a1aHR0cHM6Ly9naXZsZXJlbmdpbmVlcmluZy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b3588cb00fbf54dc0d22679903020f8ad849c071f54edd6057566d640902a5b3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d141ea8-762f-6d55-26e0-094977966c15&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=124590e9d171770285e1976e8f986515baa45828e48b81d7bfee926b1178984fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d141ea8-762f-6d55-26e0-094977966c15&amp;u=a1aHR0cHM6Ly93d3cueWVsbG93cGFnZXMuY29tL3Nhbi1hbnRvbmlvLXR4L2NpdmlsLWVuZ2luZWVycw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4e21cba7ec57e33ffe23142c8ba2676fc223d7e1954f865c427fcf8d593e1d5cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d141ea8-762f-6d55-26e0-094977966c15&amp;u=a1aHR0cHM6Ly9mdXR1cmUudXRzYS5lZHUvcHJvZ3JhbXMvdW5kZXJncmFkdWF0ZS9jaXZpbC1lbmdpbmVlcmluZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=98852d625777bbf5a1631b10be3c684eb97437b1fb8f84e7a2bddd2af97040b4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d141ea8-762f-6d55-26e0-094977966c15&amp;u=a1aHR0cHM6Ly93d3cucGFwZS1kYXdzb24uY29tL2xvY2F0aW9ucy9zYW4tYW50b25pby8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2fb66e386deb31365e3c51886f0f348352fc8ec3ac7ce15b475be56aede8ebeeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d141ea8-762f-6d55-26e0-094977966c15&amp;u=a1aHR0cHM6Ly93d3cubGF3eWVycy5jb20vY2l2aWwtbGl0aWdhdGlvbi9zYW4tYW50b25pby90ZXhhcy9sYXctZmlybXMv&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
@@ -922,7 +910,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -956,19 +944,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="G2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -976,19 +964,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="G3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -996,19 +984,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1016,19 +1004,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G5" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H5" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1036,19 +1024,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1056,19 +1044,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G7" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H7" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1076,19 +1064,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G8" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H8" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1096,19 +1084,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G9" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H9" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1116,19 +1104,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G10" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H10" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1136,19 +1124,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G11" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H11" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1156,19 +1144,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G12" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H12" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1176,19 +1164,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G13" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H13" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1196,19 +1184,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G14" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H14" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1216,19 +1204,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G15" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H15" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1236,19 +1224,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G16" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H16" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1256,19 +1244,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G17" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H17" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1276,19 +1264,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G18" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H18" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1296,19 +1284,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G19" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H19" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1316,19 +1304,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G20" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H20" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1336,19 +1324,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G21" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H21" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1356,19 +1344,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G22" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H22" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1376,19 +1364,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G23" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H23" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1396,19 +1384,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G24" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H24" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1416,19 +1404,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G25" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H25" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1436,19 +1424,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G26" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H26" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1456,19 +1444,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G27" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H27" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1476,19 +1464,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G28" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H28" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1496,19 +1484,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G29" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H29" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1516,19 +1504,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G30" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H30" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1536,19 +1524,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G31" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H31" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1556,19 +1544,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G32" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H32" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1576,19 +1564,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G33" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H33" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1596,19 +1584,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G34" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H34" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1616,19 +1604,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G35" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H35" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1636,19 +1624,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C36" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G36" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H36" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1656,19 +1644,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C37" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G37" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H37" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1676,19 +1664,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C38" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G38" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H38" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1696,19 +1684,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C39" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G39" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H39" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1716,19 +1704,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C40" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G40" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H40" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1736,19 +1724,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C41" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G41" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H41" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1756,19 +1744,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C42" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G42" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H42" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1776,19 +1764,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C43" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G43" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H43" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1796,19 +1784,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C44" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G44" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H44" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1816,19 +1804,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C45" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G45" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H45" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1836,19 +1824,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C46" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G46" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H46" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1856,19 +1844,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C47" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G47" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H47" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1876,19 +1864,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C48" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G48" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H48" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1896,19 +1884,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G49" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H49" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1916,19 +1904,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C50" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G50" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H50" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1936,19 +1924,19 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C51" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G51" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H51" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1956,19 +1944,19 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C52" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G52" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H52" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1976,19 +1964,19 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C53" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G53" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H53" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -1996,19 +1984,19 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C54" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G54" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H54" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2016,19 +2004,19 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C55" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G55" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H55" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2036,19 +2024,19 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C56" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G56" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H56" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2056,19 +2044,19 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C57" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G57" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H57" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2076,19 +2064,19 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C58" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G58" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H58" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2096,19 +2084,19 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C59" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G59" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H59" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2116,19 +2104,19 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C60" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G60" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H60" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2136,19 +2124,19 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C61" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G61" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H61" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2156,19 +2144,19 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C62" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G62" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H62" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2176,19 +2164,19 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C63" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G63" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H63" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2196,19 +2184,19 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C64" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G64" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H64" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2216,19 +2204,19 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C65" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G65" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H65" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2236,19 +2224,19 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C66" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G66" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H66" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2256,19 +2244,19 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C67" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G67" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H67" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2276,19 +2264,19 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C68" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G68" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H68" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2296,19 +2284,19 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C69" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G69" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H69" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2316,19 +2304,19 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C70" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G70" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H70" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2336,19 +2324,19 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C71" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G71" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H71" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2356,19 +2344,19 @@
         <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C72" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G72" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H72" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2376,19 +2364,19 @@
         <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C73" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G73" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H73" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2396,19 +2384,19 @@
         <v>80</v>
       </c>
       <c r="B74" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C74" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G74" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H74" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2416,19 +2404,19 @@
         <v>81</v>
       </c>
       <c r="B75" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C75" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G75" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H75" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2436,19 +2424,19 @@
         <v>82</v>
       </c>
       <c r="B76" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C76" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G76" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H76" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2456,19 +2444,19 @@
         <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C77" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G77" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H77" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -2476,19 +2464,19 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C78" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G78" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H78" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -2496,19 +2484,19 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C79" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G79" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H79" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -2516,19 +2504,19 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C80" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G80" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H80" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -2536,19 +2524,19 @@
         <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C81" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G81" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H81" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -2556,19 +2544,19 @@
         <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C82" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G82" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H82" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -2576,19 +2564,19 @@
         <v>89</v>
       </c>
       <c r="B83" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C83" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G83" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H83" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -2596,19 +2584,19 @@
         <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C84" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G84" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H84" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -2616,19 +2604,19 @@
         <v>91</v>
       </c>
       <c r="B85" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C85" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G85" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H85" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -2636,19 +2624,19 @@
         <v>92</v>
       </c>
       <c r="B86" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C86" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G86" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H86" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -2656,59 +2644,19 @@
         <v>93</v>
       </c>
       <c r="B87" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C87" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G87" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H87" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
-      <c r="A88" t="s">
-        <v>94</v>
-      </c>
-      <c r="B88" t="s">
-        <v>96</v>
-      </c>
-      <c r="C88" t="s">
-        <v>97</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="G88" t="s">
-        <v>186</v>
-      </c>
-      <c r="H88" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
-      <c r="A89" t="s">
-        <v>95</v>
-      </c>
-      <c r="B89" t="s">
-        <v>96</v>
-      </c>
-      <c r="C89" t="s">
-        <v>97</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="G89" t="s">
-        <v>186</v>
-      </c>
-      <c r="H89" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -2799,8 +2747,6 @@
     <hyperlink ref="F85" r:id="rId84"/>
     <hyperlink ref="F86" r:id="rId85"/>
     <hyperlink ref="F87" r:id="rId86"/>
-    <hyperlink ref="F88" r:id="rId87"/>
-    <hyperlink ref="F89" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/scraped_Cape_Town_Emergency_and_Rescue.xlsx
+++ b/results/scraped_Cape_Town_Emergency_and_Rescue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="188">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -40,36 +40,36 @@
     <t>Source</t>
   </si>
   <si>
+    <t>Current Fires in Washington | WFCAFireMap</t>
+  </si>
+  <si>
+    <t>Wildfire/Smoke Map - Live Tracking</t>
+  </si>
+  <si>
+    <t>AirNowFireand Smoke Map</t>
+  </si>
+  <si>
     <t>Fire-Wikipedia</t>
   </si>
   <si>
-    <t>Wildfire/Smoke Map - Live Tracking</t>
+    <t>FIRE| Foundation for Individual Rights and Expression</t>
+  </si>
+  <si>
+    <t>Live Wildfire Map: Active Fires, Smoke &amp; Alerts |FireNearby</t>
+  </si>
+  <si>
+    <t>Live Wildfire Map &amp; Tracker – Wildfires Near Me | AllFirefighter</t>
+  </si>
+  <si>
+    <t>firemap.us | see what's onfire</t>
+  </si>
+  <si>
+    <t>Current Wildfire Information - U.S. Department of the Interior</t>
   </si>
   <si>
     <t>Firefox: The fast, private browser that keeps you safe</t>
   </si>
   <si>
-    <t>FIRE| Foundation for Individual Rights and Expression</t>
-  </si>
-  <si>
-    <t>AirNowFireand Smoke Map</t>
-  </si>
-  <si>
-    <t>NIFCMaps-National Interagency Fire Center</t>
-  </si>
-  <si>
-    <t>Live Wildfire Map &amp; Tracker – Wildfires Near Me | AllFirefighter</t>
-  </si>
-  <si>
-    <t>FireMap: Track Wildfires in Real-Time with NASA &amp; Local Data</t>
-  </si>
-  <si>
-    <t>Watch Duty - Wildfire Maps &amp; Alerts</t>
-  </si>
-  <si>
-    <t>NationalFireNews -National Interagency Fire Center</t>
-  </si>
-  <si>
     <t>Emergency! (TV Series 1972–1979) - IMDb</t>
   </si>
   <si>
@@ -79,172 +79,175 @@
     <t>Emergency-Wikipedia</t>
   </si>
   <si>
+    <t>EMERGENCYDefinition &amp; Meaning -Merriam-Webster</t>
+  </si>
+  <si>
+    <t>The 'Emergency' Cast: Looking at the Actors, Then and Now 2024</t>
+  </si>
+  <si>
     <t>Emergency! | The Complete Series -YouTube</t>
   </si>
   <si>
-    <t>EMERGENCYDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>The 'Emergency' Cast: Looking at the Actors, Then and Now 2024</t>
-  </si>
-  <si>
     <t>Emergency! (TV Series 1972–1979) - Full cast &amp; crew - IMDb</t>
   </si>
   <si>
+    <t>Office ofEmergencyManagement | City of Phoenix</t>
+  </si>
+  <si>
+    <t>Plan Ahead for Disasters |Ready.gov</t>
+  </si>
+  <si>
     <t>EMERGENCY| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
+    <t>Sea-Wikipedia</t>
+  </si>
+  <si>
+    <t>Do you know the difference between ocean,sea, bay and gulf?</t>
+  </si>
+  <si>
+    <t>SeaEducation Association</t>
+  </si>
+  <si>
+    <t>Seattle-Tacoma International Airport | Port of Seattle</t>
+  </si>
+  <si>
+    <t>Sea- SimpleEnglish Wikipedia, the free encyclopedia</t>
+  </si>
+  <si>
+    <t>List of seas on Earth - Wikipedia</t>
+  </si>
+  <si>
+    <t>Sea- National Geographic Society</t>
+  </si>
+  <si>
+    <t>Ocean vs.Sea: What’s the Difference? - Encyclopedia Britannica</t>
+  </si>
+  <si>
+    <t>SEA– Seattle Education Association</t>
+  </si>
+  <si>
+    <t>Sea| Investor Relations</t>
+  </si>
+  <si>
+    <t>AKAI &lt; 0.0001 ETH - Collection | OpenSea</t>
+  </si>
+  <si>
+    <t>Max Extractors 0.0031 ETH - Collection | OpenSea</t>
+  </si>
+  <si>
+    <t>Gloomies &lt; 0.0001 ETH - Collection | OpenSea</t>
+  </si>
+  <si>
+    <t>Hush PuppiezzZ 0.0001 ETH - Collection | OpenSea</t>
+  </si>
+  <si>
+    <t>Solve et Coagula &lt; 0.0001 ETH - Collection | OpenSea</t>
+  </si>
+  <si>
+    <t>Zonks 0.0002 ETH - Collection | OpenSea</t>
+  </si>
+  <si>
+    <t>Portable Slop Drive 0.94 USDG - Collection | OpenSea</t>
+  </si>
+  <si>
+    <t>Project CPU &lt; 0.0001 ETH - Collection | OpenSea</t>
+  </si>
+  <si>
+    <t>Gameboy &lt; 0.0001 ETH - Collection | OpenSea</t>
+  </si>
+  <si>
+    <t>UNICRED 0.0041 ETH - Collection | OpenSea</t>
+  </si>
+  <si>
+    <t>Disaster-Wikipedia</t>
+  </si>
+  <si>
+    <t>Home | disasterassistance.gov</t>
+  </si>
+  <si>
+    <t>Disaster| Definition &amp; Types | Britannica</t>
+  </si>
+  <si>
+    <t>DISASTERDefinition &amp; Meaning -Merriam-Webster</t>
+  </si>
+  <si>
+    <t>Definition:Disaster| UNDRR</t>
+  </si>
+  <si>
+    <t>Disaster Information-FEMA.gov</t>
+  </si>
+  <si>
+    <t>Naturaldisaster| Causes, Types, &amp; Facts | Britannica</t>
+  </si>
+  <si>
     <t>Home |FEMA.gov</t>
   </si>
   <si>
-    <t>The Office ofEmergencyManagement | The City of Del City</t>
-  </si>
-  <si>
-    <t>Sea-Wikipedia</t>
-  </si>
-  <si>
-    <t>Do you know the difference between ocean,sea, bay and gulf?</t>
-  </si>
-  <si>
-    <t>List of seas on Earth - Wikipedia</t>
-  </si>
-  <si>
-    <t>Sea- SimpleEnglish Wikipedia, the free encyclopedia</t>
-  </si>
-  <si>
-    <t>Ocean vs.Sea: What’s the Difference? - Encyclopedia Britannica</t>
-  </si>
-  <si>
-    <t>Sea- National Geographic Society</t>
-  </si>
-  <si>
-    <t>SeaEducation Association</t>
-  </si>
-  <si>
-    <t>Sea| Investor Relations</t>
-  </si>
-  <si>
-    <t>SEADefinition &amp; Meaning - Merriam-Webster</t>
-  </si>
-  <si>
-    <t>Sea| body of water | Britannica</t>
-  </si>
-  <si>
-    <t>Mountain-Wikipedia</t>
-  </si>
-  <si>
-    <t>Mountain| Definition, Characteristics, Types, &amp; Facts | Britannica</t>
-  </si>
-  <si>
-    <t>What is a Mountain? -WorldAtlas</t>
-  </si>
-  <si>
-    <t>MOUNTAINDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>Mountain- Simple EnglishWikipedia, the free encyclopedia</t>
-  </si>
-  <si>
-    <t>What is amountain? Here’s how they form | National Geographic</t>
-  </si>
-  <si>
-    <t>MountainHabitat - National Geographic Kids</t>
-  </si>
-  <si>
-    <t>Mount Everest -Wikipedia</t>
-  </si>
-  <si>
-    <t>Mountains (U.S.National Park Service)</t>
-  </si>
-  <si>
-    <t>MOUNTAIN| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>Disaster-Wikipedia</t>
-  </si>
-  <si>
-    <t>Disaster| Definition &amp; Types | Britannica</t>
-  </si>
-  <si>
-    <t>Disaster Information-FEMA.gov</t>
-  </si>
-  <si>
-    <t>Home | disasterassistance.gov</t>
-  </si>
-  <si>
-    <t>DISASTERDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>Definition:Disaster| UNDRR</t>
-  </si>
-  <si>
-    <t>Naturaldisaster| Causes, Types, &amp; Facts | Britannica</t>
-  </si>
-  <si>
     <t>What is adisaster? - IFRC</t>
   </si>
   <si>
-    <t>DISASTER| English meaning - Cambridge Dictionary</t>
+    <t>Natural disaster-Wikipedia</t>
+  </si>
+  <si>
+    <t>FIRST| For Inspiration and Recognition of Science and Technology</t>
+  </si>
+  <si>
+    <t>FIRSTRobotics -California| Inspiring young people to be ...</t>
   </si>
   <si>
     <t>FIRSTDefinition &amp; Meaning - Merriam-Webster</t>
   </si>
   <si>
+    <t>FirstCity Credit Union |Los AngelesCounty Employees Credit ...</t>
+  </si>
+  <si>
+    <t>first- Wiktionary, the free dictionary</t>
+  </si>
+  <si>
     <t>FIRST| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
-    <t>Personal Banking, Loans, &amp; Insurance |Texas FirstBank</t>
-  </si>
-  <si>
-    <t>FIRST| For Inspiration and Recognition of Science and Technology</t>
-  </si>
-  <si>
-    <t>first- Wiktionary, the free dictionary</t>
-  </si>
-  <si>
-    <t>Digital Banking | Personal Online Banking |FirstCitizens Bank</t>
-  </si>
-  <si>
-    <t>First- Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
-  </si>
-  <si>
-    <t>First- definition offirstby The Free Dictionary</t>
-  </si>
-  <si>
-    <t>FIRSTDefinition &amp; Meaning |Dictionary.com</t>
-  </si>
-  <si>
-    <t>Find Teams &amp; Events |FIRST</t>
-  </si>
-  <si>
-    <t>WINDSOR -AmbulanceService,HoustonEmergency Medical Services</t>
-  </si>
-  <si>
-    <t>AMR -Houston</t>
-  </si>
-  <si>
-    <t>HFD MD – HFD | EMERGENCY MEDICAL SERVICES</t>
-  </si>
-  <si>
-    <t>Ambulance Services in Houston, TX- The Real Yellow Pages</t>
-  </si>
-  <si>
-    <t>Orion EMS</t>
-  </si>
-  <si>
-    <t>Emergency Medical Services - Harris Health System</t>
-  </si>
-  <si>
-    <t>HCEC - Harris County Emergency Corps</t>
-  </si>
-  <si>
-    <t>Houston AmbulanceService — ER, Discharge &amp; Facility Transfers ...</t>
-  </si>
-  <si>
-    <t>Texas-Acadian Ambulance Service</t>
-  </si>
-  <si>
-    <t>Frazer - Custom Emergency Vehicles</t>
+    <t>Los Angeles CaliforniaBank | Chinatown LA Bank |FirstBank</t>
+  </si>
+  <si>
+    <t>FirstBank | MO Bank | IL Bank |CABank | Accounts | Loans</t>
+  </si>
+  <si>
+    <t>Locations-FirstLegal</t>
+  </si>
+  <si>
+    <t>FIRST- Improving Security Together</t>
+  </si>
+  <si>
+    <t>Ambulance- Wikipedia</t>
+  </si>
+  <si>
+    <t>Canyon County Paramedics | Home</t>
+  </si>
+  <si>
+    <t>AmbulanceServices inNampa,ID- The Real Yellow Pages®</t>
+  </si>
+  <si>
+    <t>Ambulanceand Patient TransportIdaho| Acute Rescue</t>
+  </si>
+  <si>
+    <t>Canyon County Paramedics |Patient Financial Services| Pay Online</t>
+  </si>
+  <si>
+    <t>TOP 10 BESTAmbulanceService inNampa,ID- Yelp</t>
+  </si>
+  <si>
+    <t>Emergency medical services- Wikipedia</t>
+  </si>
+  <si>
+    <t>AMBULANCEDefinition &amp; Meaning - Merriam-Webster</t>
+  </si>
+  <si>
+    <t>EMS Locator inIdaho—AmbulanceStation Map | AllFirefighter</t>
+  </si>
+  <si>
+    <t>Non EmergencyAmbulanceServices inNampa,ID- Superpages</t>
   </si>
   <si>
     <t>Google</t>
@@ -256,6 +259,9 @@
     <t>YahooSearch- WebSearch</t>
   </si>
   <si>
+    <t>PrivateSearchEngine - BraveSearch</t>
+  </si>
+  <si>
     <t>Google Search- A new kind of help</t>
   </si>
   <si>
@@ -265,37 +271,37 @@
     <t>DuckDuckGo- Protection. Privacy. Peace of mind.</t>
   </si>
   <si>
-    <t>Startpage.com</t>
-  </si>
-  <si>
-    <t>Records | Bexar County,TX- Official Website</t>
-  </si>
-  <si>
-    <t>Civil District Courts| Bexar County,TX- Official Website</t>
-  </si>
-  <si>
-    <t>Lone StarCivil- Top RatedSan AntonioGeneral Contractor</t>
-  </si>
-  <si>
-    <t>CivilEngineering Firm inSan Antonio,TX|CivilTech, PLLC</t>
-  </si>
-  <si>
-    <t>CivilEngineeringSan Antonio TX- Givler Engineering Inc.</t>
+    <t>GoogleSearch</t>
+  </si>
+  <si>
+    <t>Superior Court ofLos AngelesCounty |Civil</t>
+  </si>
+  <si>
+    <t>Superior Court ofLos AngelesCounty |CivilCase Access</t>
   </si>
   <si>
     <t>CIVILDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>Civil Engineers in San Antonio, TX- The RealYellow Pages</t>
-  </si>
-  <si>
-    <t>Bachelor's Degree inCivilEngineering | UTSan Antonio</t>
-  </si>
-  <si>
-    <t>CivilEngineering Company inSan Antonio| Pape-Dawson</t>
-  </si>
-  <si>
-    <t>San Antonio, TX Civil Litigation Law Firms&amp; Lawyers</t>
+    <t>CivilDivision - LA Court</t>
+  </si>
+  <si>
+    <t>Superior Court ofLos AngelesCounty | Home</t>
+  </si>
+  <si>
+    <t>CivilServices |Los AngelesCounty Sheriff’s Department</t>
+  </si>
+  <si>
+    <t>Civil engineering-Wikipedia</t>
+  </si>
+  <si>
+    <t>Civilcases inCalifornia|CaliforniaCourts | Self Help Guide</t>
+  </si>
+  <si>
+    <t>CIVIL| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
+    <t>Civil- definition ofcivilby The Free Dictionary</t>
   </si>
   <si>
     <t>Emergency &amp; Rescue</t>
@@ -304,262 +310,268 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=405c086ea9167d1470ad46de17e922d2413cfa06baf0f8c0c8d62f2a19939089JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c51d177-a610-6353-2b05-c696a73962fc&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GaXJl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dd5da7287d9539c7f98b9646bb74741e10c9b676406f2cdd12d35713db304467JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c51d177-a610-6353-2b05-c696a73962fc&amp;u=a1aHR0cHM6Ly93aWxkZmlyZXRyYWNrZXJzLmNvbS9mL21hcA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=34cfc88e9151cf148172b4f171f3a285e70f9ae779dea86fa72f0e0d93416babJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c51d177-a610-6353-2b05-c696a73962fc&amp;u=a1aHR0cHM6Ly93d3cuZmlyZWZveC5jb20vZW4tVVMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=50e0b431db64d6f5ac40565b9565503e871e0c307a10eda9091988c46683df96JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c51d177-a610-6353-2b05-c696a73962fc&amp;u=a1aHR0cHM6Ly93d3cuZmlyZS5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=89ff7a91789fddfb0bd3183283957a3d80bff885fcf404b1c4e3447ed9b626cfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c51d177-a610-6353-2b05-c696a73962fc&amp;u=a1aHR0cHM6Ly9maXJlLmFpcm5vdy5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6993a118b7f2b5202644d8075d4c60702b3c4b8b37c6324128346b1913ff8746JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c51d177-a610-6353-2b05-c696a73962fc&amp;u=a1aHR0cHM6Ly93d3cubmlmYy5nb3YvZmlyZS1pbmZvcm1hdGlvbi9tYXBz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a4d503361b8f92fb6bb11e8db6ec3575e5c1a4b3bd8fc3faa727d8d63c0df703JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c51d177-a610-6353-2b05-c696a73962fc&amp;u=a1aHR0cHM6Ly9hbGxmaXJlZmlnaHRlci5jb20vd2lsZGZpcmVzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=96687f5390260ae0976f0ed3ccfbc44015d3b6ab822d8412a51c50c320d6b242JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c51d177-a610-6353-2b05-c696a73962fc&amp;u=a1aHR0cHM6Ly93d3cuZmlyZW1hcC5saXZlLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6a3eb76963dfae9d117191bc734f75286d2e3c889e64d50ce9f9d705135700bdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c51d177-a610-6353-2b05-c696a73962fc&amp;u=a1aHR0cHM6Ly9hcHAud2F0Y2hkdXR5Lm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=86bd1ddcbe914d34d40d8dcfcdc9a2247b90998d29d3cf7ad84ed5a063747700JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0c51d177-a610-6353-2b05-c696a73962fc&amp;u=a1aHR0cHM6Ly93d3cubmlmYy5nb3YvZmlyZS1pbmZvcm1hdGlvbi9uZm4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=36a67ae63635ec2502e5acdf8c3d51de1dde537dd0556fa943a6ada2ea06f474JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f075b96-0559-6d9e-2590-4c7704d76c47&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MDA2ODA2Ny8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e3f2621211921685fa517f0f734e8ce72c1575d403e5d4f47532bd6c5f3709ddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f075b96-0559-6d9e-2590-4c7704d76c47&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9FbWVyZ2VuY3kh&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=30a59a91d09e2b04ded839a793eec88ab2acb8da939eb12ae43c6cc3d4f198bbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f075b96-0559-6d9e-2590-4c7704d76c47&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9FbWVyZ2VuY3k&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=381303bc507aad26a1f70efc42dd053a677edc2406a0af5b735983efdb18e420JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f075b96-0559-6d9e-2590-4c7704d76c47&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9bEJyUkE1UkNZVFU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ae0feb5e6fa05f0b674341861d05e7ddc5dc94123f172d514390da003c807932JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f075b96-0559-6d9e-2590-4c7704d76c47&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VtZXJnZW5jeQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bb8f4fb1272f201c7e8ca31c6e6bf79f7647234c106db76473799a44bde69b08JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f075b96-0559-6d9e-2590-4c7704d76c47&amp;u=a1aHR0cHM6Ly9kb3lvdXJlbWVtYmVyLmNvbS8xNTg1NjEvZW1lcmdlbmN5LWNhc3QtdGhlbi1ub3c&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2e7af76bb4a88450803d0477707d8ce2e5be4edfc98bc2ece9b0e69909346193JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f075b96-0559-6d9e-2590-4c7704d76c47&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MDA2ODA2Ny9mdWxsY3JlZGl0cy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0e14b6db5be07f69c672cabe8a21c417ac168f71f0f78d346b38b499aecde68bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f075b96-0559-6d9e-2590-4c7704d76c47&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2VtZXJnZW5jeQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=068bfe31cd8c80b731514fff4218e988f9e2e45a6edc67c6ecc92634adf753e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f075b96-0559-6d9e-2590-4c7704d76c47&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bb3d3dc1385900f69f4ea6bf16b5cd6017301e544bc6655f098ed35606e322b1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f075b96-0559-6d9e-2590-4c7704d76c47&amp;u=a1aHR0cHM6Ly9jaXR5b2ZkZWxjaXR5Lmdvdi9kZXBhcnRtZW50cy9hbGwtZGVwYXJ0bWVudHMvZmlyZS1kZXBhcnRtZW50L2VtZXJnZW5jeS1tYW5hZ2VtZW50Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0032cc8d1631388416b01f50bf8da0f5ad0eb2da61cf636397cfa79523d96d0fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=328c38f2-d9f4-63b4-279d-2f13d8be6282&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9TZWE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bd21545319167b7df22bf8c418893e8d2a3cc75b6203b96b3c85ae165b3d93aeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=328c38f2-d9f4-63b4-279d-2f13d8be6282&amp;u=a1aHR0cHM6Ly90aW1lc29maW5kaWEuaW5kaWF0aW1lcy5jb20vdHJhdmVsL2Rlc3RpbmF0aW9ucy9kby15b3Uta25vdy10aGUtZGlmZmVyZW5jZS1iZXR3ZWVuLW9jZWFuLXNlYS1iYXktYW5kLWd1bGYvYXJ0aWNsZXNob3cvMTEwOTY1MTM0LmNtcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0e8187166b560ffcc44cc05912c75065b35b8e1baa635f04a4736f89dd5920d7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=328c38f2-d9f4-63b4-279d-2f13d8be6282&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9MaXN0X29mX3NlYXNfb25fRWFydGg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=43628bab3825457a8f825a94ede3a0d2112b4ea343445069402247b55f60e01aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=328c38f2-d9f4-63b4-279d-2f13d8be6282&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvU2Vh&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=54833c76efa0de8ab3cb0464b7131b4405e9a9d5bc8c1d60583d9d469a96fe3fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=328c38f2-d9f4-63b4-279d-2f13d8be6282&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9PY2Vhbi12cy1TZWEtV2hhdHMtdGhlLURpZmZlcmVuY2U&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=482ff20c64c4570c6411cb469a9b4104d59ec3184146ed02b0abf7c85642b5bcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=328c38f2-d9f4-63b4-279d-2f13d8be6282&amp;u=a1aHR0cHM6Ly9lZHVjYXRpb24ubmF0aW9uYWxnZW9ncmFwaGljLm9yZy9yZXNvdXJjZS9zZWEv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=74e81667e24310256ced9b094c2bec0d1f4927bce75de3c8989e9e68ee555b9dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=328c38f2-d9f4-63b4-279d-2f13d8be6282&amp;u=a1aHR0cHM6Ly9zZWEuZWR1Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a3e840faf6809cf3146f8646b29f21608e1683985406040cb384e7e338bf7befJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=328c38f2-d9f4-63b4-279d-2f13d8be6282&amp;u=a1aHR0cHM6Ly93d3cuc2VhLmNvbS9pbnZlc3Rvci9ob21l&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b459c1161febbad875b7dc9ff67694e1df2f107e9a46b45f8c652560bf33925bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=328c38f2-d9f4-63b4-279d-2f13d8be6282&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NlYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=69d631ac609da2648807457904c4f31a4afb231c71ef29458b7ccfbae3ed7a25JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=328c38f2-d9f4-63b4-279d-2f13d8be6282&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9zZWE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f01a9da68c43ee1f22a35d17a1e9fc9ccc1545ce83a57bb04b70f8680071ed23JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=252668b8-f30b-65f8-1193-7f59f2136439&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Nb3VudGFpbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d7b04a9b209634c4d7c86a1712654c32035ee6ef9e01725fafe12e687b02e03cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=252668b8-f30b-65f8-1193-7f59f2136439&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9tb3VudGFpbi1sYW5kZm9ybQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9367e089267867a5cecb40c21aa7c29a62ccf9a9464c85749a9eda3d213f8d3cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=252668b8-f30b-65f8-1193-7f59f2136439&amp;u=a1aHR0cHM6Ly93d3cud29ybGRhdGxhcy5jb20vYXJ0aWNsZXMvd2hhdC1pcy1hLW1vdW50YWluLmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d835a15020712401fe32d5b9af980595609783bdd8a04c9c58731af83942f1cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=252668b8-f30b-65f8-1193-7f59f2136439&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L21vdW50YWlu&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8219e4dbf5efc7195da40eab465813a1c57bb80065add0276a36398c77185919JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=252668b8-f30b-65f8-1193-7f59f2136439&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvTW91bnRhaW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3cd8ae655448f0d709b403f320b2d199b24d925774781222f8e95d8a08a4c991JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=252668b8-f30b-65f8-1193-7f59f2136439&amp;u=a1aHR0cHM6Ly93d3cubmF0aW9uYWxnZW9ncmFwaGljLmNvbS9zY2llbmNlL2FydGljbGUvbW91bnRhaW5z&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5a44d865e95948301b63fc9831c01dd7eb97adf69e71d2101f2979cbeeba68a2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=252668b8-f30b-65f8-1193-7f59f2136439&amp;u=a1aHR0cHM6Ly9raWRzLm5hdGlvbmFsZ2VvZ3JhcGhpYy5jb20vbmF0dXJlL2hhYml0YXRzL2FydGljbGUvbW91bnRhaW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=603a768d5cf32715d928884576e28ab8fc07a44a2590551e07663f44a864e9f7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=252668b8-f30b-65f8-1193-7f59f2136439&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Nb3VudF9FdmVyZXN0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=108226ede3543147ff1c9cc63b2bcb1076d1b39d711e744a2f95b35041c75361JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=252668b8-f30b-65f8-1193-7f59f2136439&amp;u=a1aHR0cHM6Ly93d3cubnBzLmdvdi9zdWJqZWN0cy9tb3VudGFpbnMvaW5kZXguaHRt&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d491cc3ce3005ccb42735cca178c09292cc80dad32d358b087dbc1a522993a85JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=252668b8-f30b-65f8-1193-7f59f2136439&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL21vdW50YWlu&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b262da16678b6a266e5785c72bd6d96f9f9d95e615250551741422572f081539JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22cf30f0-d95c-665c-26eb-2711d8a96743&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRGlzYXN0ZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=23fdd020aea652d7bb72fc7c06af2f7cde5edcb2d659553c23923e9094f6def0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22cf30f0-d95c-665c-26eb-2711d8a96743&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9kaXNhc3Rlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6b7e27eedbcffddb9fc0c27cd97cde11062d8346414eb9f73ba15ae0e6b706faJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22cf30f0-d95c-665c-26eb-2711d8a96743&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3YvZGlzYXN0ZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=df1c4809113302082550de7ac344b74f835f5fb2674d8cfb169090818f5f26adJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22cf30f0-d95c-665c-26eb-2711d8a96743&amp;u=a1aHR0cHM6Ly93d3cuZGlzYXN0ZXJhc3Npc3RhbmNlLmdvdi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e29a541cdc0054490611b20e607fcfb2d027607095c891435b4194c131996513JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22cf30f0-d95c-665c-26eb-2711d8a96743&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Rpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=60df653a9d0c4cd1f1c0a3276970a51bd09c0c8ce65b26c3fd6e0e660b9cb9ceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22cf30f0-d95c-665c-26eb-2711d8a96743&amp;u=a1aHR0cHM6Ly93d3cudW5kcnIub3JnL3Rlcm1pbm9sb2d5L2Rpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b7b550026e6d763d970cce606182c2e232a473349dec958045f102add67aee3aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22cf30f0-d95c-665c-26eb-2711d8a96743&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9uYXR1cmFsLWRpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0164a5d646c86d721a014c240530ade14ebf7ee7ccee887a7e3b2b679f7d0c5cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22cf30f0-d95c-665c-26eb-2711d8a96743&amp;u=a1aHR0cHM6Ly93d3cuaWZyYy5vcmcvb3VyLXdvcmsvZGlzYXN0ZXJzLWNsaW1hdGUtYW5kLWNyaXNlcy93aGF0LWRpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2d3c892ea5a9c2ac43da0735a7a848b6d579369a878363fa9a6f7de25437260fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=22cf30f0-d95c-665c-26eb-2711d8a96743&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Rpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b82e41fc91f53a592a5a8d6afd35a6ca8440d867016af34fca737cae1390a7cdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21cab581-9f2c-6a0d-101b-a2609ed46b5a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZpcnN0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0608ddb9119978ce9682bb1f8e45de5be414581b3c97e6d18721de27be1ffe51JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21cab581-9f2c-6a0d-101b-a2609ed46b5a&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZpcnN0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3fc4e8dfc69ad02be798fec82a4370556aa4d5d61bd4d7350dda576562739277JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21cab581-9f2c-6a0d-101b-a2609ed46b5a&amp;u=a1aHR0cHM6Ly90ZXhhc2ZpcnN0LmJhbmsvcGVyc29uYWwv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=77fdb832fff67509b316bd07a6ab9b260d60e0f0bb8392d31ec86b6885a6386fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21cab581-9f2c-6a0d-101b-a2609ed46b5a&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RpbnNwaXJlcy5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=24e34594cfd7a6a820ac3165561f3289d7463acc8ae87809f197ea692169e1a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21cab581-9f2c-6a0d-101b-a2609ed46b5a&amp;u=a1aHR0cHM6Ly9lbi53aWt0aW9uYXJ5Lm9yZy93aWtpL2ZpcnN0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ec2f10bba79cfa9f03fe04f75951b6e5c12bbd32e6c26ae447b9d9f3c684970dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21cab581-9f2c-6a0d-101b-a2609ed46b5a&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RjaXRpemVucy5jb20vcGVyc29uYWwvZGlnaXRhbC1iYW5raW5n&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f33604c7da804c336661be0b82a85a5b82fad724fcc0cf42cf29a159a34ffa2fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21cab581-9f2c-6a0d-101b-a2609ed46b5a&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9maXJzdA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ecd6aa817e287b7e576b5efc09750b8c4317e7a60950da524ded0e710b315b83JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21cab581-9f2c-6a0d-101b-a2609ed46b5a&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2ZpcnN0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=429a7c230c929a48dc2f8f5c80f4680cf372adc5eeb9019d84338fe091df4873JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21cab581-9f2c-6a0d-101b-a2609ed46b5a&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2ZpcnN0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d756bf3d689758319827c0cf7043332b52a13814666fbc3708b707b3c6e7b1d2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21cab581-9f2c-6a0d-101b-a2609ed46b5a&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RpbnNwaXJlcy5vcmcvdGVhbS1ldmVudC1zZWFyY2g&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=611cfa3c724ded5695e1f615ab70525297c64c74e9ba69ce71c3fe119055e438JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3a3ca-be59-6b76-1b30-b42bbf416a3e&amp;u=a1aHR0cHM6Ly93aW5kc29yZW1zLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a5ac2211d9ca8568ffd0ad3061f31c0cb502225956656388705f1d03d787e15eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3a3ca-be59-6b76-1b30-b42bbf416a3e&amp;u=a1aHR0cHM6Ly93d3cuYW1yLm5ldC9sb2NhdGlvbnMvdGV4YXMvaG91c3Rvbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=227bfcc3b0bc453f4afe3bc60cf4c94a6b2eed3602671f543631bd648bdc6e5aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3a3ca-be59-6b76-1b30-b42bbf416a3e&amp;u=a1aHR0cHM6Ly93d3cuaGZkbWQub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11e48ace6034219e97c3d9738b24582450bf989c60c3277d77c8675b0736ebe7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3a3ca-be59-6b76-1b30-b42bbf416a3e&amp;u=a1aHR0cHM6Ly93d3cueWVsbG93cGFnZXMuY29tL2hvdXN0b24tdHgvYW1idWxhbmNlLXNlcnZpY2Vz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=796f8ebc13e406838a129d7dbac1dd56156394ff47fa776848d915017fc3d61aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3a3ca-be59-6b76-1b30-b42bbf416a3e&amp;u=a1aHR0cHM6Ly93d3cub3Jpb25lbXMuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be9ce6f5be180c0101e1b24554580a6872666260e276893912f6e18cd4fb6170JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3a3ca-be59-6b76-1b30-b42bbf416a3e&amp;u=a1aHR0cHM6Ly93d3cuaGFycmlzaGVhbHRoLm9yZy9zZXJ2aWNlcy1oaC9jbGluaWNhbC1zZXJ2aWNlcy9QYWdlcy9lbXMuYXNweA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=012c0cd696afeed452b9049b05c283e00940f271ac58e0070a01785854e8d510JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3a3ca-be59-6b76-1b30-b42bbf416a3e&amp;u=a1aHR0cHM6Ly9oY2VjLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a26fb53cadb20c7040689cf9c92ff50059fc5a2be4435e621f4117fead3fb7cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3a3ca-be59-6b76-1b30-b42bbf416a3e&amp;u=a1aHR0cHM6Ly9wcmVmZXJyZWRlbXMuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d79e796754af602cfae082a238b9b24000d61a1cf19bd5814edc1a1c8752cdccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3a3ca-be59-6b76-1b30-b42bbf416a3e&amp;u=a1aHR0cHM6Ly9hY2FkaWFuYW1idWxhbmNlLmNvbS9sb2NhdGlvbnMvdGV4YXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c9d1d0ea586afa1347b66b88fc28e0a61dac8a41c93feee702b5496d4e7ca84eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=12c3a3ca-be59-6b76-1b30-b42bbf416a3e&amp;u=a1aHR0cHM6Ly93d3cuZnJhemVyYmlsdC5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb3b799f222ecb0ab7dc572b0d5fbcef501abbf355a865e9a9832adef4b6a066JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ae39531-4b09-6d8c-0fd9-82d04a5a6c20&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS94aHRtbC9zZWFyY2g&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=59ddeeae437311802e9273b2832fa8b19244d94b23d04386e06ff0b32884edddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0256f859-a457-6be6-0fb8-efb8a5cd6a62&amp;u=a1aHR0cHM6Ly93ZmNhLmNvbS9maXJlLW1hcC93YXNoaW5ndG9u&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed0348b6d50410b3f401aaa40231dd1221890c50eef7d6aa6bb6d5cf3687a31dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0256f859-a457-6be6-0fb8-efb8a5cd6a62&amp;u=a1aHR0cHM6Ly93aWxkZmlyZXRyYWNrZXJzLmNvbS9mL21hcA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=83066299856b3aa3cae389734b281ec0d15108767bd52054b3daf011aad9d9b2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0256f859-a457-6be6-0fb8-efb8a5cd6a62&amp;u=a1aHR0cHM6Ly9maXJlLmFpcm5vdy5nb3YvP2xhbmc9ZW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b42686a007d9e2a2efeaf5f01409a5ab3fba0ffabc9c64d19a110afdf7438440JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0256f859-a457-6be6-0fb8-efb8a5cd6a62&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GaXJl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47695b632c2cacfb9307cb0f6430cf2365176bea138291ad82258f502ac2cc9bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0256f859-a457-6be6-0fb8-efb8a5cd6a62&amp;u=a1aHR0cHM6Ly93d3cuZmlyZS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7adf2928ff685ba1ba23c0b4ed1bcb003c8c959c30415e62554ee165e933acf5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0256f859-a457-6be6-0fb8-efb8a5cd6a62&amp;u=a1aHR0cHM6Ly9maXJlbmVhcmJ5LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4a5130851c8a5c506f1ac119f0880c0a06ea66094973b9a6113f2040054c1950JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0256f859-a457-6be6-0fb8-efb8a5cd6a62&amp;u=a1aHR0cHM6Ly9hbGxmaXJlZmlnaHRlci5jb20vd2lsZGZpcmVzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fa8deeb3638ef2e5002e5547315953f593be5abc910fe8165a459a2f453b0494JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0256f859-a457-6be6-0fb8-efb8a5cd6a62&amp;u=a1aHR0cHM6Ly9maXJlbWFwLnVzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=643890d82c8e02baf45f701e41337f50b4dd17dc2b979aef5886b7e2c475a49dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0256f859-a457-6be6-0fb8-efb8a5cd6a62&amp;u=a1aHR0cHM6Ly93d3cuZG9pLmdvdi93aWxkbGFuZGZpcmVzZXJ2aWNlL2N1cnJlbnQtd2lsZGZpcmUtaW5mb3JtYXRpb24&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d80dfe84c5e710d1c3450fb57f9a7d01d987b16b56843d34b78617e055e62e4bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0256f859-a457-6be6-0fb8-efb8a5cd6a62&amp;u=a1aHR0cHM6Ly93d3cuZmlyZWZveC5jb20vZW4tVVMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=82730d69ab1c87f48c413b51ffbe2f30d236ef600c35ff7ac098eea2acdb2ed3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25f3a04e-4b07-6bbc-2fdd-b7af4ab56adf&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQwMDY4MDY3Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=850191e8fcc6499f734ccf14db55d601d82ce7d92fd7bdb3cac1080ee969ad43JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25f3a04e-4b07-6bbc-2fdd-b7af4ab56adf&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5IQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ea5881a287b90af70ed657b3ee88836c11656aaf0e842c641ffb564ccac26cc5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25f3a04e-4b07-6bbc-2fdd-b7af4ab56adf&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f0a10a8cfd4886d8ba3e981eec038ff9537df71b375a7ff4d2091a5569cf9dacJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25f3a04e-4b07-6bbc-2fdd-b7af4ab56adf&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VtZXJnZW5jeQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d0b204261eeed4dd242f5ccc00568aae29c112ca9c6ec53252298417f1d7353bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25f3a04e-4b07-6bbc-2fdd-b7af4ab56adf&amp;u=a1aHR0cHM6Ly9kb3lvdXJlbWVtYmVyLmNvbS8xNTg1NjEvZW1lcmdlbmN5LWNhc3QtdGhlbi1ub3c&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6492bac85f05fc74f6cb5fa3279894d40ae4bdc3b8e851b89bf7b430313213a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25f3a04e-4b07-6bbc-2fdd-b7af4ab56adf&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1sQnJSQTVSQ1lUVQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=17e1c09c35ee8c9b059e3a188a91c28676898d1c63010ffb44ed3e2bbfdfdca4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25f3a04e-4b07-6bbc-2fdd-b7af4ab56adf&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQwMDY4MDY3L2Z1bGxjcmVkaXRzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=faf05076599bf8cd0c60c2318f7251601ad2856e8b85db91056672703a31339cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25f3a04e-4b07-6bbc-2fdd-b7af4ab56adf&amp;u=a1aHR0cHM6Ly93d3cucGhvZW5peC5nb3YvYWRtaW5pc3RyYXRpb24vZGVwYXJ0bWVudHMvZW1lcmdlbmN5Lmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2dfcd6faa7233c6c2081043423c4c1711acd3fc6d3e25c18bcb68a8b4e8cd8ceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25f3a04e-4b07-6bbc-2fdd-b7af4ab56adf&amp;u=a1aHR0cHM6Ly93d3cucmVhZHkuZ292Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6172e622eae11813f73a6db93a8781a5bf1f1bbf52ba637f9b89cc06e0aae2a6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25f3a04e-4b07-6bbc-2fdd-b7af4ab56adf&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2VtZXJnZW5jeQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e2e596aeb65c4dee577a927403a442820b921bb0346e2d02743cf464944b8447JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=00638313-c397-6c17-021b-94f2c2a16d97&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9TZWE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8875a6915976f3a9b07ff2818497bf10100dc2d897351bd39c37f2da7d357650JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=00638313-c397-6c17-021b-94f2c2a16d97&amp;u=a1aHR0cHM6Ly90aW1lc29maW5kaWEuaW5kaWF0aW1lcy5jb20vdHJhdmVsL2Rlc3RpbmF0aW9ucy9kby15b3Uta25vdy10aGUtZGlmZmVyZW5jZS1iZXR3ZWVuLW9jZWFuLXNlYS1iYXktYW5kLWd1bGYvYXJ0aWNsZXNob3cvMTEwOTY1MTM0LmNtcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e5a494338b32d265f68fe2286d2c6291bd1f461b51790b370eca28b39c312f3fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=00638313-c397-6c17-021b-94f2c2a16d97&amp;u=a1aHR0cHM6Ly9zZWEuZWR1Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=95e42fa0c23ea43525eb9125a61762684e1cb38b78dd7d94d11e4a5217e63090JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=00638313-c397-6c17-021b-94f2c2a16d97&amp;u=a1aHR0cHM6Ly93d3cucG9ydHNlYXR0bGUub3JnL3NlYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=298ecf6c1e06f466a6b4388a3e196a007a2e4261ae72e230ccb293ac1c90218cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=00638313-c397-6c17-021b-94f2c2a16d97&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvU2Vh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9926410ef395a8d52da57ef6180905cb783fc6be335cd4279485e7525a88a35cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=00638313-c397-6c17-021b-94f2c2a16d97&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9MaXN0X29mX3NlYXNfb25fRWFydGg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb491f0710d22f9a283d98c7e0139924085e580cf94d05c1cc1d7d8c3b664b44JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=00638313-c397-6c17-021b-94f2c2a16d97&amp;u=a1aHR0cHM6Ly9lZHVjYXRpb24ubmF0aW9uYWxnZW9ncmFwaGljLm9yZy9yZXNvdXJjZS9zZWEv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a2b5a32ab6bc826a6865bfc05bb310abf10589a1e4092fab0da633f9fc18ab13JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=00638313-c397-6c17-021b-94f2c2a16d97&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9PY2Vhbi12cy1TZWEtV2hhdHMtdGhlLURpZmZlcmVuY2U&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a79954102e018c4898fb36f47b9f56410ed94dd474edb6b88cdbc8465a65cd29JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=00638313-c397-6c17-021b-94f2c2a16d97&amp;u=a1aHR0cHM6Ly9zZWF0dGxld2VhLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a4172b68e08683c84b44535d35c1d1f09822c6cdf5988c2c9cfbe3107c199686JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=00638313-c397-6c17-021b-94f2c2a16d97&amp;u=a1aHR0cHM6Ly93d3cuc2VhLmNvbS9pbnZlc3Rvci9ob21l&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5d87d6f9743c71eedf557ca93691cdab8d4a6aab8dae8d5db58d9db0ce824182JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fd16acd-ac1d-6a24-02c3-7d2cad066be6&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vYWthaWhvb2Qvb2ZmZXJz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=78394c1eaa6c7785a9c083c06551aabeedb8be8c27e53fddcb77b892e6031a3eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fd16acd-ac1d-6a24-02c3-7d2cad066be6&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vbWF4ZXh0cmFjdG9ycy9hY3Rpdml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=64c3cfa76074818a5fed9898617820e8014dd1f48d4f0c11e2c7cffd50e81135JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fd16acd-ac1d-6a24-02c3-7d2cad066be6&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vZ2xvb21pZXNyaC9hY3Rpdml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=930affa78b04974653043daaff10eb04eec8ecbb4f6e6b7a99ff09ef0cf9956bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fd16acd-ac1d-6a24-02c3-7d2cad066be6&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vaHVzaHB1cHBpZXp6ei9vZmZlcnM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=392554e4d7b34a3198f514406bdc5de6eab23588210b7e5fa8fd8865b1910ae4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fd16acd-ac1d-6a24-02c3-7d2cad066be6&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vc29sdmUtZXQtY29hZ3VsYS1yaC9hY3Rpdml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4b6ae1db7d8245612036424d17e2c03fc8b0ec048be18f093259babdd76db7e0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fd16acd-ac1d-6a24-02c3-7d2cad066be6&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vem9ua3NhcnQvb3ZlcnZpZXc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1289702b2bdc025bf72c4daca5cb731dfde56fec08a52be158e9997511b20c02JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fd16acd-ac1d-6a24-02c3-7d2cad066be6&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vcG9ydGFibGUtc2xvcC1kcml2ZS9hY3Rpdml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3b2a155ea9fa4b3739df41ea0af7782e94deabb5bed695adba833b15bbabacbbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fd16acd-ac1d-6a24-02c3-7d2cad066be6&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vcHJvamVjdGNwdS9vZmZlcnM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c346374feb187cef54b3cc958552147ed4f66dadba10f39ae3ee7bcede29f3b8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fd16acd-ac1d-6a24-02c3-7d2cad066be6&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vZ2FtZWJveS0xNjM4NTIyMDQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ebdde641f719f92fb14cd07d7d16ced79796c90e4e47381a5317a66ca6ea3247JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fd16acd-ac1d-6a24-02c3-7d2cad066be6&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vdW5pY3JlZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=48671e327f653ab3adfbcf75e22b7baed80462d79c305fe5a87961055a23c7dbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32dfbf0f-8668-6e70-0506-a8ee879a6fd7&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRGlzYXN0ZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5e8e633575955f38ff0bf9ffa2356deed1cab186ffef22b2554be8fe705d9bfbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32dfbf0f-8668-6e70-0506-a8ee879a6fd7&amp;u=a1aHR0cHM6Ly93d3cuZGlzYXN0ZXJhc3Npc3RhbmNlLmdvdi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d4576ec7d8d60fd770f99eee254f4adff73e88cd0b9ab0f220d63798727c358bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32dfbf0f-8668-6e70-0506-a8ee879a6fd7&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9kaXNhc3Rlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d20c5981d2f3cca43dc8ea50525784495172c5c24406c17b96cb25d5da0a01eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32dfbf0f-8668-6e70-0506-a8ee879a6fd7&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Rpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6300002d7884621bb3cff125aeb17de9d0456bc080541b3df57083f410868d85JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32dfbf0f-8668-6e70-0506-a8ee879a6fd7&amp;u=a1aHR0cHM6Ly93d3cudW5kcnIub3JnL3Rlcm1pbm9sb2d5L2Rpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e2f855ac2855f55813b73003894500ba0385126de7a1020ae46929ab901c1659JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32dfbf0f-8668-6e70-0506-a8ee879a6fd7&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3YvZGlzYXN0ZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b4c32acf29d59ab01da02ff622393df37203a5a8a4ebee9f0f0fedcfaa04ba98JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32dfbf0f-8668-6e70-0506-a8ee879a6fd7&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9uYXR1cmFsLWRpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8424231d2d5a7b9009506d6d2a7fe06651af3aa8cccce70aa863f893282a6f95JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32dfbf0f-8668-6e70-0506-a8ee879a6fd7&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=81e5ca7684a9936225ad41162862431e5ab749c17262f3468cafcb6762404de6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32dfbf0f-8668-6e70-0506-a8ee879a6fd7&amp;u=a1aHR0cHM6Ly93d3cuaWZyYy5vcmcvb3VyLXdvcmsvZGlzYXN0ZXJzLWNsaW1hdGUtYW5kLWNyaXNlcy93aGF0LWRpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0485ad08dc6380cd173c6ec33289e85e20b0b1be16c56d9fd1f25a7939c2bd82JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32dfbf0f-8668-6e70-0506-a8ee879a6fd7&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTmF0dXJhbF9kaXNhc3Rlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3797c72845620155ab432b44fe103d1553f4cc013c325b5a093f71216d6fafd0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=142617c9-4118-6e4b-2365-0028401d6fee&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RpbnNwaXJlcy5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0a27f764816abd231621d0f150945f4e195f95d6eb3bfb643eb236b8a3747cebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=142617c9-4118-6e4b-2365-0028401d6fee&amp;u=a1aHR0cHM6Ly9jYWZpcnN0Lm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47c6eba50ae3a670bbcf1320ca2f25a435d44be83fc222d8faf0930ac87b24bbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=142617c9-4118-6e4b-2365-0028401d6fee&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZpcnN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f75d1bdd2aef66520ab42186bff846a7c67592ee0a1371e7fcd6f49b445daa09JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=142617c9-4118-6e4b-2365-0028401d6fee&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RjaXR5Y3Uub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2924d5859197df686e785dd2b31c4a27f6839fe6be2f79e5c21dd430e4537ac8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=142617c9-4118-6e4b-2365-0028401d6fee&amp;u=a1aHR0cHM6Ly9lbi5tLndpa3Rpb25hcnkub3JnL3dpa2kvZmlyc3Q&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d36ae3972afc12e860e55f441d43fd054630b186d2d5b2b67bff8c7e08ad9bbcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=142617c9-4118-6e4b-2365-0028401d6fee&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZpcnN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e10bdfeb0c6f2840c19e549ccc2f512cf4392c76d43878cc39b86a781722bbd0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=142617c9-4118-6e4b-2365-0028401d6fee&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3QuYmFuay9BYm91dC9Mb2NhdGlvbnMvTEEtQ2hpbmF0b3du&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=de3654495c39b0793de18c1d4180a630b004d859208b94ea5e03893184e0aa11JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=142617c9-4118-6e4b-2365-0028401d6fee&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3QuYmFuay8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b43bbccb3edc6151f2e9d5b474cfa2225500644b17e3df9a6560550e9bc49d86JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=142617c9-4118-6e4b-2365-0028401d6fee&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RsZWdhbC5jb20vbG9jYXRpb25zLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0aa92f6ef2e467a40dfeabbebee11c9f5c93f7ee22177130388eff34274fb2cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=142617c9-4118-6e4b-2365-0028401d6fee&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3Qub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4045b260140d1e005bd4d3fa6dfa44abffb7d8e9bdd4527165a0490d5af8f0d3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34113335-8033-6213-19a8-24d481f4636f&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9BbWJ1bGFuY2U&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=45ad9c5c4a5a0365c7fb9994687b95fbb4b3f4f4b26d602e6cdedc84d643b605JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34113335-8033-6213-19a8-24d481f4636f&amp;u=a1aHR0cHM6Ly93d3cuY2NwYXJhbWVkaWNzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e9bc0412a3e57dffec51a3badc929f6b883cfa3fa9ecc1edc1f47572edd2a1faJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34113335-8033-6213-19a8-24d481f4636f&amp;u=a1aHR0cHM6Ly93d3cueWVsbG93cGFnZXMuY29tL25hbXBhLWlkL2FtYnVsYW5jZS1zZXJ2aWNlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=98ad5fe0cfe545df66e9a255f70858d855d5e07839395361e5359a8e74647c84JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34113335-8033-6213-19a8-24d481f4636f&amp;u=a1aHR0cHM6Ly9hY3V0ZXJlc2N1ZS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=25c42b2bea45ba9da607e174809372b16d5c490f921312df1355d8c2ad2d47ebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34113335-8033-6213-19a8-24d481f4636f&amp;u=a1aHR0cHM6Ly93d3cuY2NwYXJhbWVkaWNzLmNvbS9wYXRpZW50LWZpbi1zZXJ2aWNlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=63a73c47fb6423eeda4d4b24299d684b8d3e7e1cd3a8e26c9ad9a89891aa7ad4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34113335-8033-6213-19a8-24d481f4636f&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2ZpbmRfZGVzYz1BbWJ1bGFuY2UrU2VydmljZSZmaW5kX2xvYz1OYW1wYSUyQytJRCZtc29ja2lkPTM0MTEzMzM1ODAzMzYyMTMxOWE4MjRkNDgxZjQ2MzZm&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1cc8005c20406afd8a745c4b6704e846604849fe5880b96d5ed2f20247889589JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34113335-8033-6213-19a8-24d481f4636f&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9FbWVyZ2VuY3lfbWVkaWNhbF9zZXJ2aWNlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e578190c1086dd661d3a458b1ebf906de51646d2030680568797a5991ded8395JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34113335-8033-6213-19a8-24d481f4636f&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FtYnVsYW5jZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=74cfdc20479f9e7e89da3de679222c641f6abd96ddd0288778bdcbe422606651JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34113335-8033-6213-19a8-24d481f4636f&amp;u=a1aHR0cHM6Ly9hbGxmaXJlZmlnaHRlci5jb20vdG9vbHMvZW1zLWxvY2F0b3IvdXMvaWRhaG8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef6420bdb85b7ea5261e424fa3b5a67705743c4707fe4cbeb4ce3796113750ecJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34113335-8033-6213-19a8-24d481f4636f&amp;u=a1aHR0cHM6Ly93d3cuc3VwZXJwYWdlcy5jb20vbmFtcGEtaWQvbm9uLWVtZXJnZW5jeS1hbWJ1bGFuY2Utc2VydmljZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=61a74b7f0fbc529eeae10728124b9c6caeb34fb1d01313f2907ce049159cc5cdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04cc24f1-be7c-65b2-2167-3310bf2c64e2&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS94aHRtbC9zZWFyY2g&amp;ntb=1</t>
   </si>
   <si>
     <t>https://www.bing.com/</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=400bc358e6d1faa79876e99e88b93ba96389222b2492b562d8f3739ac140090cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ae39531-4b09-6d8c-0fd9-82d04a5a6c20&amp;u=a1aHR0cHM6Ly9zZWFyY2gueWFob28uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9848dc654cf9e584bc605af2e9073193cf3bdc0d4b95c7d4ff56afd1e5426d1dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ae39531-4b09-6d8c-0fd9-82d04a5a6c20&amp;u=a1aHR0cHM6Ly9zZWFyY2guZ29vZ2xlLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c88b988d8eeefccb43e1442516b1820770b9d0bc2d3072538ba47f75a932816bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ae39531-4b09-6d8c-0fd9-82d04a5a6c20&amp;u=a1aHR0cHM6Ly93d3cueWFob28uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6885ca8e465fbaae6c85fb7837237cf175590c7b0bfc033914f5b6985397b5ceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ae39531-4b09-6d8c-0fd9-82d04a5a6c20&amp;u=a1aHR0cHM6Ly9kdWNrZHVja2dvLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=49a1ce2e9c895911f0f612e9c8118a3402208beb487677775dca54dfdf62b535JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ae39531-4b09-6d8c-0fd9-82d04a5a6c20&amp;u=a1aHR0cHM6Ly93d3cuc3RhcnRwYWdlLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0569a219d07146ba802b2c88061e3eb1d9ca1c30207d37afaff9916d00c5463bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d141ea8-762f-6d55-26e0-094977966c15&amp;u=a1aHR0cHM6Ly93d3cuYmV4YXIub3JnLzM3MDMvUmVjb3Jkcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=438f78110ef95fbc7e86988d089b2ac21d3709fdbd1d1b1b521e0ce8ea2c5cdcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d141ea8-762f-6d55-26e0-094977966c15&amp;u=a1aHR0cHM6Ly93d3cuYmV4YXIub3JnLzE3MDMvQ2l2aWwtRGlzdHJpY3QtQ291cnRz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=79f01036f21ec82ea613ab4cdf9439b7093abde0806738e71c18874bf4536aeeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d141ea8-762f-6d55-26e0-094977966c15&amp;u=a1aHR0cHM6Ly93d3cubG9uZXN0YXJjaXZpbC5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0666923992ba06dc4f70d5d0ce800281782d65582b834b3ed49b7f68d2b30ab2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d141ea8-762f-6d55-26e0-094977966c15&amp;u=a1aHR0cHM6Ly9jaXZpbHRlY2htYy5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6926e0665ede44d16425ea35b8b99f12a1aa4697db24b44f75f4bac520786695JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d141ea8-762f-6d55-26e0-094977966c15&amp;u=a1aHR0cHM6Ly9naXZsZXJlbmdpbmVlcmluZy5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b3588cb00fbf54dc0d22679903020f8ad849c071f54edd6057566d640902a5b3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d141ea8-762f-6d55-26e0-094977966c15&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Npdmls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=124590e9d171770285e1976e8f986515baa45828e48b81d7bfee926b1178984fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d141ea8-762f-6d55-26e0-094977966c15&amp;u=a1aHR0cHM6Ly93d3cueWVsbG93cGFnZXMuY29tL3Nhbi1hbnRvbmlvLXR4L2NpdmlsLWVuZ2luZWVycw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4e21cba7ec57e33ffe23142c8ba2676fc223d7e1954f865c427fcf8d593e1d5cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d141ea8-762f-6d55-26e0-094977966c15&amp;u=a1aHR0cHM6Ly9mdXR1cmUudXRzYS5lZHUvcHJvZ3JhbXMvdW5kZXJncmFkdWF0ZS9jaXZpbC1lbmdpbmVlcmluZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=98852d625777bbf5a1631b10be3c684eb97437b1fb8f84e7a2bddd2af97040b4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d141ea8-762f-6d55-26e0-094977966c15&amp;u=a1aHR0cHM6Ly93d3cucGFwZS1kYXdzb24uY29tL2xvY2F0aW9ucy9zYW4tYW50b25pby8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2fb66e386deb31365e3c51886f0f348352fc8ec3ac7ce15b475be56aede8ebeeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3d141ea8-762f-6d55-26e0-094977966c15&amp;u=a1aHR0cHM6Ly93d3cubGF3eWVycy5jb20vY2l2aWwtbGl0aWdhdGlvbi9zYW4tYW50b25pby90ZXhhcy9sYXctZmlybXMv&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ae8820bd4ed8386deb9a72a15638ad10cfdfc6079916c8a0bc7013be95d3dd63JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04cc24f1-be7c-65b2-2167-3310bf2c64e2&amp;u=a1aHR0cHM6Ly9zZWFyY2gueWFob28uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ff57bff7128607420ffc4c7bee3484efd8ba92409949caeee017158d2b73365eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04cc24f1-be7c-65b2-2167-3310bf2c64e2&amp;u=a1aHR0cHM6Ly9zZWFyY2guYnJhdmUuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=33f5d5ca28b047feadefae9d930c0d60907e9c76440aa0bbcb8d7b8cc6190155JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04cc24f1-be7c-65b2-2167-3310bf2c64e2&amp;u=a1aHR0cHM6Ly9zZWFyY2guZ29vZ2xlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2057724fba4b65c6bb9fbc0331060ea760875e1328dd3c80a49699650fda5410JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04cc24f1-be7c-65b2-2167-3310bf2c64e2&amp;u=a1aHR0cHM6Ly93d3cueWFob28uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=81ea413a755678c38803f8d1889321d71b972fe43504f2566d22e482270c7fd7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04cc24f1-be7c-65b2-2167-3310bf2c64e2&amp;u=a1aHR0cHM6Ly9kdWNrZHVja2dvLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4ac961ba8a8578824ac218d41b60c98e6e14d15d3fe972566727a4e0279ec76dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04cc24f1-be7c-65b2-2167-3310bf2c64e2&amp;u=a1aHR0cHM6Ly9hY2NvdW50cy5nb29nbGUuY29tL0ludGVyYWN0aXZlTG9naW4_c2VydmljZT1zYWZlc2VhcmNobG9jaw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a2fe813fce613e21bea34ae8e8963128e7271715bc139f51521e6c2912cb7f28JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26719d6a-553b-64f0-286f-8a8b54336540&amp;u=a1aHR0cHM6Ly93d3cubGFjb3VydC5jYS5nb3YvcGFnZXMvbHAvY2l2aWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6cf9b35d2df28581147319f3f38e4fdb8a1ba0ba565751e3f8b4428df27a7416JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26719d6a-553b-64f0-286f-8a8b54336540&amp;u=a1aHR0cHM6Ly93d3cubGFjb3VydC5jYS5nb3YvcGFnZXMvbHAvYWNjZXNzLWEtY2FzZS90cC9maW5kLWNhc2UtaW5mb3JtYXRpb24vY3Avb3MtY2l2aWwtY2FzZS1hY2Nlc3M&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=38afdc707b5db5613fdb785b43987b3e105308edcabe61aeeb91b0d3058f41e7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26719d6a-553b-64f0-286f-8a8b54336540&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f5b71d1fd1ed4257f2d24d210c0e70724108ffa05a986bdb06b6290901667bfeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26719d6a-553b-64f0-286f-8a8b54336540&amp;u=a1aHR0cHM6Ly93d3cubGFjb3VydC5vcmcvZGl2aXNpb24vY2l2aWwvY2l2aWwuYXNweA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4c3002ed52108b05f02a35513e97493525562e7696b12c0fcaa763ec2f03b56bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26719d6a-553b-64f0-286f-8a8b54336540&amp;u=a1aHR0cHM6Ly93d3cubGFjb3VydC5vcmcvb25saW5lL2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c841a5c1540dabf6bdd9dcb3a12d91c738b2bcb755f57fbd9bf9c5349ef14688JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26719d6a-553b-64f0-286f-8a8b54336540&amp;u=a1aHR0cHM6Ly9sYXNkLm9yZy9jb3VydHNlcnZpY2VzL2NpdmlsLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=caa255dba8b100fe862c59626668d562d03a4c0d81f39c9c5952b9fd0e0bed5eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26719d6a-553b-64f0-286f-8a8b54336540&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9DaXZpbF9lbmdpbmVlcmluZw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e99995b11ff3660e069550c9e42d318bef66da87ad6688752c703ffd69e0600bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26719d6a-553b-64f0-286f-8a8b54336540&amp;u=a1aHR0cHM6Ly9zZWxmaGVscC5jb3VydHMuY2EuZ292L2NpdmlsLWxhd3N1aXQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=20373ec2cc0838906a55b64695d5d4340a9ddc5940175f5b9e63183759e96b60JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26719d6a-553b-64f0-286f-8a8b54336540&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=62256727b95245b7d502f1767bc6f567eeb8cf0939877283bf4effdbb6ecb6e7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26719d6a-553b-64f0-286f-8a8b54336540&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2Npdmls&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
@@ -910,7 +922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -944,19 +956,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -964,19 +976,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -984,19 +996,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1004,19 +1016,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H5" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1024,19 +1036,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1044,19 +1056,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G7" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H7" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1064,19 +1076,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G8" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H8" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1084,19 +1096,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G9" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H9" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1104,19 +1116,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H10" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1124,19 +1136,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G11" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H11" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1144,19 +1156,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G12" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H12" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1164,19 +1176,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G13" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H13" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1184,19 +1196,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G14" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H14" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1204,19 +1216,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G15" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H15" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1224,19 +1236,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G16" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H16" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1244,19 +1256,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G17" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H17" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1264,19 +1276,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G18" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H18" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1284,19 +1296,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G19" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H19" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1304,19 +1316,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G20" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H20" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1324,19 +1336,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G21" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H21" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1344,19 +1356,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G22" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H22" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1364,19 +1376,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G23" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H23" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1384,19 +1396,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G24" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H24" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1404,19 +1416,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G25" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H25" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1424,19 +1436,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G26" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H26" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1444,19 +1456,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G27" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H27" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1464,19 +1476,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G28" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H28" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1484,19 +1496,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G29" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H29" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1504,19 +1516,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G30" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H30" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1524,19 +1536,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G31" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H31" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1544,19 +1556,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G32" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H32" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1564,19 +1576,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G33" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H33" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1584,19 +1596,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C34" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G34" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H34" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1604,19 +1616,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C35" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G35" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H35" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1624,19 +1636,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C36" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G36" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H36" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1644,19 +1656,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C37" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G37" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H37" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1664,19 +1676,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C38" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G38" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H38" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1684,19 +1696,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G39" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H39" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1704,19 +1716,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C40" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G40" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H40" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1724,19 +1736,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C41" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G41" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H41" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1744,19 +1756,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C42" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G42" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H42" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1764,19 +1776,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C43" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G43" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H43" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1784,19 +1796,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C44" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G44" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H44" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1804,19 +1816,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C45" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G45" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H45" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1824,19 +1836,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C46" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G46" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H46" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1844,19 +1856,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C47" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G47" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H47" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1864,19 +1876,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C48" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G48" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H48" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1884,19 +1896,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C49" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G49" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H49" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1904,19 +1916,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C50" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G50" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H50" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1924,19 +1936,19 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G51" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H51" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1944,19 +1956,19 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C52" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G52" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H52" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1964,19 +1976,19 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C53" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G53" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H53" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -1984,19 +1996,19 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C54" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G54" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H54" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2004,19 +2016,19 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C55" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G55" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H55" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2024,19 +2036,19 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C56" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G56" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H56" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2044,19 +2056,19 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C57" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G57" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H57" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2064,19 +2076,19 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C58" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G58" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H58" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2084,19 +2096,19 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C59" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G59" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H59" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2104,19 +2116,19 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C60" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G60" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H60" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2124,19 +2136,19 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C61" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G61" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H61" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2144,19 +2156,19 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C62" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G62" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H62" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2164,19 +2176,19 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C63" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G63" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H63" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2184,19 +2196,19 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C64" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G64" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H64" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2204,19 +2216,19 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C65" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G65" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H65" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2224,19 +2236,19 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C66" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G66" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H66" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2244,19 +2256,19 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C67" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G67" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H67" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2264,19 +2276,19 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C68" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G68" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H68" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2284,19 +2296,19 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C69" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G69" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H69" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2304,19 +2316,19 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C70" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G70" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H70" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2324,19 +2336,19 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C71" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G71" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H71" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2344,19 +2356,19 @@
         <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C72" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G72" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H72" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2364,19 +2376,19 @@
         <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C73" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G73" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H73" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2384,19 +2396,19 @@
         <v>80</v>
       </c>
       <c r="B74" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C74" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G74" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H74" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2404,19 +2416,19 @@
         <v>81</v>
       </c>
       <c r="B75" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C75" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G75" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H75" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2424,19 +2436,19 @@
         <v>82</v>
       </c>
       <c r="B76" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C76" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G76" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H76" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2444,19 +2456,19 @@
         <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C77" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G77" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H77" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -2464,19 +2476,19 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C78" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G78" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H78" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -2484,19 +2496,19 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C79" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G79" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H79" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -2504,19 +2516,19 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C80" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G80" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H80" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -2524,19 +2536,19 @@
         <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C81" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G81" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H81" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -2544,19 +2556,19 @@
         <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C82" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G82" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H82" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -2564,19 +2576,19 @@
         <v>89</v>
       </c>
       <c r="B83" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C83" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G83" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H83" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -2584,19 +2596,19 @@
         <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C84" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G84" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H84" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -2604,19 +2616,19 @@
         <v>91</v>
       </c>
       <c r="B85" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C85" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G85" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H85" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -2624,19 +2636,19 @@
         <v>92</v>
       </c>
       <c r="B86" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C86" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G86" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H86" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -2644,19 +2656,59 @@
         <v>93</v>
       </c>
       <c r="B87" t="s">
+        <v>96</v>
+      </c>
+      <c r="C87" t="s">
+        <v>97</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G87" t="s">
+        <v>186</v>
+      </c>
+      <c r="H87" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" t="s">
         <v>94</v>
       </c>
-      <c r="C87" t="s">
+      <c r="B88" t="s">
+        <v>96</v>
+      </c>
+      <c r="C88" t="s">
+        <v>97</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G88" t="s">
+        <v>186</v>
+      </c>
+      <c r="H88" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" t="s">
         <v>95</v>
       </c>
-      <c r="F87" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="G87" t="s">
-        <v>182</v>
-      </c>
-      <c r="H87" t="s">
-        <v>183</v>
+      <c r="B89" t="s">
+        <v>96</v>
+      </c>
+      <c r="C89" t="s">
+        <v>97</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G89" t="s">
+        <v>186</v>
+      </c>
+      <c r="H89" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -2747,6 +2799,8 @@
     <hyperlink ref="F85" r:id="rId84"/>
     <hyperlink ref="F86" r:id="rId85"/>
     <hyperlink ref="F87" r:id="rId86"/>
+    <hyperlink ref="F88" r:id="rId87"/>
+    <hyperlink ref="F89" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/scraped_Cape_Town_Emergency_and_Rescue.xlsx
+++ b/results/scraped_Cape_Town_Emergency_and_Rescue.xlsx
@@ -259,21 +259,21 @@
     <t>YahooSearch- WebSearch</t>
   </si>
   <si>
+    <t>Google Search- A new kind of help</t>
+  </si>
+  <si>
+    <t>Yahoo</t>
+  </si>
+  <si>
     <t>PrivateSearchEngine - BraveSearch</t>
   </si>
   <si>
-    <t>Google Search- A new kind of help</t>
-  </si>
-  <si>
-    <t>Yahoo</t>
+    <t>How toUse Bing Search Engineon Desktop or Mobile -wikiHow</t>
   </si>
   <si>
     <t>DuckDuckGo- Protection. Privacy. Peace of mind.</t>
   </si>
   <si>
-    <t>GoogleSearch</t>
-  </si>
-  <si>
     <t>Superior Court ofLos AngelesCounty |Civil</t>
   </si>
   <si>
@@ -310,268 +310,268 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=59ddeeae437311802e9273b2832fa8b19244d94b23d04386e06ff0b32884edddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0256f859-a457-6be6-0fb8-efb8a5cd6a62&amp;u=a1aHR0cHM6Ly93ZmNhLmNvbS9maXJlLW1hcC93YXNoaW5ndG9u&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed0348b6d50410b3f401aaa40231dd1221890c50eef7d6aa6bb6d5cf3687a31dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0256f859-a457-6be6-0fb8-efb8a5cd6a62&amp;u=a1aHR0cHM6Ly93aWxkZmlyZXRyYWNrZXJzLmNvbS9mL21hcA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=83066299856b3aa3cae389734b281ec0d15108767bd52054b3daf011aad9d9b2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0256f859-a457-6be6-0fb8-efb8a5cd6a62&amp;u=a1aHR0cHM6Ly9maXJlLmFpcm5vdy5nb3YvP2xhbmc9ZW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b42686a007d9e2a2efeaf5f01409a5ab3fba0ffabc9c64d19a110afdf7438440JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0256f859-a457-6be6-0fb8-efb8a5cd6a62&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GaXJl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47695b632c2cacfb9307cb0f6430cf2365176bea138291ad82258f502ac2cc9bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0256f859-a457-6be6-0fb8-efb8a5cd6a62&amp;u=a1aHR0cHM6Ly93d3cuZmlyZS5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7adf2928ff685ba1ba23c0b4ed1bcb003c8c959c30415e62554ee165e933acf5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0256f859-a457-6be6-0fb8-efb8a5cd6a62&amp;u=a1aHR0cHM6Ly9maXJlbmVhcmJ5LmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4a5130851c8a5c506f1ac119f0880c0a06ea66094973b9a6113f2040054c1950JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0256f859-a457-6be6-0fb8-efb8a5cd6a62&amp;u=a1aHR0cHM6Ly9hbGxmaXJlZmlnaHRlci5jb20vd2lsZGZpcmVzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fa8deeb3638ef2e5002e5547315953f593be5abc910fe8165a459a2f453b0494JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0256f859-a457-6be6-0fb8-efb8a5cd6a62&amp;u=a1aHR0cHM6Ly9maXJlbWFwLnVzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=643890d82c8e02baf45f701e41337f50b4dd17dc2b979aef5886b7e2c475a49dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0256f859-a457-6be6-0fb8-efb8a5cd6a62&amp;u=a1aHR0cHM6Ly93d3cuZG9pLmdvdi93aWxkbGFuZGZpcmVzZXJ2aWNlL2N1cnJlbnQtd2lsZGZpcmUtaW5mb3JtYXRpb24&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d80dfe84c5e710d1c3450fb57f9a7d01d987b16b56843d34b78617e055e62e4bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0256f859-a457-6be6-0fb8-efb8a5cd6a62&amp;u=a1aHR0cHM6Ly93d3cuZmlyZWZveC5jb20vZW4tVVMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=82730d69ab1c87f48c413b51ffbe2f30d236ef600c35ff7ac098eea2acdb2ed3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25f3a04e-4b07-6bbc-2fdd-b7af4ab56adf&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQwMDY4MDY3Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=850191e8fcc6499f734ccf14db55d601d82ce7d92fd7bdb3cac1080ee969ad43JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25f3a04e-4b07-6bbc-2fdd-b7af4ab56adf&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5IQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ea5881a287b90af70ed657b3ee88836c11656aaf0e842c641ffb564ccac26cc5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25f3a04e-4b07-6bbc-2fdd-b7af4ab56adf&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f0a10a8cfd4886d8ba3e981eec038ff9537df71b375a7ff4d2091a5569cf9dacJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25f3a04e-4b07-6bbc-2fdd-b7af4ab56adf&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VtZXJnZW5jeQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d0b204261eeed4dd242f5ccc00568aae29c112ca9c6ec53252298417f1d7353bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25f3a04e-4b07-6bbc-2fdd-b7af4ab56adf&amp;u=a1aHR0cHM6Ly9kb3lvdXJlbWVtYmVyLmNvbS8xNTg1NjEvZW1lcmdlbmN5LWNhc3QtdGhlbi1ub3c&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6492bac85f05fc74f6cb5fa3279894d40ae4bdc3b8e851b89bf7b430313213a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25f3a04e-4b07-6bbc-2fdd-b7af4ab56adf&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1sQnJSQTVSQ1lUVQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=17e1c09c35ee8c9b059e3a188a91c28676898d1c63010ffb44ed3e2bbfdfdca4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25f3a04e-4b07-6bbc-2fdd-b7af4ab56adf&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQwMDY4MDY3L2Z1bGxjcmVkaXRzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=faf05076599bf8cd0c60c2318f7251601ad2856e8b85db91056672703a31339cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25f3a04e-4b07-6bbc-2fdd-b7af4ab56adf&amp;u=a1aHR0cHM6Ly93d3cucGhvZW5peC5nb3YvYWRtaW5pc3RyYXRpb24vZGVwYXJ0bWVudHMvZW1lcmdlbmN5Lmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2dfcd6faa7233c6c2081043423c4c1711acd3fc6d3e25c18bcb68a8b4e8cd8ceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25f3a04e-4b07-6bbc-2fdd-b7af4ab56adf&amp;u=a1aHR0cHM6Ly93d3cucmVhZHkuZ292Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6172e622eae11813f73a6db93a8781a5bf1f1bbf52ba637f9b89cc06e0aae2a6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=25f3a04e-4b07-6bbc-2fdd-b7af4ab56adf&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2VtZXJnZW5jeQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e2e596aeb65c4dee577a927403a442820b921bb0346e2d02743cf464944b8447JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=00638313-c397-6c17-021b-94f2c2a16d97&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9TZWE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8875a6915976f3a9b07ff2818497bf10100dc2d897351bd39c37f2da7d357650JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=00638313-c397-6c17-021b-94f2c2a16d97&amp;u=a1aHR0cHM6Ly90aW1lc29maW5kaWEuaW5kaWF0aW1lcy5jb20vdHJhdmVsL2Rlc3RpbmF0aW9ucy9kby15b3Uta25vdy10aGUtZGlmZmVyZW5jZS1iZXR3ZWVuLW9jZWFuLXNlYS1iYXktYW5kLWd1bGYvYXJ0aWNsZXNob3cvMTEwOTY1MTM0LmNtcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e5a494338b32d265f68fe2286d2c6291bd1f461b51790b370eca28b39c312f3fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=00638313-c397-6c17-021b-94f2c2a16d97&amp;u=a1aHR0cHM6Ly9zZWEuZWR1Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=95e42fa0c23ea43525eb9125a61762684e1cb38b78dd7d94d11e4a5217e63090JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=00638313-c397-6c17-021b-94f2c2a16d97&amp;u=a1aHR0cHM6Ly93d3cucG9ydHNlYXR0bGUub3JnL3NlYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=298ecf6c1e06f466a6b4388a3e196a007a2e4261ae72e230ccb293ac1c90218cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=00638313-c397-6c17-021b-94f2c2a16d97&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvU2Vh&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9926410ef395a8d52da57ef6180905cb783fc6be335cd4279485e7525a88a35cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=00638313-c397-6c17-021b-94f2c2a16d97&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9MaXN0X29mX3NlYXNfb25fRWFydGg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb491f0710d22f9a283d98c7e0139924085e580cf94d05c1cc1d7d8c3b664b44JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=00638313-c397-6c17-021b-94f2c2a16d97&amp;u=a1aHR0cHM6Ly9lZHVjYXRpb24ubmF0aW9uYWxnZW9ncmFwaGljLm9yZy9yZXNvdXJjZS9zZWEv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a2b5a32ab6bc826a6865bfc05bb310abf10589a1e4092fab0da633f9fc18ab13JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=00638313-c397-6c17-021b-94f2c2a16d97&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9PY2Vhbi12cy1TZWEtV2hhdHMtdGhlLURpZmZlcmVuY2U&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a79954102e018c4898fb36f47b9f56410ed94dd474edb6b88cdbc8465a65cd29JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=00638313-c397-6c17-021b-94f2c2a16d97&amp;u=a1aHR0cHM6Ly9zZWF0dGxld2VhLm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a4172b68e08683c84b44535d35c1d1f09822c6cdf5988c2c9cfbe3107c199686JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=00638313-c397-6c17-021b-94f2c2a16d97&amp;u=a1aHR0cHM6Ly93d3cuc2VhLmNvbS9pbnZlc3Rvci9ob21l&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5d87d6f9743c71eedf557ca93691cdab8d4a6aab8dae8d5db58d9db0ce824182JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fd16acd-ac1d-6a24-02c3-7d2cad066be6&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vYWthaWhvb2Qvb2ZmZXJz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=78394c1eaa6c7785a9c083c06551aabeedb8be8c27e53fddcb77b892e6031a3eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fd16acd-ac1d-6a24-02c3-7d2cad066be6&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vbWF4ZXh0cmFjdG9ycy9hY3Rpdml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=64c3cfa76074818a5fed9898617820e8014dd1f48d4f0c11e2c7cffd50e81135JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fd16acd-ac1d-6a24-02c3-7d2cad066be6&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vZ2xvb21pZXNyaC9hY3Rpdml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=930affa78b04974653043daaff10eb04eec8ecbb4f6e6b7a99ff09ef0cf9956bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fd16acd-ac1d-6a24-02c3-7d2cad066be6&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vaHVzaHB1cHBpZXp6ei9vZmZlcnM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=392554e4d7b34a3198f514406bdc5de6eab23588210b7e5fa8fd8865b1910ae4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fd16acd-ac1d-6a24-02c3-7d2cad066be6&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vc29sdmUtZXQtY29hZ3VsYS1yaC9hY3Rpdml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4b6ae1db7d8245612036424d17e2c03fc8b0ec048be18f093259babdd76db7e0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fd16acd-ac1d-6a24-02c3-7d2cad066be6&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vem9ua3NhcnQvb3ZlcnZpZXc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1289702b2bdc025bf72c4daca5cb731dfde56fec08a52be158e9997511b20c02JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fd16acd-ac1d-6a24-02c3-7d2cad066be6&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vcG9ydGFibGUtc2xvcC1kcml2ZS9hY3Rpdml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3b2a155ea9fa4b3739df41ea0af7782e94deabb5bed695adba833b15bbabacbbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fd16acd-ac1d-6a24-02c3-7d2cad066be6&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vcHJvamVjdGNwdS9vZmZlcnM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c346374feb187cef54b3cc958552147ed4f66dadba10f39ae3ee7bcede29f3b8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fd16acd-ac1d-6a24-02c3-7d2cad066be6&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vZ2FtZWJveS0xNjM4NTIyMDQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ebdde641f719f92fb14cd07d7d16ced79796c90e4e47381a5317a66ca6ea3247JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1fd16acd-ac1d-6a24-02c3-7d2cad066be6&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vdW5pY3JlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=48671e327f653ab3adfbcf75e22b7baed80462d79c305fe5a87961055a23c7dbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32dfbf0f-8668-6e70-0506-a8ee879a6fd7&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRGlzYXN0ZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5e8e633575955f38ff0bf9ffa2356deed1cab186ffef22b2554be8fe705d9bfbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32dfbf0f-8668-6e70-0506-a8ee879a6fd7&amp;u=a1aHR0cHM6Ly93d3cuZGlzYXN0ZXJhc3Npc3RhbmNlLmdvdi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d4576ec7d8d60fd770f99eee254f4adff73e88cd0b9ab0f220d63798727c358bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32dfbf0f-8668-6e70-0506-a8ee879a6fd7&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9kaXNhc3Rlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d20c5981d2f3cca43dc8ea50525784495172c5c24406c17b96cb25d5da0a01eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32dfbf0f-8668-6e70-0506-a8ee879a6fd7&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Rpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6300002d7884621bb3cff125aeb17de9d0456bc080541b3df57083f410868d85JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32dfbf0f-8668-6e70-0506-a8ee879a6fd7&amp;u=a1aHR0cHM6Ly93d3cudW5kcnIub3JnL3Rlcm1pbm9sb2d5L2Rpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e2f855ac2855f55813b73003894500ba0385126de7a1020ae46929ab901c1659JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32dfbf0f-8668-6e70-0506-a8ee879a6fd7&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3YvZGlzYXN0ZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b4c32acf29d59ab01da02ff622393df37203a5a8a4ebee9f0f0fedcfaa04ba98JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32dfbf0f-8668-6e70-0506-a8ee879a6fd7&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9uYXR1cmFsLWRpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8424231d2d5a7b9009506d6d2a7fe06651af3aa8cccce70aa863f893282a6f95JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32dfbf0f-8668-6e70-0506-a8ee879a6fd7&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=81e5ca7684a9936225ad41162862431e5ab749c17262f3468cafcb6762404de6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32dfbf0f-8668-6e70-0506-a8ee879a6fd7&amp;u=a1aHR0cHM6Ly93d3cuaWZyYy5vcmcvb3VyLXdvcmsvZGlzYXN0ZXJzLWNsaW1hdGUtYW5kLWNyaXNlcy93aGF0LWRpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0485ad08dc6380cd173c6ec33289e85e20b0b1be16c56d9fd1f25a7939c2bd82JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32dfbf0f-8668-6e70-0506-a8ee879a6fd7&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTmF0dXJhbF9kaXNhc3Rlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3797c72845620155ab432b44fe103d1553f4cc013c325b5a093f71216d6fafd0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=142617c9-4118-6e4b-2365-0028401d6fee&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RpbnNwaXJlcy5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0a27f764816abd231621d0f150945f4e195f95d6eb3bfb643eb236b8a3747cebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=142617c9-4118-6e4b-2365-0028401d6fee&amp;u=a1aHR0cHM6Ly9jYWZpcnN0Lm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47c6eba50ae3a670bbcf1320ca2f25a435d44be83fc222d8faf0930ac87b24bbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=142617c9-4118-6e4b-2365-0028401d6fee&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZpcnN0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f75d1bdd2aef66520ab42186bff846a7c67592ee0a1371e7fcd6f49b445daa09JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=142617c9-4118-6e4b-2365-0028401d6fee&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RjaXR5Y3Uub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2924d5859197df686e785dd2b31c4a27f6839fe6be2f79e5c21dd430e4537ac8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=142617c9-4118-6e4b-2365-0028401d6fee&amp;u=a1aHR0cHM6Ly9lbi5tLndpa3Rpb25hcnkub3JnL3dpa2kvZmlyc3Q&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d36ae3972afc12e860e55f441d43fd054630b186d2d5b2b67bff8c7e08ad9bbcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=142617c9-4118-6e4b-2365-0028401d6fee&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZpcnN0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e10bdfeb0c6f2840c19e549ccc2f512cf4392c76d43878cc39b86a781722bbd0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=142617c9-4118-6e4b-2365-0028401d6fee&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3QuYmFuay9BYm91dC9Mb2NhdGlvbnMvTEEtQ2hpbmF0b3du&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=de3654495c39b0793de18c1d4180a630b004d859208b94ea5e03893184e0aa11JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=142617c9-4118-6e4b-2365-0028401d6fee&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3QuYmFuay8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b43bbccb3edc6151f2e9d5b474cfa2225500644b17e3df9a6560550e9bc49d86JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=142617c9-4118-6e4b-2365-0028401d6fee&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RsZWdhbC5jb20vbG9jYXRpb25zLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0aa92f6ef2e467a40dfeabbebee11c9f5c93f7ee22177130388eff34274fb2cbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=142617c9-4118-6e4b-2365-0028401d6fee&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3Qub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4045b260140d1e005bd4d3fa6dfa44abffb7d8e9bdd4527165a0490d5af8f0d3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34113335-8033-6213-19a8-24d481f4636f&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9BbWJ1bGFuY2U&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=45ad9c5c4a5a0365c7fb9994687b95fbb4b3f4f4b26d602e6cdedc84d643b605JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34113335-8033-6213-19a8-24d481f4636f&amp;u=a1aHR0cHM6Ly93d3cuY2NwYXJhbWVkaWNzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e9bc0412a3e57dffec51a3badc929f6b883cfa3fa9ecc1edc1f47572edd2a1faJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34113335-8033-6213-19a8-24d481f4636f&amp;u=a1aHR0cHM6Ly93d3cueWVsbG93cGFnZXMuY29tL25hbXBhLWlkL2FtYnVsYW5jZS1zZXJ2aWNlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=98ad5fe0cfe545df66e9a255f70858d855d5e07839395361e5359a8e74647c84JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34113335-8033-6213-19a8-24d481f4636f&amp;u=a1aHR0cHM6Ly9hY3V0ZXJlc2N1ZS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=25c42b2bea45ba9da607e174809372b16d5c490f921312df1355d8c2ad2d47ebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34113335-8033-6213-19a8-24d481f4636f&amp;u=a1aHR0cHM6Ly93d3cuY2NwYXJhbWVkaWNzLmNvbS9wYXRpZW50LWZpbi1zZXJ2aWNlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=63a73c47fb6423eeda4d4b24299d684b8d3e7e1cd3a8e26c9ad9a89891aa7ad4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34113335-8033-6213-19a8-24d481f4636f&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2ZpbmRfZGVzYz1BbWJ1bGFuY2UrU2VydmljZSZmaW5kX2xvYz1OYW1wYSUyQytJRCZtc29ja2lkPTM0MTEzMzM1ODAzMzYyMTMxOWE4MjRkNDgxZjQ2MzZm&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1cc8005c20406afd8a745c4b6704e846604849fe5880b96d5ed2f20247889589JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34113335-8033-6213-19a8-24d481f4636f&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9FbWVyZ2VuY3lfbWVkaWNhbF9zZXJ2aWNlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e578190c1086dd661d3a458b1ebf906de51646d2030680568797a5991ded8395JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34113335-8033-6213-19a8-24d481f4636f&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FtYnVsYW5jZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=74cfdc20479f9e7e89da3de679222c641f6abd96ddd0288778bdcbe422606651JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34113335-8033-6213-19a8-24d481f4636f&amp;u=a1aHR0cHM6Ly9hbGxmaXJlZmlnaHRlci5jb20vdG9vbHMvZW1zLWxvY2F0b3IvdXMvaWRhaG8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef6420bdb85b7ea5261e424fa3b5a67705743c4707fe4cbeb4ce3796113750ecJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=34113335-8033-6213-19a8-24d481f4636f&amp;u=a1aHR0cHM6Ly93d3cuc3VwZXJwYWdlcy5jb20vbmFtcGEtaWQvbm9uLWVtZXJnZW5jeS1hbWJ1bGFuY2Utc2VydmljZXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=61a74b7f0fbc529eeae10728124b9c6caeb34fb1d01313f2907ce049159cc5cdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04cc24f1-be7c-65b2-2167-3310bf2c64e2&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS94aHRtbC9zZWFyY2g&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=94726c0aa4b6f576b9efb7ad12d4ce44d73b7075d21a11f65560acd09a539b84JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38de1e4d-e543-6977-1d2b-09ace4ce685d&amp;u=a1aHR0cHM6Ly93ZmNhLmNvbS9maXJlLW1hcC93YXNoaW5ndG9u&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bcfd6ea71177eae08272442de96588b89b874dda43893e52f54b1e4302bae27fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38de1e4d-e543-6977-1d2b-09ace4ce685d&amp;u=a1aHR0cHM6Ly93aWxkZmlyZXRyYWNrZXJzLmNvbS9mL21hcA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=86dc0cda8f99d38ef1d2e31837b33b72009ee34611ac0d5e9dac874b4efc3d69JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38de1e4d-e543-6977-1d2b-09ace4ce685d&amp;u=a1aHR0cHM6Ly9maXJlLmFpcm5vdy5nb3YvP2xhbmc9ZW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2ba80f2fa0b46ceb53755e15fdb8127586c80174ebf83fcb5be2fcb9409700cfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38de1e4d-e543-6977-1d2b-09ace4ce685d&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GaXJl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=497087c4a52a1eba5fbadfad192a4523420bc5e42f58560fd55066e04a11fc02JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38de1e4d-e543-6977-1d2b-09ace4ce685d&amp;u=a1aHR0cHM6Ly93d3cuZmlyZS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f39405ec02a84f9a091e2cb189acf1d59df72abff6dab13d5b4ac5fd8e10ba6aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38de1e4d-e543-6977-1d2b-09ace4ce685d&amp;u=a1aHR0cHM6Ly9maXJlbmVhcmJ5LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7dca5c2a4026ad57387f17dd8112ff5f9fd0de10e7490b01d974f39ab2b6f0efJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38de1e4d-e543-6977-1d2b-09ace4ce685d&amp;u=a1aHR0cHM6Ly9hbGxmaXJlZmlnaHRlci5jb20vd2lsZGZpcmVzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=925651dc067fd9b73fe2daa0003b6f65bc728b7d0d48e138af11af05c1573a3aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38de1e4d-e543-6977-1d2b-09ace4ce685d&amp;u=a1aHR0cHM6Ly9maXJlbWFwLnVzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=642ccf0fa519880e91a84a16e5e8ce6b9ea22141b049702ce2c78b45d019d788JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38de1e4d-e543-6977-1d2b-09ace4ce685d&amp;u=a1aHR0cHM6Ly93d3cuZG9pLmdvdi93aWxkbGFuZGZpcmVzZXJ2aWNlL2N1cnJlbnQtd2lsZGZpcmUtaW5mb3JtYXRpb24&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=132147c58ea5588d7dc1056150d00c7c0cbe90f6df2f76b0708e48b5e52e7fccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38de1e4d-e543-6977-1d2b-09ace4ce685d&amp;u=a1aHR0cHM6Ly93d3cuZmlyZWZveC5jb20vZW4tVVMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eae157e290a39e1852a8ba0966bffa1b765ec794a998f8afe75ae8ee1d786049JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15f92c80-e477-6686-0c15-3b61e5f36702&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQwMDY4MDY3Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=af59e9dfb1b50fc57f66d62d266546bf63e9aba88bd2790cac0d340b528ec4e7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15f92c80-e477-6686-0c15-3b61e5f36702&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5IQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1c09475d6874557affb0f70e6027fa689c0f179d891a2d18904bbaf5c01016f1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15f92c80-e477-6686-0c15-3b61e5f36702&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8b4c3a5063ad04846e267fefa675efe43b36783235d0e354b8a94646b54c4ec4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15f92c80-e477-6686-0c15-3b61e5f36702&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VtZXJnZW5jeQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e10bcb05412a350ab3e73258ce2fa888dc3afef6a4311eb53dc009f128ade8f7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15f92c80-e477-6686-0c15-3b61e5f36702&amp;u=a1aHR0cHM6Ly9kb3lvdXJlbWVtYmVyLmNvbS8xNTg1NjEvZW1lcmdlbmN5LWNhc3QtdGhlbi1ub3c&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c64c11de1bd3080036d4d3cdb27b45e03b4b67a7b24e9f58b8cd4b1f2f27c6cfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15f92c80-e477-6686-0c15-3b61e5f36702&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1sQnJSQTVSQ1lUVQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eb36bbee1a470c0f2ccd100eb0493d7f90b7c96817ba73c4a1b81315c2ad4877JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15f92c80-e477-6686-0c15-3b61e5f36702&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQwMDY4MDY3L2Z1bGxjcmVkaXRzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=97d19997808ba46c7fbc202313496a85b5f163e3c58847aa6dc8bccf63f0b731JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15f92c80-e477-6686-0c15-3b61e5f36702&amp;u=a1aHR0cHM6Ly93d3cucGhvZW5peC5nb3YvYWRtaW5pc3RyYXRpb24vZGVwYXJ0bWVudHMvZW1lcmdlbmN5Lmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a7c2c4bb9ab250ed8aa13b3dc344db92d4125a8745a2a264118ecb982f095c65JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15f92c80-e477-6686-0c15-3b61e5f36702&amp;u=a1aHR0cHM6Ly93d3cucmVhZHkuZ292Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c33698fd6fe33ff004900c3c477792676560003d8bcc02971938a3c8e0746996JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15f92c80-e477-6686-0c15-3b61e5f36702&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2VtZXJnZW5jeQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d421eae6db32c337f7839a2ad49d419eac8d5d49b04d1f6094798cce7a423626JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06eb02db-3912-6309-24f4-153a38fc62a7&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9TZWE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e304332897a02b9a2989fc0091484fa2b61892760677617bc71b5db695b2a127JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06eb02db-3912-6309-24f4-153a38fc62a7&amp;u=a1aHR0cHM6Ly90aW1lc29maW5kaWEuaW5kaWF0aW1lcy5jb20vdHJhdmVsL2Rlc3RpbmF0aW9ucy9kby15b3Uta25vdy10aGUtZGlmZmVyZW5jZS1iZXR3ZWVuLW9jZWFuLXNlYS1iYXktYW5kLWd1bGYvYXJ0aWNsZXNob3cvMTEwOTY1MTM0LmNtcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d0235cd0046ebf16b6eb96ff7faca6edab8180266313d02bd89a77282d41447fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06eb02db-3912-6309-24f4-153a38fc62a7&amp;u=a1aHR0cHM6Ly9zZWEuZWR1Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a24dd10106f4b4e871afbbf38da02b5fb143816197bb9e76585ac02d1bc564d5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06eb02db-3912-6309-24f4-153a38fc62a7&amp;u=a1aHR0cHM6Ly93d3cucG9ydHNlYXR0bGUub3JnL3NlYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1efc33a9a4d8f653f0342d6e57a86a15a8098c00f1470a9e5960203d405a7c77JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06eb02db-3912-6309-24f4-153a38fc62a7&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvU2Vh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e668c85fb8c4c8e4798487a74095aafcbce23649b914d0add3fbbd5de3898b0dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06eb02db-3912-6309-24f4-153a38fc62a7&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9MaXN0X29mX3NlYXNfb25fRWFydGg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=84c69d62cf21787066ca18fd2e8b2ed5796a079a5a9bb6f8e45cb1b3a0a63362JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06eb02db-3912-6309-24f4-153a38fc62a7&amp;u=a1aHR0cHM6Ly9lZHVjYXRpb24ubmF0aW9uYWxnZW9ncmFwaGljLm9yZy9yZXNvdXJjZS9zZWEv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a26a1956fb76ee09452e105e8f23faf8f043c96fa7380ca3e9fd2b1d03fc29d6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06eb02db-3912-6309-24f4-153a38fc62a7&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9PY2Vhbi12cy1TZWEtV2hhdHMtdGhlLURpZmZlcmVuY2U&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c8195766edba7e83fe82601cc5455b17441803309fac3d899981bd43eba209aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06eb02db-3912-6309-24f4-153a38fc62a7&amp;u=a1aHR0cHM6Ly9zZWF0dGxld2VhLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bedd6b43b26920cc6f08799f0ea2a8a6003dc82deb2717380dff8c6df34ebba5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06eb02db-3912-6309-24f4-153a38fc62a7&amp;u=a1aHR0cHM6Ly93d3cuc2VhLmNvbS9pbnZlc3Rvci9ob21l&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cc18669a08e6df15ac436f064816b03e6d485199ed79762798e5a9824057801aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ff20991-18d3-68ae-141b-1e7019a069e3&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vYWthaWhvb2Qvb2ZmZXJz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d1946cee7aae39a26e655007397ded9841a206f3b5030d086f3f17fe47c51e33JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ff20991-18d3-68ae-141b-1e7019a069e3&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vbWF4ZXh0cmFjdG9ycy9hY3Rpdml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9c09fe1f32366196a692bd17b1adf660e458062f0c1eeebfb6e80434fdb1b321JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ff20991-18d3-68ae-141b-1e7019a069e3&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vZ2xvb21pZXNyaC9hY3Rpdml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=83ff9c8a042e4c1efd895f6edaa0faf2c0ae26ea02bcebd39ab57b6ba46939fbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ff20991-18d3-68ae-141b-1e7019a069e3&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vaHVzaHB1cHBpZXp6ei9vZmZlcnM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7b05f290edef19589860f4df7d180ca5d9346280a1498d3c83c206e674c80a38JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ff20991-18d3-68ae-141b-1e7019a069e3&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vc29sdmUtZXQtY29hZ3VsYS1yaC9hY3Rpdml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0f07d475e9ba5b3dbb582f7e3a25d51a35ea9ee6043575ffd427a9b592d990bfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ff20991-18d3-68ae-141b-1e7019a069e3&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vem9ua3NhcnQvb3ZlcnZpZXc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ff473c63ee04569722ff545d2b91d21f9cae938ed88d4cf42b248ecf58d2c5eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ff20991-18d3-68ae-141b-1e7019a069e3&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vcG9ydGFibGUtc2xvcC1kcml2ZS9hY3Rpdml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d933f7400228677dcab9952d7d091461923ddeb6ed59d6616698cb64159976b5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ff20991-18d3-68ae-141b-1e7019a069e3&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vcHJvamVjdGNwdS9vZmZlcnM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0df53886bef47613aa104c58c285478098abaf6a7b131a89274da5c9b1dbcb62JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ff20991-18d3-68ae-141b-1e7019a069e3&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vZ2FtZWJveS0xNjM4NTIyMDQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=21fcd07f1cb3affb90705d6545ab50d350186a842e12d2432c822e67808a5944JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ff20991-18d3-68ae-141b-1e7019a069e3&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vdW5pY3JlZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=41289f79aa6532f9b07f5cfd04f8d2dfcf6f1dccf7c783da0145d664f41091d7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0650bcb8-33b0-6ed3-3ec7-ab5932996f33&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRGlzYXN0ZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e14fdcb2de23cf24fb66e2d1ad29da947587860ae12b9a3a76aa138f441c0ac0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0650bcb8-33b0-6ed3-3ec7-ab5932996f33&amp;u=a1aHR0cHM6Ly93d3cuZGlzYXN0ZXJhc3Npc3RhbmNlLmdvdi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a3a774598e561326a51b4c43e65f731038f9c5672e2eb50554b7f33a34029039JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0650bcb8-33b0-6ed3-3ec7-ab5932996f33&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9kaXNhc3Rlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6adae1c513e9907ee27a32b1130dfebce87f06c1d8f2fbd076d2f60378e4800cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0650bcb8-33b0-6ed3-3ec7-ab5932996f33&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Rpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5bbe9f33d9c180e69f68003b98eebd3dac917dd507c1a5f8941bfeba27e6a0ffJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0650bcb8-33b0-6ed3-3ec7-ab5932996f33&amp;u=a1aHR0cHM6Ly93d3cudW5kcnIub3JnL3Rlcm1pbm9sb2d5L2Rpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1b66cb7af9fa028c85b04013d52389706e05b0be4095f39bff469a3278fecc22JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0650bcb8-33b0-6ed3-3ec7-ab5932996f33&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3YvZGlzYXN0ZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f56ec0877cf4fe9ff022a1f2ba1b6edc3b95aecb8d2d461151657c0ad9b1aae5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0650bcb8-33b0-6ed3-3ec7-ab5932996f33&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9uYXR1cmFsLWRpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7ccd3faea5938e7c7f73a1269f34c2f0f54ed38fe1224a0cfd7ee2b6a0feb100JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0650bcb8-33b0-6ed3-3ec7-ab5932996f33&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d3ee08c0d992a50f459148c034c99b87ab66e2a2886566d9a26d779c5ad783caJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0650bcb8-33b0-6ed3-3ec7-ab5932996f33&amp;u=a1aHR0cHM6Ly93d3cuaWZyYy5vcmcvb3VyLXdvcmsvZGlzYXN0ZXJzLWNsaW1hdGUtYW5kLWNyaXNlcy93aGF0LWRpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5b8917b8fcf176846ecd120ed8a65d55d9ee5bbd3c4f5772469a3fa2260be0e8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0650bcb8-33b0-6ed3-3ec7-ab5932996f33&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTmF0dXJhbF9kaXNhc3Rlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7c0b97203585fb76237d5519a8de51bbb40962710039e7c9d7b2816a27b61d38JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=080f52c1-f12d-6ef2-3d3e-4520f02f6ff8&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RpbnNwaXJlcy5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5afe38fb9185f08a7deb615b413c267483a94ce802675888e0f9184003faafddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=080f52c1-f12d-6ef2-3d3e-4520f02f6ff8&amp;u=a1aHR0cHM6Ly9jYWZpcnN0Lm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=168f377260d588cd5ec7065140d74afcd7109236ae35f4099c674bad827ded3eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=080f52c1-f12d-6ef2-3d3e-4520f02f6ff8&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZpcnN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87af2026fe942508ca09d5d5151707a649ec5139939ff819b663c7bbaf3f4210JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=080f52c1-f12d-6ef2-3d3e-4520f02f6ff8&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RjaXR5Y3Uub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6198819c2b63b18f814d0677e3f273785adc6e4e98ffb4f10f438ab600b6f66fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=080f52c1-f12d-6ef2-3d3e-4520f02f6ff8&amp;u=a1aHR0cHM6Ly9lbi5tLndpa3Rpb25hcnkub3JnL3dpa2kvZmlyc3Q&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e04a470fbd88faa6f32b4fea6a884a1da3b9b0b23497952c876f02fdc1d3e83fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=080f52c1-f12d-6ef2-3d3e-4520f02f6ff8&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZpcnN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=630e0a6a18883f64cda5875e7ebbe75258650cb57a482f2b028998a3c2224302JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=080f52c1-f12d-6ef2-3d3e-4520f02f6ff8&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3QuYmFuay9BYm91dC9Mb2NhdGlvbnMvTEEtQ2hpbmF0b3du&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2c4f6f6cda10041e5dd0df13a7ace31bdeb59172d7a898649a968801422f11ceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=080f52c1-f12d-6ef2-3d3e-4520f02f6ff8&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3QuYmFuay8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=08c473ef753341a19cfe3b9dcf7e09f1d7fd68e812e0aa5a5aba77851d7a55ecJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=080f52c1-f12d-6ef2-3d3e-4520f02f6ff8&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RsZWdhbC5jb20vbG9jYXRpb25zLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=329eab868762f434d4cecbf1225500ecaa2e71e9d758fe7c5a8571eb5693a7b0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=080f52c1-f12d-6ef2-3d3e-4520f02f6ff8&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3Qub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f943d603774771e61b887317c229a4b04d8b6eae5465559ccad58e59de09fa46JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33714742-74ec-647f-341c-50a3758b653a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9BbWJ1bGFuY2U&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4ea1636efced116a8761624c623a2bd93606f45355eb4f7b624ad441762c9111JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33714742-74ec-647f-341c-50a3758b653a&amp;u=a1aHR0cHM6Ly93d3cuY2NwYXJhbWVkaWNzLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f4ac6a2c19af6bad3d8347d947bee170667dddcbef3fda59fa83f4a7fcb11331JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33714742-74ec-647f-341c-50a3758b653a&amp;u=a1aHR0cHM6Ly93d3cueWVsbG93cGFnZXMuY29tL25hbXBhLWlkL2FtYnVsYW5jZS1zZXJ2aWNlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=36f8b3df9b6d9c483fa28bad258ad0215cb5a33a310a5b47bb5911a32f5f5724JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33714742-74ec-647f-341c-50a3758b653a&amp;u=a1aHR0cHM6Ly9hY3V0ZXJlc2N1ZS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f88d1b036f21f6d8262aae07214caac85a6b08e4c3e1c991cdf36dd2de141d2aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33714742-74ec-647f-341c-50a3758b653a&amp;u=a1aHR0cHM6Ly93d3cuY2NwYXJhbWVkaWNzLmNvbS9wYXRpZW50LWZpbi1zZXJ2aWNlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a7e2bb164e9fc49df07a8bdb8116a2b47dae3c88d7ed4c7814b5bc2ecda5ef1eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33714742-74ec-647f-341c-50a3758b653a&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2ZpbmRfZGVzYz1BbWJ1bGFuY2UrU2VydmljZSZmaW5kX2xvYz1OYW1wYSUyQytJRCZtc29ja2lkPTMzNzE0NzQyNzRlYzY0N2YzNDFjNTBhMzc1OGI2NTNh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=06ca16f5b2d6c7368d0a8651024fc17f529038bc6ab4529785e1762dbd127d4aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33714742-74ec-647f-341c-50a3758b653a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9FbWVyZ2VuY3lfbWVkaWNhbF9zZXJ2aWNlcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f5b8d2a69e8f9524d618f6e8e343cf1c5bba0b66588a6f5f9abafbff613cae7bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33714742-74ec-647f-341c-50a3758b653a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FtYnVsYW5jZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b54b90ab9b5277fdc6697f50006109015a3a339341d2d445ab4bf21e9bdb6fd9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33714742-74ec-647f-341c-50a3758b653a&amp;u=a1aHR0cHM6Ly9hbGxmaXJlZmlnaHRlci5jb20vdG9vbHMvZW1zLWxvY2F0b3IvdXMvaWRhaG8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=799b41f9dd36466110d6850fd675f7753e044655ccb30545bc007eab2536946bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33714742-74ec-647f-341c-50a3758b653a&amp;u=a1aHR0cHM6Ly93d3cuc3VwZXJwYWdlcy5jb20vbmFtcGEtaWQvbm9uLWVtZXJnZW5jeS1hbWJ1bGFuY2Utc2VydmljZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=10a524eb3ff4fe78238ff667dad8f083aaf56f381813d6e20e2e89ce8f30d051JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f315631-6f44-64ab-0da5-41d06ed3651b&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS94aHRtbC9zZWFyY2g&amp;ntb=1</t>
   </si>
   <si>
     <t>https://www.bing.com/</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ae8820bd4ed8386deb9a72a15638ad10cfdfc6079916c8a0bc7013be95d3dd63JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04cc24f1-be7c-65b2-2167-3310bf2c64e2&amp;u=a1aHR0cHM6Ly9zZWFyY2gueWFob28uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ff57bff7128607420ffc4c7bee3484efd8ba92409949caeee017158d2b73365eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04cc24f1-be7c-65b2-2167-3310bf2c64e2&amp;u=a1aHR0cHM6Ly9zZWFyY2guYnJhdmUuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=33f5d5ca28b047feadefae9d930c0d60907e9c76440aa0bbcb8d7b8cc6190155JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04cc24f1-be7c-65b2-2167-3310bf2c64e2&amp;u=a1aHR0cHM6Ly9zZWFyY2guZ29vZ2xlLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2057724fba4b65c6bb9fbc0331060ea760875e1328dd3c80a49699650fda5410JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04cc24f1-be7c-65b2-2167-3310bf2c64e2&amp;u=a1aHR0cHM6Ly93d3cueWFob28uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=81ea413a755678c38803f8d1889321d71b972fe43504f2566d22e482270c7fd7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04cc24f1-be7c-65b2-2167-3310bf2c64e2&amp;u=a1aHR0cHM6Ly9kdWNrZHVja2dvLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4ac961ba8a8578824ac218d41b60c98e6e14d15d3fe972566727a4e0279ec76dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=04cc24f1-be7c-65b2-2167-3310bf2c64e2&amp;u=a1aHR0cHM6Ly9hY2NvdW50cy5nb29nbGUuY29tL0ludGVyYWN0aXZlTG9naW4_c2VydmljZT1zYWZlc2VhcmNobG9jaw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a2fe813fce613e21bea34ae8e8963128e7271715bc139f51521e6c2912cb7f28JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26719d6a-553b-64f0-286f-8a8b54336540&amp;u=a1aHR0cHM6Ly93d3cubGFjb3VydC5jYS5nb3YvcGFnZXMvbHAvY2l2aWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6cf9b35d2df28581147319f3f38e4fdb8a1ba0ba565751e3f8b4428df27a7416JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26719d6a-553b-64f0-286f-8a8b54336540&amp;u=a1aHR0cHM6Ly93d3cubGFjb3VydC5jYS5nb3YvcGFnZXMvbHAvYWNjZXNzLWEtY2FzZS90cC9maW5kLWNhc2UtaW5mb3JtYXRpb24vY3Avb3MtY2l2aWwtY2FzZS1hY2Nlc3M&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=38afdc707b5db5613fdb785b43987b3e105308edcabe61aeeb91b0d3058f41e7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26719d6a-553b-64f0-286f-8a8b54336540&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Npdmls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f5b71d1fd1ed4257f2d24d210c0e70724108ffa05a986bdb06b6290901667bfeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26719d6a-553b-64f0-286f-8a8b54336540&amp;u=a1aHR0cHM6Ly93d3cubGFjb3VydC5vcmcvZGl2aXNpb24vY2l2aWwvY2l2aWwuYXNweA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4c3002ed52108b05f02a35513e97493525562e7696b12c0fcaa763ec2f03b56bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26719d6a-553b-64f0-286f-8a8b54336540&amp;u=a1aHR0cHM6Ly93d3cubGFjb3VydC5vcmcvb25saW5lL2Npdmls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c841a5c1540dabf6bdd9dcb3a12d91c738b2bcb755f57fbd9bf9c5349ef14688JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26719d6a-553b-64f0-286f-8a8b54336540&amp;u=a1aHR0cHM6Ly9sYXNkLm9yZy9jb3VydHNlcnZpY2VzL2NpdmlsLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=caa255dba8b100fe862c59626668d562d03a4c0d81f39c9c5952b9fd0e0bed5eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26719d6a-553b-64f0-286f-8a8b54336540&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9DaXZpbF9lbmdpbmVlcmluZw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e99995b11ff3660e069550c9e42d318bef66da87ad6688752c703ffd69e0600bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26719d6a-553b-64f0-286f-8a8b54336540&amp;u=a1aHR0cHM6Ly9zZWxmaGVscC5jb3VydHMuY2EuZ292L2NpdmlsLWxhd3N1aXQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=20373ec2cc0838906a55b64695d5d4340a9ddc5940175f5b9e63183759e96b60JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26719d6a-553b-64f0-286f-8a8b54336540&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Npdmls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=62256727b95245b7d502f1767bc6f567eeb8cf0939877283bf4effdbb6ecb6e7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26719d6a-553b-64f0-286f-8a8b54336540&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2Npdmls&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bae016d450e8c1c1f879cba5de4170cfd1ad788d0b6ef9e7eeedab69b9a65eb9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f315631-6f44-64ab-0da5-41d06ed3651b&amp;u=a1aHR0cHM6Ly9zZWFyY2gueWFob28uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fad307aa5117de73eeefe06b4f09838c943d00a453f4913950cf0bdecef549ccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f315631-6f44-64ab-0da5-41d06ed3651b&amp;u=a1aHR0cHM6Ly9zZWFyY2guZ29vZ2xlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=224e24013b90df393b6953443adc0b03303ed6119adaed965109ceb26ff2d68fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f315631-6f44-64ab-0da5-41d06ed3651b&amp;u=a1aHR0cHM6Ly93d3cueWFob28uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c1f5bc601b768ecdf9552461259dee558b5402a86632f0111fd4ef49952c495JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f315631-6f44-64ab-0da5-41d06ed3651b&amp;u=a1aHR0cHM6Ly9zZWFyY2guYnJhdmUuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=da5d66ebb3c766b429881b1dee191ace9df59f000e723f7f80c850458dc91e49JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f315631-6f44-64ab-0da5-41d06ed3651b&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vVXNlLUJpbmctU2VhcmNoLUVuZ2luZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=03ce442c9aa2ce8014c51bdf229760e1266ef9fb0efd67a0284ce5de22cf0965JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f315631-6f44-64ab-0da5-41d06ed3651b&amp;u=a1aHR0cHM6Ly9kdWNrZHVja2dvLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=56dda566245e4a3f6254e7f3fe7ae01e1d44480f1d4de17600e574488cbfb384JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f324671-14dc-6928-0ce5-519015f568fe&amp;u=a1aHR0cHM6Ly93d3cubGFjb3VydC5jYS5nb3YvcGFnZXMvbHAvY2l2aWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3793e99b3c45ce53c420b6189beed7e1870b9e2a082440b841f8e67a20777ef1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f324671-14dc-6928-0ce5-519015f568fe&amp;u=a1aHR0cHM6Ly93d3cubGFjb3VydC5jYS5nb3YvcGFnZXMvbHAvYWNjZXNzLWEtY2FzZS90cC9maW5kLWNhc2UtaW5mb3JtYXRpb24vY3Avb3MtY2l2aWwtY2FzZS1hY2Nlc3M&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b86fcb08dae13e2cdaef61edc672064473628666a00b500d676a576842cb4ed4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f324671-14dc-6928-0ce5-519015f568fe&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c325146519d31b99a6037fe111ddb23548623454cf5b56753eb4e369ec8e71f3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f324671-14dc-6928-0ce5-519015f568fe&amp;u=a1aHR0cHM6Ly93d3cubGFjb3VydC5vcmcvZGl2aXNpb24vY2l2aWwvY2l2aWwuYXNweA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5e971a179fe88a768709553a38356458a4745fb9ba12fcc42cbb5ac2f1f4fe09JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f324671-14dc-6928-0ce5-519015f568fe&amp;u=a1aHR0cHM6Ly93d3cubGFjb3VydC5vcmcvb25saW5lL2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bdd2b777c6a28e34cc3567c937d02e612653523f15889bcad473a0a368b01910JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f324671-14dc-6928-0ce5-519015f568fe&amp;u=a1aHR0cHM6Ly9sYXNkLm9yZy9jb3VydHNlcnZpY2VzL2NpdmlsLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed9ea33bfff1414fd4e7a77f87fadbc4bbae420f5aff386c6c650cd8b35acab9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f324671-14dc-6928-0ce5-519015f568fe&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9DaXZpbF9lbmdpbmVlcmluZw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b6e62bec31ad57779f9e5f6271a7c237cc49c5fd76c3366bf685726d4b50a826JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f324671-14dc-6928-0ce5-519015f568fe&amp;u=a1aHR0cHM6Ly9zZWxmaGVscC5jb3VydHMuY2EuZ292L2NpdmlsLWxhd3N1aXQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=915538a4373139be833bf96834d6774035c40d18e65de40ca2c6658c4d1c0012JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f324671-14dc-6928-0ce5-519015f568fe&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f06a399d4eecb79f7b8aa619e46d8a1494f354cc432ddd90740d1b488c9a4e90JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f324671-14dc-6928-0ce5-519015f568fe&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2Npdmls&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>

--- a/results/scraped_Cape_Town_Emergency_and_Rescue.xlsx
+++ b/results/scraped_Cape_Town_Emergency_and_Rescue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="186">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -40,34 +40,34 @@
     <t>Source</t>
   </si>
   <si>
-    <t>Current Fires in Washington | WFCAFireMap</t>
+    <t>Fire-Wikipedia</t>
   </si>
   <si>
     <t>Wildfire/Smoke Map - Live Tracking</t>
   </si>
   <si>
+    <t>Firefox: The fast, private browser that keeps you safe</t>
+  </si>
+  <si>
+    <t>FIRE| Foundation for Individual Rights and Expression</t>
+  </si>
+  <si>
     <t>AirNowFireand Smoke Map</t>
   </si>
   <si>
-    <t>Fire-Wikipedia</t>
-  </si>
-  <si>
-    <t>FIRE| Foundation for Individual Rights and Expression</t>
-  </si>
-  <si>
-    <t>Live Wildfire Map: Active Fires, Smoke &amp; Alerts |FireNearby</t>
+    <t>NIFCMaps-National Interagency Fire Center</t>
   </si>
   <si>
     <t>Live Wildfire Map &amp; Tracker – Wildfires Near Me | AllFirefighter</t>
   </si>
   <si>
-    <t>firemap.us | see what's onfire</t>
-  </si>
-  <si>
-    <t>Current Wildfire Information - U.S. Department of the Interior</t>
-  </si>
-  <si>
-    <t>Firefox: The fast, private browser that keeps you safe</t>
+    <t>FireMap: Track Wildfires in Real-Time with NASA &amp; Local Data</t>
+  </si>
+  <si>
+    <t>Watch Duty - Wildfire Maps &amp; Alerts</t>
+  </si>
+  <si>
+    <t>NationalFireNews -National Interagency Fire Center</t>
   </si>
   <si>
     <t>Emergency! (TV Series 1972–1979) - IMDb</t>
@@ -79,85 +79,85 @@
     <t>Emergency-Wikipedia</t>
   </si>
   <si>
+    <t>Emergency! | The Complete Series -YouTube</t>
+  </si>
+  <si>
     <t>EMERGENCYDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
     <t>The 'Emergency' Cast: Looking at the Actors, Then and Now 2024</t>
   </si>
   <si>
-    <t>Emergency! | The Complete Series -YouTube</t>
-  </si>
-  <si>
     <t>Emergency! (TV Series 1972–1979) - Full cast &amp; crew - IMDb</t>
   </si>
   <si>
-    <t>Office ofEmergencyManagement | City of Phoenix</t>
-  </si>
-  <si>
-    <t>Plan Ahead for Disasters |Ready.gov</t>
-  </si>
-  <si>
     <t>EMERGENCY| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
+    <t>Home |FEMA.gov</t>
+  </si>
+  <si>
+    <t>The Office ofEmergencyManagement | The City of Del City</t>
+  </si>
+  <si>
     <t>Sea-Wikipedia</t>
   </si>
   <si>
-    <t>Do you know the difference between ocean,sea, bay and gulf?</t>
-  </si>
-  <si>
     <t>SeaEducation Association</t>
   </si>
   <si>
-    <t>Seattle-Tacoma International Airport | Port of Seattle</t>
+    <t>Ocean vs.Sea: What’s the Difference? - Encyclopedia Britannica</t>
+  </si>
+  <si>
+    <t>SeaNew York</t>
+  </si>
+  <si>
+    <t>SEADefinition &amp; Meaning - Merriam-Webster</t>
+  </si>
+  <si>
+    <t>Sea| Home</t>
+  </si>
+  <si>
+    <t>Sea- National Geographic Society</t>
   </si>
   <si>
     <t>Sea- SimpleEnglish Wikipedia, the free encyclopedia</t>
   </si>
   <si>
-    <t>List of seas on Earth - Wikipedia</t>
-  </si>
-  <si>
-    <t>Sea- National Geographic Society</t>
-  </si>
-  <si>
-    <t>Ocean vs.Sea: What’s the Difference? - Encyclopedia Britannica</t>
-  </si>
-  <si>
-    <t>SEA– Seattle Education Association</t>
-  </si>
-  <si>
-    <t>Sea| Investor Relations</t>
-  </si>
-  <si>
-    <t>AKAI &lt; 0.0001 ETH - Collection | OpenSea</t>
-  </si>
-  <si>
-    <t>Max Extractors 0.0031 ETH - Collection | OpenSea</t>
-  </si>
-  <si>
-    <t>Gloomies &lt; 0.0001 ETH - Collection | OpenSea</t>
-  </si>
-  <si>
-    <t>Hush PuppiezzZ 0.0001 ETH - Collection | OpenSea</t>
-  </si>
-  <si>
-    <t>Solve et Coagula &lt; 0.0001 ETH - Collection | OpenSea</t>
-  </si>
-  <si>
-    <t>Zonks 0.0002 ETH - Collection | OpenSea</t>
-  </si>
-  <si>
-    <t>Portable Slop Drive 0.94 USDG - Collection | OpenSea</t>
-  </si>
-  <si>
-    <t>Project CPU &lt; 0.0001 ETH - Collection | OpenSea</t>
-  </si>
-  <si>
-    <t>Gameboy &lt; 0.0001 ETH - Collection | OpenSea</t>
-  </si>
-  <si>
-    <t>UNICRED 0.0041 ETH - Collection | OpenSea</t>
+    <t>SEA, Ltd. - Forensic Engineering Services | Structural &amp; Failure Analysis</t>
+  </si>
+  <si>
+    <t>Ocean- Wikipedia</t>
+  </si>
+  <si>
+    <t>Mountain-Wikipedia</t>
+  </si>
+  <si>
+    <t>Mountain| Definition, Characteristics, Types, &amp; Facts | Britannica</t>
+  </si>
+  <si>
+    <t>Mountains -WorldAtlas</t>
+  </si>
+  <si>
+    <t>List of mountain ranges of Colorado-Wikipedia</t>
+  </si>
+  <si>
+    <t>What is amountain? Here’s how they form | National Geographic</t>
+  </si>
+  <si>
+    <t>Mountain- Simple EnglishWikipedia, the free encyclopedia</t>
+  </si>
+  <si>
+    <t>Mountain: what they are, how they are formed and more</t>
+  </si>
+  <si>
+    <t>What is a Mountain? -WorldAtlas</t>
+  </si>
+  <si>
+    <t>Lookout Mountain- Golden,CO</t>
+  </si>
+  <si>
+    <t>Mountain-ScienceDaily</t>
   </si>
   <si>
     <t>Disaster-Wikipedia</t>
@@ -172,82 +172,79 @@
     <t>DISASTERDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>Disaster Information-FEMA.gov</t>
+  </si>
+  <si>
+    <t>Naturaldisaster| Causes, Types, &amp; Facts | Britannica</t>
+  </si>
+  <si>
+    <t>DisasterRadar: Live Natural Hazard Map &amp; Alerts</t>
+  </si>
+  <si>
     <t>Definition:Disaster| UNDRR</t>
   </si>
   <si>
-    <t>Disaster Information-FEMA.gov</t>
-  </si>
-  <si>
-    <t>Naturaldisaster| Causes, Types, &amp; Facts | Britannica</t>
-  </si>
-  <si>
-    <t>Home |FEMA.gov</t>
-  </si>
-  <si>
-    <t>What is adisaster? - IFRC</t>
-  </si>
-  <si>
     <t>Natural disaster-Wikipedia</t>
   </si>
   <si>
+    <t>FIRSTDefinition &amp; Meaning - Merriam-Webster</t>
+  </si>
+  <si>
+    <t>FIRST| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
+    <t>Personal Banking, Loans, &amp; Insurance |Texas FirstBank</t>
+  </si>
+  <si>
     <t>FIRST| For Inspiration and Recognition of Science and Technology</t>
   </si>
   <si>
-    <t>FIRSTRobotics -California| Inspiring young people to be ...</t>
-  </si>
-  <si>
-    <t>FIRSTDefinition &amp; Meaning - Merriam-Webster</t>
-  </si>
-  <si>
-    <t>FirstCity Credit Union |Los AngelesCounty Employees Credit ...</t>
-  </si>
-  <si>
     <t>first- Wiktionary, the free dictionary</t>
   </si>
   <si>
-    <t>FIRST| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>Los Angeles CaliforniaBank | Chinatown LA Bank |FirstBank</t>
-  </si>
-  <si>
-    <t>FirstBank | MO Bank | IL Bank |CABank | Accounts | Loans</t>
-  </si>
-  <si>
-    <t>Locations-FirstLegal</t>
-  </si>
-  <si>
-    <t>FIRST- Improving Security Together</t>
+    <t>Digital Banking | Personal Online Banking |FirstCitizens Bank</t>
+  </si>
+  <si>
+    <t>First- Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
+  </si>
+  <si>
+    <t>First- definition offirstby The Free Dictionary</t>
+  </si>
+  <si>
+    <t>FIRSTDefinition &amp; Meaning |Dictionary.com</t>
+  </si>
+  <si>
+    <t>Find Teams &amp; Events |FIRST</t>
   </si>
   <si>
     <t>Ambulance- Wikipedia</t>
   </si>
   <si>
-    <t>Canyon County Paramedics | Home</t>
-  </si>
-  <si>
-    <t>AmbulanceServices inNampa,ID- The Real Yellow Pages®</t>
-  </si>
-  <si>
-    <t>Ambulanceand Patient TransportIdaho| Acute Rescue</t>
-  </si>
-  <si>
-    <t>Canyon County Paramedics |Patient Financial Services| Pay Online</t>
-  </si>
-  <si>
-    <t>TOP 10 BESTAmbulanceService inNampa,ID- Yelp</t>
-  </si>
-  <si>
-    <t>Emergency medical services- Wikipedia</t>
-  </si>
-  <si>
-    <t>AMBULANCEDefinition &amp; Meaning - Merriam-Webster</t>
-  </si>
-  <si>
-    <t>EMS Locator inIdaho—AmbulanceStation Map | AllFirefighter</t>
-  </si>
-  <si>
-    <t>Non EmergencyAmbulanceServices inNampa,ID- Superpages</t>
+    <t>Medstar –Michigan’s most integrated 911 EMS and mobile healthcare …</t>
+  </si>
+  <si>
+    <t>Contact – Medstar</t>
+  </si>
+  <si>
+    <t>Medstar|Clinton Township MI- Facebook</t>
+  </si>
+  <si>
+    <t>MedstarAmbulance-Clinton Township,MI(Michigan) - (586) 783 …</t>
+  </si>
+  <si>
+    <t>Ambulance Services in Clinton Township,MI- The Real Yellow Pages</t>
+  </si>
+  <si>
+    <t>Ambulance Committee | Clinton Township,MI</t>
+  </si>
+  <si>
+    <t>MEDSTAR - NPI 1124056296 -AmbulanceinClinton Township,MI</t>
+  </si>
+  <si>
+    <t>AmbulanceService in Macomb County | UniversalAmbulanceService</t>
+  </si>
+  <si>
+    <t>AmbulanceinClinton Township,MI- NPI Profile</t>
   </si>
   <si>
     <t>Google</t>
@@ -265,313 +262,310 @@
     <t>Yahoo</t>
   </si>
   <si>
-    <t>PrivateSearchEngine - BraveSearch</t>
-  </si>
-  <si>
-    <t>How toUse Bing Search Engineon Desktop or Mobile -wikiHow</t>
-  </si>
-  <si>
     <t>DuckDuckGo- Protection. Privacy. Peace of mind.</t>
   </si>
   <si>
-    <t>Superior Court ofLos AngelesCounty |Civil</t>
-  </si>
-  <si>
-    <t>Superior Court ofLos AngelesCounty |CivilCase Access</t>
+    <t>DuckDuckGo No-AI: PrivateSearchWithout AI</t>
+  </si>
+  <si>
+    <t>GoogleSearch</t>
   </si>
   <si>
     <t>CIVILDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>CivilDivision - LA Court</t>
-  </si>
-  <si>
-    <t>Superior Court ofLos AngelesCounty | Home</t>
-  </si>
-  <si>
-    <t>CivilServices |Los AngelesCounty Sheriff’s Department</t>
+    <t>CIVIL| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
+    <t>Civil: Definition, Meaning, and Examples - usdictionary.com</t>
   </si>
   <si>
     <t>Civil engineering-Wikipedia</t>
   </si>
   <si>
-    <t>Civilcases inCalifornia|CaliforniaCourts | Self Help Guide</t>
-  </si>
-  <si>
-    <t>CIVIL| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
     <t>Civil- definition ofcivilby The Free Dictionary</t>
   </si>
   <si>
+    <t>Civil- Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
+  </si>
+  <si>
+    <t>CIVILDefinition &amp; Meaning |Dictionary.com</t>
+  </si>
+  <si>
+    <t>CivilDefinition &amp; Meaning | YourDictionary</t>
+  </si>
+  <si>
+    <t>CIVIL| definition in the Cambridge English Dictionary</t>
+  </si>
+  <si>
+    <t>TOP 10 BESTCivilLawyer nearLaguna Park,TX- Yelp</t>
+  </si>
+  <si>
     <t>Emergency &amp; Rescue</t>
   </si>
   <si>
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=94726c0aa4b6f576b9efb7ad12d4ce44d73b7075d21a11f65560acd09a539b84JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38de1e4d-e543-6977-1d2b-09ace4ce685d&amp;u=a1aHR0cHM6Ly93ZmNhLmNvbS9maXJlLW1hcC93YXNoaW5ndG9u&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bcfd6ea71177eae08272442de96588b89b874dda43893e52f54b1e4302bae27fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38de1e4d-e543-6977-1d2b-09ace4ce685d&amp;u=a1aHR0cHM6Ly93aWxkZmlyZXRyYWNrZXJzLmNvbS9mL21hcA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=86dc0cda8f99d38ef1d2e31837b33b72009ee34611ac0d5e9dac874b4efc3d69JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38de1e4d-e543-6977-1d2b-09ace4ce685d&amp;u=a1aHR0cHM6Ly9maXJlLmFpcm5vdy5nb3YvP2xhbmc9ZW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2ba80f2fa0b46ceb53755e15fdb8127586c80174ebf83fcb5be2fcb9409700cfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38de1e4d-e543-6977-1d2b-09ace4ce685d&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GaXJl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=497087c4a52a1eba5fbadfad192a4523420bc5e42f58560fd55066e04a11fc02JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38de1e4d-e543-6977-1d2b-09ace4ce685d&amp;u=a1aHR0cHM6Ly93d3cuZmlyZS5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f39405ec02a84f9a091e2cb189acf1d59df72abff6dab13d5b4ac5fd8e10ba6aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38de1e4d-e543-6977-1d2b-09ace4ce685d&amp;u=a1aHR0cHM6Ly9maXJlbmVhcmJ5LmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7dca5c2a4026ad57387f17dd8112ff5f9fd0de10e7490b01d974f39ab2b6f0efJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38de1e4d-e543-6977-1d2b-09ace4ce685d&amp;u=a1aHR0cHM6Ly9hbGxmaXJlZmlnaHRlci5jb20vd2lsZGZpcmVzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=925651dc067fd9b73fe2daa0003b6f65bc728b7d0d48e138af11af05c1573a3aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38de1e4d-e543-6977-1d2b-09ace4ce685d&amp;u=a1aHR0cHM6Ly9maXJlbWFwLnVzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=642ccf0fa519880e91a84a16e5e8ce6b9ea22141b049702ce2c78b45d019d788JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38de1e4d-e543-6977-1d2b-09ace4ce685d&amp;u=a1aHR0cHM6Ly93d3cuZG9pLmdvdi93aWxkbGFuZGZpcmVzZXJ2aWNlL2N1cnJlbnQtd2lsZGZpcmUtaW5mb3JtYXRpb24&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=132147c58ea5588d7dc1056150d00c7c0cbe90f6df2f76b0708e48b5e52e7fccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38de1e4d-e543-6977-1d2b-09ace4ce685d&amp;u=a1aHR0cHM6Ly93d3cuZmlyZWZveC5jb20vZW4tVVMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eae157e290a39e1852a8ba0966bffa1b765ec794a998f8afe75ae8ee1d786049JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15f92c80-e477-6686-0c15-3b61e5f36702&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQwMDY4MDY3Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=af59e9dfb1b50fc57f66d62d266546bf63e9aba88bd2790cac0d340b528ec4e7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15f92c80-e477-6686-0c15-3b61e5f36702&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5IQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1c09475d6874557affb0f70e6027fa689c0f179d891a2d18904bbaf5c01016f1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15f92c80-e477-6686-0c15-3b61e5f36702&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8b4c3a5063ad04846e267fefa675efe43b36783235d0e354b8a94646b54c4ec4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15f92c80-e477-6686-0c15-3b61e5f36702&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VtZXJnZW5jeQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e10bcb05412a350ab3e73258ce2fa888dc3afef6a4311eb53dc009f128ade8f7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15f92c80-e477-6686-0c15-3b61e5f36702&amp;u=a1aHR0cHM6Ly9kb3lvdXJlbWVtYmVyLmNvbS8xNTg1NjEvZW1lcmdlbmN5LWNhc3QtdGhlbi1ub3c&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c64c11de1bd3080036d4d3cdb27b45e03b4b67a7b24e9f58b8cd4b1f2f27c6cfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15f92c80-e477-6686-0c15-3b61e5f36702&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1sQnJSQTVSQ1lUVQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eb36bbee1a470c0f2ccd100eb0493d7f90b7c96817ba73c4a1b81315c2ad4877JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15f92c80-e477-6686-0c15-3b61e5f36702&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQwMDY4MDY3L2Z1bGxjcmVkaXRzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=97d19997808ba46c7fbc202313496a85b5f163e3c58847aa6dc8bccf63f0b731JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15f92c80-e477-6686-0c15-3b61e5f36702&amp;u=a1aHR0cHM6Ly93d3cucGhvZW5peC5nb3YvYWRtaW5pc3RyYXRpb24vZGVwYXJ0bWVudHMvZW1lcmdlbmN5Lmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a7c2c4bb9ab250ed8aa13b3dc344db92d4125a8745a2a264118ecb982f095c65JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15f92c80-e477-6686-0c15-3b61e5f36702&amp;u=a1aHR0cHM6Ly93d3cucmVhZHkuZ292Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c33698fd6fe33ff004900c3c477792676560003d8bcc02971938a3c8e0746996JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15f92c80-e477-6686-0c15-3b61e5f36702&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2VtZXJnZW5jeQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d421eae6db32c337f7839a2ad49d419eac8d5d49b04d1f6094798cce7a423626JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06eb02db-3912-6309-24f4-153a38fc62a7&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9TZWE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e304332897a02b9a2989fc0091484fa2b61892760677617bc71b5db695b2a127JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06eb02db-3912-6309-24f4-153a38fc62a7&amp;u=a1aHR0cHM6Ly90aW1lc29maW5kaWEuaW5kaWF0aW1lcy5jb20vdHJhdmVsL2Rlc3RpbmF0aW9ucy9kby15b3Uta25vdy10aGUtZGlmZmVyZW5jZS1iZXR3ZWVuLW9jZWFuLXNlYS1iYXktYW5kLWd1bGYvYXJ0aWNsZXNob3cvMTEwOTY1MTM0LmNtcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d0235cd0046ebf16b6eb96ff7faca6edab8180266313d02bd89a77282d41447fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06eb02db-3912-6309-24f4-153a38fc62a7&amp;u=a1aHR0cHM6Ly9zZWEuZWR1Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a24dd10106f4b4e871afbbf38da02b5fb143816197bb9e76585ac02d1bc564d5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06eb02db-3912-6309-24f4-153a38fc62a7&amp;u=a1aHR0cHM6Ly93d3cucG9ydHNlYXR0bGUub3JnL3NlYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1efc33a9a4d8f653f0342d6e57a86a15a8098c00f1470a9e5960203d405a7c77JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06eb02db-3912-6309-24f4-153a38fc62a7&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvU2Vh&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e668c85fb8c4c8e4798487a74095aafcbce23649b914d0add3fbbd5de3898b0dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06eb02db-3912-6309-24f4-153a38fc62a7&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9MaXN0X29mX3NlYXNfb25fRWFydGg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=84c69d62cf21787066ca18fd2e8b2ed5796a079a5a9bb6f8e45cb1b3a0a63362JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06eb02db-3912-6309-24f4-153a38fc62a7&amp;u=a1aHR0cHM6Ly9lZHVjYXRpb24ubmF0aW9uYWxnZW9ncmFwaGljLm9yZy9yZXNvdXJjZS9zZWEv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a26a1956fb76ee09452e105e8f23faf8f043c96fa7380ca3e9fd2b1d03fc29d6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06eb02db-3912-6309-24f4-153a38fc62a7&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9PY2Vhbi12cy1TZWEtV2hhdHMtdGhlLURpZmZlcmVuY2U&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c8195766edba7e83fe82601cc5455b17441803309fac3d899981bd43eba209aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06eb02db-3912-6309-24f4-153a38fc62a7&amp;u=a1aHR0cHM6Ly9zZWF0dGxld2VhLm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bedd6b43b26920cc6f08799f0ea2a8a6003dc82deb2717380dff8c6df34ebba5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=06eb02db-3912-6309-24f4-153a38fc62a7&amp;u=a1aHR0cHM6Ly93d3cuc2VhLmNvbS9pbnZlc3Rvci9ob21l&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cc18669a08e6df15ac436f064816b03e6d485199ed79762798e5a9824057801aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ff20991-18d3-68ae-141b-1e7019a069e3&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vYWthaWhvb2Qvb2ZmZXJz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d1946cee7aae39a26e655007397ded9841a206f3b5030d086f3f17fe47c51e33JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ff20991-18d3-68ae-141b-1e7019a069e3&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vbWF4ZXh0cmFjdG9ycy9hY3Rpdml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9c09fe1f32366196a692bd17b1adf660e458062f0c1eeebfb6e80434fdb1b321JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ff20991-18d3-68ae-141b-1e7019a069e3&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vZ2xvb21pZXNyaC9hY3Rpdml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=83ff9c8a042e4c1efd895f6edaa0faf2c0ae26ea02bcebd39ab57b6ba46939fbJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ff20991-18d3-68ae-141b-1e7019a069e3&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vaHVzaHB1cHBpZXp6ei9vZmZlcnM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7b05f290edef19589860f4df7d180ca5d9346280a1498d3c83c206e674c80a38JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ff20991-18d3-68ae-141b-1e7019a069e3&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vc29sdmUtZXQtY29hZ3VsYS1yaC9hY3Rpdml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0f07d475e9ba5b3dbb582f7e3a25d51a35ea9ee6043575ffd427a9b592d990bfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ff20991-18d3-68ae-141b-1e7019a069e3&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vem9ua3NhcnQvb3ZlcnZpZXc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ff473c63ee04569722ff545d2b91d21f9cae938ed88d4cf42b248ecf58d2c5eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ff20991-18d3-68ae-141b-1e7019a069e3&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vcG9ydGFibGUtc2xvcC1kcml2ZS9hY3Rpdml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d933f7400228677dcab9952d7d091461923ddeb6ed59d6616698cb64159976b5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ff20991-18d3-68ae-141b-1e7019a069e3&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vcHJvamVjdGNwdS9vZmZlcnM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0df53886bef47613aa104c58c285478098abaf6a7b131a89274da5c9b1dbcb62JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ff20991-18d3-68ae-141b-1e7019a069e3&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vZ2FtZWJveS0xNjM4NTIyMDQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=21fcd07f1cb3affb90705d6545ab50d350186a842e12d2432c822e67808a5944JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3ff20991-18d3-68ae-141b-1e7019a069e3&amp;u=a1aHR0cHM6Ly9vcGVuc2VhLmlvL2NvbGxlY3Rpb24vdW5pY3JlZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=41289f79aa6532f9b07f5cfd04f8d2dfcf6f1dccf7c783da0145d664f41091d7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0650bcb8-33b0-6ed3-3ec7-ab5932996f33&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRGlzYXN0ZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e14fdcb2de23cf24fb66e2d1ad29da947587860ae12b9a3a76aa138f441c0ac0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0650bcb8-33b0-6ed3-3ec7-ab5932996f33&amp;u=a1aHR0cHM6Ly93d3cuZGlzYXN0ZXJhc3Npc3RhbmNlLmdvdi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a3a774598e561326a51b4c43e65f731038f9c5672e2eb50554b7f33a34029039JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0650bcb8-33b0-6ed3-3ec7-ab5932996f33&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9kaXNhc3Rlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6adae1c513e9907ee27a32b1130dfebce87f06c1d8f2fbd076d2f60378e4800cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0650bcb8-33b0-6ed3-3ec7-ab5932996f33&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Rpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5bbe9f33d9c180e69f68003b98eebd3dac917dd507c1a5f8941bfeba27e6a0ffJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0650bcb8-33b0-6ed3-3ec7-ab5932996f33&amp;u=a1aHR0cHM6Ly93d3cudW5kcnIub3JnL3Rlcm1pbm9sb2d5L2Rpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1b66cb7af9fa028c85b04013d52389706e05b0be4095f39bff469a3278fecc22JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0650bcb8-33b0-6ed3-3ec7-ab5932996f33&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3YvZGlzYXN0ZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f56ec0877cf4fe9ff022a1f2ba1b6edc3b95aecb8d2d461151657c0ad9b1aae5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0650bcb8-33b0-6ed3-3ec7-ab5932996f33&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9uYXR1cmFsLWRpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7ccd3faea5938e7c7f73a1269f34c2f0f54ed38fe1224a0cfd7ee2b6a0feb100JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0650bcb8-33b0-6ed3-3ec7-ab5932996f33&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d3ee08c0d992a50f459148c034c99b87ab66e2a2886566d9a26d779c5ad783caJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0650bcb8-33b0-6ed3-3ec7-ab5932996f33&amp;u=a1aHR0cHM6Ly93d3cuaWZyYy5vcmcvb3VyLXdvcmsvZGlzYXN0ZXJzLWNsaW1hdGUtYW5kLWNyaXNlcy93aGF0LWRpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5b8917b8fcf176846ecd120ed8a65d55d9ee5bbd3c4f5772469a3fa2260be0e8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0650bcb8-33b0-6ed3-3ec7-ab5932996f33&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTmF0dXJhbF9kaXNhc3Rlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7c0b97203585fb76237d5519a8de51bbb40962710039e7c9d7b2816a27b61d38JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=080f52c1-f12d-6ef2-3d3e-4520f02f6ff8&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RpbnNwaXJlcy5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5afe38fb9185f08a7deb615b413c267483a94ce802675888e0f9184003faafddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=080f52c1-f12d-6ef2-3d3e-4520f02f6ff8&amp;u=a1aHR0cHM6Ly9jYWZpcnN0Lm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=168f377260d588cd5ec7065140d74afcd7109236ae35f4099c674bad827ded3eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=080f52c1-f12d-6ef2-3d3e-4520f02f6ff8&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZpcnN0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87af2026fe942508ca09d5d5151707a649ec5139939ff819b663c7bbaf3f4210JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=080f52c1-f12d-6ef2-3d3e-4520f02f6ff8&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RjaXR5Y3Uub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6198819c2b63b18f814d0677e3f273785adc6e4e98ffb4f10f438ab600b6f66fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=080f52c1-f12d-6ef2-3d3e-4520f02f6ff8&amp;u=a1aHR0cHM6Ly9lbi5tLndpa3Rpb25hcnkub3JnL3dpa2kvZmlyc3Q&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e04a470fbd88faa6f32b4fea6a884a1da3b9b0b23497952c876f02fdc1d3e83fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=080f52c1-f12d-6ef2-3d3e-4520f02f6ff8&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZpcnN0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=630e0a6a18883f64cda5875e7ebbe75258650cb57a482f2b028998a3c2224302JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=080f52c1-f12d-6ef2-3d3e-4520f02f6ff8&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3QuYmFuay9BYm91dC9Mb2NhdGlvbnMvTEEtQ2hpbmF0b3du&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2c4f6f6cda10041e5dd0df13a7ace31bdeb59172d7a898649a968801422f11ceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=080f52c1-f12d-6ef2-3d3e-4520f02f6ff8&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3QuYmFuay8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=08c473ef753341a19cfe3b9dcf7e09f1d7fd68e812e0aa5a5aba77851d7a55ecJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=080f52c1-f12d-6ef2-3d3e-4520f02f6ff8&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RsZWdhbC5jb20vbG9jYXRpb25zLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=329eab868762f434d4cecbf1225500ecaa2e71e9d758fe7c5a8571eb5693a7b0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=080f52c1-f12d-6ef2-3d3e-4520f02f6ff8&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3Qub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f943d603774771e61b887317c229a4b04d8b6eae5465559ccad58e59de09fa46JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33714742-74ec-647f-341c-50a3758b653a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9BbWJ1bGFuY2U&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4ea1636efced116a8761624c623a2bd93606f45355eb4f7b624ad441762c9111JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33714742-74ec-647f-341c-50a3758b653a&amp;u=a1aHR0cHM6Ly93d3cuY2NwYXJhbWVkaWNzLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f4ac6a2c19af6bad3d8347d947bee170667dddcbef3fda59fa83f4a7fcb11331JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33714742-74ec-647f-341c-50a3758b653a&amp;u=a1aHR0cHM6Ly93d3cueWVsbG93cGFnZXMuY29tL25hbXBhLWlkL2FtYnVsYW5jZS1zZXJ2aWNlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=36f8b3df9b6d9c483fa28bad258ad0215cb5a33a310a5b47bb5911a32f5f5724JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33714742-74ec-647f-341c-50a3758b653a&amp;u=a1aHR0cHM6Ly9hY3V0ZXJlc2N1ZS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f88d1b036f21f6d8262aae07214caac85a6b08e4c3e1c991cdf36dd2de141d2aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33714742-74ec-647f-341c-50a3758b653a&amp;u=a1aHR0cHM6Ly93d3cuY2NwYXJhbWVkaWNzLmNvbS9wYXRpZW50LWZpbi1zZXJ2aWNlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a7e2bb164e9fc49df07a8bdb8116a2b47dae3c88d7ed4c7814b5bc2ecda5ef1eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33714742-74ec-647f-341c-50a3758b653a&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2ZpbmRfZGVzYz1BbWJ1bGFuY2UrU2VydmljZSZmaW5kX2xvYz1OYW1wYSUyQytJRCZtc29ja2lkPTMzNzE0NzQyNzRlYzY0N2YzNDFjNTBhMzc1OGI2NTNh&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=06ca16f5b2d6c7368d0a8651024fc17f529038bc6ab4529785e1762dbd127d4aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33714742-74ec-647f-341c-50a3758b653a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9FbWVyZ2VuY3lfbWVkaWNhbF9zZXJ2aWNlcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f5b8d2a69e8f9524d618f6e8e343cf1c5bba0b66588a6f5f9abafbff613cae7bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33714742-74ec-647f-341c-50a3758b653a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FtYnVsYW5jZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b54b90ab9b5277fdc6697f50006109015a3a339341d2d445ab4bf21e9bdb6fd9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33714742-74ec-647f-341c-50a3758b653a&amp;u=a1aHR0cHM6Ly9hbGxmaXJlZmlnaHRlci5jb20vdG9vbHMvZW1zLWxvY2F0b3IvdXMvaWRhaG8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=799b41f9dd36466110d6850fd675f7753e044655ccb30545bc007eab2536946bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33714742-74ec-647f-341c-50a3758b653a&amp;u=a1aHR0cHM6Ly93d3cuc3VwZXJwYWdlcy5jb20vbmFtcGEtaWQvbm9uLWVtZXJnZW5jeS1hbWJ1bGFuY2Utc2VydmljZXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=10a524eb3ff4fe78238ff667dad8f083aaf56f381813d6e20e2e89ce8f30d051JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f315631-6f44-64ab-0da5-41d06ed3651b&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS94aHRtbC9zZWFyY2g&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c0b40d13a084ce1f5d8428ad0b962bb931023ad09c0ce3c9903363d5beeb8de7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03ceae06-ad53-6df3-1491-b9e7ace66cf9&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GaXJl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fb057aa0e1589e874c57f5b3f9a045c2f65224c1ca16627073a58943ea0ae14dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03ceae06-ad53-6df3-1491-b9e7ace66cf9&amp;u=a1aHR0cHM6Ly93aWxkZmlyZXRyYWNrZXJzLmNvbS9mL21hcA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=512a0850556a7710107227dfa4be379e1f789a0e93fd0c261cbdcb07f96f8093JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03ceae06-ad53-6df3-1491-b9e7ace66cf9&amp;u=a1aHR0cHM6Ly93d3cuZmlyZWZveC5jb20vZW4tVVMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8b7263a81e6b54360ffd96b0098bf55e04fcd9addcf5e34fe52feedcf845f34JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03ceae06-ad53-6df3-1491-b9e7ace66cf9&amp;u=a1aHR0cHM6Ly93d3cuZmlyZS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=60d2cc66d6ffd81c25facc74c79abd87ccec2e4f1b2371def539a126a66c38f6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03ceae06-ad53-6df3-1491-b9e7ace66cf9&amp;u=a1aHR0cHM6Ly9maXJlLmFpcm5vdy5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d09b6498bf5a54ef15ca676e643bcc9de5c11c2ec490d907aebd8b2b6706991dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03ceae06-ad53-6df3-1491-b9e7ace66cf9&amp;u=a1aHR0cHM6Ly93d3cubmlmYy5nb3YvZmlyZS1pbmZvcm1hdGlvbi9tYXBz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=71b9b8e49818407eda8273aea777a11474faf1ceb6df0bacff2083989f9e9894JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03ceae06-ad53-6df3-1491-b9e7ace66cf9&amp;u=a1aHR0cHM6Ly9hbGxmaXJlZmlnaHRlci5jb20vd2lsZGZpcmVzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bc0ab216b167f9dad4915b0702df35dea4bca7e1fe03218712bae988b96c83c8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03ceae06-ad53-6df3-1491-b9e7ace66cf9&amp;u=a1aHR0cHM6Ly93d3cuZmlyZW1hcC5saXZlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=355ebbfadedd36d697c9d5bd90240b51cde43b79980c8c49a29b25256a33f34dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03ceae06-ad53-6df3-1491-b9e7ace66cf9&amp;u=a1aHR0cHM6Ly9hcHAud2F0Y2hkdXR5Lm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5bc31c546cfceb3495136ff1c9f3d7b29022e8f0f73cfee4451f705abd0959c4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03ceae06-ad53-6df3-1491-b9e7ace66cf9&amp;u=a1aHR0cHM6Ly93d3cubmlmYy5nb3YvZmlyZS1pbmZvcm1hdGlvbi9uZm4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e643f79735cc5ed11274e6985c2b7d117506fed5ddb80c5c2eb2e1b660a64b56JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23db66d0-c571-6c83-1bcd-7131c4326d67&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MDA2ODA2Ny8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef2031d4d2c152634f0c514d358e5d5706320b5c6488fa8a02ed66b66dbef62eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23db66d0-c571-6c83-1bcd-7131c4326d67&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9FbWVyZ2VuY3kh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=004975d7c5d48ad1403d41ae10754049897dacfe3dffecf458d446fa3302d9dcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23db66d0-c571-6c83-1bcd-7131c4326d67&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9FbWVyZ2VuY3k&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ac1ced5e91a10177420f52a1e0fce6e16055247f2288f076e9a0a033b2d92520JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23db66d0-c571-6c83-1bcd-7131c4326d67&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9bEJyUkE1UkNZVFU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ebd9d34d87c17057edfadd5507ab2052f8ec1b6417d70950e8f31725dc232f36JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23db66d0-c571-6c83-1bcd-7131c4326d67&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VtZXJnZW5jeQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0ed2c013b82920db501002bebb8b4fca8deba5f7628054f9466b9e9fca15253eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23db66d0-c571-6c83-1bcd-7131c4326d67&amp;u=a1aHR0cHM6Ly9kb3lvdXJlbWVtYmVyLmNvbS8xNTg1NjEvZW1lcmdlbmN5LWNhc3QtdGhlbi1ub3c&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0240167e779b2d7c54a856667d450589a520277dd94b96142fff029163e28b44JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23db66d0-c571-6c83-1bcd-7131c4326d67&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MDA2ODA2Ny9mdWxsY3JlZGl0cy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=07d99558bc2dbb199c38212b210d15ccae7ba1c715b9819d6ce8007f281c9077JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23db66d0-c571-6c83-1bcd-7131c4326d67&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2VtZXJnZW5jeQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aee3fc9f1bcc47a09cc5c78a158f509b49f12b438b1dfbe38e8a678bccf769c9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23db66d0-c571-6c83-1bcd-7131c4326d67&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f9af53af123fff8eeeeea68c4f86ca6ca34dabc21c18ed4ca2d181b903a8adf6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23db66d0-c571-6c83-1bcd-7131c4326d67&amp;u=a1aHR0cHM6Ly9jaXR5b2ZkZWxjaXR5Lmdvdi9kZXBhcnRtZW50cy9hbGwtZGVwYXJ0bWVudHMvZmlyZS1kZXBhcnRtZW50L2VtZXJnZW5jeS1tYW5hZ2VtZW50Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3aaebed9facba2d8d262fbc0c83dfb11f2830dcc74ee85c7567a67ad19c5b35cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2262b54b-3af1-6aab-3821-a2aa3b806b27&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU2Vh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=40118c9a2590c4a69f1114a46e2591ecddde460ac7d5258b3ca46d0e0f2a9e9bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2262b54b-3af1-6aab-3821-a2aa3b806b27&amp;u=a1aHR0cHM6Ly9zZWEuZWR1Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b5b7ffe7666af94948489f22ec28646f6f382bd3bcc119a23cad0ffafe436e90JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2262b54b-3af1-6aab-3821-a2aa3b806b27&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9PY2Vhbi12cy1TZWEtV2hhdHMtdGhlLURpZmZlcmVuY2U&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=059828a26a2f5cf2a04f4f005adbe85d001aaeef10ba3dcf86d82cf60d295e0eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2262b54b-3af1-6aab-3821-a2aa3b806b27&amp;u=a1aHR0cHM6Ly9zZWEtbnkuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c2cdce2ef8871aa4250cfe52c9750138fca7e0817dcd0f54a0884f1f79507249JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2262b54b-3af1-6aab-3821-a2aa3b806b27&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NlYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b96f8cf7bfb5338d3be6afc042ee55eb00e9828ee4f951972b4bb1daf469ce4dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2262b54b-3af1-6aab-3821-a2aa3b806b27&amp;u=a1aHR0cHM6Ly93d3cuc2VhLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a0629509efdcfd6d38a5c7d0c603b91e8aa85dfb34f465e7a3a3908ac85a65acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2262b54b-3af1-6aab-3821-a2aa3b806b27&amp;u=a1aHR0cHM6Ly9lZHVjYXRpb24ubmF0aW9uYWxnZW9ncmFwaGljLm9yZy9yZXNvdXJjZS9zZWEv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4174a29c5fff2d0b9a5eb1470a074fde89d0cff46c370651a6673247816f9556JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2262b54b-3af1-6aab-3821-a2aa3b806b27&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL1NlYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d808187e119d4ab53d940c800a387d27fda8d9531ad5cf9a22c3f89c66e6032aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2262b54b-3af1-6aab-3821-a2aa3b806b27&amp;u=a1aHR0cHM6Ly9zZWFsaW1pdGVkLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a1a9817de068123b40057f5564229da5fe516053a03ca3c2533b101fb825b7a3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2262b54b-3af1-6aab-3821-a2aa3b806b27&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvT2NlYW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=62532d0def00a0d79d64c2a42f9fbd8d0fb30c94e5a50baf5422e1123eaae4c2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09a270a0-0b95-67ac-2323-67410ae46628&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTW91bnRhaW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ba9edfdc049d6710f504af232a82d08a9d8e10771bfdaedf240afa9618a3bcf5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09a270a0-0b95-67ac-2323-67410ae46628&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9tb3VudGFpbi1sYW5kZm9ybQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=611883fa7d4519cf4aef59f85a7a6dea1507ed9d5ba0b467113f6eef37fdb4b7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09a270a0-0b95-67ac-2323-67410ae46628&amp;u=a1aHR0cHM6Ly93d3cud29ybGRhdGxhcy5jb20vbW91bnRhaW5zLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=35ca297fcdc88d66141a8836bf9822f622cc2c143f13d44d29e3de8777f52c54JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09a270a0-0b95-67ac-2323-67410ae46628&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTGlzdF9vZl9tb3VudGFpbl9yYW5nZXNfb2ZfQ29sb3JhZG8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e7f50a755bf02d7e7fdce060a5b83ae16b2b458ec0b3b3700d5ab6d8e0b5c8c1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09a270a0-0b95-67ac-2323-67410ae46628&amp;u=a1aHR0cHM6Ly93d3cubmF0aW9uYWxnZW9ncmFwaGljLmNvbS9zY2llbmNlL2FydGljbGUvbW91bnRhaW5z&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f5c6221fb3238a71abc7bbc1162715b2858e50f7daf218c3b595aa8e193815edJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09a270a0-0b95-67ac-2323-67410ae46628&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL01vdW50YWlu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=af22b891be4db88d9e5318e7f9944145d420fd9116c1990f74b154ad8d221fc6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09a270a0-0b95-67ac-2323-67410ae46628&amp;u=a1aHR0cHM6Ly9odW1hbmlkYWRlcy5jb20vZW4vbW91bnRhaW4v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2c20379067be2048a385c3085b28e944b4bc1b8c9320205e5b44bbefda1d284eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09a270a0-0b95-67ac-2323-67410ae46628&amp;u=a1aHR0cHM6Ly93d3cud29ybGRhdGxhcy5jb20vYXJ0aWNsZXMvd2hhdC1pcy1hLW1vdW50YWluLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=209e5217cedee60b54bab8cde01733796967fac0871f4911544110da19b90940JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09a270a0-0b95-67ac-2323-67410ae46628&amp;u=a1aHR0cHM6Ly93d3cudmlzaXRnb2xkZW4uY29tL3RoaW5ncy10by1kby9hdHRyYWN0aW9ucy9sb29rb3V0LW1vdW50YWluLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11809b93c291f4f7c15c96c7e3a96b6ef8a441da0f4f25c888b5917f76e16f1cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09a270a0-0b95-67ac-2323-67410ae46628&amp;u=a1aHR0cHM6Ly93d3cuc2NpZW5jZWRhaWx5LmNvbS90ZXJtcy9tb3VudGFpbi5odG0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e296c94d67362e805e5a3e81243ecf600e064d1589d556cc9770def5cd93d41cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28ca5f87-013d-6abb-3045-4866002d6b57&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRGlzYXN0ZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=44e29f26f0b292c9ac4aa6d571885edc029b9723cdb516ead6e5b4495ba86230JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28ca5f87-013d-6abb-3045-4866002d6b57&amp;u=a1aHR0cHM6Ly93d3cuZGlzYXN0ZXJhc3Npc3RhbmNlLmdvdi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f0f765681d693dc9abb9b439844d07c2daaffcad4067fa856812baef40d7026dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28ca5f87-013d-6abb-3045-4866002d6b57&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9kaXNhc3Rlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4a5f453edd51ddaf98e43663a1c00d7021326b80f059025e8280fa223b2f097bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28ca5f87-013d-6abb-3045-4866002d6b57&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Rpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=86974e669361edcefeb0d0f6ef77f9cf54418366d48f28bb37d66d0c3286be01JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28ca5f87-013d-6abb-3045-4866002d6b57&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3YvZGlzYXN0ZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d44f63c6f9d735631b224cf4cba2607fd53eca33e95be97d8e29af548080d3b5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28ca5f87-013d-6abb-3045-4866002d6b57&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9uYXR1cmFsLWRpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=60f6dd1ca8784cd96b745b017fdb470c00183626bf3a759cbac51b3d5d5612adJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28ca5f87-013d-6abb-3045-4866002d6b57&amp;u=a1aHR0cHM6Ly93d3cuZGlzYXN0ZXJyYWRhci5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1c204587b13cb537a20ba33489e05ec4bda86ad47cd98eb90c30b4ba1c786d57JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28ca5f87-013d-6abb-3045-4866002d6b57&amp;u=a1aHR0cHM6Ly93d3cudW5kcnIub3JnL3Rlcm1pbm9sb2d5L2Rpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ffd690e7d3b16a95d70be53b191589d5526bcdf49d92a91b73862a774fec7fabJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28ca5f87-013d-6abb-3045-4866002d6b57&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTmF0dXJhbF9kaXNhc3Rlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=89e3e314317952f085002c55c72c01b4044c1fd81cea96bb0694f54f5618d40dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ccd94a1-f960-6795-1a62-8340f87366a0&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZpcnN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7cd3c0fa5963a05dce73972a71063b274932143c01ef2c3a4d2fb28b6241cb01JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ccd94a1-f960-6795-1a62-8340f87366a0&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZpcnN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=97ca0f7b3582cb096806fd5894c3644218bbff5503467c2c9232c0167540248eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ccd94a1-f960-6795-1a62-8340f87366a0&amp;u=a1aHR0cHM6Ly90ZXhhc2ZpcnN0LmJhbmsvcGVyc29uYWwv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1d106004c390a63c69cbe833ca2c622eb53d9f4fc6e0d5e5ae396a40c2759a22JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ccd94a1-f960-6795-1a62-8340f87366a0&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RpbnNwaXJlcy5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3495565111d1080c54293981f75a42d46e73b8515781d26986e10fa07750795aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ccd94a1-f960-6795-1a62-8340f87366a0&amp;u=a1aHR0cHM6Ly9lbi53aWt0aW9uYXJ5Lm9yZy93aWtpL2ZpcnN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0ede3e5deec70342e07503e271b712fdd320840f4c766a91229029556fbadf29JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ccd94a1-f960-6795-1a62-8340f87366a0&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RjaXRpemVucy5jb20vcGVyc29uYWwvZGlnaXRhbC1iYW5raW5n&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d938a6625f1a1833d9b7426d56ce9ebf4791a9b0b6ef679a9dafb7b08181535bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ccd94a1-f960-6795-1a62-8340f87366a0&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9maXJzdA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c1c51282a09de279598bb679ed6b937b81af9bea34f929fbd54c6c1a1597422cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ccd94a1-f960-6795-1a62-8340f87366a0&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2ZpcnN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=978b3a398bc1425f977c7dbbb808381035c048f793e0daa2399d1105aeb380b9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ccd94a1-f960-6795-1a62-8340f87366a0&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2ZpcnN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dc85ce3e02f6a628a2546354a742007f88d231afc5e3e164c88e39c24860dfeeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ccd94a1-f960-6795-1a62-8340f87366a0&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RpbnNwaXJlcy5vcmcvdGVhbS1ldmVudC1zZWFyY2g&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c86ae3252256f5ba2d31812f5cff5d52d2f4915760c46cb681b756758e13ec8fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02570247-7c96-6f93-3d51-15a67dc66ed6&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQW1idWxhbmNl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5eb00de35678c99e9d8f2fe89079a5c9bfd3620f1d4a557492ee1ecbd1b74db1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02570247-7c96-6f93-3d51-15a67dc66ed6&amp;u=a1aHR0cHM6Ly9tZWRzdGFyYW1idWxhbmNlLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=075c65d5512fa76364eeece6689a15bb7999e92c25e00451e350b9a08dd8e503JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02570247-7c96-6f93-3d51-15a67dc66ed6&amp;u=a1aHR0cHM6Ly9tZWRzdGFyYW1idWxhbmNlLm9yZy9jb250YWN0Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f899a87e6dad5ba998e5466f0939120ab1b8371cd70401ba0cc2838f68babe2bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02570247-7c96-6f93-3d51-15a67dc66ed6&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL3RoZXJlYWxtZWRzdGFyLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eaee69ca74dae1d3aa8bdfc949f6bde9aba227688e6d3f41ebd946bc66c59e18JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02570247-7c96-6f93-3d51-15a67dc66ed6&amp;u=a1aHR0cHM6Ly80MTEuaW5mby9idXNpbmVzcy9NZWRzdGFyLUFtYnVsYW5jZS1DbGludG9uLVRvd25zaGlwLU1JLTI5NzIzMTI2&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=de6ffcb00059a81c5ec61b0f4c1fb8b75d2ab7775a9f18a02789137ff410a507JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02570247-7c96-6f93-3d51-15a67dc66ed6&amp;u=a1aHR0cHM6Ly93d3cueWVsbG93cGFnZXMuY29tL2NsaW50b24tdG93bnNoaXAtbWkvYW1idWxhbmNlLXNlcnZpY2Vz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef7f8ad24bbe3e1348cd09214a1aa493cf6871da0cc34e243d73b9b8e3d603a0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02570247-7c96-6f93-3d51-15a67dc66ed6&amp;u=a1aHR0cHM6Ly93d3cuY2xpbnRvbnRvd25zaGlwLmNvbS8zMjkvQW1idWxhbmNlLUNvbW1pdHRlZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2f70c101537747c067ee68192535122383425db240812482efa7baa27adbdff9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02570247-7c96-6f93-3d51-15a67dc66ed6&amp;u=a1aHR0cHM6Ly9ucGlwcm9maWxlLmNvbS9ucGkvMTEyNDA1NjI5Ng&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d8b048f8f5d5b86a326db1b703bb12a687f48641c37c48a6a631b3a9620d7342JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02570247-7c96-6f93-3d51-15a67dc66ed6&amp;u=a1aHR0cHM6Ly93d3cudW5pdmVyc2FsYW1idWxhbmNlLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=42575a0fb6a6010e261b29d403d02a1ede1314707ceeac7391ce356d63557bfeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02570247-7c96-6f93-3d51-15a67dc66ed6&amp;u=a1aHR0cHM6Ly9ucGlwcm9maWxlLmNvbS9kaXJlY3RvcnkvY2l0eS9hbWJ1bGFuY2UtaW4tY2xpbnRvbi10b3duc2hpcC1taWNoaWdhbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9c828fd347c18e1fc1eeb876a4b8193b7beee2c0ca1cd899f19641423f783f8eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01ed1949-74e7-60e2-2175-0ea875f56153&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS94aHRtbC9zZWFyY2g&amp;ntb=1</t>
   </si>
   <si>
     <t>https://www.bing.com/</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bae016d450e8c1c1f879cba5de4170cfd1ad788d0b6ef9e7eeedab69b9a65eb9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f315631-6f44-64ab-0da5-41d06ed3651b&amp;u=a1aHR0cHM6Ly9zZWFyY2gueWFob28uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fad307aa5117de73eeefe06b4f09838c943d00a453f4913950cf0bdecef549ccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f315631-6f44-64ab-0da5-41d06ed3651b&amp;u=a1aHR0cHM6Ly9zZWFyY2guZ29vZ2xlLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=224e24013b90df393b6953443adc0b03303ed6119adaed965109ceb26ff2d68fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f315631-6f44-64ab-0da5-41d06ed3651b&amp;u=a1aHR0cHM6Ly93d3cueWFob28uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0c1f5bc601b768ecdf9552461259dee558b5402a86632f0111fd4ef49952c495JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f315631-6f44-64ab-0da5-41d06ed3651b&amp;u=a1aHR0cHM6Ly9zZWFyY2guYnJhdmUuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=da5d66ebb3c766b429881b1dee191ace9df59f000e723f7f80c850458dc91e49JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f315631-6f44-64ab-0da5-41d06ed3651b&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vVXNlLUJpbmctU2VhcmNoLUVuZ2luZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=03ce442c9aa2ce8014c51bdf229760e1266ef9fb0efd67a0284ce5de22cf0965JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f315631-6f44-64ab-0da5-41d06ed3651b&amp;u=a1aHR0cHM6Ly9kdWNrZHVja2dvLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=56dda566245e4a3f6254e7f3fe7ae01e1d44480f1d4de17600e574488cbfb384JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f324671-14dc-6928-0ce5-519015f568fe&amp;u=a1aHR0cHM6Ly93d3cubGFjb3VydC5jYS5nb3YvcGFnZXMvbHAvY2l2aWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3793e99b3c45ce53c420b6189beed7e1870b9e2a082440b841f8e67a20777ef1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f324671-14dc-6928-0ce5-519015f568fe&amp;u=a1aHR0cHM6Ly93d3cubGFjb3VydC5jYS5nb3YvcGFnZXMvbHAvYWNjZXNzLWEtY2FzZS90cC9maW5kLWNhc2UtaW5mb3JtYXRpb24vY3Avb3MtY2l2aWwtY2FzZS1hY2Nlc3M&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b86fcb08dae13e2cdaef61edc672064473628666a00b500d676a576842cb4ed4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f324671-14dc-6928-0ce5-519015f568fe&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Npdmls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c325146519d31b99a6037fe111ddb23548623454cf5b56753eb4e369ec8e71f3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f324671-14dc-6928-0ce5-519015f568fe&amp;u=a1aHR0cHM6Ly93d3cubGFjb3VydC5vcmcvZGl2aXNpb24vY2l2aWwvY2l2aWwuYXNweA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5e971a179fe88a768709553a38356458a4745fb9ba12fcc42cbb5ac2f1f4fe09JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f324671-14dc-6928-0ce5-519015f568fe&amp;u=a1aHR0cHM6Ly93d3cubGFjb3VydC5vcmcvb25saW5lL2Npdmls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bdd2b777c6a28e34cc3567c937d02e612653523f15889bcad473a0a368b01910JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f324671-14dc-6928-0ce5-519015f568fe&amp;u=a1aHR0cHM6Ly9sYXNkLm9yZy9jb3VydHNlcnZpY2VzL2NpdmlsLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed9ea33bfff1414fd4e7a77f87fadbc4bbae420f5aff386c6c650cd8b35acab9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f324671-14dc-6928-0ce5-519015f568fe&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9DaXZpbF9lbmdpbmVlcmluZw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b6e62bec31ad57779f9e5f6271a7c237cc49c5fd76c3366bf685726d4b50a826JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f324671-14dc-6928-0ce5-519015f568fe&amp;u=a1aHR0cHM6Ly9zZWxmaGVscC5jb3VydHMuY2EuZ292L2NpdmlsLWxhd3N1aXQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=915538a4373139be833bf96834d6774035c40d18e65de40ca2c6658c4d1c0012JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f324671-14dc-6928-0ce5-519015f568fe&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Npdmls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f06a399d4eecb79f7b8aa619e46d8a1494f354cc432ddd90740d1b488c9a4e90JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3f324671-14dc-6928-0ce5-519015f568fe&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2Npdmls&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be7cc8b044cdb4bb78d498c39553c37cfd13f2ac2338b05b022b676b0345c1ceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01ed1949-74e7-60e2-2175-0ea875f56153&amp;u=a1aHR0cHM6Ly9zZWFyY2gueWFob28uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6018b468bb6806bbcd364a2ff29430ac85f4643624e8901cadb776d34502bf51JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01ed1949-74e7-60e2-2175-0ea875f56153&amp;u=a1aHR0cHM6Ly9zZWFyY2guZ29vZ2xlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=376974a30b0d2a2965e220036fb9260a2a6b7b702125038a5068864086fa60afJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01ed1949-74e7-60e2-2175-0ea875f56153&amp;u=a1aHR0cHM6Ly93d3cueWFob28uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=348feb6f18d5f49d0be60df7423611b99ebb01f1f4416b0820a2035fcae17c8cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01ed1949-74e7-60e2-2175-0ea875f56153&amp;u=a1aHR0cHM6Ly9kdWNrZHVja2dvLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f5c2d4c40800a447c90039c402a4b971d7eae09aa08cf8adc8673e24931dd2a6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01ed1949-74e7-60e2-2175-0ea875f56153&amp;u=a1aHR0cHM6Ly9ub2FpLmR1Y2tkdWNrZ28uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=94e002f1ac110abc2432e90b0a007234a0ac8d05a10e6d9732743bafc95ccfe6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01ed1949-74e7-60e2-2175-0ea875f56153&amp;u=a1aHR0cHM6Ly9hY2NvdW50cy5nb29nbGUuY29tL0ludGVyYWN0aXZlTG9naW4_c2VydmljZT1zYWZlc2VhcmNobG9jaw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c75079ede9b2facdcd919642b9c6defd1089c78bf37e37da31072e8e59411f28JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b95cdf-b4e6-65a4-2e4a-4b3eb58664b6&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9fb4797f24d91fe015861acf43e0f8307a6a5d2fb0d8c262d1bfe8f10e57ceb5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b95cdf-b4e6-65a4-2e4a-4b3eb58664b6&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c25c4ffe781f7653579b1e3361aad362c37adae777086c645a5936f22c99a0d8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b95cdf-b4e6-65a4-2e4a-4b3eb58664b6&amp;u=a1aHR0cHM6Ly91c2RpY3Rpb25hcnkuY29tL2RlZmluaXRpb25zL2NpdmlsLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c7eb1b64954f8301fc7a6e0ba803d40626f6f11ae65612d6c27dd9f0919873ffJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b95cdf-b4e6-65a4-2e4a-4b3eb58664b6&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9DaXZpbF9lbmdpbmVlcmluZw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=64f7833a669579b54e7a99b1939d99e639f204d41cbf85eac9d5eb55535cfbddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b95cdf-b4e6-65a4-2e4a-4b3eb58664b6&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=acacfa7a1900bf881347425d605d6f0ebe267fb7e67c0f59e30cdf2194417065JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b95cdf-b4e6-65a4-2e4a-4b3eb58664b6&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9jaXZpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4e3972a74d10a52335c0c808da19b2700c200f0c2ac46cdbc6fa916909df46d4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b95cdf-b4e6-65a4-2e4a-4b3eb58664b6&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=33801bb2e3f2d44e7430f3ac314987eb394d9dbf844ab21c3ca62fd36ac60a70JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b95cdf-b4e6-65a4-2e4a-4b3eb58664b6&amp;u=a1aHR0cHM6Ly93d3cueW91cmRpY3Rpb25hcnkuY29tL2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8463db898deb18a57a77eee407ddd07089cb468e123bbd3820cab0de663d148JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b95cdf-b4e6-65a4-2e4a-4b3eb58664b6&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b0801ed14d0904edfbfd598ad4eea643026f35ce99dcc0b0c67952c88017282fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b95cdf-b4e6-65a4-2e4a-4b3eb58664b6&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2ZpbmRfZGVzYz1DaXZpbCtMYXd5ZXImZmluZF9sb2M9TGFndW5hK1BhcmslMkMrVFgmbXNvY2tpZD0wMmI5NWNkZmI0ZTY2NWE0MmU0YTRiM2ViNTg2NjRiNg&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
@@ -922,7 +916,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -956,19 +950,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="G2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -976,19 +970,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -996,19 +990,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1016,19 +1010,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1036,19 +1030,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1056,19 +1050,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1076,19 +1070,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1096,19 +1090,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1116,19 +1110,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H10" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1136,19 +1130,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1156,19 +1150,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H12" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1176,19 +1170,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G13" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H13" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1196,19 +1190,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G14" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1216,19 +1210,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G15" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1236,19 +1230,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G16" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1256,19 +1250,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H17" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1276,19 +1270,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G18" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H18" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1296,19 +1290,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G19" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H19" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1316,19 +1310,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G20" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H20" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1336,19 +1330,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G21" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H21" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1356,19 +1350,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G22" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H22" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1376,19 +1370,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G23" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H23" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1396,19 +1390,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G24" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H24" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1416,19 +1410,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G25" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H25" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1436,19 +1430,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G26" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H26" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1456,19 +1450,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G27" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H27" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1476,19 +1470,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G28" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H28" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1496,19 +1490,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G29" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H29" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1516,19 +1510,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G30" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H30" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1536,19 +1530,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G31" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H31" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1556,19 +1550,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G32" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H32" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1576,19 +1570,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G33" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H33" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1596,19 +1590,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G34" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H34" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1616,19 +1610,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G35" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H35" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1636,19 +1630,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G36" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H36" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1656,19 +1650,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C37" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G37" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H37" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1676,19 +1670,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C38" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G38" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H38" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1696,19 +1690,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C39" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G39" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H39" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1716,19 +1710,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C40" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G40" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H40" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1736,19 +1730,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G41" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H41" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1756,19 +1750,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G42" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H42" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1776,19 +1770,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C43" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G43" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H43" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1796,19 +1790,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C44" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G44" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H44" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1816,19 +1810,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C45" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G45" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H45" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1836,19 +1830,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C46" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G46" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H46" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1856,19 +1850,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C47" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G47" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H47" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1876,19 +1870,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C48" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G48" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H48" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1896,19 +1890,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C49" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G49" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H49" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1916,19 +1910,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G50" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H50" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1936,19 +1930,19 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G51" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H51" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1956,19 +1950,19 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C52" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G52" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H52" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1976,19 +1970,19 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C53" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G53" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H53" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -1996,19 +1990,19 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C54" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G54" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H54" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2016,19 +2010,19 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C55" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G55" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H55" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2036,19 +2030,19 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C56" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G56" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H56" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2056,19 +2050,19 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C57" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G57" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H57" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2076,19 +2070,19 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C58" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G58" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H58" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2096,19 +2090,19 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C59" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G59" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H59" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2116,19 +2110,19 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C60" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G60" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H60" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2136,19 +2130,19 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C61" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G61" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H61" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2156,19 +2150,19 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C62" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G62" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H62" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2176,19 +2170,19 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C63" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G63" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H63" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2196,19 +2190,19 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C64" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G64" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H64" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2216,19 +2210,19 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C65" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G65" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H65" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2236,19 +2230,19 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C66" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G66" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H66" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2256,19 +2250,19 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C67" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G67" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H67" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2276,19 +2270,19 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C68" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G68" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H68" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2296,19 +2290,19 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C69" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G69" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H69" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2316,19 +2310,19 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G70" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H70" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2336,19 +2330,19 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C71" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G71" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H71" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2356,19 +2350,19 @@
         <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C72" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G72" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H72" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2376,19 +2370,19 @@
         <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C73" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G73" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H73" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2396,19 +2390,19 @@
         <v>80</v>
       </c>
       <c r="B74" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C74" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G74" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H74" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2416,19 +2410,19 @@
         <v>81</v>
       </c>
       <c r="B75" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C75" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G75" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H75" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2436,19 +2430,19 @@
         <v>82</v>
       </c>
       <c r="B76" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C76" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G76" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H76" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2456,19 +2450,19 @@
         <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C77" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G77" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H77" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -2476,19 +2470,19 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C78" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G78" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H78" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -2496,19 +2490,19 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C79" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G79" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H79" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -2516,19 +2510,19 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C80" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G80" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H80" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -2536,19 +2530,19 @@
         <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C81" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G81" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H81" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -2556,19 +2550,19 @@
         <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C82" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G82" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H82" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -2576,19 +2570,19 @@
         <v>89</v>
       </c>
       <c r="B83" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C83" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G83" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H83" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -2596,19 +2590,19 @@
         <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C84" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G84" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H84" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -2616,19 +2610,19 @@
         <v>91</v>
       </c>
       <c r="B85" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C85" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G85" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H85" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -2636,19 +2630,19 @@
         <v>92</v>
       </c>
       <c r="B86" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C86" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G86" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H86" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -2656,19 +2650,19 @@
         <v>93</v>
       </c>
       <c r="B87" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C87" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G87" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H87" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -2676,39 +2670,19 @@
         <v>94</v>
       </c>
       <c r="B88" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C88" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G88" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H88" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
-      <c r="A89" t="s">
-        <v>95</v>
-      </c>
-      <c r="B89" t="s">
-        <v>96</v>
-      </c>
-      <c r="C89" t="s">
-        <v>97</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="G89" t="s">
-        <v>186</v>
-      </c>
-      <c r="H89" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -2800,7 +2774,6 @@
     <hyperlink ref="F86" r:id="rId85"/>
     <hyperlink ref="F87" r:id="rId86"/>
     <hyperlink ref="F88" r:id="rId87"/>
-    <hyperlink ref="F89" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/scraped_Cape_Town_Emergency_and_Rescue.xlsx
+++ b/results/scraped_Cape_Town_Emergency_and_Rescue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="184">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -40,34 +40,34 @@
     <t>Source</t>
   </si>
   <si>
+    <t>FIRE| Foundation for Individual Rights and Expression</t>
+  </si>
+  <si>
     <t>Fire-Wikipedia</t>
   </si>
   <si>
+    <t>Firefox: The fast, private browser that keeps you safe</t>
+  </si>
+  <si>
+    <t>AirNowFireand Smoke Map</t>
+  </si>
+  <si>
     <t>Wildfire/Smoke Map - Live Tracking</t>
   </si>
   <si>
-    <t>Firefox: The fast, private browser that keeps you safe</t>
-  </si>
-  <si>
-    <t>FIRE| Foundation for Individual Rights and Expression</t>
-  </si>
-  <si>
-    <t>AirNowFireand Smoke Map</t>
-  </si>
-  <si>
-    <t>NIFCMaps-National Interagency Fire Center</t>
-  </si>
-  <si>
-    <t>Live Wildfire Map &amp; Tracker – Wildfires Near Me | AllFirefighter</t>
-  </si>
-  <si>
-    <t>FireMap: Track Wildfires in Real-Time with NASA &amp; Local Data</t>
-  </si>
-  <si>
-    <t>Watch Duty - Wildfire Maps &amp; Alerts</t>
-  </si>
-  <si>
-    <t>NationalFireNews -National Interagency Fire Center</t>
+    <t>NASA | LANCE |FIRMS</t>
+  </si>
+  <si>
+    <t>Live Wildfire Map: Active Fires, Smoke &amp; Alerts |FireNearby</t>
+  </si>
+  <si>
+    <t>Current Wildfire Information - U.S. Department of the Interior</t>
+  </si>
+  <si>
+    <t>Incidents| CALFIRE</t>
+  </si>
+  <si>
+    <t>Bladensburg VolunteerFireDepartment | Bladensburg MD -Facebook</t>
   </si>
   <si>
     <t>Emergency! (TV Series 1972–1979) - IMDb</t>
@@ -79,172 +79,175 @@
     <t>Emergency-Wikipedia</t>
   </si>
   <si>
-    <t>Emergency! | The Complete Series -YouTube</t>
-  </si>
-  <si>
     <t>EMERGENCYDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>The 'Emergency' Cast: Looking at the Actors, Then and Now 2024</t>
-  </si>
-  <si>
-    <t>Emergency! (TV Series 1972–1979) - Full cast &amp; crew - IMDb</t>
+    <t>Emergency AssistanceLanding Page</t>
+  </si>
+  <si>
+    <t>Froedtert Hospital Emergency Department, Milwaukee, Wis</t>
+  </si>
+  <si>
+    <t>EMERGENCYMEDICINE SPECIALISTS - EMS</t>
+  </si>
+  <si>
+    <t>EmergencyPreparedness and Response | CDC</t>
+  </si>
+  <si>
+    <t>EmergencyDepartments -Froedtert &amp; the Medical College of...</t>
   </si>
   <si>
     <t>EMERGENCY| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
+    <t>Sea-Wikipedia</t>
+  </si>
+  <si>
+    <t>Sea- National Geographic Society</t>
+  </si>
+  <si>
+    <t>SeaEducation Association</t>
+  </si>
+  <si>
+    <t>Do you know the difference between ocean,sea, bay and gulf?</t>
+  </si>
+  <si>
+    <t>Sea- SimpleEnglish Wikipedia, the free encyclopedia</t>
+  </si>
+  <si>
+    <t>Ocean- Wikipedia</t>
+  </si>
+  <si>
+    <t>Ocean vs.Sea: What’s the Difference? - Encyclopedia Britannica</t>
+  </si>
+  <si>
+    <t>SEADefinition &amp; Meaning - Merriam-Webster</t>
+  </si>
+  <si>
+    <t>Sea| Investor Relations</t>
+  </si>
+  <si>
+    <t>SEA, Ltd. - Forensic Engineering Services | Structural &amp; Failure Analysis</t>
+  </si>
+  <si>
+    <t>List of mountains of New York (state) -Wikipedia</t>
+  </si>
+  <si>
+    <t>Mountain-Wikipedia</t>
+  </si>
+  <si>
+    <t>Mountains -WorldAtlas</t>
+  </si>
+  <si>
+    <t>AdirondackMountains| Official Adirondack Region Website</t>
+  </si>
+  <si>
+    <t>BristolMountain|New YorkSki Resort | Canandaigua,NY</t>
+  </si>
+  <si>
+    <t>MountainBikingTrailsin WesternNew York- WNYMBA</t>
+  </si>
+  <si>
+    <t>Mountain| Definition, Characteristics, Types, &amp; Facts | Britannica</t>
+  </si>
+  <si>
+    <t>New YorkMountains – USA | PeakVisor</t>
+  </si>
+  <si>
+    <t>AlleganyMountainResort at Rainbow Lake</t>
+  </si>
+  <si>
+    <t>MOUNTAINDefinition &amp; Meaning -Merriam-Webster</t>
+  </si>
+  <si>
+    <t>Disaster-Wikipedia</t>
+  </si>
+  <si>
+    <t>Disaster| Definition &amp; Types | Britannica</t>
+  </si>
+  <si>
+    <t>DISASTERDefinition &amp; Meaning -Merriam-Webster</t>
+  </si>
+  <si>
+    <t>Home | disasterassistance.gov</t>
+  </si>
+  <si>
+    <t>Naturaldisaster| Causes, Types, &amp; Facts | Britannica</t>
+  </si>
+  <si>
     <t>Home |FEMA.gov</t>
   </si>
   <si>
-    <t>The Office ofEmergencyManagement | The City of Del City</t>
-  </si>
-  <si>
-    <t>Sea-Wikipedia</t>
-  </si>
-  <si>
-    <t>SeaEducation Association</t>
-  </si>
-  <si>
-    <t>Ocean vs.Sea: What’s the Difference? - Encyclopedia Britannica</t>
-  </si>
-  <si>
-    <t>SeaNew York</t>
-  </si>
-  <si>
-    <t>SEADefinition &amp; Meaning - Merriam-Webster</t>
-  </si>
-  <si>
-    <t>Sea| Home</t>
-  </si>
-  <si>
-    <t>Sea- National Geographic Society</t>
-  </si>
-  <si>
-    <t>Sea- SimpleEnglish Wikipedia, the free encyclopedia</t>
-  </si>
-  <si>
-    <t>SEA, Ltd. - Forensic Engineering Services | Structural &amp; Failure Analysis</t>
-  </si>
-  <si>
-    <t>Ocean- Wikipedia</t>
-  </si>
-  <si>
-    <t>Mountain-Wikipedia</t>
-  </si>
-  <si>
-    <t>Mountain| Definition, Characteristics, Types, &amp; Facts | Britannica</t>
-  </si>
-  <si>
-    <t>Mountains -WorldAtlas</t>
-  </si>
-  <si>
-    <t>List of mountain ranges of Colorado-Wikipedia</t>
-  </si>
-  <si>
-    <t>What is amountain? Here’s how they form | National Geographic</t>
-  </si>
-  <si>
-    <t>Mountain- Simple EnglishWikipedia, the free encyclopedia</t>
-  </si>
-  <si>
-    <t>Mountain: what they are, how they are formed and more</t>
-  </si>
-  <si>
-    <t>What is a Mountain? -WorldAtlas</t>
-  </si>
-  <si>
-    <t>Lookout Mountain- Golden,CO</t>
-  </si>
-  <si>
-    <t>Mountain-ScienceDaily</t>
-  </si>
-  <si>
-    <t>Disaster-Wikipedia</t>
-  </si>
-  <si>
-    <t>Home | disasterassistance.gov</t>
-  </si>
-  <si>
-    <t>Disaster| Definition &amp; Types | Britannica</t>
-  </si>
-  <si>
-    <t>DISASTERDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
     <t>Disaster Information-FEMA.gov</t>
   </si>
   <si>
-    <t>Naturaldisaster| Causes, Types, &amp; Facts | Britannica</t>
-  </si>
-  <si>
-    <t>DisasterRadar: Live Natural Hazard Map &amp; Alerts</t>
-  </si>
-  <si>
     <t>Definition:Disaster| UNDRR</t>
   </si>
   <si>
-    <t>Natural disaster-Wikipedia</t>
-  </si>
-  <si>
-    <t>FIRSTDefinition &amp; Meaning - Merriam-Webster</t>
-  </si>
-  <si>
-    <t>FIRST| English meaning - Cambridge Dictionary</t>
-  </si>
-  <si>
-    <t>Personal Banking, Loans, &amp; Insurance |Texas FirstBank</t>
-  </si>
-  <si>
-    <t>FIRST| For Inspiration and Recognition of Science and Technology</t>
-  </si>
-  <si>
-    <t>first- Wiktionary, the free dictionary</t>
-  </si>
-  <si>
-    <t>Digital Banking | Personal Online Banking |FirstCitizens Bank</t>
-  </si>
-  <si>
-    <t>First- Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
-  </si>
-  <si>
-    <t>First- definition offirstby The Free Dictionary</t>
-  </si>
-  <si>
-    <t>FIRSTDefinition &amp; Meaning |Dictionary.com</t>
-  </si>
-  <si>
-    <t>Find Teams &amp; Events |FIRST</t>
+    <t>DISASTER| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
+    <t>What is adisaster? - IFRC</t>
+  </si>
+  <si>
+    <t>Home -Richmond'sFirstBaptist Church</t>
+  </si>
+  <si>
+    <t>FirstTee GreaterRichmond| Premier Golfing in CentralVirginia</t>
+  </si>
+  <si>
+    <t>24/7FirstAlert Weather - 12 On Your Side</t>
+  </si>
+  <si>
+    <t>PatientFirst: Urgent Care, Primary Care, and Walk-In Care</t>
+  </si>
+  <si>
+    <t>Urgent Care, Telehealth, &amp; Walk-In Clinic -Patient First</t>
+  </si>
+  <si>
+    <t>FirstBankRichmond</t>
+  </si>
+  <si>
+    <t>Online Banking, Loans, &amp; Financial Services |FirstBank ...</t>
+  </si>
+  <si>
+    <t>FirstBank. There's Power In One. Business and personal banking.</t>
+  </si>
+  <si>
+    <t>FirstNational Apartments | Apartments inRichmond,VA</t>
+  </si>
+  <si>
+    <t>FirstHome Care –VirginiaTherapeutic Foster Care Services</t>
   </si>
   <si>
     <t>Ambulance- Wikipedia</t>
   </si>
   <si>
-    <t>Medstar –Michigan’s most integrated 911 EMS and mobile healthcare …</t>
-  </si>
-  <si>
-    <t>Contact – Medstar</t>
-  </si>
-  <si>
-    <t>Medstar|Clinton Township MI- Facebook</t>
-  </si>
-  <si>
-    <t>MedstarAmbulance-Clinton Township,MI(Michigan) - (586) 783 …</t>
-  </si>
-  <si>
-    <t>Ambulance Services in Clinton Township,MI- The Real Yellow Pages</t>
-  </si>
-  <si>
-    <t>Ambulance Committee | Clinton Township,MI</t>
-  </si>
-  <si>
-    <t>MEDSTAR - NPI 1124056296 -AmbulanceinClinton Township,MI</t>
-  </si>
-  <si>
-    <t>AmbulanceService in Macomb County | UniversalAmbulanceService</t>
-  </si>
-  <si>
-    <t>AmbulanceinClinton Township,MI- NPI Profile</t>
+    <t>Emergency Medical Services (EMS) -EnglewoodHealth</t>
+  </si>
+  <si>
+    <t>EnglewoodVolunteerAmbulanceCorps | EVAC</t>
+  </si>
+  <si>
+    <t>AmbulanceServices in Bergen County,New Jersey</t>
+  </si>
+  <si>
+    <t>EnglewoodVolunteerAmbulanceCorps, Inc |Englewood NJ- Facebook</t>
+  </si>
+  <si>
+    <t>AMR - EMS &amp;AmbulanceCare</t>
+  </si>
+  <si>
+    <t>HOME | BVAC | Emergency Medical Services in Bergenfield</t>
+  </si>
+  <si>
+    <t>EnglewoodVolunteerAmbulanceCorps inEnglewood,New Jersey...</t>
+  </si>
+  <si>
+    <t>AMBULANCEDefinition &amp; Meaning - Merriam-Webster</t>
+  </si>
+  <si>
+    <t>EnglewoodVolunteerAmbulanceinEnglewood,NJ- Hospital</t>
   </si>
   <si>
     <t>Google</t>
@@ -256,16 +259,19 @@
     <t>YahooSearch- WebSearch</t>
   </si>
   <si>
+    <t>DuckDuckGo- Protection. Privacy. Peace of mind.</t>
+  </si>
+  <si>
     <t>Google Search- A new kind of help</t>
   </si>
   <si>
-    <t>Yahoo</t>
-  </si>
-  <si>
-    <t>DuckDuckGo- Protection. Privacy. Peace of mind.</t>
-  </si>
-  <si>
-    <t>DuckDuckGo No-AI: PrivateSearchWithout AI</t>
+    <t>Google Images</t>
+  </si>
+  <si>
+    <t>Google Search- What IsGoogle SearchAnd How Does It Work</t>
+  </si>
+  <si>
+    <t>Startpage.com</t>
   </si>
   <si>
     <t>GoogleSearch</t>
@@ -274,31 +280,22 @@
     <t>CIVILDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>Civil engineering-Wikipedia</t>
+  </si>
+  <si>
     <t>CIVIL| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
-    <t>Civil: Definition, Meaning, and Examples - usdictionary.com</t>
-  </si>
-  <si>
-    <t>Civil engineering-Wikipedia</t>
+    <t>Civil- Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
   </si>
   <si>
     <t>Civil- definition ofcivilby The Free Dictionary</t>
   </si>
   <si>
-    <t>Civil- Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
-  </si>
-  <si>
     <t>CIVILDefinition &amp; Meaning |Dictionary.com</t>
   </si>
   <si>
-    <t>CivilDefinition &amp; Meaning | YourDictionary</t>
-  </si>
-  <si>
-    <t>CIVIL| definition in the Cambridge English Dictionary</t>
-  </si>
-  <si>
-    <t>TOP 10 BESTCivilLawyer nearLaguna Park,TX- Yelp</t>
+    <t>Autodesk Civil3DFeatures| What’s New inCivil3D 2027</t>
   </si>
   <si>
     <t>Emergency &amp; Rescue</t>
@@ -307,265 +304,262 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c0b40d13a084ce1f5d8428ad0b962bb931023ad09c0ce3c9903363d5beeb8de7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03ceae06-ad53-6df3-1491-b9e7ace66cf9&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GaXJl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fb057aa0e1589e874c57f5b3f9a045c2f65224c1ca16627073a58943ea0ae14dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03ceae06-ad53-6df3-1491-b9e7ace66cf9&amp;u=a1aHR0cHM6Ly93aWxkZmlyZXRyYWNrZXJzLmNvbS9mL21hcA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=512a0850556a7710107227dfa4be379e1f789a0e93fd0c261cbdcb07f96f8093JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03ceae06-ad53-6df3-1491-b9e7ace66cf9&amp;u=a1aHR0cHM6Ly93d3cuZmlyZWZveC5jb20vZW4tVVMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8b7263a81e6b54360ffd96b0098bf55e04fcd9addcf5e34fe52feedcf845f34JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03ceae06-ad53-6df3-1491-b9e7ace66cf9&amp;u=a1aHR0cHM6Ly93d3cuZmlyZS5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=60d2cc66d6ffd81c25facc74c79abd87ccec2e4f1b2371def539a126a66c38f6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03ceae06-ad53-6df3-1491-b9e7ace66cf9&amp;u=a1aHR0cHM6Ly9maXJlLmFpcm5vdy5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d09b6498bf5a54ef15ca676e643bcc9de5c11c2ec490d907aebd8b2b6706991dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03ceae06-ad53-6df3-1491-b9e7ace66cf9&amp;u=a1aHR0cHM6Ly93d3cubmlmYy5nb3YvZmlyZS1pbmZvcm1hdGlvbi9tYXBz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=71b9b8e49818407eda8273aea777a11474faf1ceb6df0bacff2083989f9e9894JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03ceae06-ad53-6df3-1491-b9e7ace66cf9&amp;u=a1aHR0cHM6Ly9hbGxmaXJlZmlnaHRlci5jb20vd2lsZGZpcmVzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bc0ab216b167f9dad4915b0702df35dea4bca7e1fe03218712bae988b96c83c8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03ceae06-ad53-6df3-1491-b9e7ace66cf9&amp;u=a1aHR0cHM6Ly93d3cuZmlyZW1hcC5saXZlLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=355ebbfadedd36d697c9d5bd90240b51cde43b79980c8c49a29b25256a33f34dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03ceae06-ad53-6df3-1491-b9e7ace66cf9&amp;u=a1aHR0cHM6Ly9hcHAud2F0Y2hkdXR5Lm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5bc31c546cfceb3495136ff1c9f3d7b29022e8f0f73cfee4451f705abd0959c4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03ceae06-ad53-6df3-1491-b9e7ace66cf9&amp;u=a1aHR0cHM6Ly93d3cubmlmYy5nb3YvZmlyZS1pbmZvcm1hdGlvbi9uZm4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e643f79735cc5ed11274e6985c2b7d117506fed5ddb80c5c2eb2e1b660a64b56JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23db66d0-c571-6c83-1bcd-7131c4326d67&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MDA2ODA2Ny8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef2031d4d2c152634f0c514d358e5d5706320b5c6488fa8a02ed66b66dbef62eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23db66d0-c571-6c83-1bcd-7131c4326d67&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9FbWVyZ2VuY3kh&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=004975d7c5d48ad1403d41ae10754049897dacfe3dffecf458d446fa3302d9dcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23db66d0-c571-6c83-1bcd-7131c4326d67&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9FbWVyZ2VuY3k&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ac1ced5e91a10177420f52a1e0fce6e16055247f2288f076e9a0a033b2d92520JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23db66d0-c571-6c83-1bcd-7131c4326d67&amp;u=a1aHR0cHM6Ly9tLnlvdXR1YmUuY29tL3dhdGNoP3Y9bEJyUkE1UkNZVFU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ebd9d34d87c17057edfadd5507ab2052f8ec1b6417d70950e8f31725dc232f36JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23db66d0-c571-6c83-1bcd-7131c4326d67&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VtZXJnZW5jeQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0ed2c013b82920db501002bebb8b4fca8deba5f7628054f9466b9e9fca15253eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23db66d0-c571-6c83-1bcd-7131c4326d67&amp;u=a1aHR0cHM6Ly9kb3lvdXJlbWVtYmVyLmNvbS8xNTg1NjEvZW1lcmdlbmN5LWNhc3QtdGhlbi1ub3c&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0240167e779b2d7c54a856667d450589a520277dd94b96142fff029163e28b44JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23db66d0-c571-6c83-1bcd-7131c4326d67&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MDA2ODA2Ny9mdWxsY3JlZGl0cy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=07d99558bc2dbb199c38212b210d15ccae7ba1c715b9819d6ce8007f281c9077JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23db66d0-c571-6c83-1bcd-7131c4326d67&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2VtZXJnZW5jeQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aee3fc9f1bcc47a09cc5c78a158f509b49f12b438b1dfbe38e8a678bccf769c9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23db66d0-c571-6c83-1bcd-7131c4326d67&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f9af53af123fff8eeeeea68c4f86ca6ca34dabc21c18ed4ca2d181b903a8adf6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=23db66d0-c571-6c83-1bcd-7131c4326d67&amp;u=a1aHR0cHM6Ly9jaXR5b2ZkZWxjaXR5Lmdvdi9kZXBhcnRtZW50cy9hbGwtZGVwYXJ0bWVudHMvZmlyZS1kZXBhcnRtZW50L2VtZXJnZW5jeS1tYW5hZ2VtZW50Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3aaebed9facba2d8d262fbc0c83dfb11f2830dcc74ee85c7567a67ad19c5b35cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2262b54b-3af1-6aab-3821-a2aa3b806b27&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU2Vh&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=40118c9a2590c4a69f1114a46e2591ecddde460ac7d5258b3ca46d0e0f2a9e9bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2262b54b-3af1-6aab-3821-a2aa3b806b27&amp;u=a1aHR0cHM6Ly9zZWEuZWR1Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b5b7ffe7666af94948489f22ec28646f6f382bd3bcc119a23cad0ffafe436e90JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2262b54b-3af1-6aab-3821-a2aa3b806b27&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9PY2Vhbi12cy1TZWEtV2hhdHMtdGhlLURpZmZlcmVuY2U&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=059828a26a2f5cf2a04f4f005adbe85d001aaeef10ba3dcf86d82cf60d295e0eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2262b54b-3af1-6aab-3821-a2aa3b806b27&amp;u=a1aHR0cHM6Ly9zZWEtbnkuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c2cdce2ef8871aa4250cfe52c9750138fca7e0817dcd0f54a0884f1f79507249JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2262b54b-3af1-6aab-3821-a2aa3b806b27&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NlYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b96f8cf7bfb5338d3be6afc042ee55eb00e9828ee4f951972b4bb1daf469ce4dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2262b54b-3af1-6aab-3821-a2aa3b806b27&amp;u=a1aHR0cHM6Ly93d3cuc2VhLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a0629509efdcfd6d38a5c7d0c603b91e8aa85dfb34f465e7a3a3908ac85a65acJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2262b54b-3af1-6aab-3821-a2aa3b806b27&amp;u=a1aHR0cHM6Ly9lZHVjYXRpb24ubmF0aW9uYWxnZW9ncmFwaGljLm9yZy9yZXNvdXJjZS9zZWEv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4174a29c5fff2d0b9a5eb1470a074fde89d0cff46c370651a6673247816f9556JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2262b54b-3af1-6aab-3821-a2aa3b806b27&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL1NlYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d808187e119d4ab53d940c800a387d27fda8d9531ad5cf9a22c3f89c66e6032aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2262b54b-3af1-6aab-3821-a2aa3b806b27&amp;u=a1aHR0cHM6Ly9zZWFsaW1pdGVkLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a1a9817de068123b40057f5564229da5fe516053a03ca3c2533b101fb825b7a3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2262b54b-3af1-6aab-3821-a2aa3b806b27&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvT2NlYW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=62532d0def00a0d79d64c2a42f9fbd8d0fb30c94e5a50baf5422e1123eaae4c2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09a270a0-0b95-67ac-2323-67410ae46628&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTW91bnRhaW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ba9edfdc049d6710f504af232a82d08a9d8e10771bfdaedf240afa9618a3bcf5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09a270a0-0b95-67ac-2323-67410ae46628&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9tb3VudGFpbi1sYW5kZm9ybQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=611883fa7d4519cf4aef59f85a7a6dea1507ed9d5ba0b467113f6eef37fdb4b7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09a270a0-0b95-67ac-2323-67410ae46628&amp;u=a1aHR0cHM6Ly93d3cud29ybGRhdGxhcy5jb20vbW91bnRhaW5zLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=35ca297fcdc88d66141a8836bf9822f622cc2c143f13d44d29e3de8777f52c54JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09a270a0-0b95-67ac-2323-67410ae46628&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTGlzdF9vZl9tb3VudGFpbl9yYW5nZXNfb2ZfQ29sb3JhZG8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e7f50a755bf02d7e7fdce060a5b83ae16b2b458ec0b3b3700d5ab6d8e0b5c8c1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09a270a0-0b95-67ac-2323-67410ae46628&amp;u=a1aHR0cHM6Ly93d3cubmF0aW9uYWxnZW9ncmFwaGljLmNvbS9zY2llbmNlL2FydGljbGUvbW91bnRhaW5z&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f5c6221fb3238a71abc7bbc1162715b2858e50f7daf218c3b595aa8e193815edJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09a270a0-0b95-67ac-2323-67410ae46628&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL01vdW50YWlu&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=af22b891be4db88d9e5318e7f9944145d420fd9116c1990f74b154ad8d221fc6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09a270a0-0b95-67ac-2323-67410ae46628&amp;u=a1aHR0cHM6Ly9odW1hbmlkYWRlcy5jb20vZW4vbW91bnRhaW4v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2c20379067be2048a385c3085b28e944b4bc1b8c9320205e5b44bbefda1d284eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09a270a0-0b95-67ac-2323-67410ae46628&amp;u=a1aHR0cHM6Ly93d3cud29ybGRhdGxhcy5jb20vYXJ0aWNsZXMvd2hhdC1pcy1hLW1vdW50YWluLmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=209e5217cedee60b54bab8cde01733796967fac0871f4911544110da19b90940JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09a270a0-0b95-67ac-2323-67410ae46628&amp;u=a1aHR0cHM6Ly93d3cudmlzaXRnb2xkZW4uY29tL3RoaW5ncy10by1kby9hdHRyYWN0aW9ucy9sb29rb3V0LW1vdW50YWluLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11809b93c291f4f7c15c96c7e3a96b6ef8a441da0f4f25c888b5917f76e16f1cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=09a270a0-0b95-67ac-2323-67410ae46628&amp;u=a1aHR0cHM6Ly93d3cuc2NpZW5jZWRhaWx5LmNvbS90ZXJtcy9tb3VudGFpbi5odG0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e296c94d67362e805e5a3e81243ecf600e064d1589d556cc9770def5cd93d41cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28ca5f87-013d-6abb-3045-4866002d6b57&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRGlzYXN0ZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=44e29f26f0b292c9ac4aa6d571885edc029b9723cdb516ead6e5b4495ba86230JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28ca5f87-013d-6abb-3045-4866002d6b57&amp;u=a1aHR0cHM6Ly93d3cuZGlzYXN0ZXJhc3Npc3RhbmNlLmdvdi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f0f765681d693dc9abb9b439844d07c2daaffcad4067fa856812baef40d7026dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28ca5f87-013d-6abb-3045-4866002d6b57&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9kaXNhc3Rlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4a5f453edd51ddaf98e43663a1c00d7021326b80f059025e8280fa223b2f097bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28ca5f87-013d-6abb-3045-4866002d6b57&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Rpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=86974e669361edcefeb0d0f6ef77f9cf54418366d48f28bb37d66d0c3286be01JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28ca5f87-013d-6abb-3045-4866002d6b57&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3YvZGlzYXN0ZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d44f63c6f9d735631b224cf4cba2607fd53eca33e95be97d8e29af548080d3b5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28ca5f87-013d-6abb-3045-4866002d6b57&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9uYXR1cmFsLWRpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=60f6dd1ca8784cd96b745b017fdb470c00183626bf3a759cbac51b3d5d5612adJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28ca5f87-013d-6abb-3045-4866002d6b57&amp;u=a1aHR0cHM6Ly93d3cuZGlzYXN0ZXJyYWRhci5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1c204587b13cb537a20ba33489e05ec4bda86ad47cd98eb90c30b4ba1c786d57JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28ca5f87-013d-6abb-3045-4866002d6b57&amp;u=a1aHR0cHM6Ly93d3cudW5kcnIub3JnL3Rlcm1pbm9sb2d5L2Rpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ffd690e7d3b16a95d70be53b191589d5526bcdf49d92a91b73862a774fec7fabJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28ca5f87-013d-6abb-3045-4866002d6b57&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTmF0dXJhbF9kaXNhc3Rlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=89e3e314317952f085002c55c72c01b4044c1fd81cea96bb0694f54f5618d40dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ccd94a1-f960-6795-1a62-8340f87366a0&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZpcnN0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7cd3c0fa5963a05dce73972a71063b274932143c01ef2c3a4d2fb28b6241cb01JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ccd94a1-f960-6795-1a62-8340f87366a0&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZpcnN0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=97ca0f7b3582cb096806fd5894c3644218bbff5503467c2c9232c0167540248eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ccd94a1-f960-6795-1a62-8340f87366a0&amp;u=a1aHR0cHM6Ly90ZXhhc2ZpcnN0LmJhbmsvcGVyc29uYWwv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1d106004c390a63c69cbe833ca2c622eb53d9f4fc6e0d5e5ae396a40c2759a22JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ccd94a1-f960-6795-1a62-8340f87366a0&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RpbnNwaXJlcy5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3495565111d1080c54293981f75a42d46e73b8515781d26986e10fa07750795aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ccd94a1-f960-6795-1a62-8340f87366a0&amp;u=a1aHR0cHM6Ly9lbi53aWt0aW9uYXJ5Lm9yZy93aWtpL2ZpcnN0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0ede3e5deec70342e07503e271b712fdd320840f4c766a91229029556fbadf29JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ccd94a1-f960-6795-1a62-8340f87366a0&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RjaXRpemVucy5jb20vcGVyc29uYWwvZGlnaXRhbC1iYW5raW5n&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d938a6625f1a1833d9b7426d56ce9ebf4791a9b0b6ef679a9dafb7b08181535bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ccd94a1-f960-6795-1a62-8340f87366a0&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9maXJzdA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c1c51282a09de279598bb679ed6b937b81af9bea34f929fbd54c6c1a1597422cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ccd94a1-f960-6795-1a62-8340f87366a0&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2ZpcnN0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=978b3a398bc1425f977c7dbbb808381035c048f793e0daa2399d1105aeb380b9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ccd94a1-f960-6795-1a62-8340f87366a0&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2ZpcnN0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dc85ce3e02f6a628a2546354a742007f88d231afc5e3e164c88e39c24860dfeeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ccd94a1-f960-6795-1a62-8340f87366a0&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RpbnNwaXJlcy5vcmcvdGVhbS1ldmVudC1zZWFyY2g&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c86ae3252256f5ba2d31812f5cff5d52d2f4915760c46cb681b756758e13ec8fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02570247-7c96-6f93-3d51-15a67dc66ed6&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQW1idWxhbmNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5eb00de35678c99e9d8f2fe89079a5c9bfd3620f1d4a557492ee1ecbd1b74db1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02570247-7c96-6f93-3d51-15a67dc66ed6&amp;u=a1aHR0cHM6Ly9tZWRzdGFyYW1idWxhbmNlLm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=075c65d5512fa76364eeece6689a15bb7999e92c25e00451e350b9a08dd8e503JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02570247-7c96-6f93-3d51-15a67dc66ed6&amp;u=a1aHR0cHM6Ly9tZWRzdGFyYW1idWxhbmNlLm9yZy9jb250YWN0Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f899a87e6dad5ba998e5466f0939120ab1b8371cd70401ba0cc2838f68babe2bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02570247-7c96-6f93-3d51-15a67dc66ed6&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL3RoZXJlYWxtZWRzdGFyLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eaee69ca74dae1d3aa8bdfc949f6bde9aba227688e6d3f41ebd946bc66c59e18JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02570247-7c96-6f93-3d51-15a67dc66ed6&amp;u=a1aHR0cHM6Ly80MTEuaW5mby9idXNpbmVzcy9NZWRzdGFyLUFtYnVsYW5jZS1DbGludG9uLVRvd25zaGlwLU1JLTI5NzIzMTI2&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=de6ffcb00059a81c5ec61b0f4c1fb8b75d2ab7775a9f18a02789137ff410a507JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02570247-7c96-6f93-3d51-15a67dc66ed6&amp;u=a1aHR0cHM6Ly93d3cueWVsbG93cGFnZXMuY29tL2NsaW50b24tdG93bnNoaXAtbWkvYW1idWxhbmNlLXNlcnZpY2Vz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef7f8ad24bbe3e1348cd09214a1aa493cf6871da0cc34e243d73b9b8e3d603a0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02570247-7c96-6f93-3d51-15a67dc66ed6&amp;u=a1aHR0cHM6Ly93d3cuY2xpbnRvbnRvd25zaGlwLmNvbS8zMjkvQW1idWxhbmNlLUNvbW1pdHRlZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2f70c101537747c067ee68192535122383425db240812482efa7baa27adbdff9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02570247-7c96-6f93-3d51-15a67dc66ed6&amp;u=a1aHR0cHM6Ly9ucGlwcm9maWxlLmNvbS9ucGkvMTEyNDA1NjI5Ng&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d8b048f8f5d5b86a326db1b703bb12a687f48641c37c48a6a631b3a9620d7342JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02570247-7c96-6f93-3d51-15a67dc66ed6&amp;u=a1aHR0cHM6Ly93d3cudW5pdmVyc2FsYW1idWxhbmNlLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=42575a0fb6a6010e261b29d403d02a1ede1314707ceeac7391ce356d63557bfeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02570247-7c96-6f93-3d51-15a67dc66ed6&amp;u=a1aHR0cHM6Ly9ucGlwcm9maWxlLmNvbS9kaXJlY3RvcnkvY2l0eS9hbWJ1bGFuY2UtaW4tY2xpbnRvbi10b3duc2hpcC1taWNoaWdhbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9c828fd347c18e1fc1eeb876a4b8193b7beee2c0ca1cd899f19641423f783f8eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01ed1949-74e7-60e2-2175-0ea875f56153&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS94aHRtbC9zZWFyY2g&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e2bf621f68dca88867fc28af1a63f2e0bf27833da98c59a660dee7950a675809JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=167d9bb6-9ae1-6e09-3d4a-8c579b1d6f27&amp;u=a1aHR0cHM6Ly93d3cuZmlyZS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d4d132124bab9379c3016d48aa2cabfd6e1f5c3d5a52240114a089906ebee731JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=167d9bb6-9ae1-6e09-3d4a-8c579b1d6f27&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmlyZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=91f1923b06bc4e7bbf8ce07b96c457b7185282852905f148d55ed9a6a0c3eb71JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=167d9bb6-9ae1-6e09-3d4a-8c579b1d6f27&amp;u=a1aHR0cHM6Ly93d3cuZmlyZWZveC5jb20vZW4tVVMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=349469ac0b0f2ef86fc694746f8d94ea39331ee2ccd61f9988414463df08b7dcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=167d9bb6-9ae1-6e09-3d4a-8c579b1d6f27&amp;u=a1aHR0cHM6Ly9maXJlLmFpcm5vdy5nb3YvP2xhbmc9ZW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=30e9ca243aa4114cb667c03f280a58b47e63fe077e353e2bf2e93312bbdb04d6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=167d9bb6-9ae1-6e09-3d4a-8c579b1d6f27&amp;u=a1aHR0cHM6Ly93aWxkZmlyZXRyYWNrZXJzLmNvbS9mL21hcA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=75fb48e96ab8ba9aaad6790bd69a2706d35625d658e1accaafcabf5ff4a7ee7fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=167d9bb6-9ae1-6e09-3d4a-8c579b1d6f27&amp;u=a1aHR0cHM6Ly9maXJtcy5tb2RhcHMuZW9zZGlzLm5hc2EuZ292L21hcC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=354ad1022619bf329361faed027bdc0a92eb6378a58c6aca4d4cdbb530c82406JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=167d9bb6-9ae1-6e09-3d4a-8c579b1d6f27&amp;u=a1aHR0cHM6Ly9maXJlbmVhcmJ5LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0fc4d731ecdaae136f01cf668434effe6ba3a5e2dd6ba73fbdb1d86a9c7cc566JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=167d9bb6-9ae1-6e09-3d4a-8c579b1d6f27&amp;u=a1aHR0cHM6Ly93d3cuZG9pLmdvdi93aWxkbGFuZGZpcmVzZXJ2aWNlL2N1cnJlbnQtd2lsZGZpcmUtaW5mb3JtYXRpb24&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=78d6cfa3fb9eac53982b559489bed3bcfd49d05635dbaa3feb565b8e89365f0cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=167d9bb6-9ae1-6e09-3d4a-8c579b1d6f27&amp;u=a1aHR0cHM6Ly93d3cuZmlyZS5jYS5nb3YvaW5jaWRlbnRzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=adbd2098e25979b11c1e5f2905eb2c180d045b74a356f9db44bba7e6dc438f38JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=167d9bb6-9ae1-6e09-3d4a-8c579b1d6f27&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL2JsYWRlbnNidXJnY28uOS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8e7f85b329a9cf5b4016fbf3a388499278a35510e0408e03911ae60fb5f60308JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136922df-fae3-66cb-355a-353efbe0672a&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MDA2ODA2Ny8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=332dfeaa36a275028989f4267ee26ff713d8de9205c749a1acc1abffa6d6fbedJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136922df-fae3-66cb-355a-353efbe0672a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9FbWVyZ2VuY3kh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b2a443d4f41542819f59dc08ab817eed1a9fde8ea19b50ed57b5a68cf54e3059JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136922df-fae3-66cb-355a-353efbe0672a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9FbWVyZ2VuY3k&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e89dbb07dd7b5e22a0be48e9cb2efec63e9efec0ba0f4df6ba99e7862c98f7f1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136922df-fae3-66cb-355a-353efbe0672a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VtZXJnZW5jeQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4e4407ec7e6a45aa828152b62737529f2512e94ef834a6d06ba5a9082a28f121JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136922df-fae3-66cb-355a-353efbe0672a&amp;u=a1aHR0cHM6Ly9kY2Yud2lzY29uc2luLmdvdi9lYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c883804f7dfa88731214e0298c4262763ccec10c17fff3880e99f880bae31d46JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136922df-fae3-66cb-355a-353efbe0672a&amp;u=a1aHR0cHM6Ly93d3cuZnJvZWR0ZXJ0LmNvbS9sb2NhdGlvbnMvZW1lcmdlbmN5LWRlcGFydG1lbnQvZnJvZWR0ZXJ0LWhvc3BpdGFsLWVtZXJnZW5jeS1kZXBhcnRtZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ee06ab99b58ad20071b22c9f1b6391f41304151c793ba44956655041d28d26a1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136922df-fae3-66cb-355a-353efbe0672a&amp;u=a1aHR0cHM6Ly9lbXMtd2kuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fdf787dba895303a210d2c1772decf39020d520ddaa874c67889125b00c53dbfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136922df-fae3-66cb-355a-353efbe0672a&amp;u=a1aHR0cHM6Ly93d3cuY2RjLmdvdi9lbWVyZ2VuY3kvaW5kZXguaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=72cf35c0d5a61f0a0545b75f2e39cd2ad2253915405f037451c33cef582cd26fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136922df-fae3-66cb-355a-353efbe0672a&amp;u=a1aHR0cHM6Ly93d3cuZnJvZWR0ZXJ0LmNvbS9lbWVyZ2VuY3k&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=832a10ca3a9e9664fa7f81821f146284e9c31e7ad172752492f5fa1d5ecfa047JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136922df-fae3-66cb-355a-353efbe0672a&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2VtZXJnZW5jeQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ae0327d8f0b1e84f6224b267ff0cc5b7114a3cae92efe5c96bfd929cce3854c0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39e36cca-6673-6727-3e75-7b2b67a66602&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU2Vh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=71ce15c8695aa776b3a55578e3a8c4a44d9bece286d20d47db506c0d64c72d9dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39e36cca-6673-6727-3e75-7b2b67a66602&amp;u=a1aHR0cHM6Ly9lZHVjYXRpb24ubmF0aW9uYWxnZW9ncmFwaGljLm9yZy9yZXNvdXJjZS9zZWEv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47de5426b6d4e682385230f6ff0b627f0977db115373b5f09eb6fafa2cff06caJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39e36cca-6673-6727-3e75-7b2b67a66602&amp;u=a1aHR0cHM6Ly9zZWEuZWR1Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3e1756b701731d032d4a94ec9ab66e5b4b16af60dffe132616874f9b963a8883JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39e36cca-6673-6727-3e75-7b2b67a66602&amp;u=a1aHR0cHM6Ly90aW1lc29maW5kaWEuaW5kaWF0aW1lcy5jb20vdHJhdmVsL2Rlc3RpbmF0aW9ucy9kby15b3Uta25vdy10aGUtZGlmZmVyZW5jZS1iZXR3ZWVuLW9jZWFuLXNlYS1iYXktYW5kLWd1bGYvYXJ0aWNsZXNob3cvMTEwOTY1MTM0LmNtcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ffa67f86c4855cb52bc022ba714b09ed7d0534f332813a2e549f242b2abc81f9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39e36cca-6673-6727-3e75-7b2b67a66602&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL1NlYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d254bab894241fe78e5f4dca4bcfdeef2438ae902ce4314e088ef9a77ebab42dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39e36cca-6673-6727-3e75-7b2b67a66602&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvT2NlYW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7217eaf55ea36441fe3a8c6576e68d802965885dbe31d914b47468269abd71f7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39e36cca-6673-6727-3e75-7b2b67a66602&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9PY2Vhbi12cy1TZWEtV2hhdHMtdGhlLURpZmZlcmVuY2U&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f68f5aa7d6d22110a9b2ea1108eea2c9109ce262f0e5b01d418fbf5e5316c332JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39e36cca-6673-6727-3e75-7b2b67a66602&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NlYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7d059fe491e75c65afa3fe98157310bd2b91c27a2e1b3bf02989703de2c56855JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39e36cca-6673-6727-3e75-7b2b67a66602&amp;u=a1aHR0cHM6Ly93d3cuc2VhLmNvbS9pbnZlc3Rvci9ob21l&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8a2062488a1520cf009608768ce1b66422cf41b85905bd026b8726c0732ba7eeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39e36cca-6673-6727-3e75-7b2b67a66602&amp;u=a1aHR0cHM6Ly9zZWFsaW1pdGVkLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7b9aa9a2d2a0d295efb72ae79bacac0d2a8a657a6eed682313d0da98922b1831JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15fbc2e6-0bed-6059-26ba-d5070ae261bf&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTGlzdF9vZl9tb3VudGFpbnNfb2ZfTmV3X1lvcmtfKHN0YXRlKQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9ae56de8cc39a84a45ba97d0bcd6b857966e1c76ea4bcf97b78a8e1b82220aceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15fbc2e6-0bed-6059-26ba-d5070ae261bf&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTW91bnRhaW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8af9e9a6fb14ec68533b4f58c8c0a0e4798b753a5819d46cd2c1b187a9b545a4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15fbc2e6-0bed-6059-26ba-d5070ae261bf&amp;u=a1aHR0cHM6Ly93d3cud29ybGRhdGxhcy5jb20vbW91bnRhaW5zLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b92f180bd2511c1fdba974a134fe23ce500bd9c23f848470f354ea6463c81d61JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15fbc2e6-0bed-6059-26ba-d5070ae261bf&amp;u=a1aHR0cHM6Ly92aXNpdGFkaXJvbmRhY2tzLmNvbS9hYm91dC9tb3VudGFpbnM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c0e2744fa0f1221076036740c76cd54de1fb69c097a48abc0e8a7b325a3eb5aaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15fbc2e6-0bed-6059-26ba-d5070ae261bf&amp;u=a1aHR0cHM6Ly93d3cuYnJpc3RvbG1vdW50YWluLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=40b2c815458a8c127656c69940b5963215ec80d678c235c28dcbc27b2114174dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15fbc2e6-0bed-6059-26ba-d5070ae261bf&amp;u=a1aHR0cHM6Ly93bnltYmEub3JnL3RyYWlscy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d752b039de7b5593249ce39196e2c82e06ecccc57c4b4dd2059d1ddc2ead0ce0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15fbc2e6-0bed-6059-26ba-d5070ae261bf&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9tb3VudGFpbi1sYW5kZm9ybQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d25b24c93b4f689c530c459349e9409eb32240775caadfb25816a19a8a30af02JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15fbc2e6-0bed-6059-26ba-d5070ae261bf&amp;u=a1aHR0cHM6Ly9wZWFrdmlzb3IuY29tL2FkbS9uZXcteW9yay5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=75c3acb20c48166015a1d68847f5f04d66d167ba70e9455d4695142ac4c307bcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15fbc2e6-0bed-6059-26ba-d5070ae261bf&amp;u=a1aHR0cHM6Ly9hbGxlZ2FueW1vdW50YWlucmVzb3J0LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c0af50a20ba840b42a6975390a6618967a8fd55c0f1cfc22463e16d13d93959fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15fbc2e6-0bed-6059-26ba-d5070ae261bf&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L21vdW50YWlu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c9460fc61b9ff042039422c532c5dd4fdd0e8849b93cc5ff227f7db68df25c91JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15d8aa5f-1e08-62ee-24ae-bdbe1f0f63fa&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRGlzYXN0ZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bd71144f5897d1b042160b6ba21705062ed020f3bf9d4b70db4b7c6ec2a14589JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15d8aa5f-1e08-62ee-24ae-bdbe1f0f63fa&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9kaXNhc3Rlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=90a831bd6d402572bf37cfac2d6a67681103a286a143182c71832eb4f3fcd226JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15d8aa5f-1e08-62ee-24ae-bdbe1f0f63fa&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Rpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d772a3224432d96d1bcab6ab048c5f3463972ed4a5a6f5cdcb1a2d2b98db9cc4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15d8aa5f-1e08-62ee-24ae-bdbe1f0f63fa&amp;u=a1aHR0cHM6Ly93d3cuZGlzYXN0ZXJhc3Npc3RhbmNlLmdvdi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87f9bab060669c4dee8aa04da01e31c0d8b92e1ab36db32b25f4a8548ed3e4b0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15d8aa5f-1e08-62ee-24ae-bdbe1f0f63fa&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9uYXR1cmFsLWRpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6a19e389917f67701e1705fdb39a5e4cda5e900292748a3e965050fdda59ee25JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15d8aa5f-1e08-62ee-24ae-bdbe1f0f63fa&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2b767970510bb6fcf97901be4424dd167649be0ce3c80633e3b3a1a5ac372680JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15d8aa5f-1e08-62ee-24ae-bdbe1f0f63fa&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3YvZGlzYXN0ZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=95e7cfd9f6a1ec7a2bd65101d9cc58f7160bdd8c5c7f3925e6a6376a082d7bc1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15d8aa5f-1e08-62ee-24ae-bdbe1f0f63fa&amp;u=a1aHR0cHM6Ly93d3cudW5kcnIub3JnL3Rlcm1pbm9sb2d5L2Rpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bb741f654451b8e8f1216036d58973f9c36d130f228bb71435dcc9539f5411dcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15d8aa5f-1e08-62ee-24ae-bdbe1f0f63fa&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Rpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=722b61307500f864caddfa681b742cf57653f916169c9dfae93e236fdba30433JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15d8aa5f-1e08-62ee-24ae-bdbe1f0f63fa&amp;u=a1aHR0cHM6Ly93d3cuaWZyYy5vcmcvb3VyLXdvcmsvZGlzYXN0ZXJzLWNsaW1hdGUtYW5kLWNyaXNlcy93aGF0LWRpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d9a4c612cb9a74d6abb5d985924f28e84da6e2600999cf6f3c052390077e1c6aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=220731dc-0951-632e-3351-263d082362da&amp;u=a1aHR0cHM6Ly9mYmNyaWNobW9uZC5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bc90f192d9b1289892f51846125252be28e7d9437257847e98225fd03d2577c0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=220731dc-0951-632e-3351-263d082362da&amp;u=a1aHR0cHM6Ly9wbGF5Z29sZnJ2YS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=300492377b8a8765cd41ab346306fd49d33faa197c807d1b2f544fc15cd711ecJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=220731dc-0951-632e-3351-263d082362da&amp;u=a1aHR0cHM6Ly93d3cuMTJvbnlvdXJzaWRlLmNvbS93ZWF0aGVyLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b33276277f94ad1fc4551fabf9b983921ca1f1bc87a3d7aff503f70588b36052JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=220731dc-0951-632e-3351-263d082362da&amp;u=a1aHR0cHM6Ly93d3cucGF0aWVudGZpcnN0LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3fe8a621de1804fc2967ba8dbacac087221e85e81b70ed3ccdd917af464adccdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=220731dc-0951-632e-3351-263d082362da&amp;u=a1aHR0cHM6Ly93d3cucGF0aWVudGZpcnN0LmNvbS9sb2NhdGlvbnMvcmljaG1vbmQvbWVjaGFuaWNzdmlsbGU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=00c36d9eb316df98726b1e99d887303c79e22cbf205f5880ef3c22033767c3aaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=220731dc-0951-632e-3351-263d082362da&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RiYW5rcmljaG1vbmQuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5be2d0484e32a4d40859878524c00fca7f7d5a226044084349a9fa0de020a755JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=220731dc-0951-632e-3351-263d082362da&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RiYW5rLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=444afbcffb892990a40458f36fcb1c4d90f5b6101dbbb5c762fcaad0930e5bebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=220731dc-0951-632e-3351-263d082362da&amp;u=a1aHR0cHM6Ly93d3cuZmJ2aXJnaW5pYS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=daa1e6e3e6cccb00eb294e5702387a60ae4fa8a1c9ec02543da44eb87bdc2a2aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=220731dc-0951-632e-3351-263d082362da&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RuYXRpb25hbGFwdHMuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7253a2c204282956f6f55ff3ebf19339e89ac6634cd6339cfe5492c7094a01b6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=220731dc-0951-632e-3351-263d082362da&amp;u=a1aHR0cHM6Ly9maXJzdGhvbWVjYXJlLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=64460f61cc523fa7ae3845366808fe499f84a3d91082b56d0c74af4bd9a6868bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=181814b7-4671-69dd-2d1f-03564759688b&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQW1idWxhbmNl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9fb8ebb8c47c7a444ade1380f44369db3b251ed69618c4cd2607cd91ab843c40JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=181814b7-4671-69dd-2d1f-03564759688b&amp;u=a1aHR0cHM6Ly93d3cuZW5nbGV3b29kaGVhbHRoLm9yZy9zZXJ2aWNlL2VtZXJnZW5jeS1tZWRpY2FsLXNlcnZpY2VzLWVtcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6191370be3d56d2bf5efe70e89e31ab13ee9823cdd4bb8359d32547549d07c3cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=181814b7-4671-69dd-2d1f-03564759688b&amp;u=a1aHR0cHM6Ly93d3cuZW5nbGV3b29kdmFjLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4993b9aff0944ba0f052a049c376594d7d20d36446c7b00ccf09cbe89d28e9daJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=181814b7-4671-69dd-2d1f-03564759688b&amp;u=a1aHR0cHM6Ly93d3cubG9jYWxvZmZpY2VzLm9yZy9hbWJ1bGFuY2UvbmV3LWplcnNleS9iZXJnZW4tY291bnR5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b316bfce3f5ee50e6f459d36f6dd222bc2d2c7c31eca68672a54b5492092feffJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=181814b7-4671-69dd-2d1f-03564759688b&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL3Blb3BsZS9FbmdsZXdvb2QtVm9sdW50ZWVyLUFtYnVsYW5jZS1Db3Jwcy1JbmMvMTAwMDU3Mzg5OTIyNTY3Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e0d2881ce58413e585db2ded3c97170a80f512b191815708b29f7b8f9fdada2bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=181814b7-4671-69dd-2d1f-03564759688b&amp;u=a1aHR0cHM6Ly93d3cuYW1yLm5ldC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0af727b3bace9e45b98534301dbdb5a10692c6b242cef0d43a02ab444f3ee855JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=181814b7-4671-69dd-2d1f-03564759688b&amp;u=a1aHR0cHM6Ly93d3cuYmVyZ2VuZmllbGRhbWJ1bGFuY2Uub3JnLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5f242d393cf0f670836805bfd1f7aa45bd6184c522dba8477166ebf120788bc1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=181814b7-4671-69dd-2d1f-03564759688b&amp;u=a1aHR0cHM6Ly9ucGluby5jb20vYW1idWxhbmNlLXNlcnZpY2UvMTM5NjAwOTExNC1lbmdsZXdvb2Qtdm9sdW50ZWVyLWFtYnVsYW5jZS1jb3Jwcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3146a2ae722eb0e513a2bd2cc3e7961482005d69d99b09bb82836fcf1fe68c28JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=181814b7-4671-69dd-2d1f-03564759688b&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FtYnVsYW5jZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f45fa3a083019fc11248eec94c2f674f2c44bd0e253a5c05f88dae7e98fc2302JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=181814b7-4671-69dd-2d1f-03564759688b&amp;u=a1aHR0cHM6Ly9ob3NwaXRhbC5ob3Vyc2d1aWRlLmNvbS9maW5kLWNhcmUvYW1idWxhbmNlLXNlcnZpY2UvZW5nbGV3b29kLXZvbHVudGVlci1hbWJ1bGFuY2UtODkyODEv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f9829403ba5ea4573f7c2f8d4241751b80aafc5faa0e9a82e4c22e5328f5f027JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d5d5cd-3ea9-6192-2dee-c22c3f756021&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS94aHRtbC9zZWFyY2g&amp;ntb=1</t>
   </si>
   <si>
     <t>https://www.bing.com/</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be7cc8b044cdb4bb78d498c39553c37cfd13f2ac2338b05b022b676b0345c1ceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01ed1949-74e7-60e2-2175-0ea875f56153&amp;u=a1aHR0cHM6Ly9zZWFyY2gueWFob28uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6018b468bb6806bbcd364a2ff29430ac85f4643624e8901cadb776d34502bf51JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01ed1949-74e7-60e2-2175-0ea875f56153&amp;u=a1aHR0cHM6Ly9zZWFyY2guZ29vZ2xlLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=376974a30b0d2a2965e220036fb9260a2a6b7b702125038a5068864086fa60afJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01ed1949-74e7-60e2-2175-0ea875f56153&amp;u=a1aHR0cHM6Ly93d3cueWFob28uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=348feb6f18d5f49d0be60df7423611b99ebb01f1f4416b0820a2035fcae17c8cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01ed1949-74e7-60e2-2175-0ea875f56153&amp;u=a1aHR0cHM6Ly9kdWNrZHVja2dvLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f5c2d4c40800a447c90039c402a4b971d7eae09aa08cf8adc8673e24931dd2a6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01ed1949-74e7-60e2-2175-0ea875f56153&amp;u=a1aHR0cHM6Ly9ub2FpLmR1Y2tkdWNrZ28uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=94e002f1ac110abc2432e90b0a007234a0ac8d05a10e6d9732743bafc95ccfe6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01ed1949-74e7-60e2-2175-0ea875f56153&amp;u=a1aHR0cHM6Ly9hY2NvdW50cy5nb29nbGUuY29tL0ludGVyYWN0aXZlTG9naW4_c2VydmljZT1zYWZlc2VhcmNobG9jaw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c75079ede9b2facdcd919642b9c6defd1089c78bf37e37da31072e8e59411f28JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b95cdf-b4e6-65a4-2e4a-4b3eb58664b6&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Npdmls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9fb4797f24d91fe015861acf43e0f8307a6a5d2fb0d8c262d1bfe8f10e57ceb5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b95cdf-b4e6-65a4-2e4a-4b3eb58664b6&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Npdmls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c25c4ffe781f7653579b1e3361aad362c37adae777086c645a5936f22c99a0d8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b95cdf-b4e6-65a4-2e4a-4b3eb58664b6&amp;u=a1aHR0cHM6Ly91c2RpY3Rpb25hcnkuY29tL2RlZmluaXRpb25zL2NpdmlsLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c7eb1b64954f8301fc7a6e0ba803d40626f6f11ae65612d6c27dd9f0919873ffJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b95cdf-b4e6-65a4-2e4a-4b3eb58664b6&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9DaXZpbF9lbmdpbmVlcmluZw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=64f7833a669579b54e7a99b1939d99e639f204d41cbf85eac9d5eb55535cfbddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b95cdf-b4e6-65a4-2e4a-4b3eb58664b6&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2Npdmls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=acacfa7a1900bf881347425d605d6f0ebe267fb7e67c0f59e30cdf2194417065JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b95cdf-b4e6-65a4-2e4a-4b3eb58664b6&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9jaXZpbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4e3972a74d10a52335c0c808da19b2700c200f0c2ac46cdbc6fa916909df46d4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b95cdf-b4e6-65a4-2e4a-4b3eb58664b6&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2Npdmls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=33801bb2e3f2d44e7430f3ac314987eb394d9dbf844ab21c3ca62fd36ac60a70JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b95cdf-b4e6-65a4-2e4a-4b3eb58664b6&amp;u=a1aHR0cHM6Ly93d3cueW91cmRpY3Rpb25hcnkuY29tL2Npdmls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c8463db898deb18a57a77eee407ddd07089cb468e123bbd3820cab0de663d148JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b95cdf-b4e6-65a4-2e4a-4b3eb58664b6&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2Npdmls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b0801ed14d0904edfbfd598ad4eea643026f35ce99dcc0b0c67952c88017282fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02b95cdf-b4e6-65a4-2e4a-4b3eb58664b6&amp;u=a1aHR0cHM6Ly93d3cueWVscC5jb20vc2VhcmNoP2ZpbmRfZGVzYz1DaXZpbCtMYXd5ZXImZmluZF9sb2M9TGFndW5hK1BhcmslMkMrVFgmbXNvY2tpZD0wMmI5NWNkZmI0ZTY2NWE0MmU0YTRiM2ViNTg2NjRiNg&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=745648f603c95c7067e7862e7427acde5901a63eb7dd09b5b464b8f2450354c2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d5d5cd-3ea9-6192-2dee-c22c3f756021&amp;u=a1aHR0cHM6Ly9zZWFyY2gueWFob28uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4f91b49658a5d84950bac9f6181ecdb89886d969e1b8ee0186a5077bf3f1b405JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d5d5cd-3ea9-6192-2dee-c22c3f756021&amp;u=a1aHR0cHM6Ly9kdWNrZHVja2dvLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=760423b9b9bb7257b7dc5986a2faf1c9781f598d5fb3782d691c95065804c4f3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d5d5cd-3ea9-6192-2dee-c22c3f756021&amp;u=a1aHR0cHM6Ly9zZWFyY2guZ29vZ2xlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=539157b18b6fb68139871c1adbda9cf84c7b038669285ae8e7699bf7a191d16cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d5d5cd-3ea9-6192-2dee-c22c3f756021&amp;u=a1aHR0cHM6Ly9pbWFnZXMuZ29vZ2xlLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9195e22c5337e27e479277a8455468d43b82ac6328257c3da7ae4bda9879c801JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d5d5cd-3ea9-6192-2dee-c22c3f756021&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS9pbnRsL2VuX3VzL3NlYXJjaC9ob3dzZWFyY2h3b3Jrcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a65a19da9fabbb00854a388f01d2a9fcfb89db56501254ca2ef6925593238890JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d5d5cd-3ea9-6192-2dee-c22c3f756021&amp;u=a1aHR0cHM6Ly93d3cuc3RhcnRwYWdlLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4b1ab60a00fa9b11a9a0a87f8eeb739967929386329314b2a0c58039499a2861JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d5d5cd-3ea9-6192-2dee-c22c3f756021&amp;u=a1aHR0cHM6Ly9hY2NvdW50cy5nb29nbGUuY29tL0ludGVyYWN0aXZlTG9naW4_c2VydmljZT1zYWZlc2VhcmNobG9jaw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=10a7b972b39297da7fa386d1e6dfc10910d49d2cc201364f6017a8e497f93914JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33e4b93e-31ec-6833-3e97-aedf30b869a7&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7e2adcd3dc0bc96d30abfd2f0aea52bedb961ffe0d1c2d81a40daa66a374772bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33e4b93e-31ec-6833-3e97-aedf30b869a7&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ2l2aWxfZW5naW5lZXJpbmc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f895ffa1d2f02ba8a9aff049d40be1d0d224c8240c84fc7e04b629a11c556089JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33e4b93e-31ec-6833-3e97-aedf30b869a7&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8592c4fdfc43030a6319f664ad874433676ff5a17645d30efac5feb375073c6aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33e4b93e-31ec-6833-3e97-aedf30b869a7&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9jaXZpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d1785402602b28bb244d71dc4f7f9b844ff7994d4553c0d5c271f3a43a50dd8eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33e4b93e-31ec-6833-3e97-aedf30b869a7&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=10d8a6238e1fb05979b961fd0f994d16335b0ac2255a43872fa25430d936ea4cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33e4b93e-31ec-6833-3e97-aedf30b869a7&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4a7017c5433c19e6e3484a5420b6f23f7efda45d9d3a37b53bfc15cec62ce990JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33e4b93e-31ec-6833-3e97-aedf30b869a7&amp;u=a1aHR0cHM6Ly93d3cuYXV0b2Rlc2suY29tL3Byb2R1Y3RzL2NpdmlsLTNkL3Byb2R1Y3QtZGV0YWlscz9tc29ja2lkPTMzZTRiOTNlMzFlYzY4MzMzZTk3YWVkZjMwYjg2OWE3&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
@@ -916,7 +910,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -950,19 +944,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="G2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -970,19 +964,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -990,19 +984,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1010,19 +1004,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1030,19 +1024,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1050,19 +1044,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1070,19 +1064,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1090,19 +1084,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1110,19 +1104,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G10" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H10" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1130,19 +1124,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1150,19 +1144,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1170,19 +1164,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G13" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H13" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1190,19 +1184,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G14" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1210,19 +1204,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G15" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H15" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1230,19 +1224,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G16" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H16" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1250,19 +1244,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G17" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H17" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1270,19 +1264,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G18" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H18" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1290,19 +1284,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G19" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H19" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1310,19 +1304,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G20" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H20" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1330,19 +1324,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1350,19 +1344,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G22" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H22" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1370,19 +1364,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G23" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H23" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1390,19 +1384,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G24" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H24" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1410,19 +1404,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G25" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H25" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1430,19 +1424,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G26" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H26" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1450,19 +1444,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G27" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H27" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1470,19 +1464,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G28" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H28" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1490,19 +1484,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G29" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H29" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1510,19 +1504,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G30" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H30" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1530,19 +1524,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G31" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H31" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1550,19 +1544,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H32" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1570,19 +1564,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G33" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H33" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1590,19 +1584,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G34" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H34" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1610,19 +1604,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G35" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H35" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1630,19 +1624,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G36" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H36" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1650,19 +1644,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C37" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G37" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H37" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1670,19 +1664,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G38" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H38" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1690,19 +1684,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G39" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H39" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1710,19 +1704,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G40" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H40" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1730,19 +1724,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C41" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G41" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H41" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1750,19 +1744,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G42" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H42" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1770,19 +1764,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C43" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G43" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H43" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1790,19 +1784,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C44" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G44" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H44" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1810,19 +1804,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C45" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G45" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H45" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1830,19 +1824,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C46" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G46" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H46" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1850,19 +1844,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C47" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G47" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H47" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1870,19 +1864,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C48" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G48" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H48" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1890,19 +1884,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C49" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G49" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H49" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1910,19 +1904,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C50" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G50" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H50" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1930,19 +1924,19 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G51" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H51" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1950,19 +1944,19 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C52" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G52" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H52" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1970,19 +1964,19 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C53" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G53" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H53" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -1990,19 +1984,19 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C54" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G54" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H54" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2010,19 +2004,19 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C55" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G55" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H55" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2030,19 +2024,19 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C56" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G56" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H56" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2050,19 +2044,19 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C57" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G57" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H57" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2070,19 +2064,19 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C58" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G58" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H58" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2090,19 +2084,19 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C59" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G59" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H59" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2110,19 +2104,19 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C60" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G60" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H60" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2130,19 +2124,19 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C61" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G61" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H61" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2150,19 +2144,19 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C62" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G62" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H62" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2170,19 +2164,19 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C63" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G63" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H63" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2190,19 +2184,19 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C64" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G64" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H64" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2210,19 +2204,19 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C65" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G65" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H65" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2230,19 +2224,19 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C66" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G66" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H66" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2250,19 +2244,19 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C67" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G67" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H67" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2270,19 +2264,19 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C68" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G68" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H68" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2290,19 +2284,19 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C69" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G69" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H69" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2310,19 +2304,19 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C70" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G70" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H70" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2330,19 +2324,19 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C71" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G71" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H71" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2350,19 +2344,19 @@
         <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C72" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G72" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H72" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2370,19 +2364,19 @@
         <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C73" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G73" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H73" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2390,19 +2384,19 @@
         <v>80</v>
       </c>
       <c r="B74" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C74" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G74" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H74" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2410,19 +2404,19 @@
         <v>81</v>
       </c>
       <c r="B75" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C75" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G75" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H75" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2430,19 +2424,19 @@
         <v>82</v>
       </c>
       <c r="B76" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C76" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G76" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H76" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2450,19 +2444,19 @@
         <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C77" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G77" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H77" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -2470,19 +2464,19 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C78" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G78" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H78" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -2490,19 +2484,19 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C79" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G79" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H79" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -2510,19 +2504,19 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C80" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G80" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H80" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -2530,19 +2524,19 @@
         <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C81" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G81" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H81" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -2550,19 +2544,19 @@
         <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C82" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G82" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H82" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -2570,19 +2564,19 @@
         <v>89</v>
       </c>
       <c r="B83" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C83" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G83" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H83" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -2590,19 +2584,19 @@
         <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C84" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G84" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H84" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -2610,19 +2604,19 @@
         <v>91</v>
       </c>
       <c r="B85" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C85" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G85" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H85" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -2630,19 +2624,19 @@
         <v>92</v>
       </c>
       <c r="B86" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C86" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G86" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H86" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -2650,39 +2644,19 @@
         <v>93</v>
       </c>
       <c r="B87" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C87" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G87" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H87" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
-      <c r="A88" t="s">
-        <v>94</v>
-      </c>
-      <c r="B88" t="s">
-        <v>95</v>
-      </c>
-      <c r="C88" t="s">
-        <v>96</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G88" t="s">
-        <v>184</v>
-      </c>
-      <c r="H88" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -2773,7 +2747,6 @@
     <hyperlink ref="F85" r:id="rId84"/>
     <hyperlink ref="F86" r:id="rId85"/>
     <hyperlink ref="F87" r:id="rId86"/>
-    <hyperlink ref="F88" r:id="rId87"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/scraped_Cape_Town_Emergency_and_Rescue.xlsx
+++ b/results/scraped_Cape_Town_Emergency_and_Rescue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="182">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -40,36 +40,36 @@
     <t>Source</t>
   </si>
   <si>
+    <t>Current Fires in Washington | WFCAFireMap</t>
+  </si>
+  <si>
+    <t>Wildfire/Smoke Map - Live Tracking</t>
+  </si>
+  <si>
+    <t>AirNowFireand Smoke Map</t>
+  </si>
+  <si>
+    <t>Fire-Wikipedia</t>
+  </si>
+  <si>
     <t>FIRE| Foundation for Individual Rights and Expression</t>
   </si>
   <si>
-    <t>Fire-Wikipedia</t>
+    <t>Live Wildfire Map: Active Fires, Smoke &amp; Alerts |FireNearby</t>
+  </si>
+  <si>
+    <t>Live Wildfire Map &amp; Tracker – Wildfires Near Me | AllFirefighter</t>
+  </si>
+  <si>
+    <t>firemap.us | see what's onfire</t>
+  </si>
+  <si>
+    <t>Current Wildfire Information - U.S. Department of the Interior</t>
   </si>
   <si>
     <t>Firefox: The fast, private browser that keeps you safe</t>
   </si>
   <si>
-    <t>AirNowFireand Smoke Map</t>
-  </si>
-  <si>
-    <t>Wildfire/Smoke Map - Live Tracking</t>
-  </si>
-  <si>
-    <t>NASA | LANCE |FIRMS</t>
-  </si>
-  <si>
-    <t>Live Wildfire Map: Active Fires, Smoke &amp; Alerts |FireNearby</t>
-  </si>
-  <si>
-    <t>Current Wildfire Information - U.S. Department of the Interior</t>
-  </si>
-  <si>
-    <t>Incidents| CALFIRE</t>
-  </si>
-  <si>
-    <t>Bladensburg VolunteerFireDepartment | Bladensburg MD -Facebook</t>
-  </si>
-  <si>
     <t>Emergency! (TV Series 1972–1979) - IMDb</t>
   </si>
   <si>
@@ -79,85 +79,85 @@
     <t>Emergency-Wikipedia</t>
   </si>
   <si>
+    <t>The 'Emergency' Cast: Looking at the Actors, Then and Now 2024</t>
+  </si>
+  <si>
+    <t>Emergency! | The Complete Series -YouTube</t>
+  </si>
+  <si>
+    <t>Emergency! (TV Series 1972–1979) - Full cast &amp; crew - IMDb</t>
+  </si>
+  <si>
     <t>EMERGENCYDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>Emergency AssistanceLanding Page</t>
-  </si>
-  <si>
-    <t>Froedtert Hospital Emergency Department, Milwaukee, Wis</t>
-  </si>
-  <si>
-    <t>EMERGENCYMEDICINE SPECIALISTS - EMS</t>
-  </si>
-  <si>
-    <t>EmergencyPreparedness and Response | CDC</t>
-  </si>
-  <si>
-    <t>EmergencyDepartments -Froedtert &amp; the Medical College of...</t>
-  </si>
-  <si>
-    <t>EMERGENCY| English meaning - Cambridge Dictionary</t>
+    <t>EmergencyManagement -Snohomish County, WA - Official Website</t>
+  </si>
+  <si>
+    <t>Emergency Services| Providence Regional Medical Center Everett ...</t>
+  </si>
+  <si>
+    <t>Emergency management| Everett, WA - Official Website</t>
   </si>
   <si>
     <t>Sea-Wikipedia</t>
   </si>
   <si>
+    <t>Seattle-Tacoma International Airport | Port of Seattle</t>
+  </si>
+  <si>
+    <t>SEA– Seattle Education Association</t>
+  </si>
+  <si>
+    <t>Sea- SimpleEnglish Wikipedia, the free encyclopedia</t>
+  </si>
+  <si>
+    <t>List of seas on Earth - Wikipedia</t>
+  </si>
+  <si>
+    <t>SeaEducation Association</t>
+  </si>
+  <si>
+    <t>Ocean vs.Sea: What’s the Difference? - Encyclopedia Britannica</t>
+  </si>
+  <si>
     <t>Sea- National Geographic Society</t>
   </si>
   <si>
-    <t>SeaEducation Association</t>
-  </si>
-  <si>
-    <t>Do you know the difference between ocean,sea, bay and gulf?</t>
-  </si>
-  <si>
-    <t>Sea- SimpleEnglish Wikipedia, the free encyclopedia</t>
-  </si>
-  <si>
-    <t>Ocean- Wikipedia</t>
-  </si>
-  <si>
-    <t>Ocean vs.Sea: What’s the Difference? - Encyclopedia Britannica</t>
+    <t>Sea| Investor Relations</t>
   </si>
   <si>
     <t>SEADefinition &amp; Meaning - Merriam-Webster</t>
   </si>
   <si>
-    <t>Sea| Investor Relations</t>
-  </si>
-  <si>
-    <t>SEA, Ltd. - Forensic Engineering Services | Structural &amp; Failure Analysis</t>
-  </si>
-  <si>
-    <t>List of mountains of New York (state) -Wikipedia</t>
-  </si>
-  <si>
     <t>Mountain-Wikipedia</t>
   </si>
   <si>
+    <t>Mountain| Definition, Characteristics, Types, &amp; Facts ...</t>
+  </si>
+  <si>
     <t>Mountains -WorldAtlas</t>
   </si>
   <si>
-    <t>AdirondackMountains| Official Adirondack Region Website</t>
-  </si>
-  <si>
-    <t>BristolMountain|New YorkSki Resort | Canandaigua,NY</t>
-  </si>
-  <si>
-    <t>MountainBikingTrailsin WesternNew York- WNYMBA</t>
-  </si>
-  <si>
-    <t>Mountain| Definition, Characteristics, Types, &amp; Facts | Britannica</t>
-  </si>
-  <si>
-    <t>New YorkMountains – USA | PeakVisor</t>
-  </si>
-  <si>
-    <t>AlleganyMountainResort at Rainbow Lake</t>
-  </si>
-  <si>
-    <t>MOUNTAINDefinition &amp; Meaning -Merriam-Webster</t>
+    <t>Whatmountainam I looking at? How to identifyWashington...</t>
+  </si>
+  <si>
+    <t>What is amountain? Here’s how they form | National Geographic</t>
+  </si>
+  <si>
+    <t>MountainPacific Bank</t>
+  </si>
+  <si>
+    <t>Mountain- Simple EnglishWikipedia, the free encyclopedia</t>
+  </si>
+  <si>
+    <t>Portal:Mountains-Wikipedia</t>
+  </si>
+  <si>
+    <t>11 BreathtakingMountainPeaks You Can See From Seattle</t>
+  </si>
+  <si>
+    <t>What is a Mountain? -WorldAtlas</t>
   </si>
   <si>
     <t>Disaster-Wikipedia</t>
@@ -172,82 +172,82 @@
     <t>Home | disasterassistance.gov</t>
   </si>
   <si>
+    <t>Disaster Information-FEMA.gov</t>
+  </si>
+  <si>
+    <t>Home |FEMA.gov</t>
+  </si>
+  <si>
+    <t>Definition:Disaster| UNDRR</t>
+  </si>
+  <si>
     <t>Naturaldisaster| Causes, Types, &amp; Facts | Britannica</t>
   </si>
   <si>
-    <t>Home |FEMA.gov</t>
-  </si>
-  <si>
-    <t>Disaster Information-FEMA.gov</t>
-  </si>
-  <si>
-    <t>Definition:Disaster| UNDRR</t>
-  </si>
-  <si>
-    <t>DISASTER| English meaning - Cambridge Dictionary</t>
+    <t>DisasterRadar: Live Natural Hazard Map &amp; Alerts</t>
   </si>
   <si>
     <t>What is adisaster? - IFRC</t>
   </si>
   <si>
-    <t>Home -Richmond'sFirstBaptist Church</t>
-  </si>
-  <si>
-    <t>FirstTee GreaterRichmond| Premier Golfing in CentralVirginia</t>
-  </si>
-  <si>
-    <t>24/7FirstAlert Weather - 12 On Your Side</t>
-  </si>
-  <si>
-    <t>PatientFirst: Urgent Care, Primary Care, and Walk-In Care</t>
-  </si>
-  <si>
-    <t>Urgent Care, Telehealth, &amp; Walk-In Clinic -Patient First</t>
-  </si>
-  <si>
-    <t>FirstBankRichmond</t>
-  </si>
-  <si>
-    <t>Online Banking, Loans, &amp; Financial Services |FirstBank ...</t>
-  </si>
-  <si>
-    <t>FirstBank. There's Power In One. Business and personal banking.</t>
-  </si>
-  <si>
-    <t>FirstNational Apartments | Apartments inRichmond,VA</t>
-  </si>
-  <si>
-    <t>FirstHome Care –VirginiaTherapeutic Foster Care Services</t>
+    <t>Best Breakfast atFirstWatchGilbert,AZ|FirstWatch</t>
+  </si>
+  <si>
+    <t>Arizona-FirstAmerican Title -GilbertSan Tan</t>
+  </si>
+  <si>
+    <t>ArizonaBanks Near Me -GilbertGateway :FirstFidelity Bank ...</t>
+  </si>
+  <si>
+    <t>First Impression Ironworks|Gilbert AZ- Facebook</t>
+  </si>
+  <si>
+    <t>Gilbertproperty management | FirstService Residential</t>
+  </si>
+  <si>
+    <t>Urgent CareinGilbert,AZ| HealthFirst Urgent Care</t>
+  </si>
+  <si>
+    <t>Gilbert AZ|FirstInternational Bank &amp; Trust - FIBT</t>
+  </si>
+  <si>
+    <t>FirstUnited Methodist Church ofGilbert|Gilbert AZ- Facebook</t>
+  </si>
+  <si>
+    <t>GilbertSecurity Doors | Iron Doors | Wrought Iron Gates ...</t>
+  </si>
+  <si>
+    <t>Security Doors Phoenix | Iron Entry Doors | Iron or Wood ...</t>
   </si>
   <si>
     <t>Ambulance- Wikipedia</t>
   </si>
   <si>
-    <t>Emergency Medical Services (EMS) -EnglewoodHealth</t>
-  </si>
-  <si>
-    <t>EnglewoodVolunteerAmbulanceCorps | EVAC</t>
-  </si>
-  <si>
-    <t>AmbulanceServices in Bergen County,New Jersey</t>
-  </si>
-  <si>
-    <t>EnglewoodVolunteerAmbulanceCorps, Inc |Englewood NJ- Facebook</t>
-  </si>
-  <si>
-    <t>AMR - EMS &amp;AmbulanceCare</t>
-  </si>
-  <si>
-    <t>HOME | BVAC | Emergency Medical Services in Bergenfield</t>
-  </si>
-  <si>
-    <t>EnglewoodVolunteerAmbulanceCorps inEnglewood,New Jersey...</t>
-  </si>
-  <si>
-    <t>AMBULANCEDefinition &amp; Meaning - Merriam-Webster</t>
-  </si>
-  <si>
-    <t>EnglewoodVolunteerAmbulanceinEnglewood,NJ- Hospital</t>
+    <t>NorthwestAmbulance- Seattle | Puget Sound Region</t>
+  </si>
+  <si>
+    <t>City OfBothellinBothell,Washington-AmbulanceService Address …</t>
+  </si>
+  <si>
+    <t>AmbulanceServices inBothell,WA- The Real Yellow Pages®</t>
+  </si>
+  <si>
+    <t>AmbulanceServices inBothell,Washington- Address, Contact</t>
+  </si>
+  <si>
+    <t>AmbulanceinBothell,WA- 2 Records - NPI Profile</t>
+  </si>
+  <si>
+    <t>Best 29AmbulanceServices inBothell,WA| superpages.com</t>
+  </si>
+  <si>
+    <t>Emergency medical services- Wikipedia</t>
+  </si>
+  <si>
+    <t>Protection-1 -AmbulanceServices -Bothell,WA</t>
+  </si>
+  <si>
+    <t>City OfBothell-Bothell,WALand TransportAmbulance</t>
   </si>
   <si>
     <t>Google</t>
@@ -259,307 +259,301 @@
     <t>YahooSearch- WebSearch</t>
   </si>
   <si>
+    <t>Google Search- A new kind of help</t>
+  </si>
+  <si>
+    <t>Yahoo</t>
+  </si>
+  <si>
+    <t>PrivateSearchEngine - BraveSearch</t>
+  </si>
+  <si>
+    <t>How toUse Bing Search Engineon Desktop or Mobile -wikiHow</t>
+  </si>
+  <si>
     <t>DuckDuckGo- Protection. Privacy. Peace of mind.</t>
   </si>
   <si>
-    <t>Google Search- A new kind of help</t>
-  </si>
-  <si>
-    <t>Google Images</t>
-  </si>
-  <si>
-    <t>Google Search- What IsGoogle SearchAnd How Does It Work</t>
-  </si>
-  <si>
-    <t>Startpage.com</t>
-  </si>
-  <si>
-    <t>GoogleSearch</t>
-  </si>
-  <si>
     <t>CIVILDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
+    <t>Civil- El Dorado County,California</t>
+  </si>
+  <si>
+    <t>CIVIL| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
     <t>Civil engineering-Wikipedia</t>
   </si>
   <si>
-    <t>CIVIL| English meaning - Cambridge Dictionary</t>
+    <t>Civil- definition ofcivilby The Free Dictionary</t>
   </si>
   <si>
     <t>Civil- Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
   </si>
   <si>
-    <t>Civil- definition ofcivilby The Free Dictionary</t>
-  </si>
-  <si>
     <t>CIVILDefinition &amp; Meaning |Dictionary.com</t>
   </si>
   <si>
-    <t>Autodesk Civil3DFeatures| What’s New inCivil3D 2027</t>
-  </si>
-  <si>
     <t>Emergency &amp; Rescue</t>
   </si>
   <si>
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e2bf621f68dca88867fc28af1a63f2e0bf27833da98c59a660dee7950a675809JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=167d9bb6-9ae1-6e09-3d4a-8c579b1d6f27&amp;u=a1aHR0cHM6Ly93d3cuZmlyZS5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d4d132124bab9379c3016d48aa2cabfd6e1f5c3d5a52240114a089906ebee731JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=167d9bb6-9ae1-6e09-3d4a-8c579b1d6f27&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRmlyZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=91f1923b06bc4e7bbf8ce07b96c457b7185282852905f148d55ed9a6a0c3eb71JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=167d9bb6-9ae1-6e09-3d4a-8c579b1d6f27&amp;u=a1aHR0cHM6Ly93d3cuZmlyZWZveC5jb20vZW4tVVMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=349469ac0b0f2ef86fc694746f8d94ea39331ee2ccd61f9988414463df08b7dcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=167d9bb6-9ae1-6e09-3d4a-8c579b1d6f27&amp;u=a1aHR0cHM6Ly9maXJlLmFpcm5vdy5nb3YvP2xhbmc9ZW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=30e9ca243aa4114cb667c03f280a58b47e63fe077e353e2bf2e93312bbdb04d6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=167d9bb6-9ae1-6e09-3d4a-8c579b1d6f27&amp;u=a1aHR0cHM6Ly93aWxkZmlyZXRyYWNrZXJzLmNvbS9mL21hcA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=75fb48e96ab8ba9aaad6790bd69a2706d35625d658e1accaafcabf5ff4a7ee7fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=167d9bb6-9ae1-6e09-3d4a-8c579b1d6f27&amp;u=a1aHR0cHM6Ly9maXJtcy5tb2RhcHMuZW9zZGlzLm5hc2EuZ292L21hcC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=354ad1022619bf329361faed027bdc0a92eb6378a58c6aca4d4cdbb530c82406JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=167d9bb6-9ae1-6e09-3d4a-8c579b1d6f27&amp;u=a1aHR0cHM6Ly9maXJlbmVhcmJ5LmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0fc4d731ecdaae136f01cf668434effe6ba3a5e2dd6ba73fbdb1d86a9c7cc566JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=167d9bb6-9ae1-6e09-3d4a-8c579b1d6f27&amp;u=a1aHR0cHM6Ly93d3cuZG9pLmdvdi93aWxkbGFuZGZpcmVzZXJ2aWNlL2N1cnJlbnQtd2lsZGZpcmUtaW5mb3JtYXRpb24&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=78d6cfa3fb9eac53982b559489bed3bcfd49d05635dbaa3feb565b8e89365f0cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=167d9bb6-9ae1-6e09-3d4a-8c579b1d6f27&amp;u=a1aHR0cHM6Ly93d3cuZmlyZS5jYS5nb3YvaW5jaWRlbnRzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=adbd2098e25979b11c1e5f2905eb2c180d045b74a356f9db44bba7e6dc438f38JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=167d9bb6-9ae1-6e09-3d4a-8c579b1d6f27&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL2JsYWRlbnNidXJnY28uOS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8e7f85b329a9cf5b4016fbf3a388499278a35510e0408e03911ae60fb5f60308JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136922df-fae3-66cb-355a-353efbe0672a&amp;u=a1aHR0cHM6Ly9tLmltZGIuY29tL3RpdGxlL3R0MDA2ODA2Ny8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=332dfeaa36a275028989f4267ee26ff713d8de9205c749a1acc1abffa6d6fbedJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136922df-fae3-66cb-355a-353efbe0672a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9FbWVyZ2VuY3kh&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b2a443d4f41542819f59dc08ab817eed1a9fde8ea19b50ed57b5a68cf54e3059JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136922df-fae3-66cb-355a-353efbe0672a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9FbWVyZ2VuY3k&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e89dbb07dd7b5e22a0be48e9cb2efec63e9efec0ba0f4df6ba99e7862c98f7f1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136922df-fae3-66cb-355a-353efbe0672a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VtZXJnZW5jeQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4e4407ec7e6a45aa828152b62737529f2512e94ef834a6d06ba5a9082a28f121JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136922df-fae3-66cb-355a-353efbe0672a&amp;u=a1aHR0cHM6Ly9kY2Yud2lzY29uc2luLmdvdi9lYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c883804f7dfa88731214e0298c4262763ccec10c17fff3880e99f880bae31d46JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136922df-fae3-66cb-355a-353efbe0672a&amp;u=a1aHR0cHM6Ly93d3cuZnJvZWR0ZXJ0LmNvbS9sb2NhdGlvbnMvZW1lcmdlbmN5LWRlcGFydG1lbnQvZnJvZWR0ZXJ0LWhvc3BpdGFsLWVtZXJnZW5jeS1kZXBhcnRtZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ee06ab99b58ad20071b22c9f1b6391f41304151c793ba44956655041d28d26a1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136922df-fae3-66cb-355a-353efbe0672a&amp;u=a1aHR0cHM6Ly9lbXMtd2kuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fdf787dba895303a210d2c1772decf39020d520ddaa874c67889125b00c53dbfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136922df-fae3-66cb-355a-353efbe0672a&amp;u=a1aHR0cHM6Ly93d3cuY2RjLmdvdi9lbWVyZ2VuY3kvaW5kZXguaHRtbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=72cf35c0d5a61f0a0545b75f2e39cd2ad2253915405f037451c33cef582cd26fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136922df-fae3-66cb-355a-353efbe0672a&amp;u=a1aHR0cHM6Ly93d3cuZnJvZWR0ZXJ0LmNvbS9lbWVyZ2VuY3k&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=832a10ca3a9e9664fa7f81821f146284e9c31e7ad172752492f5fa1d5ecfa047JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=136922df-fae3-66cb-355a-353efbe0672a&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2VtZXJnZW5jeQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ae0327d8f0b1e84f6224b267ff0cc5b7114a3cae92efe5c96bfd929cce3854c0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39e36cca-6673-6727-3e75-7b2b67a66602&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU2Vh&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=71ce15c8695aa776b3a55578e3a8c4a44d9bece286d20d47db506c0d64c72d9dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39e36cca-6673-6727-3e75-7b2b67a66602&amp;u=a1aHR0cHM6Ly9lZHVjYXRpb24ubmF0aW9uYWxnZW9ncmFwaGljLm9yZy9yZXNvdXJjZS9zZWEv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47de5426b6d4e682385230f6ff0b627f0977db115373b5f09eb6fafa2cff06caJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39e36cca-6673-6727-3e75-7b2b67a66602&amp;u=a1aHR0cHM6Ly9zZWEuZWR1Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3e1756b701731d032d4a94ec9ab66e5b4b16af60dffe132616874f9b963a8883JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39e36cca-6673-6727-3e75-7b2b67a66602&amp;u=a1aHR0cHM6Ly90aW1lc29maW5kaWEuaW5kaWF0aW1lcy5jb20vdHJhdmVsL2Rlc3RpbmF0aW9ucy9kby15b3Uta25vdy10aGUtZGlmZmVyZW5jZS1iZXR3ZWVuLW9jZWFuLXNlYS1iYXktYW5kLWd1bGYvYXJ0aWNsZXNob3cvMTEwOTY1MTM0LmNtcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ffa67f86c4855cb52bc022ba714b09ed7d0534f332813a2e549f242b2abc81f9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39e36cca-6673-6727-3e75-7b2b67a66602&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL1NlYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d254bab894241fe78e5f4dca4bcfdeef2438ae902ce4314e088ef9a77ebab42dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39e36cca-6673-6727-3e75-7b2b67a66602&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvT2NlYW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7217eaf55ea36441fe3a8c6576e68d802965885dbe31d914b47468269abd71f7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39e36cca-6673-6727-3e75-7b2b67a66602&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9PY2Vhbi12cy1TZWEtV2hhdHMtdGhlLURpZmZlcmVuY2U&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f68f5aa7d6d22110a9b2ea1108eea2c9109ce262f0e5b01d418fbf5e5316c332JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39e36cca-6673-6727-3e75-7b2b67a66602&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NlYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7d059fe491e75c65afa3fe98157310bd2b91c27a2e1b3bf02989703de2c56855JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39e36cca-6673-6727-3e75-7b2b67a66602&amp;u=a1aHR0cHM6Ly93d3cuc2VhLmNvbS9pbnZlc3Rvci9ob21l&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8a2062488a1520cf009608768ce1b66422cf41b85905bd026b8726c0732ba7eeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=39e36cca-6673-6727-3e75-7b2b67a66602&amp;u=a1aHR0cHM6Ly9zZWFsaW1pdGVkLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7b9aa9a2d2a0d295efb72ae79bacac0d2a8a657a6eed682313d0da98922b1831JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15fbc2e6-0bed-6059-26ba-d5070ae261bf&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTGlzdF9vZl9tb3VudGFpbnNfb2ZfTmV3X1lvcmtfKHN0YXRlKQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9ae56de8cc39a84a45ba97d0bcd6b857966e1c76ea4bcf97b78a8e1b82220aceJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15fbc2e6-0bed-6059-26ba-d5070ae261bf&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTW91bnRhaW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8af9e9a6fb14ec68533b4f58c8c0a0e4798b753a5819d46cd2c1b187a9b545a4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15fbc2e6-0bed-6059-26ba-d5070ae261bf&amp;u=a1aHR0cHM6Ly93d3cud29ybGRhdGxhcy5jb20vbW91bnRhaW5zLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b92f180bd2511c1fdba974a134fe23ce500bd9c23f848470f354ea6463c81d61JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15fbc2e6-0bed-6059-26ba-d5070ae261bf&amp;u=a1aHR0cHM6Ly92aXNpdGFkaXJvbmRhY2tzLmNvbS9hYm91dC9tb3VudGFpbnM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c0e2744fa0f1221076036740c76cd54de1fb69c097a48abc0e8a7b325a3eb5aaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15fbc2e6-0bed-6059-26ba-d5070ae261bf&amp;u=a1aHR0cHM6Ly93d3cuYnJpc3RvbG1vdW50YWluLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=40b2c815458a8c127656c69940b5963215ec80d678c235c28dcbc27b2114174dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15fbc2e6-0bed-6059-26ba-d5070ae261bf&amp;u=a1aHR0cHM6Ly93bnltYmEub3JnL3RyYWlscy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d752b039de7b5593249ce39196e2c82e06ecccc57c4b4dd2059d1ddc2ead0ce0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15fbc2e6-0bed-6059-26ba-d5070ae261bf&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9tb3VudGFpbi1sYW5kZm9ybQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d25b24c93b4f689c530c459349e9409eb32240775caadfb25816a19a8a30af02JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15fbc2e6-0bed-6059-26ba-d5070ae261bf&amp;u=a1aHR0cHM6Ly9wZWFrdmlzb3IuY29tL2FkbS9uZXcteW9yay5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=75c3acb20c48166015a1d68847f5f04d66d167ba70e9455d4695142ac4c307bcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15fbc2e6-0bed-6059-26ba-d5070ae261bf&amp;u=a1aHR0cHM6Ly9hbGxlZ2FueW1vdW50YWlucmVzb3J0LmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c0af50a20ba840b42a6975390a6618967a8fd55c0f1cfc22463e16d13d93959fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15fbc2e6-0bed-6059-26ba-d5070ae261bf&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L21vdW50YWlu&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c9460fc61b9ff042039422c532c5dd4fdd0e8849b93cc5ff227f7db68df25c91JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15d8aa5f-1e08-62ee-24ae-bdbe1f0f63fa&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRGlzYXN0ZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bd71144f5897d1b042160b6ba21705062ed020f3bf9d4b70db4b7c6ec2a14589JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15d8aa5f-1e08-62ee-24ae-bdbe1f0f63fa&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9kaXNhc3Rlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=90a831bd6d402572bf37cfac2d6a67681103a286a143182c71832eb4f3fcd226JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15d8aa5f-1e08-62ee-24ae-bdbe1f0f63fa&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Rpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d772a3224432d96d1bcab6ab048c5f3463972ed4a5a6f5cdcb1a2d2b98db9cc4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15d8aa5f-1e08-62ee-24ae-bdbe1f0f63fa&amp;u=a1aHR0cHM6Ly93d3cuZGlzYXN0ZXJhc3Npc3RhbmNlLmdvdi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87f9bab060669c4dee8aa04da01e31c0d8b92e1ab36db32b25f4a8548ed3e4b0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15d8aa5f-1e08-62ee-24ae-bdbe1f0f63fa&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9uYXR1cmFsLWRpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6a19e389917f67701e1705fdb39a5e4cda5e900292748a3e965050fdda59ee25JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15d8aa5f-1e08-62ee-24ae-bdbe1f0f63fa&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2b767970510bb6fcf97901be4424dd167649be0ce3c80633e3b3a1a5ac372680JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15d8aa5f-1e08-62ee-24ae-bdbe1f0f63fa&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3YvZGlzYXN0ZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=95e7cfd9f6a1ec7a2bd65101d9cc58f7160bdd8c5c7f3925e6a6376a082d7bc1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15d8aa5f-1e08-62ee-24ae-bdbe1f0f63fa&amp;u=a1aHR0cHM6Ly93d3cudW5kcnIub3JnL3Rlcm1pbm9sb2d5L2Rpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bb741f654451b8e8f1216036d58973f9c36d130f228bb71435dcc9539f5411dcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15d8aa5f-1e08-62ee-24ae-bdbe1f0f63fa&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Rpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=722b61307500f864caddfa681b742cf57653f916169c9dfae93e236fdba30433JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15d8aa5f-1e08-62ee-24ae-bdbe1f0f63fa&amp;u=a1aHR0cHM6Ly93d3cuaWZyYy5vcmcvb3VyLXdvcmsvZGlzYXN0ZXJzLWNsaW1hdGUtYW5kLWNyaXNlcy93aGF0LWRpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d9a4c612cb9a74d6abb5d985924f28e84da6e2600999cf6f3c052390077e1c6aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=220731dc-0951-632e-3351-263d082362da&amp;u=a1aHR0cHM6Ly9mYmNyaWNobW9uZC5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bc90f192d9b1289892f51846125252be28e7d9437257847e98225fd03d2577c0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=220731dc-0951-632e-3351-263d082362da&amp;u=a1aHR0cHM6Ly9wbGF5Z29sZnJ2YS5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=300492377b8a8765cd41ab346306fd49d33faa197c807d1b2f544fc15cd711ecJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=220731dc-0951-632e-3351-263d082362da&amp;u=a1aHR0cHM6Ly93d3cuMTJvbnlvdXJzaWRlLmNvbS93ZWF0aGVyLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b33276277f94ad1fc4551fabf9b983921ca1f1bc87a3d7aff503f70588b36052JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=220731dc-0951-632e-3351-263d082362da&amp;u=a1aHR0cHM6Ly93d3cucGF0aWVudGZpcnN0LmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3fe8a621de1804fc2967ba8dbacac087221e85e81b70ed3ccdd917af464adccdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=220731dc-0951-632e-3351-263d082362da&amp;u=a1aHR0cHM6Ly93d3cucGF0aWVudGZpcnN0LmNvbS9sb2NhdGlvbnMvcmljaG1vbmQvbWVjaGFuaWNzdmlsbGU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=00c36d9eb316df98726b1e99d887303c79e22cbf205f5880ef3c22033767c3aaJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=220731dc-0951-632e-3351-263d082362da&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RiYW5rcmljaG1vbmQuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5be2d0484e32a4d40859878524c00fca7f7d5a226044084349a9fa0de020a755JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=220731dc-0951-632e-3351-263d082362da&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RiYW5rLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=444afbcffb892990a40458f36fcb1c4d90f5b6101dbbb5c762fcaad0930e5bebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=220731dc-0951-632e-3351-263d082362da&amp;u=a1aHR0cHM6Ly93d3cuZmJ2aXJnaW5pYS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=daa1e6e3e6cccb00eb294e5702387a60ae4fa8a1c9ec02543da44eb87bdc2a2aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=220731dc-0951-632e-3351-263d082362da&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RuYXRpb25hbGFwdHMuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7253a2c204282956f6f55ff3ebf19339e89ac6634cd6339cfe5492c7094a01b6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=220731dc-0951-632e-3351-263d082362da&amp;u=a1aHR0cHM6Ly9maXJzdGhvbWVjYXJlLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=64460f61cc523fa7ae3845366808fe499f84a3d91082b56d0c74af4bd9a6868bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=181814b7-4671-69dd-2d1f-03564759688b&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQW1idWxhbmNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9fb8ebb8c47c7a444ade1380f44369db3b251ed69618c4cd2607cd91ab843c40JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=181814b7-4671-69dd-2d1f-03564759688b&amp;u=a1aHR0cHM6Ly93d3cuZW5nbGV3b29kaGVhbHRoLm9yZy9zZXJ2aWNlL2VtZXJnZW5jeS1tZWRpY2FsLXNlcnZpY2VzLWVtcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6191370be3d56d2bf5efe70e89e31ab13ee9823cdd4bb8359d32547549d07c3cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=181814b7-4671-69dd-2d1f-03564759688b&amp;u=a1aHR0cHM6Ly93d3cuZW5nbGV3b29kdmFjLm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4993b9aff0944ba0f052a049c376594d7d20d36446c7b00ccf09cbe89d28e9daJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=181814b7-4671-69dd-2d1f-03564759688b&amp;u=a1aHR0cHM6Ly93d3cubG9jYWxvZmZpY2VzLm9yZy9hbWJ1bGFuY2UvbmV3LWplcnNleS9iZXJnZW4tY291bnR5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b316bfce3f5ee50e6f459d36f6dd222bc2d2c7c31eca68672a54b5492092feffJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=181814b7-4671-69dd-2d1f-03564759688b&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL3Blb3BsZS9FbmdsZXdvb2QtVm9sdW50ZWVyLUFtYnVsYW5jZS1Db3Jwcy1JbmMvMTAwMDU3Mzg5OTIyNTY3Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e0d2881ce58413e585db2ded3c97170a80f512b191815708b29f7b8f9fdada2bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=181814b7-4671-69dd-2d1f-03564759688b&amp;u=a1aHR0cHM6Ly93d3cuYW1yLm5ldC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0af727b3bace9e45b98534301dbdb5a10692c6b242cef0d43a02ab444f3ee855JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=181814b7-4671-69dd-2d1f-03564759688b&amp;u=a1aHR0cHM6Ly93d3cuYmVyZ2VuZmllbGRhbWJ1bGFuY2Uub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5f242d393cf0f670836805bfd1f7aa45bd6184c522dba8477166ebf120788bc1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=181814b7-4671-69dd-2d1f-03564759688b&amp;u=a1aHR0cHM6Ly9ucGluby5jb20vYW1idWxhbmNlLXNlcnZpY2UvMTM5NjAwOTExNC1lbmdsZXdvb2Qtdm9sdW50ZWVyLWFtYnVsYW5jZS1jb3Jwcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3146a2ae722eb0e513a2bd2cc3e7961482005d69d99b09bb82836fcf1fe68c28JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=181814b7-4671-69dd-2d1f-03564759688b&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FtYnVsYW5jZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f45fa3a083019fc11248eec94c2f674f2c44bd0e253a5c05f88dae7e98fc2302JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=181814b7-4671-69dd-2d1f-03564759688b&amp;u=a1aHR0cHM6Ly9ob3NwaXRhbC5ob3Vyc2d1aWRlLmNvbS9maW5kLWNhcmUvYW1idWxhbmNlLXNlcnZpY2UvZW5nbGV3b29kLXZvbHVudGVlci1hbWJ1bGFuY2UtODkyODEv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f9829403ba5ea4573f7c2f8d4241751b80aafc5faa0e9a82e4c22e5328f5f027JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d5d5cd-3ea9-6192-2dee-c22c3f756021&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS94aHRtbC9zZWFyY2g&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9d313f008831e6d73bbaea4125d1e85288f0753efec2323a657fc4ab65ac4e12JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1564ea5b-4224-6fc5-086a-fdba43336e51&amp;u=a1aHR0cHM6Ly93ZmNhLmNvbS9maXJlLW1hcC93YXNoaW5ndG9u&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=17fdb0b0ac550a68dac7fd827c6e404d2f19750b6c76460a97533eea6012c043JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1564ea5b-4224-6fc5-086a-fdba43336e51&amp;u=a1aHR0cHM6Ly93aWxkZmlyZXRyYWNrZXJzLmNvbS9mL21hcA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=526f5790389f4ce57a8af16edae9e26e4102ba132842075aa6ea2ea693daedb8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1564ea5b-4224-6fc5-086a-fdba43336e51&amp;u=a1aHR0cHM6Ly9maXJlLmFpcm5vdy5nb3YvP2xhbmc9ZW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d9d9f6afb1a9e770d9aab5c322884431d21ec8c5e6ea9d52a2938f954fc5e10eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1564ea5b-4224-6fc5-086a-fdba43336e51&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GaXJl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1dbd2a3ecbfdc4649abb29551e0653df5a9520b63557aeb9fbd4922562ca7185JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1564ea5b-4224-6fc5-086a-fdba43336e51&amp;u=a1aHR0cHM6Ly93d3cuZmlyZS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1fd91d3d6442d5b526c69e3adb6102ffe625a099e93ca2b0c875064bb4496cd2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1564ea5b-4224-6fc5-086a-fdba43336e51&amp;u=a1aHR0cHM6Ly9maXJlbmVhcmJ5LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2b84007603956ca754fb31b531d32d6400ab6782a69f752376ce728ff752ccc4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1564ea5b-4224-6fc5-086a-fdba43336e51&amp;u=a1aHR0cHM6Ly9hbGxmaXJlZmlnaHRlci5jb20vd2lsZGZpcmVzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=33a698ffb0a12a2fa5f64763c414f0d244457d606cca129aae46602002915699JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1564ea5b-4224-6fc5-086a-fdba43336e51&amp;u=a1aHR0cHM6Ly9maXJlbWFwLnVzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b89d5aae8eaf5444012e55918c7de543840bc91152ae6422663fd75765738c0aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1564ea5b-4224-6fc5-086a-fdba43336e51&amp;u=a1aHR0cHM6Ly93d3cuZG9pLmdvdi93aWxkbGFuZGZpcmVzZXJ2aWNlL2N1cnJlbnQtd2lsZGZpcmUtaW5mb3JtYXRpb24&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11ba83dee0c66fe1dc8a5ac5748d66a1b0b02ac8b6a8bc2c225fca79585c0cc4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1564ea5b-4224-6fc5-086a-fdba43336e51&amp;u=a1aHR0cHM6Ly93d3cuZmlyZWZveC5jb20vZW4tVVMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5ae4c62b1c78332164df72219a20426e44316500dc3c30702c98533e0f126030JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=082b35d8-8318-6a87-16a2-223982656b6d&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQwMDY4MDY3Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=815a0842a93a08922052d86302ee5ceb881a6746eba5598a4337b2d3b9b33114JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=082b35d8-8318-6a87-16a2-223982656b6d&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5IQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e6620ac9c7a902506197a71aaa2466d801613eead3ffc98e6e8987424da833d5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=082b35d8-8318-6a87-16a2-223982656b6d&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f62839c62174f78602a8ac5e30f65e5a9cd1447165efd6a74c44030427ef660dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=082b35d8-8318-6a87-16a2-223982656b6d&amp;u=a1aHR0cHM6Ly9kb3lvdXJlbWVtYmVyLmNvbS8xNTg1NjEvZW1lcmdlbmN5LWNhc3QtdGhlbi1ub3c&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=44e559761906ac49fe767b859512ca1c9275c2ba33236150e345e2ea26b4f6a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=082b35d8-8318-6a87-16a2-223982656b6d&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1sQnJSQTVSQ1lUVQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=133c258b04d8bbf9a7ea08d1b17c8608f572911cc11d0520cfa96a733386040bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=082b35d8-8318-6a87-16a2-223982656b6d&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQwMDY4MDY3L2Z1bGxjcmVkaXRzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=16700a6ee12b16d3540e05b9d0a343133b5505771e809222cc0040b6b926244eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=082b35d8-8318-6a87-16a2-223982656b6d&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VtZXJnZW5jeQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e491d0afc9ebfb4d409cb2ad37d8eee261e82f18f107488fb7b0e819d56c4c43JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=082b35d8-8318-6a87-16a2-223982656b6d&amp;u=a1aHR0cHM6Ly9zbm9ob21pc2hjb3VudHl3YS5nb3YvMTgwL0VtZXJnZW5jeS1NYW5hZ2VtZW50&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be9e90d91c332427bcecd155cbd688c646356e62ed54a919894a3c5c8cf86477JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=082b35d8-8318-6a87-16a2-223982656b6d&amp;u=a1aHR0cHM6Ly93d3cucHJvdmlkZW5jZS5vcmcvbG9jYXRpb25zL3dhL3Byb3ZpZGVuY2UtcmVnaW9uYWwtbWVkaWNhbC1jZW50ZXItZXZlcmV0dC9lbWVyZ2VuY3ktc2VydmljZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cc6f0e36245a5468df0275bc1d732c5db4130304a6448b62679452c56604e36fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=082b35d8-8318-6a87-16a2-223982656b6d&amp;u=a1aHR0cHM6Ly93d3cuZXZlcmV0dHdhLmdvdi8yNDEvRW1lcmdlbmN5LU1hbmFnZW1lbnQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c9e54d21deacdf514687b7b58f94b5380697ba2f533b634779f51428516e5b1bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a440da7-7ac0-62cf-04b8-1a467b64639a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9TZWE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f3c5134158cfe33477fbb5c17fbbd88b96640203d7da8b0272aa7ba64c2a29b8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a440da7-7ac0-62cf-04b8-1a467b64639a&amp;u=a1aHR0cHM6Ly93d3cucG9ydHNlYXR0bGUub3JnL3NlYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=41cac52f2e04670f224fe0af52f12af1e0c79912e794468fbb2c88e5b8a9bc5bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a440da7-7ac0-62cf-04b8-1a467b64639a&amp;u=a1aHR0cHM6Ly9zZWF0dGxld2VhLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e6c5f8c7a61dc52b459a1e03dd761820b1afffa3c6d1062aa5d20fd524d4914aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a440da7-7ac0-62cf-04b8-1a467b64639a&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvU2Vh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=28c4ac7fe3f7fac53a376be8360135a2701d9afd76782e181756722ad2bfe4d4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a440da7-7ac0-62cf-04b8-1a467b64639a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9MaXN0X29mX3NlYXNfb25fRWFydGg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7f85c5a6c2c50d331f4769ded82ca6ca8a2f6aa9df824230f5b0cfccfcda5502JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a440da7-7ac0-62cf-04b8-1a467b64639a&amp;u=a1aHR0cHM6Ly9zZWEuZWR1Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=453e236096c6cc98696e11f42b4676cb81ce9d4305e7d76da2521c2548c90cdcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a440da7-7ac0-62cf-04b8-1a467b64639a&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9PY2Vhbi12cy1TZWEtV2hhdHMtdGhlLURpZmZlcmVuY2U&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=716a7e3b04288b8041cc07eec82bd3e7409f2e497b98a0dafe7df8f14e490863JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a440da7-7ac0-62cf-04b8-1a467b64639a&amp;u=a1aHR0cHM6Ly9lZHVjYXRpb24ubmF0aW9uYWxnZW9ncmFwaGljLm9yZy9yZXNvdXJjZS9zZWEv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=167d28c1666df1e3fa10b204877ca6922b001f6d3893b1af93b8d6efec2c0c00JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a440da7-7ac0-62cf-04b8-1a467b64639a&amp;u=a1aHR0cHM6Ly93d3cuc2VhLmNvbS9pbnZlc3Rvci9ob21l&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2e98206d9ecc118be91cc7e2f9ed47d93fd7978d44aa574d1416fced5aa8a0aeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a440da7-7ac0-62cf-04b8-1a467b64639a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NlYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4b5a595f466c06a7cde053318f2c58419c616ff09f6ddac852d545e94542f216JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311f3b12-12fc-603c-091c-2cf31356611a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Nb3VudGFpbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3298b5f91925c4ed5679b00eaf9de35aaf6196fc6226babdf10193ac4de356a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311f3b12-12fc-603c-091c-2cf31356611a&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9tb3VudGFpbi1sYW5kZm9ybQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=49459bc99df41eacfb5a38bd8005b5bb1ec31fc144c045d6ca6d1f20598d1d3aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311f3b12-12fc-603c-091c-2cf31356611a&amp;u=a1aHR0cHM6Ly93d3cud29ybGRhdGxhcy5jb20vbW91bnRhaW5zLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c1876706c0d3e0db81ee656245a105f51f9ae109a8abeb20f739b0a9d346275eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311f3b12-12fc-603c-091c-2cf31356611a&amp;u=a1aHR0cHM6Ly93d3cua2luZzUuY29tL2FydGljbGUvd2VhdGhlci9tb3VudGFpbi1yZWNyZWF0aW9uL2V2ZXJ5dGhpbmctbmVlZC1rbm93LXdhc2hpbmd0b25zLW1vdW50YWlucy8yODEtYzcyZTEzMmItMGVhYy00MDliLWI0YzctOTkwZTZhODhhYWQ3&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1e6915cbac057aa3723e944ebe1866a8b3c552eb60a7111bb0f8d670e0f617ccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311f3b12-12fc-603c-091c-2cf31356611a&amp;u=a1aHR0cHM6Ly93d3cubmF0aW9uYWxnZW9ncmFwaGljLmNvbS9zY2llbmNlL2FydGljbGUvbW91bnRhaW5z&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fd2c80c2170dd1ed9b6499f87f643deedc7bb8dd5fdfb0004f6f3d3b21ec04deJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311f3b12-12fc-603c-091c-2cf31356611a&amp;u=a1aHR0cHM6Ly9tcC5iYW5rLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7b05aa223af32e91ae9244f58c4f86a2d9e2eac77b6eec5d33d94abba3baf73cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311f3b12-12fc-603c-091c-2cf31356611a&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvTW91bnRhaW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef5b457e7ed7361c559ce9d6b3a7b5ab89a85ed39be2a0eb39c6619b2ffde634JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311f3b12-12fc-603c-091c-2cf31356611a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Qb3J0YWw6TW91bnRhaW5z&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=842925689c32d551860ff543f098f272668e99e18267b0b714ac54c5ac23ceb6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311f3b12-12fc-603c-091c-2cf31356611a&amp;u=a1aHR0cHM6Ly9zZWF0dGxldHJhdmVsLmNvbS93aGF0LW1vdW50YWlucy1jYW4teW91LXNlZS1mcm9tLXNlYXR0bGUtMTEtYnJlYXRodGFraW5nLW1vdW50YWluLXBlYWtzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=89cbb26648959f4ba20a2c651d73a90e7ebbd16707e6d0326ec13b80a8ae8eedJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311f3b12-12fc-603c-091c-2cf31356611a&amp;u=a1aHR0cHM6Ly93d3cud29ybGRhdGxhcy5jb20vYXJ0aWNsZXMvd2hhdC1pcy1hLW1vdW50YWluLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1de33e7efc0af0d1735f8674ec8a1cd034c54c5b11a1a5f56f132b4c0a53fdddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4ee86c-edd6-65a9-1ca0-ff8dec2f6419&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRGlzYXN0ZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6ba32380a2f56101a5c369d2903261cc825e1edafab23d0e44664b24871666b0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4ee86c-edd6-65a9-1ca0-ff8dec2f6419&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9kaXNhc3Rlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0af15a7b97349ca2fd07fd7e932b4aef3b03bd6240502a5b8273dce6d4e07f96JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4ee86c-edd6-65a9-1ca0-ff8dec2f6419&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Rpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f29c2536a8ce0e91f7bbac88d4abf6d6f51765e80c4d6311e07a770b95c7eaf4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4ee86c-edd6-65a9-1ca0-ff8dec2f6419&amp;u=a1aHR0cHM6Ly93d3cuZGlzYXN0ZXJhc3Npc3RhbmNlLmdvdi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0de35970e119c59dbe5c707b8ae1c8a135254447be5ade78266fa8662f3704edJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4ee86c-edd6-65a9-1ca0-ff8dec2f6419&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3YvZGlzYXN0ZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1e2a9c75c79e0f26ba9c7f9d0da82e887cd1a943c1f1937dd8afe233a8f51721JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4ee86c-edd6-65a9-1ca0-ff8dec2f6419&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6a94249ce826045868592d14e278acc8ddfce7c94a19f0f935fee2f5c4c2e9f7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4ee86c-edd6-65a9-1ca0-ff8dec2f6419&amp;u=a1aHR0cHM6Ly93d3cudW5kcnIub3JnL3Rlcm1pbm9sb2d5L2Rpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=005ef0024502225404d35af8d78e55c2a40866af9dcf3aeb4821a30846824137JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4ee86c-edd6-65a9-1ca0-ff8dec2f6419&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9uYXR1cmFsLWRpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=228352c4a6c28c84333a7d7fbf3a2860c0617bec88b19276598447e6c308b706JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4ee86c-edd6-65a9-1ca0-ff8dec2f6419&amp;u=a1aHR0cHM6Ly93d3cuZGlzYXN0ZXJyYWRhci5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=21bcedb46b8ecfd335bffaed528afb92d4e430d761712755c04ce7c7a216601bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4ee86c-edd6-65a9-1ca0-ff8dec2f6419&amp;u=a1aHR0cHM6Ly93d3cuaWZyYy5vcmcvb3VyLXdvcmsvZGlzYXN0ZXJzLWNsaW1hdGUtYW5kLWNyaXNlcy93aGF0LWRpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a89e31cf6af9e631f270b2e5dacd3d8093b7414d5f040aafbbdc73805b915d1aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3601d4cc-0efb-6c30-1978-c32d0f5c6df5&amp;u=a1aHR0cHM6Ly9maXJzdHdhdGNoLmNvbS9sb2NhdGlvbnMvZ2lsYmVydC1hbmQtZ2VybWFubg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a0c47d47641154f83440612fd6abdd9d7a490e7292a058b6c036a4f69e4665e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3601d4cc-0efb-6c30-1978-c32d0f5c6df5&amp;u=a1aHR0cHM6Ly9sb2NhbC5maXJzdGFtLmNvbS9hei9vZmZpY2VzL2dpbGJlcnQtc2FuLXRhbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=adfffd07f127c795d3428a22e2f5eb752911866c80dd0b818f99b33917182afcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3601d4cc-0efb-6c30-1978-c32d0f5c6df5&amp;u=a1aHR0cHM6Ly93d3cuZmZiLmNvbS9sb2NhdGlvbnMvYXJpem9uYS9naWxiZXJ0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dca2d087b5db39d95dd61aa8b22742ffa8150ea6a4691d4c52e08fd419289126JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3601d4cc-0efb-6c30-1978-c32d0f5c6df5&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL2ZpcnN0aW1wcmVzc2lvbmlyb253b3Jrcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c0b0b82e19f6a84a526185973b33456b860428d185a314a868720a52f38b5d0fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3601d4cc-0efb-6c30-1978-c32d0f5c6df5&amp;u=a1aHR0cHM6Ly93d3cuZnNyZXNpZGVudGlhbC5jb20vYXJpem9uYS9vZmZpY2VzL2dpbGJlcnQtb2ZmaWNlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c2e96c2e9219462b85a618598bc0ed008afc0bf2b90659d5365e990712976b5fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3601d4cc-0efb-6c30-1978-c32d0f5c6df5&amp;u=a1aHR0cDovL2hlYWx0aGZpcnN0dXJnZW50Y2FyZS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=495a3af175cd2c77024818740d09f19e541b36ac3ee7a456ba03a36f74ced453JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3601d4cc-0efb-6c30-1978-c32d0f5c6df5&amp;u=a1aHR0cHM6Ly93d3cuZmlidC5jb20vbG9jYXRpb25zLWhvdXJzL2FyaXpvbmEvZ2lsYmVydC1hei8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0bd6cf50cbd1c29c94cebcab5336c5592f56a29c0cc353ee8e45b46f7983c40aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3601d4cc-0efb-6c30-1978-c32d0f5c6df5&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL0ZVTUNvZmdpbGJlcnQv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed56b2f60b243a48c019b460b3401d20570b9fefa7ab1259a369071bd55202c6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3601d4cc-0efb-6c30-1978-c32d0f5c6df5&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RpbXByZXNzaW9uc2VjdXJpdHlkb29ycy5jb20vbG9jYXRpb25zL2dpbGJlcnQtaXJvbi1zaG93cm9vbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6752f735e4bc88632c4a765f983b5232e129ae8c84c607f3ac9bad7eb26436d1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3601d4cc-0efb-6c30-1978-c32d0f5c6df5&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RpbXByZXNzaW9uc2VjdXJpdHlkb29ycy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fa648046fe35fc9bdd0fb3ab6be609de4e32fd8179103c22116e1a4440a0ce95JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31741729-fc0d-6492-21d3-00c8fdfa651e&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQW1idWxhbmNl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=415ae39daa943bfa2f907e0335afcd7ce3cbaf6b92df089e6b0d7bdc748c2b6cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31741729-fc0d-6492-21d3-00c8fdfa651e&amp;u=a1aHR0cHM6Ly93d3cubndhbWIudXMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bc2af6b5df51acefc734bc623c3bea879a745315f52dbba9a5b71dc2c41f49dcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31741729-fc0d-6492-21d3-00c8fdfa651e&amp;u=a1aHR0cHM6Ly9ucGluby5jb20vYW1idWxhbmNlLXNlcnZpY2UvMTE4NDcxNTQ3Ni1jaXR5LW9mLWJvdGhlbGwv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8ae5700e699aba0813992a8602b673bc600bcc3b1a3d8ee3ff93167760221c94JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31741729-fc0d-6492-21d3-00c8fdfa651e&amp;u=a1aHR0cHM6Ly93d3cueWVsbG93cGFnZXMuY29tL2JvdGhlbGwtd2EvYW1idWxhbmNlLXNlcnZpY2Vz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3e8ca949f985443f09235c49227a749ba8e3c54f0e8c7b6d011a47e6e608769dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31741729-fc0d-6492-21d3-00c8fdfa651e&amp;u=a1aHR0cHM6Ly9ucGluby5jb20vYW1idWxhbmNlLXNlcnZpY2VzL3dhL2JvdGhlbGwv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ae214ccf1dee624a16c8257d66c834af5e0a834df6fceeb156351ffbeefba6c4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31741729-fc0d-6492-21d3-00c8fdfa651e&amp;u=a1aHR0cHM6Ly9ucGlwcm9maWxlLmNvbS9kaXJlY3RvcnkvY2l0eS9hbWJ1bGFuY2UtaW4tYm90aGVsbC13YXNoaW5ndG9u&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2f739d79bc86f959290a68fd9ec37dfae458670e7a026f96af7c3161efe29bc0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31741729-fc0d-6492-21d3-00c8fdfa651e&amp;u=a1aHR0cHM6Ly93d3cuc3VwZXJwYWdlcy5jb20vYm90aGVsbC13YS9hbWJ1bGFuY2Utc2VydmljZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=538231cd2757759e2751cb8a42d4d59d96b77fcec6d6aeb941da8b362c2d8e32JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31741729-fc0d-6492-21d3-00c8fdfa651e&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5X21lZGljYWxfc2VydmljZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bce8e11d5bbc0648c180aaa768201c78a3a9544f0e469db7f91f4217797fc2f2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31741729-fc0d-6492-21d3-00c8fdfa651e&amp;u=a1aHR0cHM6Ly9wcm90ZWN0aW9uMXdhLmxvY2Fsc2VhcmNoLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=714683f706119da462ce5e8da91dfffcf4faf6bde9d29bfa2ee53d1652fd721eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31741729-fc0d-6492-21d3-00c8fdfa651e&amp;u=a1aHR0cHM6Ly93d3cuZWhlYWx0aHNjb3Jlcy5jb20vY2FyZS1sbHdwemx4cHpjLWNpdHktb2YtYm90aGVsbC1ib3RoZWxsLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5f76b29129b5413521f65df71771d45285fc9d4f024a19e72c3d5342a196b583JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2879dff9-e2ab-6c4a-1324-c818e35a6d75&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS94aHRtbC9zZWFyY2g&amp;ntb=1</t>
   </si>
   <si>
     <t>https://www.bing.com/</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=745648f603c95c7067e7862e7427acde5901a63eb7dd09b5b464b8f2450354c2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d5d5cd-3ea9-6192-2dee-c22c3f756021&amp;u=a1aHR0cHM6Ly9zZWFyY2gueWFob28uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4f91b49658a5d84950bac9f6181ecdb89886d969e1b8ee0186a5077bf3f1b405JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d5d5cd-3ea9-6192-2dee-c22c3f756021&amp;u=a1aHR0cHM6Ly9kdWNrZHVja2dvLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=760423b9b9bb7257b7dc5986a2faf1c9781f598d5fb3782d691c95065804c4f3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d5d5cd-3ea9-6192-2dee-c22c3f756021&amp;u=a1aHR0cHM6Ly9zZWFyY2guZ29vZ2xlLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=539157b18b6fb68139871c1adbda9cf84c7b038669285ae8e7699bf7a191d16cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d5d5cd-3ea9-6192-2dee-c22c3f756021&amp;u=a1aHR0cHM6Ly9pbWFnZXMuZ29vZ2xlLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9195e22c5337e27e479277a8455468d43b82ac6328257c3da7ae4bda9879c801JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d5d5cd-3ea9-6192-2dee-c22c3f756021&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS9pbnRsL2VuX3VzL3NlYXJjaC9ob3dzZWFyY2h3b3Jrcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a65a19da9fabbb00854a388f01d2a9fcfb89db56501254ca2ef6925593238890JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d5d5cd-3ea9-6192-2dee-c22c3f756021&amp;u=a1aHR0cHM6Ly93d3cuc3RhcnRwYWdlLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4b1ab60a00fa9b11a9a0a87f8eeb739967929386329314b2a0c58039499a2861JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d5d5cd-3ea9-6192-2dee-c22c3f756021&amp;u=a1aHR0cHM6Ly9hY2NvdW50cy5nb29nbGUuY29tL0ludGVyYWN0aXZlTG9naW4_c2VydmljZT1zYWZlc2VhcmNobG9jaw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=10a7b972b39297da7fa386d1e6dfc10910d49d2cc201364f6017a8e497f93914JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33e4b93e-31ec-6833-3e97-aedf30b869a7&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Npdmls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7e2adcd3dc0bc96d30abfd2f0aea52bedb961ffe0d1c2d81a40daa66a374772bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33e4b93e-31ec-6833-3e97-aedf30b869a7&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ2l2aWxfZW5naW5lZXJpbmc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f895ffa1d2f02ba8a9aff049d40be1d0d224c8240c84fc7e04b629a11c556089JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33e4b93e-31ec-6833-3e97-aedf30b869a7&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Npdmls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8592c4fdfc43030a6319f664ad874433676ff5a17645d30efac5feb375073c6aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33e4b93e-31ec-6833-3e97-aedf30b869a7&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9jaXZpbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d1785402602b28bb244d71dc4f7f9b844ff7994d4553c0d5c271f3a43a50dd8eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33e4b93e-31ec-6833-3e97-aedf30b869a7&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2Npdmls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=10d8a6238e1fb05979b961fd0f994d16335b0ac2255a43872fa25430d936ea4cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33e4b93e-31ec-6833-3e97-aedf30b869a7&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2Npdmls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4a7017c5433c19e6e3484a5420b6f23f7efda45d9d3a37b53bfc15cec62ce990JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33e4b93e-31ec-6833-3e97-aedf30b869a7&amp;u=a1aHR0cHM6Ly93d3cuYXV0b2Rlc2suY29tL3Byb2R1Y3RzL2NpdmlsLTNkL3Byb2R1Y3QtZGV0YWlscz9tc29ja2lkPTMzZTRiOTNlMzFlYzY4MzMzZTk3YWVkZjMwYjg2OWE3&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7931d688ea59d2c904fb75d53e2be9001a11145a1051c8721e5b52a4a052217eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2879dff9-e2ab-6c4a-1324-c818e35a6d75&amp;u=a1aHR0cHM6Ly9zZWFyY2gueWFob28uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=12b6e886571f0183dcf38e8057dccdf3b1b9ba5ba3fab3c241c4a2c6856d1a51JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2879dff9-e2ab-6c4a-1324-c818e35a6d75&amp;u=a1aHR0cHM6Ly9zZWFyY2guZ29vZ2xlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e370a7c1a6247c5f6bb18302cd77327f80bd27f333ba3562966dbf897f1de553JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2879dff9-e2ab-6c4a-1324-c818e35a6d75&amp;u=a1aHR0cHM6Ly93d3cueWFob28uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c01ceb58134002ea1b79da03ac46160e6ee4d4a36d546125fb81de754df84a9cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2879dff9-e2ab-6c4a-1324-c818e35a6d75&amp;u=a1aHR0cHM6Ly9zZWFyY2guYnJhdmUuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d880edf1b22caf5fc044aa6a6cb81ec3890a5ecb74e7d95c3b862cc9326ca8d6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2879dff9-e2ab-6c4a-1324-c818e35a6d75&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vVXNlLUJpbmctU2VhcmNoLUVuZ2luZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2182493f826a34e0019b3f830b87fb97f6b57f138c3f112539e48efae96d04eeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2879dff9-e2ab-6c4a-1324-c818e35a6d75&amp;u=a1aHR0cHM6Ly9kdWNrZHVja2dvLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=61cd5ffafe5a1b47df18d2b7c458c752af3df9719dda16f4c8cec4103de7a78bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0c77bb-ba39-6e79-21a5-605abba06fe8&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6219d2dd7bcc1fd21f4fa7e5fe4ea652c582cfd565e54d85376509d0cbbb75c9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0c77bb-ba39-6e79-21a5-605abba06fe8&amp;u=a1aHR0cHM6Ly93d3cuZWxkb3JhZG9jb3VudHkuY2EuZ292L1B1YmxpYy1TYWZldHktSnVzdGljZS9TYWZldHktSnVzdGljZS9zaGVyaWZmL3N1cHBvcnRfc2VydmljZXMvY2l2aWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2295bd3802bf737b82357fcef0c4480a40256647a59351e106cfe4dda79d44c9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0c77bb-ba39-6e79-21a5-605abba06fe8&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dde43163b213c3d61d88a6fcb8af6c8a8775ac48ab7bcb9b4d5829ace5487df2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0c77bb-ba39-6e79-21a5-605abba06fe8&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ2l2aWxfZW5naW5lZXJpbmc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7abcd9176d37361c56435d4fd4ee4b4d1d2c8f0a4bf6cb649c4365606078e611JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0c77bb-ba39-6e79-21a5-605abba06fe8&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d6bbc055232683bb63627afda9cb39ff4e11e30b083095c9c8f5ad0fa996310dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0c77bb-ba39-6e79-21a5-605abba06fe8&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9jaXZpbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6788ecbe8306c8f957bfc6174dffd4a91a8787cbdcdc15cbb7a22c287b4927d9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0c77bb-ba39-6e79-21a5-605abba06fe8&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2Npdmls&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
@@ -910,7 +904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -944,19 +938,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="G2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -964,19 +958,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -984,19 +978,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1004,19 +998,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1024,19 +1018,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1044,19 +1038,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1064,19 +1058,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1084,19 +1078,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1104,19 +1098,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G10" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H10" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1124,19 +1118,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1144,19 +1138,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1164,19 +1158,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H13" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1184,19 +1178,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1204,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G15" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H15" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1224,19 +1218,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G16" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H16" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1244,19 +1238,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H17" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1264,19 +1258,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G18" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H18" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1284,19 +1278,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G19" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H19" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1304,19 +1298,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G20" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H20" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1324,19 +1318,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G21" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H21" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1344,19 +1338,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G22" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H22" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1364,19 +1358,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G23" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H23" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1384,19 +1378,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H24" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1404,19 +1398,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G25" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H25" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1424,19 +1418,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G26" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H26" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1444,19 +1438,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G27" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H27" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1464,19 +1458,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G28" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H28" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1484,19 +1478,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G29" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H29" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1504,19 +1498,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G30" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H30" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1524,19 +1518,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G31" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H31" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1544,19 +1538,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G32" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H32" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1564,19 +1558,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G33" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H33" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1584,19 +1578,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G34" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H34" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1604,19 +1598,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C35" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G35" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H35" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1624,19 +1618,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G36" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H36" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1644,19 +1638,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G37" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H37" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1664,19 +1658,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C38" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G38" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H38" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1684,19 +1678,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G39" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H39" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1704,19 +1698,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C40" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G40" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H40" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1724,19 +1718,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G41" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H41" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1744,19 +1738,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G42" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H42" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1764,19 +1758,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C43" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G43" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H43" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1784,19 +1778,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C44" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G44" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1804,19 +1798,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G45" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H45" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1824,19 +1818,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C46" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G46" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H46" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1844,19 +1838,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C47" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G47" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H47" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1864,19 +1858,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C48" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G48" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H48" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1884,19 +1878,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G49" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H49" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1904,19 +1898,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G50" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H50" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1924,19 +1918,19 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G51" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H51" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1944,19 +1938,19 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C52" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G52" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H52" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1964,19 +1958,19 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C53" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G53" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H53" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -1984,19 +1978,19 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G54" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H54" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2004,19 +1998,19 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C55" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G55" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H55" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2024,19 +2018,19 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C56" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G56" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H56" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2044,19 +2038,19 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G57" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H57" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2064,19 +2058,19 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C58" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G58" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H58" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2084,19 +2078,19 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C59" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G59" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H59" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2104,19 +2098,19 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C60" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G60" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H60" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2124,19 +2118,19 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C61" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G61" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H61" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2144,19 +2138,19 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C62" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G62" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H62" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2164,19 +2158,19 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C63" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G63" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H63" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2184,19 +2178,19 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C64" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G64" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H64" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2204,19 +2198,19 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C65" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G65" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H65" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2224,19 +2218,19 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C66" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G66" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H66" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2244,19 +2238,19 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C67" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G67" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H67" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2264,19 +2258,19 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G68" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H68" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2284,19 +2278,19 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C69" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G69" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H69" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2304,19 +2298,19 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C70" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G70" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H70" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2324,19 +2318,19 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C71" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G71" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H71" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2344,19 +2338,19 @@
         <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C72" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G72" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H72" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2364,19 +2358,19 @@
         <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C73" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G73" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H73" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2384,19 +2378,19 @@
         <v>80</v>
       </c>
       <c r="B74" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C74" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G74" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H74" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2404,19 +2398,19 @@
         <v>81</v>
       </c>
       <c r="B75" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C75" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G75" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H75" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2424,19 +2418,19 @@
         <v>82</v>
       </c>
       <c r="B76" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C76" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G76" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H76" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2444,19 +2438,19 @@
         <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C77" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G77" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H77" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -2464,19 +2458,19 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G78" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H78" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -2484,19 +2478,19 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C79" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G79" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H79" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -2504,19 +2498,19 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C80" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G80" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H80" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -2524,19 +2518,19 @@
         <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C81" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G81" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H81" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -2544,19 +2538,19 @@
         <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C82" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G82" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H82" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -2564,19 +2558,19 @@
         <v>89</v>
       </c>
       <c r="B83" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C83" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G83" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H83" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -2584,19 +2578,19 @@
         <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C84" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G84" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H84" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -2604,19 +2598,19 @@
         <v>91</v>
       </c>
       <c r="B85" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C85" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G85" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H85" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -2624,39 +2618,19 @@
         <v>92</v>
       </c>
       <c r="B86" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C86" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G86" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H86" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
-      <c r="A87" t="s">
-        <v>93</v>
-      </c>
-      <c r="B87" t="s">
-        <v>94</v>
-      </c>
-      <c r="C87" t="s">
-        <v>95</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="G87" t="s">
-        <v>182</v>
-      </c>
-      <c r="H87" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2746,7 +2720,6 @@
     <hyperlink ref="F84" r:id="rId83"/>
     <hyperlink ref="F85" r:id="rId84"/>
     <hyperlink ref="F86" r:id="rId85"/>
-    <hyperlink ref="F87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/scraped_Cape_Town_Emergency_and_Rescue.xlsx
+++ b/results/scraped_Cape_Town_Emergency_and_Rescue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="190">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -40,34 +40,34 @@
     <t>Source</t>
   </si>
   <si>
-    <t>Current Fires in Washington | WFCAFireMap</t>
+    <t>Fire-Wikipedia</t>
   </si>
   <si>
     <t>Wildfire/Smoke Map - Live Tracking</t>
   </si>
   <si>
+    <t>Firefox: The fast, private browser that keeps you safe</t>
+  </si>
+  <si>
+    <t>Active Fires - City of San Antonio</t>
+  </si>
+  <si>
+    <t>FIRE| Foundation for Individual Rights and Expression</t>
+  </si>
+  <si>
+    <t>ActiveFireIncidents Map - Smart Cities</t>
+  </si>
+  <si>
+    <t>Garena FreeFire. Best survival Battle Royale on mobile!</t>
+  </si>
+  <si>
     <t>AirNowFireand Smoke Map</t>
   </si>
   <si>
-    <t>Fire-Wikipedia</t>
-  </si>
-  <si>
-    <t>FIRE| Foundation for Individual Rights and Expression</t>
-  </si>
-  <si>
-    <t>Live Wildfire Map: Active Fires, Smoke &amp; Alerts |FireNearby</t>
-  </si>
-  <si>
-    <t>Live Wildfire Map &amp; Tracker – Wildfires Near Me | AllFirefighter</t>
-  </si>
-  <si>
-    <t>firemap.us | see what's onfire</t>
-  </si>
-  <si>
-    <t>Current Wildfire Information - U.S. Department of the Interior</t>
-  </si>
-  <si>
-    <t>Firefox: The fast, private browser that keeps you safe</t>
+    <t>Active SAFD Calls- San Antonio</t>
+  </si>
+  <si>
+    <t>Fire- City of San Antonio</t>
   </si>
   <si>
     <t>Emergency! (TV Series 1972–1979) - IMDb</t>
@@ -85,475 +85,499 @@
     <t>Emergency! | The Complete Series -YouTube</t>
   </si>
   <si>
+    <t>EMERGENCYDefinition &amp; Meaning -Merriam-Webster</t>
+  </si>
+  <si>
     <t>Emergency! (TV Series 1972–1979) - Full cast &amp; crew - IMDb</t>
   </si>
   <si>
-    <t>EMERGENCYDefinition &amp; Meaning -Merriam-Webster</t>
-  </si>
-  <si>
-    <t>EmergencyManagement -Snohomish County, WA - Official Website</t>
-  </si>
-  <si>
-    <t>Emergency Services| Providence Regional Medical Center Everett ...</t>
-  </si>
-  <si>
-    <t>Emergency management| Everett, WA - Official Website</t>
+    <t>EMERGENCYonSteam</t>
+  </si>
+  <si>
+    <t>EMERGENCY</t>
+  </si>
+  <si>
+    <t>WatchEmergency! (1972) Online for Free - The Roku Channel</t>
   </si>
   <si>
     <t>Sea-Wikipedia</t>
   </si>
   <si>
-    <t>Seattle-Tacoma International Airport | Port of Seattle</t>
-  </si>
-  <si>
-    <t>SEA– Seattle Education Association</t>
+    <t>Sea- National Geographic Society</t>
   </si>
   <si>
     <t>Sea- SimpleEnglish Wikipedia, the free encyclopedia</t>
   </si>
   <si>
-    <t>List of seas on Earth - Wikipedia</t>
+    <t>Ocean vs.Sea: What’s the Difference? - Encyclopedia Britannica</t>
+  </si>
+  <si>
+    <t>Ocean- Wikipedia</t>
+  </si>
+  <si>
+    <t>Sea| Investor Relations</t>
   </si>
   <si>
     <t>SeaEducation Association</t>
   </si>
   <si>
-    <t>Ocean vs.Sea: What’s the Difference? - Encyclopedia Britannica</t>
-  </si>
-  <si>
-    <t>Sea- National Geographic Society</t>
-  </si>
-  <si>
-    <t>Sea| Investor Relations</t>
+    <t>Sea- New World Encyclopedia</t>
   </si>
   <si>
     <t>SEADefinition &amp; Meaning - Merriam-Webster</t>
   </si>
   <si>
+    <t>Sea| body of water | Britannica</t>
+  </si>
+  <si>
     <t>Mountain-Wikipedia</t>
   </si>
   <si>
-    <t>Mountain| Definition, Characteristics, Types, &amp; Facts ...</t>
+    <t>Mountain| Definition, Characteristics, Types, &amp; Facts | Britannica</t>
   </si>
   <si>
     <t>Mountains -WorldAtlas</t>
   </si>
   <si>
-    <t>Whatmountainam I looking at? How to identifyWashington...</t>
+    <t>Mountain (band) -Wikipedia</t>
+  </si>
+  <si>
+    <t>What is a Mountain? -WorldAtlas</t>
+  </si>
+  <si>
+    <t>Mountain- Simple EnglishWikipedia, the free encyclopedia</t>
   </si>
   <si>
     <t>What is amountain? Here’s how they form | National Geographic</t>
   </si>
   <si>
-    <t>MountainPacific Bank</t>
-  </si>
-  <si>
-    <t>Mountain- Simple EnglishWikipedia, the free encyclopedia</t>
-  </si>
-  <si>
-    <t>Portal:Mountains-Wikipedia</t>
-  </si>
-  <si>
-    <t>11 BreathtakingMountainPeaks You Can See From Seattle</t>
-  </si>
-  <si>
-    <t>What is a Mountain? -WorldAtlas</t>
+    <t>Mountain: what they are, how they are formed and more</t>
+  </si>
+  <si>
+    <t>Mountain-ScienceDaily</t>
+  </si>
+  <si>
+    <t>What are mountains? -BBC Bitesize</t>
   </si>
   <si>
     <t>Disaster-Wikipedia</t>
   </si>
   <si>
+    <t>Home | disasterassistance.gov</t>
+  </si>
+  <si>
     <t>Disaster| Definition &amp; Types | Britannica</t>
   </si>
   <si>
     <t>DISASTERDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>Home | disasterassistance.gov</t>
-  </si>
-  <si>
     <t>Disaster Information-FEMA.gov</t>
   </si>
   <si>
+    <t>Naturaldisaster| Causes, Types, &amp; Facts | Britannica</t>
+  </si>
+  <si>
+    <t>DisasterRadar: Live Natural Hazard Map &amp; Alerts</t>
+  </si>
+  <si>
+    <t>Definition:Disaster| UNDRR</t>
+  </si>
+  <si>
     <t>Home |FEMA.gov</t>
   </si>
   <si>
-    <t>Definition:Disaster| UNDRR</t>
-  </si>
-  <si>
-    <t>Naturaldisaster| Causes, Types, &amp; Facts | Britannica</t>
-  </si>
-  <si>
-    <t>DisasterRadar: Live Natural Hazard Map &amp; Alerts</t>
-  </si>
-  <si>
-    <t>What is adisaster? - IFRC</t>
-  </si>
-  <si>
-    <t>Best Breakfast atFirstWatchGilbert,AZ|FirstWatch</t>
-  </si>
-  <si>
-    <t>Arizona-FirstAmerican Title -GilbertSan Tan</t>
-  </si>
-  <si>
-    <t>ArizonaBanks Near Me -GilbertGateway :FirstFidelity Bank ...</t>
-  </si>
-  <si>
-    <t>First Impression Ironworks|Gilbert AZ- Facebook</t>
-  </si>
-  <si>
-    <t>Gilbertproperty management | FirstService Residential</t>
-  </si>
-  <si>
-    <t>Urgent CareinGilbert,AZ| HealthFirst Urgent Care</t>
-  </si>
-  <si>
-    <t>Gilbert AZ|FirstInternational Bank &amp; Trust - FIBT</t>
-  </si>
-  <si>
-    <t>FirstUnited Methodist Church ofGilbert|Gilbert AZ- Facebook</t>
-  </si>
-  <si>
-    <t>GilbertSecurity Doors | Iron Doors | Wrought Iron Gates ...</t>
-  </si>
-  <si>
-    <t>Security Doors Phoenix | Iron Entry Doors | Iron or Wood ...</t>
+    <t>Natural disaster-Wikipedia</t>
+  </si>
+  <si>
+    <t>Login ·FirstFinancial Bank</t>
+  </si>
+  <si>
+    <t>FIRSTDefinition &amp; Meaning - Merriam-Webster</t>
+  </si>
+  <si>
+    <t>FIRST| For Inspiration and Recognition of Science and Technology</t>
+  </si>
+  <si>
+    <t>FIRST| English meaning - Cambridge Dictionary</t>
+  </si>
+  <si>
+    <t>Personal Banking | Checking, Savings &amp; Loans |FirstFinancial Bank</t>
+  </si>
+  <si>
+    <t>FirstFinancial Bank</t>
+  </si>
+  <si>
+    <t>IndianapolisRegional Headquarters |FirstMerchants Bank</t>
+  </si>
+  <si>
+    <t>FIRST| definitioninthe Cambridge English Dictionary</t>
+  </si>
+  <si>
+    <t>Online Banking &amp; Digital Banking |First Internet Bank</t>
+  </si>
+  <si>
+    <t>Helping You Prosper |FirstMerchants Bank</t>
   </si>
   <si>
     <t>Ambulance- Wikipedia</t>
   </si>
   <si>
-    <t>NorthwestAmbulance- Seattle | Puget Sound Region</t>
-  </si>
-  <si>
-    <t>City OfBothellinBothell,Washington-AmbulanceService Address …</t>
-  </si>
-  <si>
-    <t>AmbulanceServices inBothell,WA- The Real Yellow Pages®</t>
-  </si>
-  <si>
-    <t>AmbulanceServices inBothell,Washington- Address, Contact</t>
-  </si>
-  <si>
-    <t>AmbulanceinBothell,WA- 2 Records - NPI Profile</t>
-  </si>
-  <si>
-    <t>Best 29AmbulanceServices inBothell,WA| superpages.com</t>
+    <t>City OfJoshuaEms -Joshua,TXLand TransportAmbulance</t>
+  </si>
+  <si>
+    <t>Service Providers - Johnson County ESD 1</t>
   </si>
   <si>
     <t>Emergency medical services- Wikipedia</t>
   </si>
   <si>
-    <t>Protection-1 -AmbulanceServices -Bothell,WA</t>
-  </si>
-  <si>
-    <t>City OfBothell-Bothell,WALand TransportAmbulance</t>
+    <t>AMR - EMS &amp;AmbulanceCare</t>
+  </si>
+  <si>
+    <t>AMBULANCEDefinition &amp; Meaning - Merriam-Webster</t>
+  </si>
+  <si>
+    <t>Ride N' Safe | Non-Emergency Medical Transportation</t>
+  </si>
+  <si>
+    <t>Services – CityAmbulance</t>
+  </si>
+  <si>
+    <t>JoshuaFire Department inJoshua,Texas-AmbulanceService …</t>
+  </si>
+  <si>
+    <t>Home - AmericanAmbulanceAssociation</t>
+  </si>
+  <si>
+    <t>Search- Microsoft Bing</t>
   </si>
   <si>
     <t>Google</t>
   </si>
   <si>
-    <t>Search- Microsoft Bing</t>
-  </si>
-  <si>
     <t>YahooSearch- WebSearch</t>
   </si>
   <si>
+    <t>DuckDuckGo- Protection. Privacy. Peace of mind.</t>
+  </si>
+  <si>
+    <t>PrivateSearchEngine - BraveSearch</t>
+  </si>
+  <si>
+    <t>Google Images</t>
+  </si>
+  <si>
     <t>Google Search- A new kind of help</t>
   </si>
   <si>
-    <t>Yahoo</t>
-  </si>
-  <si>
-    <t>PrivateSearchEngine - BraveSearch</t>
-  </si>
-  <si>
-    <t>How toUse Bing Search Engineon Desktop or Mobile -wikiHow</t>
-  </si>
-  <si>
-    <t>DuckDuckGo- Protection. Privacy. Peace of mind.</t>
+    <t>GoogleAdvanced Search</t>
+  </si>
+  <si>
+    <t>Search-Search History- Bing</t>
   </si>
   <si>
     <t>CIVILDefinition &amp; Meaning -Merriam-Webster</t>
   </si>
   <si>
-    <t>Civil- El Dorado County,California</t>
+    <t>Civil Court| Courts |MilwaukeeCounty</t>
+  </si>
+  <si>
+    <t>Civil &amp; Environmental Engineering- College of Engineering &amp; Applied ...</t>
+  </si>
+  <si>
+    <t>Civil Engineering–College of Engineering &amp; Applied Science</t>
+  </si>
+  <si>
+    <t>Civil engineering-Wikipedia</t>
   </si>
   <si>
     <t>CIVIL| English meaning - Cambridge Dictionary</t>
   </si>
   <si>
-    <t>Civil engineering-Wikipedia</t>
+    <t>Wisconsin CourtSystem -Case search</t>
+  </si>
+  <si>
+    <t>County ofMilwaukee|CivilProcess</t>
+  </si>
+  <si>
+    <t>Civil: Definition, Meaning, and Examples - usdictionary.com</t>
   </si>
   <si>
     <t>Civil- definition ofcivilby The Free Dictionary</t>
   </si>
   <si>
-    <t>Civil- Definition, Meaning &amp; Synonyms | Vocabulary.com</t>
-  </si>
-  <si>
-    <t>CIVILDefinition &amp; Meaning |Dictionary.com</t>
-  </si>
-  <si>
     <t>Emergency &amp; Rescue</t>
   </si>
   <si>
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9d313f008831e6d73bbaea4125d1e85288f0753efec2323a657fc4ab65ac4e12JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1564ea5b-4224-6fc5-086a-fdba43336e51&amp;u=a1aHR0cHM6Ly93ZmNhLmNvbS9maXJlLW1hcC93YXNoaW5ndG9u&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=17fdb0b0ac550a68dac7fd827c6e404d2f19750b6c76460a97533eea6012c043JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1564ea5b-4224-6fc5-086a-fdba43336e51&amp;u=a1aHR0cHM6Ly93aWxkZmlyZXRyYWNrZXJzLmNvbS9mL21hcA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=526f5790389f4ce57a8af16edae9e26e4102ba132842075aa6ea2ea693daedb8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1564ea5b-4224-6fc5-086a-fdba43336e51&amp;u=a1aHR0cHM6Ly9maXJlLmFpcm5vdy5nb3YvP2xhbmc9ZW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d9d9f6afb1a9e770d9aab5c322884431d21ec8c5e6ea9d52a2938f954fc5e10eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1564ea5b-4224-6fc5-086a-fdba43336e51&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GaXJl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1dbd2a3ecbfdc4649abb29551e0653df5a9520b63557aeb9fbd4922562ca7185JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1564ea5b-4224-6fc5-086a-fdba43336e51&amp;u=a1aHR0cHM6Ly93d3cuZmlyZS5vcmcv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1fd91d3d6442d5b526c69e3adb6102ffe625a099e93ca2b0c875064bb4496cd2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1564ea5b-4224-6fc5-086a-fdba43336e51&amp;u=a1aHR0cHM6Ly9maXJlbmVhcmJ5LmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2b84007603956ca754fb31b531d32d6400ab6782a69f752376ce728ff752ccc4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1564ea5b-4224-6fc5-086a-fdba43336e51&amp;u=a1aHR0cHM6Ly9hbGxmaXJlZmlnaHRlci5jb20vd2lsZGZpcmVzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=33a698ffb0a12a2fa5f64763c414f0d244457d606cca129aae46602002915699JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1564ea5b-4224-6fc5-086a-fdba43336e51&amp;u=a1aHR0cHM6Ly9maXJlbWFwLnVzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b89d5aae8eaf5444012e55918c7de543840bc91152ae6422663fd75765738c0aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1564ea5b-4224-6fc5-086a-fdba43336e51&amp;u=a1aHR0cHM6Ly93d3cuZG9pLmdvdi93aWxkbGFuZGZpcmVzZXJ2aWNlL2N1cnJlbnQtd2lsZGZpcmUtaW5mb3JtYXRpb24&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11ba83dee0c66fe1dc8a5ac5748d66a1b0b02ac8b6a8bc2c225fca79585c0cc4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1564ea5b-4224-6fc5-086a-fdba43336e51&amp;u=a1aHR0cHM6Ly93d3cuZmlyZWZveC5jb20vZW4tVVMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5ae4c62b1c78332164df72219a20426e44316500dc3c30702c98533e0f126030JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=082b35d8-8318-6a87-16a2-223982656b6d&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQwMDY4MDY3Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=815a0842a93a08922052d86302ee5ceb881a6746eba5598a4337b2d3b9b33114JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=082b35d8-8318-6a87-16a2-223982656b6d&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5IQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e6620ac9c7a902506197a71aaa2466d801613eead3ffc98e6e8987424da833d5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=082b35d8-8318-6a87-16a2-223982656b6d&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f62839c62174f78602a8ac5e30f65e5a9cd1447165efd6a74c44030427ef660dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=082b35d8-8318-6a87-16a2-223982656b6d&amp;u=a1aHR0cHM6Ly9kb3lvdXJlbWVtYmVyLmNvbS8xNTg1NjEvZW1lcmdlbmN5LWNhc3QtdGhlbi1ub3c&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=44e559761906ac49fe767b859512ca1c9275c2ba33236150e345e2ea26b4f6a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=082b35d8-8318-6a87-16a2-223982656b6d&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1sQnJSQTVSQ1lUVQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=133c258b04d8bbf9a7ea08d1b17c8608f572911cc11d0520cfa96a733386040bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=082b35d8-8318-6a87-16a2-223982656b6d&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQwMDY4MDY3L2Z1bGxjcmVkaXRzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=16700a6ee12b16d3540e05b9d0a343133b5505771e809222cc0040b6b926244eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=082b35d8-8318-6a87-16a2-223982656b6d&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VtZXJnZW5jeQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e491d0afc9ebfb4d409cb2ad37d8eee261e82f18f107488fb7b0e819d56c4c43JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=082b35d8-8318-6a87-16a2-223982656b6d&amp;u=a1aHR0cHM6Ly9zbm9ob21pc2hjb3VudHl3YS5nb3YvMTgwL0VtZXJnZW5jeS1NYW5hZ2VtZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=be9e90d91c332427bcecd155cbd688c646356e62ed54a919894a3c5c8cf86477JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=082b35d8-8318-6a87-16a2-223982656b6d&amp;u=a1aHR0cHM6Ly93d3cucHJvdmlkZW5jZS5vcmcvbG9jYXRpb25zL3dhL3Byb3ZpZGVuY2UtcmVnaW9uYWwtbWVkaWNhbC1jZW50ZXItZXZlcmV0dC9lbWVyZ2VuY3ktc2VydmljZXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cc6f0e36245a5468df0275bc1d732c5db4130304a6448b62679452c56604e36fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=082b35d8-8318-6a87-16a2-223982656b6d&amp;u=a1aHR0cHM6Ly93d3cuZXZlcmV0dHdhLmdvdi8yNDEvRW1lcmdlbmN5LU1hbmFnZW1lbnQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c9e54d21deacdf514687b7b58f94b5380697ba2f533b634779f51428516e5b1bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a440da7-7ac0-62cf-04b8-1a467b64639a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9TZWE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f3c5134158cfe33477fbb5c17fbbd88b96640203d7da8b0272aa7ba64c2a29b8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a440da7-7ac0-62cf-04b8-1a467b64639a&amp;u=a1aHR0cHM6Ly93d3cucG9ydHNlYXR0bGUub3JnL3NlYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=41cac52f2e04670f224fe0af52f12af1e0c79912e794468fbb2c88e5b8a9bc5bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a440da7-7ac0-62cf-04b8-1a467b64639a&amp;u=a1aHR0cHM6Ly9zZWF0dGxld2VhLm9yZy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e6c5f8c7a61dc52b459a1e03dd761820b1afffa3c6d1062aa5d20fd524d4914aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a440da7-7ac0-62cf-04b8-1a467b64639a&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvU2Vh&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=28c4ac7fe3f7fac53a376be8360135a2701d9afd76782e181756722ad2bfe4d4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a440da7-7ac0-62cf-04b8-1a467b64639a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9MaXN0X29mX3NlYXNfb25fRWFydGg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7f85c5a6c2c50d331f4769ded82ca6ca8a2f6aa9df824230f5b0cfccfcda5502JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a440da7-7ac0-62cf-04b8-1a467b64639a&amp;u=a1aHR0cHM6Ly9zZWEuZWR1Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=453e236096c6cc98696e11f42b4676cb81ce9d4305e7d76da2521c2548c90cdcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a440da7-7ac0-62cf-04b8-1a467b64639a&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9PY2Vhbi12cy1TZWEtV2hhdHMtdGhlLURpZmZlcmVuY2U&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=716a7e3b04288b8041cc07eec82bd3e7409f2e497b98a0dafe7df8f14e490863JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a440da7-7ac0-62cf-04b8-1a467b64639a&amp;u=a1aHR0cHM6Ly9lZHVjYXRpb24ubmF0aW9uYWxnZW9ncmFwaGljLm9yZy9yZXNvdXJjZS9zZWEv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=167d28c1666df1e3fa10b204877ca6922b001f6d3893b1af93b8d6efec2c0c00JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a440da7-7ac0-62cf-04b8-1a467b64639a&amp;u=a1aHR0cHM6Ly93d3cuc2VhLmNvbS9pbnZlc3Rvci9ob21l&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2e98206d9ecc118be91cc7e2f9ed47d93fd7978d44aa574d1416fced5aa8a0aeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2a440da7-7ac0-62cf-04b8-1a467b64639a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NlYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4b5a595f466c06a7cde053318f2c58419c616ff09f6ddac852d545e94542f216JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311f3b12-12fc-603c-091c-2cf31356611a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Nb3VudGFpbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3298b5f91925c4ed5679b00eaf9de35aaf6196fc6226babdf10193ac4de356a5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311f3b12-12fc-603c-091c-2cf31356611a&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9tb3VudGFpbi1sYW5kZm9ybQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=49459bc99df41eacfb5a38bd8005b5bb1ec31fc144c045d6ca6d1f20598d1d3aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311f3b12-12fc-603c-091c-2cf31356611a&amp;u=a1aHR0cHM6Ly93d3cud29ybGRhdGxhcy5jb20vbW91bnRhaW5zLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c1876706c0d3e0db81ee656245a105f51f9ae109a8abeb20f739b0a9d346275eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311f3b12-12fc-603c-091c-2cf31356611a&amp;u=a1aHR0cHM6Ly93d3cua2luZzUuY29tL2FydGljbGUvd2VhdGhlci9tb3VudGFpbi1yZWNyZWF0aW9uL2V2ZXJ5dGhpbmctbmVlZC1rbm93LXdhc2hpbmd0b25zLW1vdW50YWlucy8yODEtYzcyZTEzMmItMGVhYy00MDliLWI0YzctOTkwZTZhODhhYWQ3&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1e6915cbac057aa3723e944ebe1866a8b3c552eb60a7111bb0f8d670e0f617ccJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311f3b12-12fc-603c-091c-2cf31356611a&amp;u=a1aHR0cHM6Ly93d3cubmF0aW9uYWxnZW9ncmFwaGljLmNvbS9zY2llbmNlL2FydGljbGUvbW91bnRhaW5z&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fd2c80c2170dd1ed9b6499f87f643deedc7bb8dd5fdfb0004f6f3d3b21ec04deJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311f3b12-12fc-603c-091c-2cf31356611a&amp;u=a1aHR0cHM6Ly9tcC5iYW5rLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7b05aa223af32e91ae9244f58c4f86a2d9e2eac77b6eec5d33d94abba3baf73cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311f3b12-12fc-603c-091c-2cf31356611a&amp;u=a1aHR0cHM6Ly9zaW1wbGUubS53aWtpcGVkaWEub3JnL3dpa2kvTW91bnRhaW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef5b457e7ed7361c559ce9d6b3a7b5ab89a85ed39be2a0eb39c6619b2ffde634JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311f3b12-12fc-603c-091c-2cf31356611a&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9Qb3J0YWw6TW91bnRhaW5z&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=842925689c32d551860ff543f098f272668e99e18267b0b714ac54c5ac23ceb6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311f3b12-12fc-603c-091c-2cf31356611a&amp;u=a1aHR0cHM6Ly9zZWF0dGxldHJhdmVsLmNvbS93aGF0LW1vdW50YWlucy1jYW4teW91LXNlZS1mcm9tLXNlYXR0bGUtMTEtYnJlYXRodGFraW5nLW1vdW50YWluLXBlYWtzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=89cbb26648959f4ba20a2c651d73a90e7ebbd16707e6d0326ec13b80a8ae8eedJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=311f3b12-12fc-603c-091c-2cf31356611a&amp;u=a1aHR0cHM6Ly93d3cud29ybGRhdGxhcy5jb20vYXJ0aWNsZXMvd2hhdC1pcy1hLW1vdW50YWluLmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1de33e7efc0af0d1735f8674ec8a1cd034c54c5b11a1a5f56f132b4c0a53fdddJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4ee86c-edd6-65a9-1ca0-ff8dec2f6419&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRGlzYXN0ZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6ba32380a2f56101a5c369d2903261cc825e1edafab23d0e44664b24871666b0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4ee86c-edd6-65a9-1ca0-ff8dec2f6419&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9kaXNhc3Rlcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0af15a7b97349ca2fd07fd7e932b4aef3b03bd6240502a5b8273dce6d4e07f96JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4ee86c-edd6-65a9-1ca0-ff8dec2f6419&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Rpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f29c2536a8ce0e91f7bbac88d4abf6d6f51765e80c4d6311e07a770b95c7eaf4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4ee86c-edd6-65a9-1ca0-ff8dec2f6419&amp;u=a1aHR0cHM6Ly93d3cuZGlzYXN0ZXJhc3Npc3RhbmNlLmdvdi8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0de35970e119c59dbe5c707b8ae1c8a135254447be5ade78266fa8662f3704edJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4ee86c-edd6-65a9-1ca0-ff8dec2f6419&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3YvZGlzYXN0ZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1e2a9c75c79e0f26ba9c7f9d0da82e887cd1a943c1f1937dd8afe233a8f51721JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4ee86c-edd6-65a9-1ca0-ff8dec2f6419&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3Yv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6a94249ce826045868592d14e278acc8ddfce7c94a19f0f935fee2f5c4c2e9f7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4ee86c-edd6-65a9-1ca0-ff8dec2f6419&amp;u=a1aHR0cHM6Ly93d3cudW5kcnIub3JnL3Rlcm1pbm9sb2d5L2Rpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=005ef0024502225404d35af8d78e55c2a40866af9dcf3aeb4821a30846824137JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4ee86c-edd6-65a9-1ca0-ff8dec2f6419&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9uYXR1cmFsLWRpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=228352c4a6c28c84333a7d7fbf3a2860c0617bec88b19276598447e6c308b706JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4ee86c-edd6-65a9-1ca0-ff8dec2f6419&amp;u=a1aHR0cHM6Ly93d3cuZGlzYXN0ZXJyYWRhci5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=21bcedb46b8ecfd335bffaed528afb92d4e430d761712755c04ce7c7a216601bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c4ee86c-edd6-65a9-1ca0-ff8dec2f6419&amp;u=a1aHR0cHM6Ly93d3cuaWZyYy5vcmcvb3VyLXdvcmsvZGlzYXN0ZXJzLWNsaW1hdGUtYW5kLWNyaXNlcy93aGF0LWRpc2FzdGVy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a89e31cf6af9e631f270b2e5dacd3d8093b7414d5f040aafbbdc73805b915d1aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3601d4cc-0efb-6c30-1978-c32d0f5c6df5&amp;u=a1aHR0cHM6Ly9maXJzdHdhdGNoLmNvbS9sb2NhdGlvbnMvZ2lsYmVydC1hbmQtZ2VybWFubg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a0c47d47641154f83440612fd6abdd9d7a490e7292a058b6c036a4f69e4665e4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3601d4cc-0efb-6c30-1978-c32d0f5c6df5&amp;u=a1aHR0cHM6Ly9sb2NhbC5maXJzdGFtLmNvbS9hei9vZmZpY2VzL2dpbGJlcnQtc2FuLXRhbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=adfffd07f127c795d3428a22e2f5eb752911866c80dd0b818f99b33917182afcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3601d4cc-0efb-6c30-1978-c32d0f5c6df5&amp;u=a1aHR0cHM6Ly93d3cuZmZiLmNvbS9sb2NhdGlvbnMvYXJpem9uYS9naWxiZXJ0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dca2d087b5db39d95dd61aa8b22742ffa8150ea6a4691d4c52e08fd419289126JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3601d4cc-0efb-6c30-1978-c32d0f5c6df5&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL2ZpcnN0aW1wcmVzc2lvbmlyb253b3Jrcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c0b0b82e19f6a84a526185973b33456b860428d185a314a868720a52f38b5d0fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3601d4cc-0efb-6c30-1978-c32d0f5c6df5&amp;u=a1aHR0cHM6Ly93d3cuZnNyZXNpZGVudGlhbC5jb20vYXJpem9uYS9vZmZpY2VzL2dpbGJlcnQtb2ZmaWNlLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c2e96c2e9219462b85a618598bc0ed008afc0bf2b90659d5365e990712976b5fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3601d4cc-0efb-6c30-1978-c32d0f5c6df5&amp;u=a1aHR0cDovL2hlYWx0aGZpcnN0dXJnZW50Y2FyZS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=495a3af175cd2c77024818740d09f19e541b36ac3ee7a456ba03a36f74ced453JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3601d4cc-0efb-6c30-1978-c32d0f5c6df5&amp;u=a1aHR0cHM6Ly93d3cuZmlidC5jb20vbG9jYXRpb25zLWhvdXJzL2FyaXpvbmEvZ2lsYmVydC1hei8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0bd6cf50cbd1c29c94cebcab5336c5592f56a29c0cc353ee8e45b46f7983c40aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3601d4cc-0efb-6c30-1978-c32d0f5c6df5&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL0ZVTUNvZmdpbGJlcnQv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed56b2f60b243a48c019b460b3401d20570b9fefa7ab1259a369071bd55202c6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3601d4cc-0efb-6c30-1978-c32d0f5c6df5&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RpbXByZXNzaW9uc2VjdXJpdHlkb29ycy5jb20vbG9jYXRpb25zL2dpbGJlcnQtaXJvbi1zaG93cm9vbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6752f735e4bc88632c4a765f983b5232e129ae8c84c607f3ac9bad7eb26436d1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3601d4cc-0efb-6c30-1978-c32d0f5c6df5&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RpbXByZXNzaW9uc2VjdXJpdHlkb29ycy5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fa648046fe35fc9bdd0fb3ab6be609de4e32fd8179103c22116e1a4440a0ce95JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31741729-fc0d-6492-21d3-00c8fdfa651e&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQW1idWxhbmNl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=415ae39daa943bfa2f907e0335afcd7ce3cbaf6b92df089e6b0d7bdc748c2b6cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31741729-fc0d-6492-21d3-00c8fdfa651e&amp;u=a1aHR0cHM6Ly93d3cubndhbWIudXMv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bc2af6b5df51acefc734bc623c3bea879a745315f52dbba9a5b71dc2c41f49dcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31741729-fc0d-6492-21d3-00c8fdfa651e&amp;u=a1aHR0cHM6Ly9ucGluby5jb20vYW1idWxhbmNlLXNlcnZpY2UvMTE4NDcxNTQ3Ni1jaXR5LW9mLWJvdGhlbGwv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8ae5700e699aba0813992a8602b673bc600bcc3b1a3d8ee3ff93167760221c94JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31741729-fc0d-6492-21d3-00c8fdfa651e&amp;u=a1aHR0cHM6Ly93d3cueWVsbG93cGFnZXMuY29tL2JvdGhlbGwtd2EvYW1idWxhbmNlLXNlcnZpY2Vz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3e8ca949f985443f09235c49227a749ba8e3c54f0e8c7b6d011a47e6e608769dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31741729-fc0d-6492-21d3-00c8fdfa651e&amp;u=a1aHR0cHM6Ly9ucGluby5jb20vYW1idWxhbmNlLXNlcnZpY2VzL3dhL2JvdGhlbGwv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ae214ccf1dee624a16c8257d66c834af5e0a834df6fceeb156351ffbeefba6c4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31741729-fc0d-6492-21d3-00c8fdfa651e&amp;u=a1aHR0cHM6Ly9ucGlwcm9maWxlLmNvbS9kaXJlY3RvcnkvY2l0eS9hbWJ1bGFuY2UtaW4tYm90aGVsbC13YXNoaW5ndG9u&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2f739d79bc86f959290a68fd9ec37dfae458670e7a026f96af7c3161efe29bc0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31741729-fc0d-6492-21d3-00c8fdfa651e&amp;u=a1aHR0cHM6Ly93d3cuc3VwZXJwYWdlcy5jb20vYm90aGVsbC13YS9hbWJ1bGFuY2Utc2VydmljZXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=538231cd2757759e2751cb8a42d4d59d96b77fcec6d6aeb941da8b362c2d8e32JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31741729-fc0d-6492-21d3-00c8fdfa651e&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5X21lZGljYWxfc2VydmljZXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bce8e11d5bbc0648c180aaa768201c78a3a9544f0e469db7f91f4217797fc2f2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31741729-fc0d-6492-21d3-00c8fdfa651e&amp;u=a1aHR0cHM6Ly9wcm90ZWN0aW9uMXdhLmxvY2Fsc2VhcmNoLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=714683f706119da462ce5e8da91dfffcf4faf6bde9d29bfa2ee53d1652fd721eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=31741729-fc0d-6492-21d3-00c8fdfa651e&amp;u=a1aHR0cHM6Ly93d3cuZWhlYWx0aHNjb3Jlcy5jb20vY2FyZS1sbHdwemx4cHpjLWNpdHktb2YtYm90aGVsbC1ib3RoZWxsLmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5f76b29129b5413521f65df71771d45285fc9d4f024a19e72c3d5342a196b583JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2879dff9-e2ab-6c4a-1324-c818e35a6d75&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS94aHRtbC9zZWFyY2g&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a40cd58aa4e2f25a38572d748b29080e53f1849a0a3773fb7d62a203800aa706JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29a2ac92-fcf4-6712-333c-bb73fd6c66ae&amp;u=a1aHR0cHM6Ly9lbi5tLndpa2lwZWRpYS5vcmcvd2lraS9GaXJl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7c3593253d683bd60ce91273c9dffce5a4c3d8a72d0c720c460ec92e8f4e350cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29a2ac92-fcf4-6712-333c-bb73fd6c66ae&amp;u=a1aHR0cHM6Ly93aWxkZmlyZXRyYWNrZXJzLmNvbS9mL21hcA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=348e12d144d55d3f352aac7763fd8462f3962677c374e8d6cab8174e74175274JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29a2ac92-fcf4-6712-333c-bb73fd6c66ae&amp;u=a1aHR0cHM6Ly93d3cuZmlyZWZveC5jb20vZW4tVVMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d714ab4cf5941618472ee4164c88dae439b19159efab6b68100ae577ad6b1779JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29a2ac92-fcf4-6712-333c-bb73fd6c66ae&amp;u=a1aHR0cHM6Ly93d3cuc2EuZ292L0RpcmVjdG9yeS9EZXBhcnRtZW50cy9TQUZEL1RyYW5zcGFyZW5jeS1PcGVuLURhdGEvQWN0aXZlLUZpcmVz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9a35e1c76f8b5fe3e858cc2ad5eebfb938107345425aea45fa41f8fdbe1682b0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29a2ac92-fcf4-6712-333c-bb73fd6c66ae&amp;u=a1aHR0cHM6Ly93d3cuZmlyZS5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=144acd92ad085761a3af1215c4623e6323c831b7bee4a925565c6ce3bd0c3d8fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29a2ac92-fcf4-6712-333c-bb73fd6c66ae&amp;u=a1aHR0cHM6Ly9zbWFydGNpdHkudGFjYy51dGV4YXMuZWR1L0ZpcmVJbmNpZGVudC9GaXJlSW5jaWRlbnRNYXAuaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b6e6da204d01f2b4e018e16c4790bd526737b7b97f86ef1a8f734a807e0c0c0bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29a2ac92-fcf4-6712-333c-bb73fd6c66ae&amp;u=a1aHR0cHM6Ly9mZi5nYXJlbmEuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5f134f9eafe2668dfb3a227b3df844616423581bc2bdf908195c80fc836d246fJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29a2ac92-fcf4-6712-333c-bb73fd6c66ae&amp;u=a1aHR0cHM6Ly9maXJlLmFpcm5vdy5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f85a69c09852d2e29da35a5987ad1c22c325b65cb9a6f6fbe9c8e1771b79ca8dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29a2ac92-fcf4-6712-333c-bb73fd6c66ae&amp;u=a1aHR0cHM6Ly93ZWJhcHAzLnNhbmFudG9uaW8uZ292L2FjdGl2ZWZpcmUvRmlyZS5hc3B4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=65bb1b15a3b82d0e0c3afd0b9500addca9be72c562782495e7cfbf3c4c5d60bfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=29a2ac92-fcf4-6712-333c-bb73fd6c66ae&amp;u=a1aHR0cHM6Ly93d3cuc2EuZ292L0RpcmVjdG9yeS9EZXBhcnRtZW50cy9TQUZE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8695fd12f8f8480169d939854e776ec6e25bbc8237136b23d5e8fc431e181461JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1994c251-62c7-66af-284a-d5b06359670a&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQwMDY4MDY3Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a31c8d7bbe6cd7b95b4e41d42f7c8f3c623060a7e13e889c0111cccb1e344d27JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1994c251-62c7-66af-284a-d5b06359670a&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5IQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5967c009134a7ec3c551b4bbf48918b55cec5edac1e19918b194aced1c17f5f2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1994c251-62c7-66af-284a-d5b06359670a&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1b78d5cc6c7b0e9ff4dbcdcfcc1caf28297707075169b7788caa71f729dbd469JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1994c251-62c7-66af-284a-d5b06359670a&amp;u=a1aHR0cHM6Ly9kb3lvdXJlbWVtYmVyLmNvbS8xNTg1NjEvZW1lcmdlbmN5LWNhc3QtdGhlbi1ub3c&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b1a9e63a5545f6d6e609b4011940bb6845e861ff292e4a72f45ab614a7d622b9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1994c251-62c7-66af-284a-d5b06359670a&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1sQnJSQTVSQ1lUVQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=42e1390c25be02ddc9686e69e395c8183159e16f6bf3603077221966b827078cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1994c251-62c7-66af-284a-d5b06359670a&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2VtZXJnZW5jeQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a11de1372b98270c7e1f61aa7690f5642daaa507fbe8252668191be00c114666JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1994c251-62c7-66af-284a-d5b06359670a&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vdGl0bGUvdHQwMDY4MDY3L2Z1bGxjcmVkaXRzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=013bd8f4e868ad27c9abdf2bec07e4ce864d2c3b34f73d38c4e470d3fd2d81f4JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1994c251-62c7-66af-284a-d5b06359670a&amp;u=a1aHR0cHM6Ly9zdG9yZS5zdGVhbXBvd2VyZWQuY29tL2FwcC84NTAxNzAvRU1FUkdFTkNZLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b2d60354ccf63ac7c968839be7f80f6c81ce1a465d34fdfdf55cf9cadf7127bcJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1994c251-62c7-66af-284a-d5b06359670a&amp;u=a1aHR0cHM6Ly9lbi5lbWVyZ2VuY3kuaXQv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d77fb015a095c1edf82f0ac9d77a86a92d3c7eae85ea5c5de54f81f7466ef6c5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1994c251-62c7-66af-284a-d5b06359670a&amp;u=a1aHR0cHM6Ly90aGVyb2t1Y2hhbm5lbC5yb2t1LmNvbS9kZXRhaWxzL2RjMTc4NmVjZTYxZDU5ZDdhYTc2ZmE5OGQxMDEyOWZhL2VtZXJnZW5jeQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4dde8e7a95df52d177ba46dc1360e0273baf11c53f5e7b4487890ef43f7be180JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0bf015ee-6c6c-6e1f-0244-020f6d466f5b&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvU2Vh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=633467b7a736ba33abad136edf3e33f72e5f1a5b4f0fa43e80f92d16cc08d809JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0bf015ee-6c6c-6e1f-0244-020f6d466f5b&amp;u=a1aHR0cHM6Ly9lZHVjYXRpb24ubmF0aW9uYWxnZW9ncmFwaGljLm9yZy9yZXNvdXJjZS9zZWEv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b203b3c1192529455365b3430eb67e98118b1bb82cc4eda8fa131f2075d740a7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0bf015ee-6c6c-6e1f-0244-020f6d466f5b&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL1NlYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d4ca33358e72818d936cb664e7f75bd7536dfaabb1bc40fa6d32c21d2317244dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0bf015ee-6c6c-6e1f-0244-020f6d466f5b&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9PY2Vhbi12cy1TZWEtV2hhdHMtdGhlLURpZmZlcmVuY2U&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6016700208602ed7bcdedb36c5fd8812fc48c7cc03a48ec72433b544efd178c3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0bf015ee-6c6c-6e1f-0244-020f6d466f5b&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvT2NlYW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4cafc2bab0988c15c230c858a039cf97cf94083bf731e89650ca39942060a997JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0bf015ee-6c6c-6e1f-0244-020f6d466f5b&amp;u=a1aHR0cHM6Ly93d3cuc2VhLmNvbS9pbnZlc3Rvci9ob21l&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3d7c0ef667114402daed9b9d3ca57c33c48b098ea0e14510f26a82939f5b6032JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0bf015ee-6c6c-6e1f-0244-020f6d466f5b&amp;u=a1aHR0cHM6Ly9zZWEuZWR1Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9dd2711044128af9032d29853ece05f778151f4f20000d6cfce409b8d10cd3d5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0bf015ee-6c6c-6e1f-0244-020f6d466f5b&amp;u=a1aHR0cHM6Ly93d3cubmV3d29ybGRlbmN5Y2xvcGVkaWEub3JnL2VudHJ5L1NlYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a883f5c1b5cd0b5bdb20f90d6d211358d2c123e06529697312c74ca39dc476dfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0bf015ee-6c6c-6e1f-0244-020f6d466f5b&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L3NlYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=72c1f3dd4eb743d914af70a8105238c78a779b2381617e2bb024cfec28a5780aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0bf015ee-6c6c-6e1f-0244-020f6d466f5b&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9zZWE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=614c284ba4d7b47a2a504a2067b3fe40deee798e4bae774b2b6aac4869b768c8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=088e4ddd-8ce2-6a0a-2a95-5a3c8d7c6b7d&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTW91bnRhaW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e4a7756b76960346e987d6400501cf76fd1adaefa95949351c4743310ba1ab57JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=088e4ddd-8ce2-6a0a-2a95-5a3c8d7c6b7d&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9tb3VudGFpbi1sYW5kZm9ybQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c15ac5fe6f9febb97471761e72a31244bab65cc9355141e6aa62eb34afd14876JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=088e4ddd-8ce2-6a0a-2a95-5a3c8d7c6b7d&amp;u=a1aHR0cHM6Ly93d3cud29ybGRhdGxhcy5jb20vbW91bnRhaW5zLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3db49c1f17d696fe7c736e3ba035dd865b442eefa998d8d9a6ced3abed307385JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=088e4ddd-8ce2-6a0a-2a95-5a3c8d7c6b7d&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTW91bnRhaW5fKGJhbmQp&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=18c941dc222a360dccfc8c0300307cf1045c14c3725122f47c2b919d140ff6b1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=088e4ddd-8ce2-6a0a-2a95-5a3c8d7c6b7d&amp;u=a1aHR0cHM6Ly93d3cud29ybGRhdGxhcy5jb20vYXJ0aWNsZXMvd2hhdC1pcy1hLW1vdW50YWluLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a0250fc5684836cdb709824089d96217b7ed96d052c0f0b03960da07ec0eb96bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=088e4ddd-8ce2-6a0a-2a95-5a3c8d7c6b7d&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL01vdW50YWlu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5b98bef3234d3a71ed6426545ddf6e4b73960e675661cbc4670f6dc24b4e09b1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=088e4ddd-8ce2-6a0a-2a95-5a3c8d7c6b7d&amp;u=a1aHR0cHM6Ly93d3cubmF0aW9uYWxnZW9ncmFwaGljLmNvbS9zY2llbmNlL2FydGljbGUvbW91bnRhaW5z&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=76beb3eac347d5e32376be36a37797a5640cfde569fa4bc6cd79c6f73d53aa09JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=088e4ddd-8ce2-6a0a-2a95-5a3c8d7c6b7d&amp;u=a1aHR0cHM6Ly9odW1hbmlkYWRlcy5jb20vZW4vbW91bnRhaW4v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7d9e3fb9a4bb3d48fd5b5d9c8a913f9e9841e0e720cf4a73b6d81cf527a68e60JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=088e4ddd-8ce2-6a0a-2a95-5a3c8d7c6b7d&amp;u=a1aHR0cHM6Ly93d3cuc2NpZW5jZWRhaWx5LmNvbS90ZXJtcy9tb3VudGFpbi5odG0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e16803d22e292f1879055a0a55d6bf9d2dfc35a3c44a1ff19f37a2c5c4d27b5eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=088e4ddd-8ce2-6a0a-2a95-5a3c8d7c6b7d&amp;u=a1aHR0cHM6Ly93d3cuYmJjLmNvLnVrL2JpdGVzaXplL2FydGljbGVzL3p5aGYzajY&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=37c229f0a8167d8e1f7f013835ad5546bd5762d94aa3682cf03a1bcb72c542bfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1acfe030-ea7b-6425-23f7-f7d1eb196591&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRGlzYXN0ZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=20da35b4a54958934adc0978bf93ce853eb4adc3aa1377afdc9c74c53c66baa5JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1acfe030-ea7b-6425-23f7-f7d1eb196591&amp;u=a1aHR0cHM6Ly93d3cuZGlzYXN0ZXJhc3Npc3RhbmNlLmdvdi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e90ab41c598494f897b551017f80577f660d713324a048e5cf2376b9136631e8JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1acfe030-ea7b-6425-23f7-f7d1eb196591&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9kaXNhc3Rlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=87ccfccab3658007b642b583116ff966f0b47a3f1a0728999366f0fb536f3addJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1acfe030-ea7b-6425-23f7-f7d1eb196591&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Rpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=059d0fa2b426b5ed9bbc9822054df72fd07e7a696dc39f05bcecdd6b6d51989bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1acfe030-ea7b-6425-23f7-f7d1eb196591&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3YvZGlzYXN0ZXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c5caf83cdab85502e9e54799d1e3e8e2909a0aac36d2bd0f775f544f1578ae45JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1acfe030-ea7b-6425-23f7-f7d1eb196591&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vc2NpZW5jZS9uYXR1cmFsLWRpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0bf376b6a97e9019d4fefe690363b72a47bc2dff3214e5dc32e9c059d7c31b5dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1acfe030-ea7b-6425-23f7-f7d1eb196591&amp;u=a1aHR0cHM6Ly93d3cuZGlzYXN0ZXJyYWRhci5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=20e466cf828f80d31d1351a1a0c4511478f8a992b899f899dda14c6a81bbcf0eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1acfe030-ea7b-6425-23f7-f7d1eb196591&amp;u=a1aHR0cHM6Ly93d3cudW5kcnIub3JnL3Rlcm1pbm9sb2d5L2Rpc2FzdGVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b1d73991b621be55b4b98beec7575b0196e4ccf0765f6bd1a2a96ff426145bebJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1acfe030-ea7b-6425-23f7-f7d1eb196591&amp;u=a1aHR0cHM6Ly93d3cuZmVtYS5nb3Yv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=554beebb21499b48b8d4b2cf74ba11509d49b67f43e506c5c3b7605c5c40af0dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1acfe030-ea7b-6425-23f7-f7d1eb196591&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTmF0dXJhbF9kaXNhc3Rlcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef274e19fb360d7c50173b777ff4aa99dbdacb94c511d6fe0cba89ff6696b1e7JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03fa81ac-cb59-6cae-326a-964dca186dca&amp;u=a1aHR0cHM6Ly9zZWN1cmUuYmFua2F0Zmlyc3QuY29tL2xvZ2lu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b854f5d4a9bd281f012f3cc5eff0bfbd78d17335dd589743127b930ab1d58e12JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03fa81ac-cb59-6cae-326a-964dca186dca&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2ZpcnN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=09a0628ede53e77bc5652f9c4392b91787bd750c31f6a1b01a0bc43a617a059dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03fa81ac-cb59-6cae-326a-964dca186dca&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RpbnNwaXJlcy5vcmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5def40b6733a30d6cc401c0a35b202a222ea15455e2cf58ff5bd37800b76ee90JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03fa81ac-cb59-6cae-326a-964dca186dca&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2ZpcnN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1bbddc5e761dd35a0eeab39bb97e7ec6bf024ac4bd53126f3ad9733efaecb7bdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03fa81ac-cb59-6cae-326a-964dca186dca&amp;u=a1aHR0cHM6Ly93d3cuYmFua2F0Zmlyc3QuY29tL3BlcnNvbmFsLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2994e437e162b5f14885ad0cc36e2b2bd5989b71b847b3649d5d6c3d5601254dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03fa81ac-cb59-6cae-326a-964dca186dca&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3Qtb25saW5lLmJhbmsv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=08291aa3e83886d86995ab627b3411a90ce199f7b7844a0119675b3d54f5520aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03fa81ac-cb59-6cae-326a-964dca186dca&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RtZXJjaGFudHMuY29tL2xvY2F0aW9ucy9pbmRpYW5hcG9saXMtcmVnaW9uYWwtaGVhZHF1YXJ0ZXJz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3da0cf481c76725553433793720d87ea8cdbde312da05cb68596545502497babJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03fa81ac-cb59-6cae-326a-964dca186dca&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2ZpcnN0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c7b13d993f3d2f187fd0b9b9ea1c141bb8c5c881f57d99072bef12d772787709JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03fa81ac-cb59-6cae-326a-964dca186dca&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RpYi5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=341635f9f00d5f046a1de4192048c622ab010ca3bb6c7be650bf9ee074bfb500JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03fa81ac-cb59-6cae-326a-964dca186dca&amp;u=a1aHR0cHM6Ly93d3cuZmlyc3RtZXJjaGFudHMuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1f0eb42942c2bc1125c61f9112209688f986d8870511f0649458086594e40e31JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=051422ec-8ad8-6ae9-094b-350d8b4d6b3f&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQW1idWxhbmNl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5249b7552c00e01d0acf96db3ce6efe8dc6ac0ad0234ee6e08dbdb2a0175072bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=051422ec-8ad8-6ae9-094b-350d8b4d6b3f&amp;u=a1aHR0cHM6Ly93d3cuZWhlYWx0aHNjb3Jlcy5jb20vY2FyZS1sendmY3FxY3NxLWNpdHktb2Ytam9zaHVhLWVtcy1qb3NodWEuaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3eb88173792c4b081c6ccddbcb8133eb558d3434cd2ccb68d4840978951efb18JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=051422ec-8ad8-6ae9-094b-350d8b4d6b3f&amp;u=a1aHR0cHM6Ly93d3cuam9obnNvbmNvdW50eWZpcmUub3JnL2ZpcmUtZW1z&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e7e9f9aa87754da108a2c1d50170f437cbaa83898671b7047415f13b858dc30cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=051422ec-8ad8-6ae9-094b-350d8b4d6b3f&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRW1lcmdlbmN5X21lZGljYWxfc2VydmljZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=af44b405b73abad77e0a24c99b55af93b7fbf776f339b2d5a18928bf5c9bc6c0JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=051422ec-8ad8-6ae9-094b-350d8b4d6b3f&amp;u=a1aHR0cHM6Ly93d3cuYW1yLm5ldC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9b46deb76f40278cda11d6df4da013a072df05beca3f791afefbe16e2aba9c42JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=051422ec-8ad8-6ae9-094b-350d8b4d6b3f&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2FtYnVsYW5jZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bd2e0c1d8bc9d86eb140a0f39a1f04868a2cb0f8e5d3e89eddb8b202dd41421bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=051422ec-8ad8-6ae9-094b-350d8b4d6b3f&amp;u=a1aHR0cHM6Ly93d3cucmlkZW5zYWZlLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=70b11b9c194698fa20a6c2a2c719dbab3412bb5c00d970187feab4def00f4195JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=051422ec-8ad8-6ae9-094b-350d8b4d6b3f&amp;u=a1aHR0cHM6Ly9jaXR5YW1idWxhbmNlLm5ldC9zZXJ2aWNlcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2d201feead99a86e8c23d62f5ed2167afa8ca3a4479bb6e89320d17fc97546f2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=051422ec-8ad8-6ae9-094b-350d8b4d6b3f&amp;u=a1aHR0cHM6Ly9ucGluby5jb20vYW1idWxhbmNlLXNlcnZpY2UvMTc4MDY5OTYyOS1qb3NodWEtZmlyZS1kZXBhcnRtZW50Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=099503fe5694f04677d980de9fbc752da368314709ac29626a86eb9fc7816150JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=051422ec-8ad8-6ae9-094b-350d8b4d6b3f&amp;u=a1aHR0cHM6Ly9hbWJ1bGFuY2Uub3JnLw&amp;ntb=1</t>
   </si>
   <si>
     <t>https://www.bing.com/</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7931d688ea59d2c904fb75d53e2be9001a11145a1051c8721e5b52a4a052217eJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2879dff9-e2ab-6c4a-1324-c818e35a6d75&amp;u=a1aHR0cHM6Ly9zZWFyY2gueWFob28uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=12b6e886571f0183dcf38e8057dccdf3b1b9ba5ba3fab3c241c4a2c6856d1a51JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2879dff9-e2ab-6c4a-1324-c818e35a6d75&amp;u=a1aHR0cHM6Ly9zZWFyY2guZ29vZ2xlLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e370a7c1a6247c5f6bb18302cd77327f80bd27f333ba3562966dbf897f1de553JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2879dff9-e2ab-6c4a-1324-c818e35a6d75&amp;u=a1aHR0cHM6Ly93d3cueWFob28uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c01ceb58134002ea1b79da03ac46160e6ee4d4a36d546125fb81de754df84a9cJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2879dff9-e2ab-6c4a-1324-c818e35a6d75&amp;u=a1aHR0cHM6Ly9zZWFyY2guYnJhdmUuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d880edf1b22caf5fc044aa6a6cb81ec3890a5ecb74e7d95c3b862cc9326ca8d6JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2879dff9-e2ab-6c4a-1324-c818e35a6d75&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vVXNlLUJpbmctU2VhcmNoLUVuZ2luZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2182493f826a34e0019b3f830b87fb97f6b57f138c3f112539e48efae96d04eeJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2879dff9-e2ab-6c4a-1324-c818e35a6d75&amp;u=a1aHR0cHM6Ly9kdWNrZHVja2dvLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=61cd5ffafe5a1b47df18d2b7c458c752af3df9719dda16f4c8cec4103de7a78bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0c77bb-ba39-6e79-21a5-605abba06fe8&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Npdmls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6219d2dd7bcc1fd21f4fa7e5fe4ea652c582cfd565e54d85376509d0cbbb75c9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0c77bb-ba39-6e79-21a5-605abba06fe8&amp;u=a1aHR0cHM6Ly93d3cuZWxkb3JhZG9jb3VudHkuY2EuZ292L1B1YmxpYy1TYWZldHktSnVzdGljZS9TYWZldHktSnVzdGljZS9zaGVyaWZmL3N1cHBvcnRfc2VydmljZXMvY2l2aWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2295bd3802bf737b82357fcef0c4480a40256647a59351e106cfe4dda79d44c9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0c77bb-ba39-6e79-21a5-605abba06fe8&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Npdmls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dde43163b213c3d61d88a6fcb8af6c8a8775ac48ab7bcb9b4d5829ace5487df2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0c77bb-ba39-6e79-21a5-605abba06fe8&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ2l2aWxfZW5naW5lZXJpbmc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7abcd9176d37361c56435d4fd4ee4b4d1d2c8f0a4bf6cb649c4365606078e611JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0c77bb-ba39-6e79-21a5-605abba06fe8&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2Npdmls&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d6bbc055232683bb63627afda9cb39ff4e11e30b083095c9c8f5ad0fa996310dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0c77bb-ba39-6e79-21a5-605abba06fe8&amp;u=a1aHR0cHM6Ly93d3cudm9jYWJ1bGFyeS5jb20vZGljdGlvbmFyeS9jaXZpbA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6788ecbe8306c8f957bfc6174dffd4a91a8787cbdcdc15cbb7a22c287b4927d9JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2f0c77bb-ba39-6e79-21a5-605abba06fe8&amp;u=a1aHR0cHM6Ly93d3cuZGljdGlvbmFyeS5jb20vYnJvd3NlL2Npdmls&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7246290a6cfcc2acd62f0127baa9ecfff5243821b127687eea288efa101e4317JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35a58692-b419-6bae-31d7-9173b5a36aac&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3b8657f2a5a91ccf1c0e14d0914d549b0284d9153e78e4c641620f30549171e3JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35a58692-b419-6bae-31d7-9173b5a36aac&amp;u=a1aHR0cHM6Ly9zZWFyY2gueWFob28uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7c9a8c91991633e81430ef56dd108d3705b4e259948e925f8939c9e7cb908f45JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35a58692-b419-6bae-31d7-9173b5a36aac&amp;u=a1aHR0cHM6Ly9kdWNrZHVja2dvLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=081ff1b0a21b12883338cd8f883e5256db7d7e38a8229f0a976c819110b734e1JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35a58692-b419-6bae-31d7-9173b5a36aac&amp;u=a1aHR0cHM6Ly9zZWFyY2guYnJhdmUuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb160575fa951906a6e00c1a2771c795767e9c65caa4d9b2aed7b5346b73a52bJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35a58692-b419-6bae-31d7-9173b5a36aac&amp;u=a1aHR0cHM6Ly9pbWFnZXMuZ29vZ2xlLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=24c19350c2ca40b29348549980650f4d5b56f63fc9299f4c8fac5be53bec5da2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35a58692-b419-6bae-31d7-9173b5a36aac&amp;u=a1aHR0cHM6Ly9zZWFyY2guZ29vZ2xlLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=155f17a31045b998e9f499f77cda52129b558e1a87ae39404987267485b2b5a2JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=35a58692-b419-6bae-31d7-9173b5a36aac&amp;u=a1aHR0cHM6Ly93d3cuZ29vZ2xlLmNvbS9hZHZhbmNlZF9zZWFyY2g&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/profile/history</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=71caa5d94e0b39aff987a9b40cfd1cf8ccb7c167d2a51219199042c31a995067JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e7e4019-d0d9-6be2-1269-57f8d1cc6aff&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3ed41d2cfc0b20692758edba05d48bfaaf782a009ebb3fc8f1565d84f459894aJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e7e4019-d0d9-6be2-1269-57f8d1cc6aff&amp;u=a1aHR0cHM6Ly9jb3VudHkubWlsd2F1a2VlLmdvdi9FTi9Db3VydHMvQ291cnQtRGl2aXNpb25zL0NpdmlsLUNvdXJ0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2408c09a470396ceb894571456596cfb1243a1afa1de5e5b8996f9373fb17fadJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e7e4019-d0d9-6be2-1269-57f8d1cc6aff&amp;u=a1aHR0cHM6Ly91d20uZWR1L2VuZ2luZWVyaW5nL2RlcGFydG1lbnRzL2NpdmlsLWVudmlyb25tZW50YWwtZW5naW5lZXJpbmcv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=74a2aa6badad40b79b4dbaf2bd7257ee84bc6f9145a21703de38563ade500a24JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e7e4019-d0d9-6be2-1269-57f8d1cc6aff&amp;u=a1aHR0cHM6Ly91d20uZWR1L2VuZ2luZWVyaW5nL2FjYWRlbWljcy9jaXZpbC1lbmdpbmVlcmluZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b2c82c5bd2e0f00217e821f666e0b3d1ba0e2138ff7f6bd7ed79797929b704bfJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e7e4019-d0d9-6be2-1269-57f8d1cc6aff&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ2l2aWxfZW5naW5lZXJpbmc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5d5f3c32d36635034c9181e3fffb17fc150056e87b1cff1193c5903af33ceb89JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e7e4019-d0d9-6be2-1269-57f8d1cc6aff&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Npdmls&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5a7cdf724f4716210fc514f59e8224cc5155f98178f377b006887240bc80c285JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e7e4019-d0d9-6be2-1269-57f8d1cc6aff&amp;u=a1aHR0cHM6Ly93d3cud2ljb3VydHMuZ292L2Nhc2VzZWFyY2guaHRt&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=081f7af341dce62d5c35efb9ff1c5fe3f71c9f7c3f528ea79cdef38e714f52cdJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e7e4019-d0d9-6be2-1269-57f8d1cc6aff&amp;u=a1aHR0cHM6Ly9jb3VudHkubWlsd2F1a2VlLmdvdi9FTi9TaGVyaWZmL0RpdmlzaW9ucy9DaXZpbC1Qcm9jZXNz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cc51b0ad1812a6ab9e7284a4e80ccae27e69d41b378204d29e596623e4bad565JmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e7e4019-d0d9-6be2-1269-57f8d1cc6aff&amp;u=a1aHR0cHM6Ly91c2RpY3Rpb25hcnkuY29tL2RlZmluaXRpb25zL2NpdmlsLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1474e78ea9819731be2c1e005a7e795d6abdeb652361a2c0124bff92cab8899dJmltdHM9MTc5MDQ2NzIwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1e7e4019-d0d9-6be2-1269-57f8d1cc6aff&amp;u=a1aHR0cHM6Ly93d3cudGhlZnJlZWRpY3Rpb25hcnkuY29tL2Npdmls&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
@@ -904,7 +928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -938,19 +962,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H2" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -958,19 +982,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G3" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -978,19 +1002,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G4" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -998,19 +1022,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G5" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H5" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1018,19 +1042,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G6" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H6" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1038,19 +1062,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G7" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H7" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1058,19 +1082,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G8" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H8" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1078,19 +1102,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G9" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H9" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1098,19 +1122,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G10" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H10" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1118,19 +1142,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G11" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H11" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1138,19 +1162,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G12" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H12" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1158,19 +1182,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G13" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H13" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1178,19 +1202,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G14" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H14" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1198,19 +1222,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G15" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H15" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1218,19 +1242,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G16" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H16" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1238,19 +1262,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G17" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H17" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1258,19 +1282,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G18" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H18" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1278,19 +1302,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G19" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H19" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1298,19 +1322,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G20" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H20" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1318,19 +1342,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G21" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H21" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1338,19 +1362,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G22" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H22" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1358,19 +1382,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G23" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H23" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1378,19 +1402,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G24" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H24" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1398,19 +1422,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G25" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H25" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1418,19 +1442,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G26" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H26" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1438,19 +1462,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G27" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H27" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1458,19 +1482,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G28" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H28" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1478,19 +1502,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G29" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H29" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1498,19 +1522,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G30" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H30" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1518,19 +1542,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G31" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H31" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1538,19 +1562,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G32" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H32" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1558,19 +1582,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G33" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H33" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1578,19 +1602,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G34" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H34" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1598,19 +1622,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G35" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H35" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1618,19 +1642,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G36" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H36" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1638,19 +1662,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C37" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G37" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H37" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1658,19 +1682,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C38" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G38" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H38" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1678,19 +1702,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C39" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G39" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H39" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1698,19 +1722,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C40" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G40" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H40" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1718,19 +1742,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C41" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G41" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H41" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1738,19 +1762,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C42" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G42" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H42" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1758,19 +1782,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C43" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G43" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H43" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1778,19 +1802,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C44" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G44" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H44" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1798,19 +1822,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C45" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G45" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H45" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1818,19 +1842,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C46" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G46" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H46" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1838,19 +1862,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C47" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G47" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H47" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1858,19 +1882,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C48" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G48" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H48" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1878,19 +1902,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C49" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G49" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H49" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1898,19 +1922,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C50" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G50" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H50" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1918,19 +1942,19 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C51" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="G51" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H51" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1938,19 +1962,19 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C52" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G52" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H52" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1958,19 +1982,19 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C53" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G53" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H53" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -1978,19 +2002,19 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C54" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G54" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H54" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -1998,19 +2022,19 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C55" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G55" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H55" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2018,19 +2042,19 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C56" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G56" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H56" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2038,19 +2062,19 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C57" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G57" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H57" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2058,19 +2082,19 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C58" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G58" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H58" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2078,19 +2102,19 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C59" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G59" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H59" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2098,19 +2122,19 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C60" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G60" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H60" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2118,19 +2142,19 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C61" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G61" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H61" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2138,19 +2162,19 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C62" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G62" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H62" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2158,19 +2182,19 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C63" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G63" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H63" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2178,19 +2202,19 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C64" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G64" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H64" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2198,19 +2222,19 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C65" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G65" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H65" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2218,19 +2242,19 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C66" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G66" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H66" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2238,19 +2262,19 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C67" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G67" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H67" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2258,19 +2282,19 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C68" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G68" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H68" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2278,19 +2302,19 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C69" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G69" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H69" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2298,19 +2322,19 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C70" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G70" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H70" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2318,19 +2342,19 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C71" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G71" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H71" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2338,19 +2362,19 @@
         <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C72" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G72" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H72" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2358,19 +2382,19 @@
         <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C73" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G73" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H73" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2378,19 +2402,19 @@
         <v>80</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C74" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G74" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H74" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2398,19 +2422,19 @@
         <v>81</v>
       </c>
       <c r="B75" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C75" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="G75" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H75" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2418,19 +2442,19 @@
         <v>82</v>
       </c>
       <c r="B76" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C76" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G76" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H76" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2438,19 +2462,19 @@
         <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C77" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="G77" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H77" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -2458,19 +2482,19 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C78" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H78" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -2478,19 +2502,19 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C79" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G79" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H79" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -2498,19 +2522,19 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C80" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G80" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H80" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -2518,19 +2542,19 @@
         <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C81" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G81" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H81" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -2538,19 +2562,19 @@
         <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C82" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G82" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H82" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -2558,19 +2582,19 @@
         <v>89</v>
       </c>
       <c r="B83" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C83" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G83" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H83" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -2578,19 +2602,19 @@
         <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C84" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G84" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H84" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -2598,19 +2622,19 @@
         <v>91</v>
       </c>
       <c r="B85" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C85" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G85" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H85" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -2618,19 +2642,99 @@
         <v>92</v>
       </c>
       <c r="B86" t="s">
+        <v>97</v>
+      </c>
+      <c r="C86" t="s">
+        <v>98</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G86" t="s">
+        <v>188</v>
+      </c>
+      <c r="H86" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" t="s">
         <v>93</v>
       </c>
-      <c r="C86" t="s">
+      <c r="B87" t="s">
+        <v>97</v>
+      </c>
+      <c r="C87" t="s">
+        <v>98</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G87" t="s">
+        <v>188</v>
+      </c>
+      <c r="H87" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" t="s">
         <v>94</v>
       </c>
-      <c r="F86" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="G86" t="s">
-        <v>180</v>
-      </c>
-      <c r="H86" t="s">
-        <v>181</v>
+      <c r="B88" t="s">
+        <v>97</v>
+      </c>
+      <c r="C88" t="s">
+        <v>98</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G88" t="s">
+        <v>188</v>
+      </c>
+      <c r="H88" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" t="s">
+        <v>95</v>
+      </c>
+      <c r="B89" t="s">
+        <v>97</v>
+      </c>
+      <c r="C89" t="s">
+        <v>98</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="G89" t="s">
+        <v>188</v>
+      </c>
+      <c r="H89" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" t="s">
+        <v>96</v>
+      </c>
+      <c r="B90" t="s">
+        <v>97</v>
+      </c>
+      <c r="C90" t="s">
+        <v>98</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G90" t="s">
+        <v>188</v>
+      </c>
+      <c r="H90" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -2720,6 +2824,10 @@
     <hyperlink ref="F84" r:id="rId83"/>
     <hyperlink ref="F85" r:id="rId84"/>
     <hyperlink ref="F86" r:id="rId85"/>
+    <hyperlink ref="F87" r:id="rId86"/>
+    <hyperlink ref="F88" r:id="rId87"/>
+    <hyperlink ref="F89" r:id="rId88"/>
+    <hyperlink ref="F90" r:id="rId89"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
